--- a/Egyptian_Speech_Therapy_Centers.xlsx
+++ b/Egyptian_Speech_Therapy_Centers.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G355"/>
+  <dimension ref="A1:G351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -710,7 +710,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>مركز شباب موشا للتخاطب</t>
@@ -727,26 +727,22 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب صدفا للتخاطب</t>
-        </is>
-      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>منفلوط</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>صدفا</t>
-        </is>
-      </c>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>منفلوط</t>
+          <t>ديروط</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -759,7 +755,7 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ديروط</t>
+          <t>الوقف</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -772,7 +768,7 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>الوقف</t>
+          <t>أبيدوس</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -785,7 +781,7 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>أبيدوس</t>
+          <t>سوهاج</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -798,7 +794,7 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>سوهاج</t>
+          <t>البدارى</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -811,7 +807,7 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>البدارى</t>
+          <t>فلنج</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -824,7 +820,7 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>فلنج</t>
+          <t>أراب العوامر</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -837,7 +833,7 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>أراب العوامر</t>
+          <t>الغنايم</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -847,10 +843,10 @@
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
+      <c r="A23" s="6" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>الغنايم</t>
+          <t>الفيوم الجديدة</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -860,48 +856,48 @@
       <c r="G23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>الأقصر</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>الفيوم الجديدة</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
+          <t>الأقصر</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمركز شباب نجع الخطباء</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب نجع الخطباء</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>الأقصر</t>
-        </is>
-      </c>
+      <c r="A25" s="5" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>الأقصر</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بمركز شباب نجع الخطباء</t>
-        </is>
-      </c>
+          <t>الكرنك</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب نجع الخطباء</t>
-        </is>
-      </c>
+      <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>الكرنك</t>
+          <t>البر الغربي</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -914,7 +910,7 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>البر الغربي</t>
+          <t>الضفة الغربية</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -927,7 +923,7 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>الضفة الغربية</t>
+          <t>وادي الملوك</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -940,7 +936,7 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>وادي الملوك</t>
+          <t>معبد الدير البحري</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -953,7 +949,7 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>معبد الدير البحري</t>
+          <t>مدينة الأقصر</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -966,7 +962,7 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>مدينة الأقصر</t>
+          <t>إسنا</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -976,10 +972,10 @@
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
+      <c r="A32" s="6" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>إسنا</t>
+          <t>أرمنت</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -989,32 +985,36 @@
       <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>الإسكندرية</t>
+        </is>
+      </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>أرمنت</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
+          <t>الإسكندرية</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>مركز الوطنية للإرشاد النفسي</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>الإسكندرية</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>الإسكندرية</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>الإسكندرية</t>
-        </is>
-      </c>
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>مركز الوطنية للإرشاد النفسي</t>
+          <t>مركز سموحة للتخاطب</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>الإسكندرية</t>
+          <t>سموحة، الإسكندرية</t>
         </is>
       </c>
     </row>
@@ -1031,15 +1031,19 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>مركز سموحة للتخاطب</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
+          <t>مركز د/ نهى رسلان لتدريب النطق والكلام</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>د. نهى رسلان</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>سموحة، الإسكندرية</t>
+          <t>الإسكندرية</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1052,12 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>مركز د/ نهى رسلان لتدريب النطق والكلام</t>
+          <t>مركز د/ هبة سلامة</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>د. نهى رسلان</t>
+          <t>د. هبة سلامة</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -1069,14 +1073,10 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>مركز د/ هبة سلامة</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>د. هبة سلامة</t>
-        </is>
-      </c>
+          <t>أكاديمية زويل</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
@@ -1087,10 +1087,10 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
+      <c r="B38" s="6" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>أكاديمية زويل</t>
+          <t>جمعية إشراق الشمس</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
@@ -1104,26 +1104,22 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>جمعية إشراق الشمس</t>
-        </is>
-      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>برج العرب</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>الإسكندرية</t>
-        </is>
-      </c>
+      <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>برج العرب</t>
+          <t>مونتازا</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1136,46 +1132,62 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>مونتازا</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
+          <t>سيدي بشر</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>مركز كلام عيال للتخاطب وتنمية مهارات</t>
+        </is>
+      </c>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>144 شارع جمال عبد الناصر سيدي بشر</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>سيدي بشر</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>عيادة تخاطب شارع الطفولة السعيدة</t>
+        </is>
+      </c>
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>شارع الطفولة السعيدة، سيدي بشر</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>أبي قير</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>مركز تومورو للتخاطب</t>
+        </is>
+      </c>
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>البيطاش وسيدي بشر والجيزة</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>الدخيلة</t>
+          <t>أبي قير</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1188,7 +1200,7 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>كوم الدكة</t>
+          <t>الدخيلة</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1201,7 +1213,7 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>ستانلي</t>
+          <t>كوم الدكة</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1214,7 +1226,7 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>الشاطبي</t>
+          <t>ستانلي</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -1227,7 +1239,7 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>رشدي</t>
+          <t>الشاطبي</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -1240,7 +1252,7 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>الرملة</t>
+          <t>رشدي</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -1253,7 +1265,7 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>الإبراهيمية</t>
+          <t>الرملة</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -1266,7 +1278,7 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>القنطرة</t>
+          <t>الإبراهيمية</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -1279,7 +1291,7 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>القنطرة</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -1292,7 +1304,7 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>الحمام</t>
+          <t>كفر عبده</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -1305,7 +1317,7 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>مارينا</t>
+          <t>الحمام</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -1318,7 +1330,7 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>عمومية</t>
+          <t>مارينا</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -1328,10 +1340,10 @@
       <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
+      <c r="A56" s="5" t="n"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>ضواحي</t>
+          <t>عمومية</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -1341,14 +1353,10 @@
       <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>الإسماعيلية</t>
-        </is>
-      </c>
+      <c r="A57" s="6" t="n"/>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>الإسماعيلية</t>
+          <t>ضواحي</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -1358,10 +1366,14 @@
       <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>الإسماعيلية</t>
+        </is>
+      </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>الإسماعيلية</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -1374,7 +1386,7 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>السويس</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -1387,7 +1399,7 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>القنطرة غرب</t>
+          <t>السويس</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -1400,7 +1412,7 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>القنطرة شرق</t>
+          <t>القنطرة غرب</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -1413,7 +1425,7 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>فايد</t>
+          <t>القنطرة شرق</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -1426,7 +1438,7 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>تل الكبير</t>
+          <t>فايد</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -1439,7 +1451,7 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>الشلوفة</t>
+          <t>تل الكبير</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -1449,10 +1461,10 @@
       <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
+      <c r="A65" s="5" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>الدفرسوار</t>
+          <t>الشلوفة</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -1462,36 +1474,32 @@
       <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>البحر الأحمر</t>
-        </is>
-      </c>
+      <c r="A66" s="6" t="n"/>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>الغردقة</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب الغردقة بمركز شباب الغردقة</t>
-        </is>
-      </c>
+          <t>الدفرسوار</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب الغردقة</t>
-        </is>
-      </c>
+      <c r="G66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="6" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>البحر الأحمر</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>الغردقة</t>
+        </is>
+      </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>مركز تخاطب سفاجة</t>
+          <t>مركز تخاطب الغردقة بمركز شباب الغردقة</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -1499,28 +1507,32 @@
       <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>سفاجة</t>
+          <t>مركز شباب الغردقة</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>سفاجة</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب سفاجة</t>
+        </is>
+      </c>
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>سفاجة</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>القصير</t>
+          <t>سفاجة</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -1533,7 +1545,7 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>مرسى علم</t>
+          <t>القصير</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -1546,7 +1558,7 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>شلاتين</t>
+          <t>مرسى علم</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -1559,7 +1571,7 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>حلايب</t>
+          <t>شلاتين</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -1572,7 +1584,7 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>أبو رماد</t>
+          <t>حلايب</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -1585,7 +1597,7 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>قصير الجديدة</t>
+          <t>أبو رماد</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -1598,7 +1610,7 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>رأس غارب</t>
+          <t>قصير الجديدة</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -1608,10 +1620,10 @@
       <c r="G75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n"/>
+      <c r="A76" s="5" t="n"/>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>دهب</t>
+          <t>رأس غارب</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -1621,82 +1633,82 @@
       <c r="G76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>البحيرة</t>
-        </is>
-      </c>
+      <c r="A77" s="6" t="n"/>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>دمنهور</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>مركز لايف للتخاطب</t>
-        </is>
-      </c>
+          <t>دهب</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>21 شارع إبراهيم مظهر، ميدان الساعة</t>
-        </is>
-      </c>
+      <c r="G77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>البحيرة</t>
+        </is>
+      </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>كفر الدوار</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr"/>
+          <t>دمنهور</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>مركز لايف للتخاطب</t>
+        </is>
+      </c>
       <c r="D78" s="4" t="inlineStr"/>
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>21 شارع إبراهيم مظهر، ميدان الساعة</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>رشيد</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>مركز الإيمان للتخاطب</t>
-        </is>
-      </c>
+          <t>كفر الدوار</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>شارع عبد السلام عارف</t>
-        </is>
-      </c>
+      <c r="G79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>إدكو</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
+          <t>رشيد</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>مركز الإيمان للتخاطب</t>
+        </is>
+      </c>
       <c r="D80" s="4" t="inlineStr"/>
       <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>شارع عبد السلام عارف</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>أبو حمص</t>
+          <t>إدكو</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -1709,7 +1721,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>كوم حمادة</t>
+          <t>أبو حمص</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -1722,7 +1734,7 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>شبراخيت</t>
+          <t>كوم حمادة</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -1735,7 +1747,7 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>كفر الشيخ</t>
+          <t>شبراخيت</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -1748,7 +1760,7 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>نوقة</t>
+          <t>كفر الشيخ</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -1761,7 +1773,7 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>الحامول</t>
+          <t>نوقة</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -1774,7 +1786,7 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>شرقية</t>
+          <t>الحامول</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -1787,7 +1799,7 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>الدلنجات</t>
+          <t>شرقية</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -1800,7 +1812,7 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>إيتاي البارود</t>
+          <t>الدلنجات</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -1813,7 +1825,7 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>بسيون</t>
+          <t>إيتاي البارود</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -1823,10 +1835,10 @@
       <c r="G90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n"/>
+      <c r="A91" s="5" t="n"/>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>سنجور</t>
+          <t>بسيون</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -1836,36 +1848,32 @@
       <c r="G91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
+      <c r="A92" s="6" t="n"/>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب النموذجي</t>
-        </is>
-      </c>
+          <t>سنجور</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
       <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>شارع النيل، العجوزة</t>
-        </is>
-      </c>
+      <c r="G92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>مركز تخاطب وسمع واتزان</t>
+          <t>مركز التخاطب النموذجي</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
@@ -1873,7 +1881,7 @@
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>شارع نادي إمبابة الرياضي، إمبابة</t>
+          <t>شارع النيل، العجوزة</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1890,7 @@
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>مركز قدرات للتخاطب</t>
+          <t>مركز تخاطب وسمع واتزان</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -1890,7 +1898,7 @@
       <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>119 شارع الهرم، الهرم</t>
+          <t>شارع نادي إمبابة الرياضي، إمبابة</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1907,7 @@
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>مركز مكة للتخاطب وتنمية مهارات</t>
+          <t>مركز قدرات للتخاطب</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -1907,16 +1915,16 @@
       <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>الهرم، الجيزة</t>
+          <t>119 شارع الهرم، الهرم</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
-      <c r="B96" s="6" t="n"/>
+      <c r="B96" s="5" t="n"/>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>مركز القادة للتخاطب وتنمية المهارات</t>
+          <t>مركز مكة للتخاطب وتنمية مهارات</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -1930,22 +1938,26 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>مدينة 6 أكتوبر</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>مركز القادة للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr"/>
       <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>الهرم، الجيزة</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>مدينة 6 أكتوبر</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -1958,7 +1970,7 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>البدرشين</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -1971,7 +1983,7 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>دهشور</t>
+          <t>البدرشين</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -1984,7 +1996,7 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>أبو رواش</t>
+          <t>دهشور</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -1997,7 +2009,7 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>الوراق</t>
+          <t>أبو رواش</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -2010,7 +2022,7 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>الساحل</t>
+          <t>الوراق</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -2023,7 +2035,7 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>الكيت كات</t>
+          <t>الساحل</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -2036,7 +2048,7 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>الهرم</t>
+          <t>الكيت كات</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -2049,46 +2061,62 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>إمبابة</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr"/>
+          <t>الهرم</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>مركز هووب للتخاطب</t>
+        </is>
+      </c>
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>الهرم وفيصل</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>العمرانية</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>مركز طريقنا للتخاطب</t>
+        </is>
+      </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>10 شارع أحمد عبد المحسن، التعاون</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>الحوامدية</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr"/>
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>مركز الأهرام للتخاطب</t>
+        </is>
+      </c>
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>شارع اللبيني، المريوطية</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>أطفيح</t>
+          <t>إمبابة</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
@@ -2101,7 +2129,7 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>بني سويف الجديدة</t>
+          <t>العمرانية</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr"/>
@@ -2111,10 +2139,10 @@
       <c r="G110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="n"/>
+      <c r="A111" s="5" t="n"/>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>المنيل</t>
+          <t>الحوامدية</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
@@ -2124,95 +2152,91 @@
       <c r="G111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>الدقهلية</t>
-        </is>
-      </c>
+      <c r="A112" s="5" t="n"/>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>المنصورة</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>مركز رعاية وتنمية الطفولة - جامعة المنصورة</t>
-        </is>
-      </c>
+          <t>أطفيح</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr"/>
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="4" t="inlineStr"/>
       <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>جامعة المنصورة</t>
-        </is>
-      </c>
+      <c r="G112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>مركز الدلتا للتخاطب</t>
-        </is>
-      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>بني سويف الجديدة</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr"/>
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="4" t="inlineStr"/>
       <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>شارع جلاء، برج البستان</t>
-        </is>
-      </c>
+      <c r="G113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n"/>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>وحدة أمراض التخاطب - كلية الطب</t>
-        </is>
-      </c>
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>المنيل</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
       <c r="D114" s="4" t="inlineStr"/>
       <c r="E114" s="4" t="inlineStr"/>
       <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>جامعة المنصورة</t>
-        </is>
-      </c>
+      <c r="G114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>الدقهلية</t>
+        </is>
+      </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>طلخا</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
+          <t>المنصورة</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعاية وتنمية الطفولة - جامعة المنصورة</t>
+        </is>
+      </c>
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="4" t="inlineStr"/>
       <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>جامعة المنصورة</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>آجا</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr"/>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>مركز الدلتا للتخاطب</t>
+        </is>
+      </c>
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="4" t="inlineStr"/>
       <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>شارع جلاء، برج البستان</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>مِت غمر</t>
+          <t>طلخا</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
@@ -2225,7 +2249,7 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>شربين</t>
+          <t>آجا</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
@@ -2238,7 +2262,7 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>بلقاس</t>
+          <t>مِت غمر</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -2251,7 +2275,7 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>جمصة</t>
+          <t>شربين</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
@@ -2264,7 +2288,7 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>السنبلاوين</t>
+          <t>بلقاس</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
@@ -2277,7 +2301,7 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ميت سلسيل</t>
+          <t>جمصة</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
@@ -2290,7 +2314,7 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>أجا</t>
+          <t>السنبلاوين</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
@@ -2303,7 +2327,7 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>المتينة</t>
+          <t>ميت سلسيل</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr"/>
@@ -2316,7 +2340,7 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>منية النصر</t>
+          <t>أجا</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr"/>
@@ -2326,10 +2350,10 @@
       <c r="G125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="n"/>
+      <c r="A126" s="5" t="n"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>كفر سعد</t>
+          <t>المتينة</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr"/>
@@ -2339,39 +2363,23 @@
       <c r="G126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>السويس</t>
-        </is>
-      </c>
+      <c r="A127" s="5" t="n"/>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>السويس</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>مركز دار مكة للتخاطب</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>د. سارة فاتحة</t>
-        </is>
-      </c>
+          <t>منية النصر</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr"/>
+      <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="4" t="inlineStr"/>
       <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>شارع عبد المنعم رياض - جسر السويس - بجوار محطة الجراج</t>
-        </is>
-      </c>
+      <c r="G127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n"/>
+      <c r="A128" s="6" t="n"/>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>عين سخنة</t>
+          <t>كفر سعد</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr"/>
@@ -2381,23 +2389,39 @@
       <c r="G128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>السويس</t>
+        </is>
+      </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>عطاقة</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr"/>
-      <c r="D129" s="4" t="inlineStr"/>
+          <t>السويس</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>مركز دار مكة للتخاطب</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>د. سارة فاتحة</t>
+        </is>
+      </c>
       <c r="E129" s="4" t="inlineStr"/>
       <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>شارع عبد المنعم رياض - جسر السويس</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>الجنايين</t>
+          <t>عين سخنة</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr"/>
@@ -2410,7 +2434,7 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>فايد</t>
+          <t>عطاقة</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr"/>
@@ -2423,7 +2447,7 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ناقصة</t>
+          <t>الجنايين</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -2436,7 +2460,7 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>القصير</t>
+          <t>فايد</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr"/>
@@ -2446,10 +2470,10 @@
       <c r="G133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="n"/>
+      <c r="A134" s="5" t="n"/>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>الدفرسوار</t>
+          <t>ناقصة</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr"/>
@@ -2459,103 +2483,103 @@
       <c r="G134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>الشرقية</t>
-        </is>
-      </c>
+      <c r="A135" s="5" t="n"/>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>الزقازيق</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>مركز كيان للتدريب والتأهيل التخاطبي</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>د. محمد فريد الغزاوي</t>
-        </is>
-      </c>
+          <t>القصير</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr"/>
+      <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="4" t="inlineStr"/>
       <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>شارع الشيبة (شارع المنشية) بجوار محطة المنيا</t>
-        </is>
-      </c>
+      <c r="G135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n"/>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>مركز السلام للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
+      <c r="A136" s="6" t="n"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>الدفرسوار</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr"/>
       <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="4" t="inlineStr"/>
       <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="4" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>الشرقية</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>الزقازيق</t>
         </is>
       </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="n"/>
-      <c r="B137" s="6" t="n"/>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>مركز الحياة للتخاطب وتنمية المهارات</t>
+          <t>مركز كيان للتدريب والتأهيل التخاطبي</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>د. شيرين أيوب</t>
+          <t>د. محمد فريد الغزاوي</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
       <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>الزقازيق</t>
+          <t>شارع الشيبة (شارع المنشية)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>الإسماعيلية</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr"/>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>مركز السلام للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
       <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="4" t="inlineStr"/>
       <c r="F138" s="4" t="inlineStr"/>
-      <c r="G138" s="4" t="inlineStr"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>الزقازيق</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>بلبيس</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr"/>
-      <c r="D139" s="4" t="inlineStr"/>
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>مركز الحياة للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>د. شيرين أيوب</t>
+        </is>
+      </c>
       <c r="E139" s="4" t="inlineStr"/>
       <c r="F139" s="4" t="inlineStr"/>
-      <c r="G139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>الزقازيق</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>مدينة 10 رمضان</t>
+          <t>الإسماعيلية</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr"/>
@@ -2568,20 +2592,32 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr"/>
-      <c r="D141" s="4" t="inlineStr"/>
+          <t>بلبيس</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>مركز تأهيل متخصص للتخاطب</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>د. مي صلاح</t>
+        </is>
+      </c>
       <c r="E141" s="4" t="inlineStr"/>
       <c r="F141" s="4" t="inlineStr"/>
-      <c r="G141" s="4" t="inlineStr"/>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>بلبيس</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>فاقوس</t>
+          <t>مدينة 10 رمضان</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr"/>
@@ -2594,7 +2630,7 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>القنايات</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr"/>
@@ -2607,33 +2643,45 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>أبو حماد</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr"/>
+          <t>فاقوس</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>أكاديمية كيان للتخاطب والتدريب</t>
+        </is>
+      </c>
       <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="4" t="inlineStr"/>
       <c r="F144" s="4" t="inlineStr"/>
-      <c r="G144" s="4" t="inlineStr"/>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>فاقوس</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>الجزيرة</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr"/>
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>مركز كِنان للتخاطب والتأهيل</t>
+        </is>
+      </c>
       <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="4" t="inlineStr"/>
-      <c r="G145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>الصالحية القديمة، فاقوس</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ههيا</t>
+          <t>القنايات</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
@@ -2646,7 +2694,7 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>درب السلام</t>
+          <t>أبو حماد</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr"/>
@@ -2656,10 +2704,10 @@
       <c r="G147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="n"/>
+      <c r="A148" s="5" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>الصالحية</t>
+          <t>الجزيرة</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr"/>
@@ -2669,90 +2717,66 @@
       <c r="G148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>الغربية</t>
-        </is>
-      </c>
+      <c r="A149" s="5" t="n"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>طنطا</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>مركز أتكلم TALK للتخاطب</t>
-        </is>
-      </c>
+          <t>ههيا</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr"/>
       <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="4" t="inlineStr"/>
       <c r="F149" s="4" t="inlineStr"/>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>شارع البحر أمام مستشفى المنشاوي، برج التكية</t>
-        </is>
-      </c>
+      <c r="G149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>أكاديمية المعرفة للتخاطب</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>د. شيرين محمد طه</t>
-        </is>
-      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>درب السلام</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr"/>
+      <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr"/>
       <c r="F150" s="4" t="inlineStr"/>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>آخر شارع سعيد، برج السمان الدور الأول</t>
-        </is>
-      </c>
+      <c r="G150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>مركز القمة للتدريب والتأهيل</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>د. محمد علي غراب</t>
-        </is>
-      </c>
+      <c r="A151" s="6" t="n"/>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>الصالحية</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr"/>
+      <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="4" t="inlineStr"/>
-      <c r="G151" s="4" t="inlineStr">
-        <is>
-          <t>شارع عبد العزيز الغول</t>
-        </is>
-      </c>
+      <c r="G151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n"/>
-      <c r="B152" s="5" t="n"/>
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>الغربية</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>طنطا</t>
+        </is>
+      </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>عيادة الدكتورة إيناس أحمد</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>د. إيناس أحمد</t>
-        </is>
-      </c>
+          <t>مركز أتكلم TALK للتخاطب</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="4" t="inlineStr"/>
       <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>شارع عمر زعفان</t>
+          <t>شارع البحر أمام مستشفى المنشاوي، برج التكية</t>
         </is>
       </c>
     </row>
@@ -2761,70 +2785,86 @@
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>مركز الدلتا لأمراض التخاطب</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>أكاديمية المعرفة للتخاطب</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>د. شيرين محمد طه</t>
+        </is>
+      </c>
       <c r="E153" s="4" t="inlineStr"/>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>طنطا</t>
+          <t>آخر شارع سعيد، برج السمان الدور الأول</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
-      <c r="B154" s="6" t="n"/>
+      <c r="B154" s="5" t="n"/>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>مراكز الربيع للتخاطب</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr"/>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>01003545009</t>
-        </is>
-      </c>
+          <t>مركز القمة للتدريب والتأهيل</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد علي غراب</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr"/>
       <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>طنطا</t>
+          <t>شارع عبد العزيز الغول</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>كفر الزيات</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr"/>
-      <c r="D155" s="4" t="inlineStr"/>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>عيادة الدكتورة إيناس أحمد</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>د. إيناس أحمد</t>
+        </is>
+      </c>
       <c r="E155" s="4" t="inlineStr"/>
       <c r="F155" s="4" t="inlineStr"/>
-      <c r="G155" s="4" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>شارع عمر زعفان</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>سمنود</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr"/>
+      <c r="B156" s="6" t="n"/>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>مركز الدلتا لأمراض التخاطب</t>
+        </is>
+      </c>
       <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="4" t="inlineStr"/>
       <c r="F156" s="4" t="inlineStr"/>
-      <c r="G156" s="4" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>طنطا</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>زفتا</t>
+          <t>كفر الزيات</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr"/>
@@ -2837,7 +2877,7 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>المحلة الكبرى</t>
+          <t>سمنود</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr"/>
@@ -2850,7 +2890,7 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>قطور</t>
+          <t>زفتا</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr"/>
@@ -2863,105 +2903,101 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>سان الحجر</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr"/>
+          <t>المحلة الكبرى</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>مركز أزهار القلوب للتخاطب</t>
+        </is>
+      </c>
       <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="4" t="inlineStr"/>
       <c r="F160" s="4" t="inlineStr"/>
-      <c r="G160" s="4" t="inlineStr"/>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>المحلة الكبرى</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>بسيون</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr"/>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>مركز كيدز الأمل للعلاج الطبيعي</t>
+        </is>
+      </c>
       <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="4" t="inlineStr"/>
       <c r="F161" s="4" t="inlineStr"/>
-      <c r="G161" s="4" t="inlineStr"/>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>بجوار مستشفى بدر</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="6" t="n"/>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>الدلتا الجديدة</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr"/>
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="6" t="n"/>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>مركز صن رايز للتخاطب</t>
+        </is>
+      </c>
       <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="4" t="inlineStr"/>
       <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr"/>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>موقف طلعت حرب وكوبري الرباب</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>الفيوم</t>
-        </is>
-      </c>
+      <c r="A163" s="5" t="n"/>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>الفيوم</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب القاهفة للتخاطب</t>
-        </is>
-      </c>
+          <t>قطور</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr"/>
       <c r="D163" s="4" t="inlineStr"/>
       <c r="E163" s="4" t="inlineStr"/>
       <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>الفيوم</t>
-        </is>
-      </c>
+      <c r="G163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العمرية للتخاطب</t>
-        </is>
-      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>سان الحجر</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr"/>
       <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="inlineStr"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>الفيوم</t>
-        </is>
-      </c>
+      <c r="G164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
-      <c r="B165" s="6" t="n"/>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بمركز شباب الشواشنة</t>
-        </is>
-      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>بسيون</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr"/>
       <c r="D165" s="4" t="inlineStr"/>
       <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="inlineStr"/>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>الشواشنة</t>
-        </is>
-      </c>
+      <c r="G165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n"/>
+      <c r="A166" s="6" t="n"/>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>سيوه</t>
+          <t>الدلتا الجديدة</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr"/>
@@ -2971,36 +3007,52 @@
       <c r="G166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="n"/>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>الفيوم</t>
+        </is>
+      </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>القرين</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr"/>
+          <t>الفيوم</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب القاهفة للتخاطب</t>
+        </is>
+      </c>
       <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="inlineStr"/>
-      <c r="G167" s="4" t="inlineStr"/>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>الفيوم</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>إبشواي</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr"/>
+      <c r="B168" s="6" t="n"/>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمركز شباب الشواشنة</t>
+        </is>
+      </c>
       <c r="D168" s="4" t="inlineStr"/>
       <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="inlineStr"/>
-      <c r="G168" s="4" t="inlineStr"/>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>الشواشنة</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>سنوريس</t>
+          <t>سيوه</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr"/>
@@ -3013,7 +3065,7 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>طامية</t>
+          <t>القرين</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr"/>
@@ -3026,7 +3078,7 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>اطسا</t>
+          <t>إبشواي</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr"/>
@@ -3039,7 +3091,7 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>يوسف الصديق</t>
+          <t>سنوريس</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr"/>
@@ -3052,7 +3104,7 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>طامية</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
@@ -3062,10 +3114,10 @@
       <c r="G173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="n"/>
+      <c r="A174" s="5" t="n"/>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>آثار</t>
+          <t>اطسا</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr"/>
@@ -3075,95 +3127,79 @@
       <c r="G174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>القاهرة</t>
-        </is>
-      </c>
+      <c r="A175" s="5" t="n"/>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>القاهرة</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>د. وفاء وافي</t>
-        </is>
-      </c>
+          <t>يوسف الصديق</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr"/>
+      <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="4" t="inlineStr"/>
       <c r="F175" s="4" t="inlineStr"/>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>1 شارع المنتزه خلف مستشفى هليوبوليس، مصر الجديدة</t>
-        </is>
-      </c>
+      <c r="G175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
-      <c r="B176" s="5" t="n"/>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب المرح لعلاج الأطفال والكبار</t>
-        </is>
-      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>العدوة</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr"/>
       <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr"/>
       <c r="F176" s="4" t="inlineStr"/>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا</t>
-        </is>
-      </c>
+      <c r="G176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="n"/>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>مركز هليوبوليس للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
+      <c r="A177" s="6" t="n"/>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>آثار</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
       <c r="D177" s="4" t="inlineStr"/>
       <c r="E177" s="4" t="inlineStr"/>
       <c r="F177" s="4" t="inlineStr"/>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>28 شارع محمد عبيد من شارع النزهة، مصر الجديدة</t>
-        </is>
-      </c>
+      <c r="G177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="n"/>
-      <c r="B178" s="6" t="n"/>
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>مركز Speak للتخاطب</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
+          <t>مركز التخاطب الشامل وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>د. وفاء وافي</t>
+        </is>
+      </c>
       <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>زهراء مدينة نصر - المرحلة الأولى</t>
+          <t>1 شارع المنتزه خلف مستشفى هليوبوليس، مصر الجديدة</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>مدينة نصر</t>
-        </is>
-      </c>
+      <c r="B179" s="5" t="n"/>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>المركز الذهبي التخصصي (GSC)</t>
+          <t>مركز تخاطب المرح لعلاج الأطفال والكبار</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr"/>
@@ -3171,92 +3207,112 @@
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>مدينة نصر، القاهرة</t>
+          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
+      <c r="B180" s="5" t="n"/>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>مركز التخاطب الشامل و صعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>د. وفاء وافي</t>
-        </is>
-      </c>
+          <t>مركز هليوبوليس للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr"/>
       <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>مصر الجديدة</t>
+          <t>28 شارع محمد عبيد من شارع النزهة، مصر الجديدة</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>الزمالك</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>مركز Speak للتخاطب</t>
+        </is>
+      </c>
       <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="inlineStr"/>
-      <c r="G181" s="4" t="inlineStr"/>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>زهراء مدينة نصر - المرحلة الأولى</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr"/>
+      <c r="B182" s="6" t="n"/>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>مركز Almony للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
       <c r="D182" s="4" t="inlineStr"/>
       <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="inlineStr"/>
-      <c r="G182" s="4" t="inlineStr"/>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>8 عمارات منتصر، بجانب مسجد عبد الرحمن، حدائق حلوان</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>العبّاسية</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr"/>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>المركز الذهبي التخصصي (GSC)</t>
+        </is>
+      </c>
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="inlineStr"/>
-      <c r="G183" s="4" t="inlineStr"/>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>مدينة نصر، القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>مدينة 6 أكتوبر</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr"/>
-      <c r="D184" s="4" t="inlineStr"/>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل و صعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>د. وفاء وافي</t>
+        </is>
+      </c>
       <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="inlineStr"/>
-      <c r="G184" s="4" t="inlineStr"/>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>مدينة الشروق</t>
+          <t>الزمالك</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
@@ -3269,28 +3325,20 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>مدينة بدر</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>مركز متخصص للتخاطب</t>
-        </is>
-      </c>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr"/>
       <c r="D186" s="4" t="inlineStr"/>
       <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="inlineStr"/>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>مدينة بدر، القاهرة</t>
-        </is>
-      </c>
+      <c r="G186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>مدينة 15 مايو</t>
+          <t>العبّاسية</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr"/>
@@ -3303,7 +3351,7 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>مدينة 6 أكتوبر</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
@@ -3316,7 +3364,7 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>مدينة الشروق</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
@@ -3329,20 +3377,28 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr"/>
+          <t>مدينة بدر</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>مركز متخصص للتخاطب</t>
+        </is>
+      </c>
       <c r="D190" s="4" t="inlineStr"/>
       <c r="E190" s="4" t="inlineStr"/>
       <c r="F190" s="4" t="inlineStr"/>
-      <c r="G190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>مدينة بدر، القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>القاهرة الجديدة</t>
+          <t>مدينة 15 مايو</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
@@ -3355,33 +3411,49 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زايد</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr"/>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب بزهراء المعادي</t>
+        </is>
+      </c>
       <c r="D192" s="4" t="inlineStr"/>
       <c r="E192" s="4" t="inlineStr"/>
       <c r="F192" s="4" t="inlineStr"/>
-      <c r="G192" s="4" t="inlineStr"/>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>شارع الأرقم بن الأرقم، الدائري، بستان</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>الرحاب</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr"/>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>مركز Almony للتخاطب</t>
+        </is>
+      </c>
       <c r="D193" s="4" t="inlineStr"/>
       <c r="E193" s="4" t="inlineStr"/>
       <c r="F193" s="4" t="inlineStr"/>
-      <c r="G193" s="4" t="inlineStr"/>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>حدائق حلوان</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>الحي العاشر</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
@@ -3394,7 +3466,7 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>المنيل</t>
+          <t>القاهرة الجديدة</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr"/>
@@ -3407,7 +3479,7 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>الدقي</t>
+          <t>الشيخ زايد</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr"/>
@@ -3420,7 +3492,7 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
+          <t>الرحاب</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr"/>
@@ -3433,7 +3505,7 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>الموسكي</t>
+          <t>الحي العاشر</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr"/>
@@ -3446,7 +3518,7 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>الفجالة</t>
+          <t>المنيل</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
@@ -3459,7 +3531,7 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>باب الشعرية</t>
+          <t>الدقي</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr"/>
@@ -3472,7 +3544,7 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>الساحل</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr"/>
@@ -3485,7 +3557,7 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>المطرية</t>
+          <t>الموسكي</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr"/>
@@ -3498,7 +3570,7 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>عين شمس</t>
+          <t>الفجالة</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr"/>
@@ -3511,7 +3583,7 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>باب الشعرية</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr"/>
@@ -3524,7 +3596,7 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>وسيط</t>
+          <t>الساحل</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr"/>
@@ -3537,7 +3609,7 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>المنصورية</t>
+          <t>المطرية</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr"/>
@@ -3550,7 +3622,7 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>الدراسة</t>
+          <t>عين شمس</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr"/>
@@ -3563,7 +3635,7 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>درب الجنينة</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr"/>
@@ -3576,7 +3648,7 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>الشرابية</t>
+          <t>وسيط</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr"/>
@@ -3589,7 +3661,7 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>النزهة</t>
+          <t>المنصورية</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr"/>
@@ -3602,7 +3674,7 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>الرويسي</t>
+          <t>الدراسة</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr"/>
@@ -3615,7 +3687,7 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>قصر النيل</t>
+          <t>درب الجنينة</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
@@ -3628,7 +3700,7 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>الفسطاط</t>
+          <t>الشرابية</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
@@ -3638,10 +3710,10 @@
       <c r="G213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="n"/>
+      <c r="A214" s="5" t="n"/>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>الرحاب</t>
+          <t>النزهة</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
@@ -3651,87 +3723,71 @@
       <c r="G214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>القليوبية</t>
-        </is>
-      </c>
+      <c r="A215" s="5" t="n"/>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>بنها</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب برج مكة</t>
-        </is>
-      </c>
+          <t>الرويسي</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr"/>
       <c r="D215" s="4" t="inlineStr"/>
       <c r="E215" s="4" t="inlineStr"/>
       <c r="F215" s="4" t="inlineStr"/>
-      <c r="G215" s="4" t="inlineStr">
-        <is>
-          <t>شارع جميل أمام بنك القاهرة</t>
-        </is>
-      </c>
+      <c r="G215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
-      <c r="B216" s="5" t="n"/>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الجزار</t>
-        </is>
-      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>قصر النيل</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr"/>
       <c r="D216" s="4" t="inlineStr"/>
       <c r="E216" s="4" t="inlineStr"/>
       <c r="F216" s="4" t="inlineStr"/>
-      <c r="G216" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
-      <c r="B217" s="5" t="n"/>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العمار</t>
-        </is>
-      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>الفسطاط</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr"/>
       <c r="D217" s="4" t="inlineStr"/>
       <c r="E217" s="4" t="inlineStr"/>
       <c r="F217" s="4" t="inlineStr"/>
-      <c r="G217" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="n"/>
-      <c r="B218" s="5" t="n"/>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مساكن اسكو</t>
-        </is>
-      </c>
+      <c r="A218" s="6" t="n"/>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>الرحاب</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr"/>
       <c r="D218" s="4" t="inlineStr"/>
       <c r="E218" s="4" t="inlineStr"/>
       <c r="F218" s="4" t="inlineStr"/>
-      <c r="G218" s="4" t="inlineStr">
+      <c r="G218" s="4" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>القليوبية</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
         <is>
           <t>بنها</t>
         </is>
       </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="5" t="n"/>
-      <c r="B219" s="6" t="n"/>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب الأحراز</t>
+          <t>مركز تخاطب برج مكة</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr"/>
@@ -3739,33 +3795,33 @@
       <c r="F219" s="4" t="inlineStr"/>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>بنها</t>
+          <t>شارع جميل أمام بنك القاهرة</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>قليوب</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الجزار</t>
+        </is>
+      </c>
       <c r="D220" s="4" t="inlineStr"/>
       <c r="E220" s="4" t="inlineStr"/>
       <c r="F220" s="4" t="inlineStr"/>
-      <c r="G220" s="4" t="inlineStr"/>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>شبرا الخيمة</t>
-        </is>
-      </c>
+      <c r="B221" s="6" t="n"/>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
+          <t>مركز شباب العمار</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr"/>
@@ -3773,33 +3829,33 @@
       <c r="F221" s="4" t="inlineStr"/>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>75 شارع حنفي الشيخوني</t>
+          <t>بنها</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
-      <c r="B222" s="5" t="n"/>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>مركز النور الهدى الطبي</t>
-        </is>
-      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>قليوب</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr"/>
       <c r="D222" s="4" t="inlineStr"/>
       <c r="E222" s="4" t="inlineStr"/>
       <c r="F222" s="4" t="inlineStr"/>
-      <c r="G222" s="4" t="inlineStr">
-        <is>
-          <t>شارع محمد القطان</t>
-        </is>
-      </c>
+      <c r="G222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
-      <c r="B223" s="5" t="n"/>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>شبرا الخيمة</t>
+        </is>
+      </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>مركز تواصل للتخاطب</t>
+          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -3807,16 +3863,16 @@
       <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>2 شارع أحمد عبد ربه</t>
+          <t>75 شارع حنفي الشيخوني</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
-      <c r="B224" s="6" t="n"/>
+      <c r="B224" s="5" t="n"/>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>مركز ابني للتخاطب</t>
+          <t>مركز النور الهدى الطبي</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr"/>
@@ -3824,28 +3880,32 @@
       <c r="F224" s="4" t="inlineStr"/>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>شبرا الخيمة</t>
+          <t>شارع محمد القطان</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>الخانكة</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr"/>
+      <c r="B225" s="6" t="n"/>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>مركز تواصل للتخاطب</t>
+        </is>
+      </c>
       <c r="D225" s="4" t="inlineStr"/>
       <c r="E225" s="4" t="inlineStr"/>
       <c r="F225" s="4" t="inlineStr"/>
-      <c r="G225" s="4" t="inlineStr"/>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>2 شارع أحمد عبد ربه</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>رمسيس</t>
+          <t>الخانكة</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr"/>
@@ -3858,7 +3918,7 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>مدينة 10 رمضان</t>
+          <t>رمسيس</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr"/>
@@ -3871,7 +3931,7 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زايد</t>
+          <t>مدينة 10 رمضان</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr"/>
@@ -3884,7 +3944,7 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>القناطر الخيرية</t>
+          <t>الشيخ زايد</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr"/>
@@ -3897,7 +3957,7 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>قها</t>
+          <t>القناطر الخيرية</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr"/>
@@ -3910,7 +3970,7 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>الدقهلية</t>
+          <t>قها</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr"/>
@@ -3923,7 +3983,7 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
+          <t>الدقهلية</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr"/>
@@ -3936,7 +3996,7 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>أوسيم</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr"/>
@@ -3949,7 +4009,7 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>طره</t>
+          <t>أوسيم</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr"/>
@@ -3962,7 +4022,7 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>الخصوص</t>
+          <t>طره</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr"/>
@@ -3972,10 +4032,10 @@
       <c r="G235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="n"/>
+      <c r="A236" s="5" t="n"/>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>القنطرة</t>
+          <t>الخصوص</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr"/>
@@ -3985,14 +4045,10 @@
       <c r="G236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>المنوفية</t>
-        </is>
-      </c>
+      <c r="A237" s="6" t="n"/>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>شبين الكوم</t>
+          <t>القنطرة</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr"/>
@@ -4002,10 +4058,14 @@
       <c r="G237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n"/>
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>المنوفية</t>
+        </is>
+      </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>منوف</t>
+          <t>شبين الكوم</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr"/>
@@ -4018,7 +4078,7 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>شبين القناطر</t>
+          <t>منوف</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr"/>
@@ -4031,7 +4091,7 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>مدينة السادات</t>
+          <t>شبين القناطر</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr"/>
@@ -4044,7 +4104,7 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>باقور</t>
+          <t>مدينة السادات</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -4057,7 +4117,7 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>تلا</t>
+          <t>باقور</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr"/>
@@ -4070,7 +4130,7 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>قويسنا</t>
+          <t>تلا</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr"/>
@@ -4083,75 +4143,75 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>أشمون</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب أشمون للتخاطب</t>
-        </is>
-      </c>
+          <t>قويسنا</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr"/>
       <c r="D244" s="4" t="inlineStr"/>
       <c r="E244" s="4" t="inlineStr"/>
       <c r="F244" s="4" t="inlineStr"/>
-      <c r="G244" s="4" t="inlineStr">
-        <is>
-          <t>أشمون</t>
-        </is>
-      </c>
+      <c r="G244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>البرجايه</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr"/>
+          <t>أشمون</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب أشمون للتخاطب</t>
+        </is>
+      </c>
       <c r="D245" s="4" t="inlineStr"/>
       <c r="E245" s="4" t="inlineStr"/>
       <c r="F245" s="4" t="inlineStr"/>
-      <c r="G245" s="4" t="inlineStr"/>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب وصعوبات تعلم</t>
-        </is>
-      </c>
+          <t>البرجايه</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr"/>
       <c r="D246" s="4" t="inlineStr"/>
       <c r="E246" s="4" t="inlineStr"/>
       <c r="F246" s="4" t="inlineStr"/>
-      <c r="G246" s="4" t="inlineStr">
-        <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
+      <c r="G246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>منوف الجديدة</t>
-        </is>
-      </c>
-      <c r="C247" s="4" t="inlineStr"/>
+          <t>بركة السبع</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب وصعوبات تعلم</t>
+        </is>
+      </c>
       <c r="D247" s="4" t="inlineStr"/>
       <c r="E247" s="4" t="inlineStr"/>
       <c r="F247" s="4" t="inlineStr"/>
-      <c r="G247" s="4" t="inlineStr"/>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="6" t="n"/>
+      <c r="A248" s="5" t="n"/>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>منوف الجديدة</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr"/>
@@ -4161,36 +4221,32 @@
       <c r="G248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="A249" s="6" t="n"/>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>المنيا</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب بني أحمد للتخاطب</t>
-        </is>
-      </c>
+          <t>كفر عبده</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr"/>
       <c r="D249" s="4" t="inlineStr"/>
       <c r="E249" s="4" t="inlineStr"/>
       <c r="F249" s="4" t="inlineStr"/>
-      <c r="G249" s="4" t="inlineStr">
+      <c r="G249" s="4" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>المنيا</t>
         </is>
       </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="5" t="n"/>
-      <c r="B250" s="5" t="n"/>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب مقوسة للتخاطب</t>
+          <t>مركز شباب بني أحمد للتخاطب</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr"/>
@@ -4204,10 +4260,10 @@
     </row>
     <row r="251">
       <c r="A251" s="5" t="n"/>
-      <c r="B251" s="5" t="n"/>
+      <c r="B251" s="6" t="n"/>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>مركز المعجزة للتخاطب وتأهيل الإعاقة</t>
+          <t>مركز شباب مقوسة للتخاطب</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr"/>
@@ -4215,36 +4271,28 @@
       <c r="F251" s="4" t="inlineStr"/>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>شارع العرفاني، الملوي</t>
+          <t>المنيا</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n"/>
-      <c r="B252" s="6" t="n"/>
-      <c r="C252" s="4" t="inlineStr">
-        <is>
-          <t>مركز الحياة للتخاطب</t>
-        </is>
-      </c>
-      <c r="D252" s="4" t="inlineStr">
-        <is>
-          <t>د. مي عادل عبد الرشيد</t>
-        </is>
-      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>سمالوط</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr"/>
+      <c r="D252" s="4" t="inlineStr"/>
       <c r="E252" s="4" t="inlineStr"/>
       <c r="F252" s="4" t="inlineStr"/>
-      <c r="G252" s="4" t="inlineStr">
-        <is>
-          <t>الملوي</t>
-        </is>
-      </c>
+      <c r="G252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>سمالوط</t>
+          <t>بني حسن</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr"/>
@@ -4257,7 +4305,7 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>بني حسن</t>
+          <t>هرموبوليس</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr"/>
@@ -4270,7 +4318,7 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>هرموبوليس</t>
+          <t>ملوي</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr"/>
@@ -4283,7 +4331,7 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>ملوي</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr"/>
@@ -4296,7 +4344,7 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>ديروط الشريف</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr"/>
@@ -4309,7 +4357,7 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>ديروط الشريف</t>
+          <t>أبوقرقاص</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr"/>
@@ -4322,7 +4370,7 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>أبوقرقاص</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr"/>
@@ -4335,7 +4383,7 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>بني مازن</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr"/>
@@ -4345,10 +4393,10 @@
       <c r="G260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="n"/>
+      <c r="A261" s="6" t="n"/>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>بني مازن</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr"/>
@@ -4358,32 +4406,40 @@
       <c r="G261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="6" t="n"/>
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>الوادي الجديد</t>
+        </is>
+      </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr"/>
+          <t>الخارجة</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب الخارجة للتخاطب</t>
+        </is>
+      </c>
       <c r="D262" s="4" t="inlineStr"/>
       <c r="E262" s="4" t="inlineStr"/>
       <c r="F262" s="4" t="inlineStr"/>
-      <c r="G262" s="4" t="inlineStr"/>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>الخارجة</t>
+        </is>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>الوادي الجديد</t>
-        </is>
-      </c>
+      <c r="A263" s="5" t="n"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>الخارجة</t>
+          <t>الداخلة</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب الخارجة للتخاطب</t>
+          <t>مركز شباب باريس للتخاطب</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr"/>
@@ -4391,7 +4447,7 @@
       <c r="F263" s="4" t="inlineStr"/>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>الخارجة</t>
+          <t>باريس</t>
         </is>
       </c>
     </row>
@@ -4399,49 +4455,33 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب باريس للتخاطب</t>
-        </is>
-      </c>
+          <t>موط</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr"/>
       <c r="D264" s="4" t="inlineStr"/>
       <c r="E264" s="4" t="inlineStr"/>
       <c r="F264" s="4" t="inlineStr"/>
-      <c r="G264" s="4" t="inlineStr">
-        <is>
-          <t>باريس</t>
-        </is>
-      </c>
+      <c r="G264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>موط</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بموط</t>
-        </is>
-      </c>
+          <t>بلاط</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr"/>
       <c r="D265" s="4" t="inlineStr"/>
       <c r="E265" s="4" t="inlineStr"/>
       <c r="F265" s="4" t="inlineStr"/>
-      <c r="G265" s="4" t="inlineStr">
-        <is>
-          <t>موط</t>
-        </is>
-      </c>
+      <c r="G265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>بلاط</t>
+          <t>فرافرة</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr"/>
@@ -4454,7 +4494,7 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>فرافرة</t>
+          <t>باريس</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr"/>
@@ -4467,7 +4507,7 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr"/>
@@ -4480,7 +4520,7 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>تينيدة</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr"/>
@@ -4490,10 +4530,10 @@
       <c r="G269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="n"/>
+      <c r="A270" s="6" t="n"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>تينيدة</t>
+          <t>دوش</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr"/>
@@ -4503,48 +4543,48 @@
       <c r="G270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="n"/>
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>دوش</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr"/>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العبور للتخاطب</t>
+        </is>
+      </c>
       <c r="D271" s="4" t="inlineStr"/>
       <c r="E271" s="4" t="inlineStr"/>
       <c r="F271" s="4" t="inlineStr"/>
-      <c r="G271" s="4" t="inlineStr"/>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="A272" s="5" t="n"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العبور للتخاطب</t>
-        </is>
-      </c>
+          <t>الفشن</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr"/>
       <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr"/>
       <c r="F272" s="4" t="inlineStr"/>
-      <c r="G272" s="4" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="G272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>ساماستا</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr"/>
@@ -4557,7 +4597,7 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>ساماستا</t>
+          <t>إبشواي</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr"/>
@@ -4570,7 +4610,7 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>إبشواي</t>
+          <t>الجندية</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr"/>
@@ -4583,7 +4623,7 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>الجندية</t>
+          <t>ناصر</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr"/>
@@ -4596,7 +4636,7 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>ناصر</t>
+          <t>هواره</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr"/>
@@ -4609,7 +4649,7 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>هواره</t>
+          <t>موشية</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr"/>
@@ -4622,7 +4662,7 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>موشية</t>
+          <t>نصار البحرية</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr"/>
@@ -4632,10 +4672,10 @@
       <c r="G279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="n"/>
+      <c r="A280" s="6" t="n"/>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>نصار البحرية</t>
+          <t>أحمد حمزة</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr"/>
@@ -4645,10 +4685,14 @@
       <c r="G280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="n"/>
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>أحمد حمزة</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr"/>
@@ -4658,14 +4702,10 @@
       <c r="G281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>بورسعيد</t>
-        </is>
-      </c>
+      <c r="A282" s="5" t="n"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>بورفؤاد</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr"/>
@@ -4678,7 +4718,7 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>بورفؤاد</t>
+          <t>الجميل</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr"/>
@@ -4691,7 +4731,7 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>الجميل</t>
+          <t>الزهور</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr"/>
@@ -4704,7 +4744,7 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>الزهور</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr"/>
@@ -4717,7 +4757,7 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>الكنتاوي</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr"/>
@@ -4727,10 +4767,10 @@
       <c r="G286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="n"/>
+      <c r="A287" s="6" t="n"/>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>الكنتاوي</t>
+          <t>الضواحي</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr"/>
@@ -4740,10 +4780,14 @@
       <c r="G287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="6" t="n"/>
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>الضواحي</t>
+          <t>شرم الشيخ</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr"/>
@@ -4753,14 +4797,10 @@
       <c r="G288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>جنوب سيناء</t>
-        </is>
-      </c>
+      <c r="A289" s="5" t="n"/>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>شرم الشيخ</t>
+          <t>داهب</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr"/>
@@ -4773,7 +4813,7 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>داهب</t>
+          <t>نويبع</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr"/>
@@ -4786,7 +4826,7 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>نويبع</t>
+          <t>سانت كاترين</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr"/>
@@ -4799,7 +4839,7 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>سانت كاترين</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr"/>
@@ -4812,7 +4852,7 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>رأس محمد</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr"/>
@@ -4825,7 +4865,7 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>رأس محمد</t>
+          <t>أم سيد</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr"/>
@@ -4835,10 +4875,10 @@
       <c r="G294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="n"/>
+      <c r="A295" s="6" t="n"/>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>أم سيد</t>
+          <t>مدينة شرم الشيخ</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr"/>
@@ -4848,10 +4888,14 @@
       <c r="G295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="n"/>
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>مدينة شرم الشيخ</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr"/>
@@ -4861,14 +4905,10 @@
       <c r="G296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
+      <c r="A297" s="5" t="n"/>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr"/>
@@ -4881,7 +4921,7 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>واحة الفيوم</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr"/>
@@ -4894,7 +4934,7 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>واحة الفيوم</t>
+          <t>وادي حوف</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr"/>
@@ -4907,7 +4947,7 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>وادي حوف</t>
+          <t>عين سخنة</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr"/>
@@ -4920,7 +4960,7 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>عين سخنة</t>
+          <t>الطور</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr"/>
@@ -4933,7 +4973,7 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr"/>
@@ -4943,10 +4983,10 @@
       <c r="G302" s="4" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="n"/>
+      <c r="A303" s="6" t="n"/>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr"/>
@@ -4956,48 +4996,48 @@
       <c r="G303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="6" t="n"/>
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
-        </is>
-      </c>
-      <c r="C304" s="4" t="inlineStr"/>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>مركز حلم ابني للتخاطب</t>
+        </is>
+      </c>
       <c r="D304" s="4" t="inlineStr"/>
       <c r="E304" s="4" t="inlineStr"/>
       <c r="F304" s="4" t="inlineStr"/>
-      <c r="G304" s="4" t="inlineStr"/>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>دمياط ودمياط الجديدة</t>
+        </is>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
+      <c r="A305" s="5" t="n"/>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>مركز حلم ابني للتخاطب</t>
-        </is>
-      </c>
+          <t>دمياط الجديدة</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr"/>
       <c r="D305" s="4" t="inlineStr"/>
       <c r="E305" s="4" t="inlineStr"/>
       <c r="F305" s="4" t="inlineStr"/>
-      <c r="G305" s="4" t="inlineStr">
-        <is>
-          <t>دمياط ودمياط الجديدة</t>
-        </is>
-      </c>
+      <c r="G305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>دمياط الجديدة</t>
+          <t>بورت فؤاد</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr"/>
@@ -5010,7 +5050,7 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>بورت فؤاد</t>
+          <t>كفر البطة</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr"/>
@@ -5023,7 +5063,7 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>كفر البطة</t>
+          <t>كفر سعيد</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr"/>
@@ -5036,7 +5076,7 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>كفر سعيد</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr"/>
@@ -5049,7 +5089,7 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>الزرقا</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr"/>
@@ -5062,7 +5102,7 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>الزرقا</t>
+          <t>فارسكور</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr"/>
@@ -5072,10 +5112,10 @@
       <c r="G311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="5" t="n"/>
+      <c r="A312" s="6" t="n"/>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>فارسكور</t>
+          <t>رومانية</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr"/>
@@ -5085,53 +5125,77 @@
       <c r="G312" s="4" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="6" t="n"/>
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>شمال سيناء</t>
+        </is>
+      </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>رومانية</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr"/>
+          <t>العريش</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش للتخاطب</t>
+        </is>
+      </c>
       <c r="D313" s="4" t="inlineStr"/>
       <c r="E313" s="4" t="inlineStr"/>
       <c r="F313" s="4" t="inlineStr"/>
-      <c r="G313" s="4" t="inlineStr"/>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش</t>
+        </is>
+      </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>شمال سيناء</t>
-        </is>
-      </c>
+      <c r="A314" s="5" t="n"/>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>العريش</t>
-        </is>
-      </c>
-      <c r="C314" s="4" t="inlineStr"/>
+          <t>رفح</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب رفح</t>
+        </is>
+      </c>
       <c r="D314" s="4" t="inlineStr"/>
       <c r="E314" s="4" t="inlineStr"/>
       <c r="F314" s="4" t="inlineStr"/>
-      <c r="G314" s="4" t="inlineStr"/>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>رفح</t>
-        </is>
-      </c>
-      <c r="C315" s="4" t="inlineStr"/>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
+        </is>
+      </c>
       <c r="D315" s="4" t="inlineStr"/>
       <c r="E315" s="4" t="inlineStr"/>
       <c r="F315" s="4" t="inlineStr"/>
-      <c r="G315" s="4" t="inlineStr"/>
+      <c r="G315" s="4" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زويد</t>
+          <t>بئر العبد</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr"/>
@@ -5144,7 +5208,7 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>بئر العبد</t>
+          <t>القنطرة، سيناء</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr"/>
@@ -5157,7 +5221,7 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>القنطرة، سيناء</t>
+          <t>نخل</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr"/>
@@ -5170,7 +5234,7 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>نخل</t>
+          <t>جديدة، حسنة</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr"/>
@@ -5183,7 +5247,7 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>جديدة، حسنة</t>
+          <t>دهب الشرقية</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr"/>
@@ -5193,10 +5257,10 @@
       <c r="G320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="n"/>
+      <c r="A321" s="6" t="n"/>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>دهب الشرقية</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr"/>
@@ -5206,32 +5270,36 @@
       <c r="G321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="n"/>
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
-        </is>
-      </c>
-      <c r="C322" s="4" t="inlineStr"/>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمدينة العمال</t>
+        </is>
+      </c>
       <c r="D322" s="4" t="inlineStr"/>
       <c r="E322" s="4" t="inlineStr"/>
       <c r="F322" s="4" t="inlineStr"/>
-      <c r="G322" s="4" t="inlineStr"/>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>مدينة العمال، قنا</t>
+        </is>
+      </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
-      <c r="B323" s="3" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="A323" s="5" t="n"/>
+      <c r="B323" s="6" t="n"/>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>مركز التخاطب بمدينة العمال</t>
+          <t>مركز شباب حجير خزام</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr"/>
@@ -5239,49 +5307,41 @@
       <c r="F323" s="4" t="inlineStr"/>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>مدينة العمال، قنا</t>
+          <t>قنا</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="n"/>
-      <c r="B324" s="5" t="n"/>
-      <c r="C324" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب حجير خزام</t>
-        </is>
-      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>نجع حمادي</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr"/>
       <c r="D324" s="4" t="inlineStr"/>
       <c r="E324" s="4" t="inlineStr"/>
       <c r="F324" s="4" t="inlineStr"/>
-      <c r="G324" s="4" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="G324" s="4" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="5" t="n"/>
-      <c r="B325" s="6" t="n"/>
-      <c r="C325" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب نجا سلمة</t>
-        </is>
-      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>دندرة</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr"/>
       <c r="D325" s="4" t="inlineStr"/>
       <c r="E325" s="4" t="inlineStr"/>
       <c r="F325" s="4" t="inlineStr"/>
-      <c r="G325" s="4" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="G325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>نجع حمادي</t>
+          <t>أبيدوس</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr"/>
@@ -5294,7 +5354,7 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>دندرة</t>
+          <t>قفطي</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr"/>
@@ -5307,7 +5367,7 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>أبيدوس</t>
+          <t>أخميم</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr"/>
@@ -5320,7 +5380,7 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>قفطي</t>
+          <t>سوهاج القديمة</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr"/>
@@ -5333,7 +5393,7 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>أخميم</t>
+          <t>النجع البحري</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr"/>
@@ -5343,10 +5403,10 @@
       <c r="G330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="5" t="n"/>
+      <c r="A331" s="6" t="n"/>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>سوهاج القديمة</t>
+          <t>الشنقي</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr"/>
@@ -5356,95 +5416,95 @@
       <c r="G331" s="4" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="5" t="n"/>
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>النجع البحري</t>
-        </is>
-      </c>
-      <c r="C332" s="4" t="inlineStr"/>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الشيخ للتخاطب</t>
+        </is>
+      </c>
       <c r="D332" s="4" t="inlineStr"/>
       <c r="E332" s="4" t="inlineStr"/>
       <c r="F332" s="4" t="inlineStr"/>
-      <c r="G332" s="4" t="inlineStr"/>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
     </row>
     <row r="333">
-      <c r="A333" s="6" t="n"/>
+      <c r="A333" s="5" t="n"/>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>الشنقي</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="inlineStr"/>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
+        </is>
+      </c>
       <c r="D333" s="4" t="inlineStr"/>
       <c r="E333" s="4" t="inlineStr"/>
       <c r="F333" s="4" t="inlineStr"/>
-      <c r="G333" s="4" t="inlineStr"/>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
+        </is>
+      </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="A334" s="5" t="n"/>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="C334" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الشيخ للتخاطب</t>
-        </is>
-      </c>
+          <t>بلامون</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr"/>
       <c r="D334" s="4" t="inlineStr"/>
       <c r="E334" s="4" t="inlineStr"/>
       <c r="F334" s="4" t="inlineStr"/>
-      <c r="G334" s="4" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="G334" s="4" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="5" t="n"/>
-      <c r="B335" s="5" t="n"/>
-      <c r="C335" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب قبريط للتخاطب</t>
-        </is>
-      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr"/>
       <c r="D335" s="4" t="inlineStr"/>
       <c r="E335" s="4" t="inlineStr"/>
       <c r="F335" s="4" t="inlineStr"/>
-      <c r="G335" s="4" t="inlineStr">
-        <is>
-          <t>قبريط</t>
-        </is>
-      </c>
+      <c r="G335" s="4" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="5" t="n"/>
-      <c r="B336" s="6" t="n"/>
-      <c r="C336" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب سيدي سالم للتخاطب</t>
-        </is>
-      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>سيدي سالم</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr"/>
       <c r="D336" s="4" t="inlineStr"/>
       <c r="E336" s="4" t="inlineStr"/>
       <c r="F336" s="4" t="inlineStr"/>
-      <c r="G336" s="4" t="inlineStr">
-        <is>
-          <t>سيدي سالم</t>
-        </is>
-      </c>
+      <c r="G336" s="4" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>دسوق</t>
+          <t>الحامول</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr"/>
@@ -5457,7 +5517,7 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>بلامون</t>
+          <t>برج البرلس</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr"/>
@@ -5470,7 +5530,7 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>الرياض</t>
+          <t>مطوبس</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr"/>
@@ -5483,7 +5543,7 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>سيدي سالم</t>
+          <t>المحمودية</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr"/>
@@ -5493,10 +5553,10 @@
       <c r="G340" s="4" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="5" t="n"/>
+      <c r="A341" s="6" t="n"/>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>الحامول</t>
+          <t>بيلا</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr"/>
@@ -5506,10 +5566,14 @@
       <c r="G341" s="4" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="5" t="n"/>
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>برج البرلس</t>
+          <t>مطروح</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr"/>
@@ -5519,10 +5583,14 @@
       <c r="G342" s="4" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="5" t="n"/>
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>مطوبس</t>
+          <t>سيوه</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr"/>
@@ -5532,10 +5600,14 @@
       <c r="G343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="5" t="n"/>
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>المحمودية</t>
+          <t>السلوم</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr"/>
@@ -5545,10 +5617,14 @@
       <c r="G344" s="4" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="6" t="n"/>
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>بيلا</t>
+          <t>سيدي براني</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr"/>
@@ -5565,22 +5641,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="C346" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مطروح للتخاطب (تحت الإنشاء)</t>
-        </is>
-      </c>
+          <t>العلمين</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr"/>
       <c r="D346" s="4" t="inlineStr"/>
       <c r="E346" s="4" t="inlineStr"/>
       <c r="F346" s="4" t="inlineStr"/>
-      <c r="G346" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مطروح</t>
-        </is>
-      </c>
+      <c r="G346" s="4" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -5590,7 +5658,7 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>سيوه</t>
+          <t>مارينا</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr"/>
@@ -5607,7 +5675,7 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>السلوم</t>
+          <t>توريدو</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr"/>
@@ -5624,7 +5692,7 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>سيدي براني</t>
+          <t>جنوب سيوه</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr"/>
@@ -5641,7 +5709,7 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>العلمين</t>
+          <t>شمال سيوه</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr"/>
@@ -5658,7 +5726,7 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>مارينا</t>
+          <t>كشته</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr"/>
@@ -5666,74 +5734,6 @@
       <c r="E351" s="4" t="inlineStr"/>
       <c r="F351" s="4" t="inlineStr"/>
       <c r="G351" s="4" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>توريدو</t>
-        </is>
-      </c>
-      <c r="C352" s="4" t="inlineStr"/>
-      <c r="D352" s="4" t="inlineStr"/>
-      <c r="E352" s="4" t="inlineStr"/>
-      <c r="F352" s="4" t="inlineStr"/>
-      <c r="G352" s="4" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B353" s="3" t="inlineStr">
-        <is>
-          <t>جنوب سيوه</t>
-        </is>
-      </c>
-      <c r="C353" s="4" t="inlineStr"/>
-      <c r="D353" s="4" t="inlineStr"/>
-      <c r="E353" s="4" t="inlineStr"/>
-      <c r="F353" s="4" t="inlineStr"/>
-      <c r="G353" s="4" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B354" s="3" t="inlineStr">
-        <is>
-          <t>شمال سيوه</t>
-        </is>
-      </c>
-      <c r="C354" s="4" t="inlineStr"/>
-      <c r="D354" s="4" t="inlineStr"/>
-      <c r="E354" s="4" t="inlineStr"/>
-      <c r="F354" s="4" t="inlineStr"/>
-      <c r="G354" s="4" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B355" s="3" t="inlineStr">
-        <is>
-          <t>كشته</t>
-        </is>
-      </c>
-      <c r="C355" s="4" t="inlineStr"/>
-      <c r="D355" s="4" t="inlineStr"/>
-      <c r="E355" s="4" t="inlineStr"/>
-      <c r="F355" s="4" t="inlineStr"/>
-      <c r="G355" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="313">
@@ -5741,10 +5741,10 @@
     <mergeCell ref="B133"/>
     <mergeCell ref="B204"/>
     <mergeCell ref="B198"/>
-    <mergeCell ref="B334:B336"/>
-    <mergeCell ref="B149:B154"/>
+    <mergeCell ref="B296"/>
     <mergeCell ref="B4"/>
     <mergeCell ref="B75"/>
+    <mergeCell ref="B135"/>
     <mergeCell ref="B306"/>
     <mergeCell ref="B62"/>
     <mergeCell ref="B233"/>
@@ -5753,128 +5753,136 @@
     <mergeCell ref="B199"/>
     <mergeCell ref="B291"/>
     <mergeCell ref="B70"/>
-    <mergeCell ref="A314:A322"/>
     <mergeCell ref="B228"/>
-    <mergeCell ref="A323:A333"/>
-    <mergeCell ref="A149:A162"/>
     <mergeCell ref="B293"/>
-    <mergeCell ref="B215:B219"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A219:A237"/>
     <mergeCell ref="B17"/>
     <mergeCell ref="B88"/>
     <mergeCell ref="B82"/>
+    <mergeCell ref="B152:B156"/>
     <mergeCell ref="B19"/>
     <mergeCell ref="B146"/>
     <mergeCell ref="B317"/>
+    <mergeCell ref="B217"/>
+    <mergeCell ref="B65"/>
     <mergeCell ref="B83"/>
     <mergeCell ref="B344"/>
     <mergeCell ref="B319"/>
     <mergeCell ref="B123"/>
     <mergeCell ref="B110"/>
+    <mergeCell ref="A262:A270"/>
     <mergeCell ref="B141"/>
+    <mergeCell ref="B248"/>
     <mergeCell ref="B297"/>
     <mergeCell ref="B235"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B312"/>
+    <mergeCell ref="B14"/>
     <mergeCell ref="B299"/>
     <mergeCell ref="B78"/>
     <mergeCell ref="B243"/>
     <mergeCell ref="B314"/>
+    <mergeCell ref="A332:A341"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B325"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="B91"/>
     <mergeCell ref="B25"/>
-    <mergeCell ref="B156"/>
     <mergeCell ref="B327"/>
-    <mergeCell ref="B155"/>
-    <mergeCell ref="B220"/>
+    <mergeCell ref="A178:A218"/>
+    <mergeCell ref="B149"/>
     <mergeCell ref="B247"/>
-    <mergeCell ref="B182"/>
+    <mergeCell ref="B223:B225"/>
+    <mergeCell ref="B262"/>
     <mergeCell ref="B84"/>
     <mergeCell ref="B246"/>
     <mergeCell ref="B40"/>
     <mergeCell ref="B338"/>
     <mergeCell ref="B15"/>
+    <mergeCell ref="B313"/>
     <mergeCell ref="B104"/>
     <mergeCell ref="B340"/>
     <mergeCell ref="B79"/>
     <mergeCell ref="B315"/>
     <mergeCell ref="B302"/>
-    <mergeCell ref="B106"/>
     <mergeCell ref="B81"/>
+    <mergeCell ref="B252"/>
     <mergeCell ref="B208"/>
-    <mergeCell ref="A334:A345"/>
     <mergeCell ref="B210"/>
     <mergeCell ref="B318"/>
     <mergeCell ref="B170"/>
     <mergeCell ref="B157"/>
     <mergeCell ref="B328"/>
-    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B333"/>
     <mergeCell ref="B234"/>
+    <mergeCell ref="A322:A331"/>
     <mergeCell ref="B172"/>
     <mergeCell ref="B28"/>
-    <mergeCell ref="B270"/>
     <mergeCell ref="B99"/>
     <mergeCell ref="B186"/>
+    <mergeCell ref="B137:B139"/>
     <mergeCell ref="B257"/>
     <mergeCell ref="B30"/>
-    <mergeCell ref="A34:A56"/>
+    <mergeCell ref="A115:A128"/>
     <mergeCell ref="B265"/>
     <mergeCell ref="B54"/>
-    <mergeCell ref="B321"/>
     <mergeCell ref="B125"/>
-    <mergeCell ref="B249:B252"/>
-    <mergeCell ref="B145"/>
+    <mergeCell ref="B56"/>
+    <mergeCell ref="B176"/>
     <mergeCell ref="B120"/>
-    <mergeCell ref="B181"/>
+    <mergeCell ref="B219:B221"/>
     <mergeCell ref="B147"/>
-    <mergeCell ref="A272:A281"/>
     <mergeCell ref="B245"/>
-    <mergeCell ref="A305:A313"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="B207"/>
+    <mergeCell ref="B334"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B113"/>
     <mergeCell ref="B173"/>
-    <mergeCell ref="B163:B165"/>
     <mergeCell ref="B100"/>
-    <mergeCell ref="B115"/>
+    <mergeCell ref="B271"/>
+    <mergeCell ref="B336"/>
     <mergeCell ref="B31"/>
     <mergeCell ref="B202"/>
     <mergeCell ref="B102"/>
     <mergeCell ref="B273"/>
-    <mergeCell ref="A215:A236"/>
+    <mergeCell ref="B39"/>
+    <mergeCell ref="A67:A77"/>
     <mergeCell ref="B191"/>
     <mergeCell ref="B349"/>
-    <mergeCell ref="B128"/>
     <mergeCell ref="B255"/>
     <mergeCell ref="B226"/>
     <mergeCell ref="B49"/>
     <mergeCell ref="B192"/>
     <mergeCell ref="B284"/>
+    <mergeCell ref="B222"/>
+    <mergeCell ref="A313:A321"/>
     <mergeCell ref="B63"/>
     <mergeCell ref="B197"/>
     <mergeCell ref="B50"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A12:A24"/>
+    <mergeCell ref="A78:A92"/>
     <mergeCell ref="B286"/>
-    <mergeCell ref="B261"/>
     <mergeCell ref="B27"/>
-    <mergeCell ref="B166"/>
     <mergeCell ref="B337"/>
-    <mergeCell ref="B116"/>
-    <mergeCell ref="B352"/>
     <mergeCell ref="B103"/>
+    <mergeCell ref="B174"/>
     <mergeCell ref="B230"/>
     <mergeCell ref="B205"/>
-    <mergeCell ref="B168"/>
     <mergeCell ref="B339"/>
     <mergeCell ref="B118"/>
-    <mergeCell ref="A66:A76"/>
     <mergeCell ref="B55"/>
+    <mergeCell ref="A288:A295"/>
     <mergeCell ref="B169"/>
+    <mergeCell ref="B322:B323"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="B129"/>
     <mergeCell ref="B200"/>
+    <mergeCell ref="B134"/>
     <mergeCell ref="B194"/>
     <mergeCell ref="B121"/>
     <mergeCell ref="B292"/>
     <mergeCell ref="B71"/>
     <mergeCell ref="B131"/>
+    <mergeCell ref="B236"/>
     <mergeCell ref="B307"/>
     <mergeCell ref="B58"/>
     <mergeCell ref="B52"/>
@@ -5883,11 +5891,13 @@
     <mergeCell ref="B2"/>
     <mergeCell ref="B195"/>
     <mergeCell ref="B60"/>
+    <mergeCell ref="A58:A66"/>
     <mergeCell ref="B231"/>
-    <mergeCell ref="B287"/>
-    <mergeCell ref="A112:A126"/>
+    <mergeCell ref="A24:A32"/>
     <mergeCell ref="B53"/>
+    <mergeCell ref="A152:A166"/>
     <mergeCell ref="B289"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="B241"/>
     <mergeCell ref="B124"/>
     <mergeCell ref="B142"/>
@@ -5895,159 +5905,149 @@
     <mergeCell ref="B213"/>
     <mergeCell ref="B305"/>
     <mergeCell ref="B188"/>
-    <mergeCell ref="A263:A271"/>
-    <mergeCell ref="B144"/>
+    <mergeCell ref="B126"/>
     <mergeCell ref="B242"/>
     <mergeCell ref="B190"/>
     <mergeCell ref="B46"/>
     <mergeCell ref="B282"/>
+    <mergeCell ref="A271:A280"/>
     <mergeCell ref="B48"/>
     <mergeCell ref="B346"/>
-    <mergeCell ref="A297:A304"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B73"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="B308"/>
-    <mergeCell ref="B221:B224"/>
     <mergeCell ref="B74"/>
-    <mergeCell ref="B68"/>
     <mergeCell ref="B201"/>
-    <mergeCell ref="B139"/>
     <mergeCell ref="B239"/>
     <mergeCell ref="B310"/>
     <mergeCell ref="B5"/>
+    <mergeCell ref="B76"/>
     <mergeCell ref="B203"/>
     <mergeCell ref="B232"/>
+    <mergeCell ref="B150"/>
     <mergeCell ref="B326"/>
+    <mergeCell ref="B215"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="B263"/>
     <mergeCell ref="B244"/>
     <mergeCell ref="B229"/>
-    <mergeCell ref="B23"/>
+    <mergeCell ref="B93:B97"/>
+    <mergeCell ref="A167:A177"/>
     <mergeCell ref="B283"/>
     <mergeCell ref="B87"/>
     <mergeCell ref="B258"/>
-    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="A238:A249"/>
     <mergeCell ref="B298"/>
     <mergeCell ref="B285"/>
     <mergeCell ref="B260"/>
     <mergeCell ref="B64"/>
     <mergeCell ref="B51"/>
-    <mergeCell ref="A175:A214"/>
-    <mergeCell ref="B138"/>
+    <mergeCell ref="B163"/>
     <mergeCell ref="B309"/>
     <mergeCell ref="B209"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B165"/>
     <mergeCell ref="B140"/>
     <mergeCell ref="B311"/>
     <mergeCell ref="B238"/>
-    <mergeCell ref="B77"/>
-    <mergeCell ref="A92:A111"/>
     <mergeCell ref="B253"/>
     <mergeCell ref="B240"/>
+    <mergeCell ref="B33:B38"/>
     <mergeCell ref="A2:A11"/>
     <mergeCell ref="B29"/>
     <mergeCell ref="B158"/>
     <mergeCell ref="B329"/>
     <mergeCell ref="B316"/>
+    <mergeCell ref="B24"/>
     <mergeCell ref="B266"/>
     <mergeCell ref="B89"/>
-    <mergeCell ref="B160"/>
-    <mergeCell ref="B331"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B92:B96"/>
     <mergeCell ref="B26"/>
     <mergeCell ref="B330"/>
-    <mergeCell ref="B97"/>
     <mergeCell ref="B268"/>
+    <mergeCell ref="B324"/>
     <mergeCell ref="B90"/>
     <mergeCell ref="B184"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="B179"/>
+    <mergeCell ref="B148"/>
     <mergeCell ref="B44"/>
+    <mergeCell ref="B304"/>
     <mergeCell ref="B279"/>
-    <mergeCell ref="B108"/>
-    <mergeCell ref="A163:A174"/>
+    <mergeCell ref="B115:B116"/>
     <mergeCell ref="B254"/>
     <mergeCell ref="B143"/>
+    <mergeCell ref="B281"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="B85"/>
     <mergeCell ref="B256"/>
+    <mergeCell ref="A137:A151"/>
+    <mergeCell ref="B160:B162"/>
     <mergeCell ref="B159"/>
-    <mergeCell ref="B135:B137"/>
-    <mergeCell ref="B167"/>
     <mergeCell ref="B272"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B161"/>
     <mergeCell ref="B332"/>
     <mergeCell ref="B259"/>
+    <mergeCell ref="B111"/>
     <mergeCell ref="B98"/>
-    <mergeCell ref="B225"/>
     <mergeCell ref="B274"/>
+    <mergeCell ref="B175"/>
+    <mergeCell ref="A129:A136"/>
     <mergeCell ref="B267"/>
     <mergeCell ref="B269"/>
     <mergeCell ref="B187"/>
-    <mergeCell ref="A249:A262"/>
+    <mergeCell ref="B178:B182"/>
     <mergeCell ref="B189"/>
     <mergeCell ref="B45"/>
+    <mergeCell ref="B216"/>
     <mergeCell ref="B343"/>
     <mergeCell ref="B109"/>
-    <mergeCell ref="B280"/>
     <mergeCell ref="B47"/>
-    <mergeCell ref="B351"/>
+    <mergeCell ref="B345"/>
     <mergeCell ref="B59"/>
     <mergeCell ref="B22"/>
     <mergeCell ref="B193"/>
     <mergeCell ref="B264"/>
     <mergeCell ref="B320"/>
-    <mergeCell ref="B295"/>
-    <mergeCell ref="A237:A248"/>
+    <mergeCell ref="A296:A303"/>
     <mergeCell ref="B86"/>
     <mergeCell ref="B101"/>
-    <mergeCell ref="A77:A91"/>
+    <mergeCell ref="A304:A312"/>
+    <mergeCell ref="A281:A287"/>
     <mergeCell ref="B211"/>
+    <mergeCell ref="B144:B145"/>
     <mergeCell ref="B300"/>
     <mergeCell ref="B183"/>
     <mergeCell ref="B275"/>
-    <mergeCell ref="B41"/>
+    <mergeCell ref="B164"/>
+    <mergeCell ref="B335"/>
     <mergeCell ref="B212"/>
     <mergeCell ref="B206"/>
     <mergeCell ref="B277"/>
-    <mergeCell ref="B180"/>
+    <mergeCell ref="A250:A261"/>
     <mergeCell ref="B130"/>
     <mergeCell ref="B117"/>
-    <mergeCell ref="B353"/>
     <mergeCell ref="B61"/>
     <mergeCell ref="B132"/>
     <mergeCell ref="B119"/>
     <mergeCell ref="B290"/>
     <mergeCell ref="B69"/>
     <mergeCell ref="B196"/>
-    <mergeCell ref="B354"/>
+    <mergeCell ref="B112"/>
+    <mergeCell ref="A33:A57"/>
+    <mergeCell ref="B288"/>
     <mergeCell ref="B348"/>
     <mergeCell ref="B127"/>
-    <mergeCell ref="A25:A33"/>
-    <mergeCell ref="A127:A134"/>
-    <mergeCell ref="A135:A148"/>
-    <mergeCell ref="A282:A288"/>
-    <mergeCell ref="A289:A296"/>
-    <mergeCell ref="B237"/>
     <mergeCell ref="B185"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
     <mergeCell ref="B301"/>
     <mergeCell ref="B122"/>
-    <mergeCell ref="B175:B178"/>
+    <mergeCell ref="B106:B108"/>
     <mergeCell ref="B105"/>
     <mergeCell ref="B276"/>
-    <mergeCell ref="B43"/>
+    <mergeCell ref="B214"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="B347"/>
-    <mergeCell ref="B341"/>
-    <mergeCell ref="B323:B325"/>
-    <mergeCell ref="B303"/>
-    <mergeCell ref="B107"/>
     <mergeCell ref="B278"/>
-    <mergeCell ref="B57"/>
+    <mergeCell ref="A93:A114"/>
     <mergeCell ref="B171"/>
     <mergeCell ref="B342"/>
   </mergeCells>

--- a/Egyptian_Speech_Therapy_Centers.xlsx
+++ b/Egyptian_Speech_Therapy_Centers.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:G360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
+      <c r="B37" s="6" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>أكاديمية زويل</t>
@@ -1087,26 +1087,22 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>جمعية إشراق الشمس</t>
-        </is>
-      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>برج العرب</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>الإسكندرية</t>
-        </is>
-      </c>
+      <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>برج العرب</t>
+          <t>مونتازا</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1119,25 +1115,29 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>مونتازا</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
+          <t>سيدي بشر</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>مركز كلام عيال للتخاطب وتنمية مهارات</t>
+        </is>
+      </c>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>144 شارع جمال عبد الناصر سيدي بشر</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>سيدي بشر</t>
-        </is>
-      </c>
+      <c r="B41" s="5" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>مركز كلام عيال للتخاطب وتنمية مهارات</t>
+          <t>عيادة تخاطب شارع الطفولة السعيدة</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr"/>
@@ -1145,16 +1145,16 @@
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>144 شارع جمال عبد الناصر سيدي بشر</t>
+          <t>شارع الطفولة السعيدة، سيدي بشر</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
+      <c r="B42" s="6" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>عيادة تخاطب شارع الطفولة السعيدة</t>
+          <t>مركز تومورو للتخاطب</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
@@ -1162,32 +1162,28 @@
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>شارع الطفولة السعيدة، سيدي بشر</t>
+          <t>البيطاش وسيدي بشر والجيزة</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>مركز تومورو للتخاطب</t>
-        </is>
-      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>أبي قير</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>البيطاش وسيدي بشر والجيزة</t>
-        </is>
-      </c>
+      <c r="G43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>أبي قير</t>
+          <t>الدخيلة</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1200,7 +1196,7 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>الدخيلة</t>
+          <t>كوم الدكة</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1213,7 +1209,7 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>كوم الدكة</t>
+          <t>ستانلي</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1226,7 +1222,7 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>ستانلي</t>
+          <t>الشاطبي</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -1239,7 +1235,7 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>الشاطبي</t>
+          <t>رشدي</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -1252,7 +1248,7 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>رشدي</t>
+          <t>الرملة</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -1265,7 +1261,7 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>الرملة</t>
+          <t>الإبراهيمية</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -1278,7 +1274,7 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>الإبراهيمية</t>
+          <t>القنطرة</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -1291,7 +1287,7 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>القنطرة</t>
+          <t>كفر عبده</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -1304,7 +1300,7 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>الحمام</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -1317,7 +1313,7 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>الحمام</t>
+          <t>مارينا</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -1330,7 +1326,7 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>مارينا</t>
+          <t>عمومية</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -1340,10 +1336,10 @@
       <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n"/>
+      <c r="A56" s="6" t="n"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>عمومية</t>
+          <t>ضواحي</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -1353,10 +1349,14 @@
       <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>الإسماعيلية</t>
+        </is>
+      </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ضواحي</t>
+          <t>الإسماعيلية</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -1366,14 +1366,10 @@
       <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>الإسماعيلية</t>
-        </is>
-      </c>
+      <c r="A58" s="5" t="n"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>الإسماعيلية</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -1386,7 +1382,7 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>السويس</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -1399,7 +1395,7 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>السويس</t>
+          <t>القنطرة غرب</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -1412,7 +1408,7 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>القنطرة غرب</t>
+          <t>القنطرة شرق</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -1425,7 +1421,7 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>القنطرة شرق</t>
+          <t>فايد</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -1438,7 +1434,7 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>فايد</t>
+          <t>تل الكبير</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -1451,7 +1447,7 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>تل الكبير</t>
+          <t>الشلوفة</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -1461,10 +1457,10 @@
       <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n"/>
+      <c r="A65" s="6" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>الشلوفة</t>
+          <t>الدفرسوار</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -1474,32 +1470,36 @@
       <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>البحر الأحمر</t>
+        </is>
+      </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>الدفرسوار</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr"/>
+          <t>الغردقة</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الغردقة بمركز شباب الغردقة</t>
+        </is>
+      </c>
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب الغردقة</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>البحر الأحمر</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>الغردقة</t>
-        </is>
-      </c>
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="6" t="n"/>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>مركز تخاطب الغردقة بمركز شباب الغردقة</t>
+          <t>مركز تخاطب سفاجة</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -1507,32 +1507,28 @@
       <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب الغردقة</t>
+          <t>سفاجة</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب سفاجة</t>
-        </is>
-      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>سفاجة</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>سفاجة</t>
-        </is>
-      </c>
+      <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>سفاجة</t>
+          <t>القصير</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -1545,7 +1541,7 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>القصير</t>
+          <t>مرسى علم</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -1558,7 +1554,7 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>مرسى علم</t>
+          <t>شلاتين</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -1571,7 +1567,7 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>شلاتين</t>
+          <t>حلايب</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -1584,7 +1580,7 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>حلايب</t>
+          <t>أبو رماد</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -1597,7 +1593,7 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>أبو رماد</t>
+          <t>قصير الجديدة</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -1610,7 +1606,7 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>قصير الجديدة</t>
+          <t>رأس غارب</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -1620,10 +1616,10 @@
       <c r="G75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n"/>
+      <c r="A76" s="6" t="n"/>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>رأس غارب</t>
+          <t>دهب</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -1633,82 +1629,82 @@
       <c r="G76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>البحيرة</t>
+        </is>
+      </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>دهب</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
+          <t>دمنهور</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>مركز لايف للتخاطب</t>
+        </is>
+      </c>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>21 شارع إبراهيم مظهر، ميدان الساعة</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>البحيرة</t>
-        </is>
-      </c>
+      <c r="A78" s="5" t="n"/>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>دمنهور</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>مركز لايف للتخاطب</t>
-        </is>
-      </c>
+          <t>كفر الدوار</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
       <c r="D78" s="4" t="inlineStr"/>
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>21 شارع إبراهيم مظهر، ميدان الساعة</t>
-        </is>
-      </c>
+      <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>كفر الدوار</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr"/>
+          <t>رشيد</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>مركز الإيمان للتخاطب</t>
+        </is>
+      </c>
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>شارع عبد السلام عارف</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>رشيد</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>مركز الإيمان للتخاطب</t>
-        </is>
-      </c>
+          <t>إدكو</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
       <c r="D80" s="4" t="inlineStr"/>
       <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>شارع عبد السلام عارف</t>
-        </is>
-      </c>
+      <c r="G80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>إدكو</t>
+          <t>أبو حمص</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -1721,7 +1717,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>أبو حمص</t>
+          <t>كوم حمادة</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -1734,7 +1730,7 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>كوم حمادة</t>
+          <t>شبراخيت</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -1747,7 +1743,7 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>شبراخيت</t>
+          <t>كفر الشيخ</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -1760,7 +1756,7 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>كفر الشيخ</t>
+          <t>نوقة</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -1773,7 +1769,7 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>نوقة</t>
+          <t>الحامول</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -1786,7 +1782,7 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>الحامول</t>
+          <t>شرقية</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -1799,7 +1795,7 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>شرقية</t>
+          <t>الدلنجات</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -1812,7 +1808,7 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>الدلنجات</t>
+          <t>إيتاي البارود</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -1825,7 +1821,7 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>إيتاي البارود</t>
+          <t>بسيون</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -1835,10 +1831,10 @@
       <c r="G90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n"/>
+      <c r="A91" s="6" t="n"/>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>بسيون</t>
+          <t>سنجور</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -1848,32 +1844,36 @@
       <c r="G91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>سنجور</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب النموذجي</t>
+        </is>
+      </c>
       <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>شارع النيل، العجوزة</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>مركز التخاطب النموذجي</t>
+          <t>مركز تخاطب وسمع واتزان</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>شارع النيل، العجوزة</t>
+          <t>شارع نادي إمبابة الرياضي، إمبابة</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>مركز تخاطب وسمع واتزان</t>
+          <t>مركز قدرات للتخاطب</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
       <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>شارع نادي إمبابة الرياضي، إمبابة</t>
+          <t>119 شارع الهرم، الهرم</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>مركز قدرات للتخاطب</t>
+          <t>مركز مكة للتخاطب وتنمية مهارات</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -1915,16 +1915,16 @@
       <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>119 شارع الهرم، الهرم</t>
+          <t>الهرم، الجيزة</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
-      <c r="B96" s="5" t="n"/>
+      <c r="B96" s="6" t="n"/>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>مركز مكة للتخاطب وتنمية مهارات</t>
+          <t>مركز القادة للتخاطب وتنمية المهارات</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -1938,26 +1938,22 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>مركز القادة للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>مدينة 6 أكتوبر</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr"/>
       <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>الهرم، الجيزة</t>
-        </is>
-      </c>
+      <c r="G97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>مدينة 6 أكتوبر</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -1970,7 +1966,7 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>البدرشين</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -1983,7 +1979,7 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>البدرشين</t>
+          <t>دهشور</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -1996,7 +1992,7 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>دهشور</t>
+          <t>أبو رواش</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -2009,7 +2005,7 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>أبو رواش</t>
+          <t>الوراق</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -2022,7 +2018,7 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>الوراق</t>
+          <t>الساحل</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -2035,7 +2031,7 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>الساحل</t>
+          <t>الكيت كات</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -2048,25 +2044,29 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>الكيت كات</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr"/>
+          <t>الهرم</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>مركز هووب للتخاطب</t>
+        </is>
+      </c>
       <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>الهرم وفيصل</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>الهرم</t>
-        </is>
-      </c>
+      <c r="B106" s="5" t="n"/>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>مركز هووب للتخاطب</t>
+          <t>مركز طريقنا للتخاطب</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -2074,16 +2074,16 @@
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>الهرم وفيصل</t>
+          <t>10 شارع أحمد عبد المحسن، التعاون</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
-      <c r="B107" s="5" t="n"/>
+      <c r="B107" s="6" t="n"/>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>مركز طريقنا للتخاطب</t>
+          <t>مركز الأهرام للتخاطب</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
@@ -2091,16 +2091,20 @@
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>10 شارع أحمد عبد المحسن، التعاون</t>
+          <t>شارع اللبيني، المريوطية</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
-      <c r="B108" s="6" t="n"/>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>إمبابة</t>
+        </is>
+      </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>مركز الأهرام للتخاطب</t>
+          <t>معهد السمع والكلام بإمبابة</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
@@ -2108,22 +2112,26 @@
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>شارع اللبيني، المريوطية</t>
+          <t>1 شارع الطيار فكري، بجوار مستشفى الحميات</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>إمبابة</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب شارع عزبة الصعايدة</t>
+        </is>
+      </c>
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr"/>
       <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>عزبة الصعايدة أعلى مسجد أولاد عمرو، متفرع من شارع ترعة السواحل</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -3186,7 +3194,11 @@
           <t>د. وفاء وافي</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr"/>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr">
         <is>
@@ -3216,15 +3228,19 @@
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>مركز هليوبوليس للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr"/>
+          <t>مركز تخاطب أخصائية التخاطب هبة المصري</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>د. هبة المصري</t>
+        </is>
+      </c>
       <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>28 شارع محمد عبيد من شارع النزهة، مصر الجديدة</t>
+          <t>ترعة القبة، مساكن الأميرية الجنوبية، حدائق القبة</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3249,7 @@
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>مركز Speak للتخاطب</t>
+          <t>مركز نور الحياة للتخاطب</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr"/>
@@ -3241,16 +3257,16 @@
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>زهراء مدينة نصر - المرحلة الأولى</t>
+          <t>شارع شبرا الخلفاوي، قسم الساحل</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
-      <c r="B182" s="6" t="n"/>
+      <c r="B182" s="5" t="n"/>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>مركز Almony للتخاطب وصعوبات التعلم</t>
+          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr"/>
@@ -3258,20 +3274,16 @@
       <c r="F182" s="4" t="inlineStr"/>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>8 عمارات منتصر، بجانب مسجد عبد الرحمن، حدائق حلوان</t>
+          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>مدينة نصر</t>
-        </is>
-      </c>
+      <c r="B183" s="5" t="n"/>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>المركز الذهبي التخصصي (GSC)</t>
+          <t>معهد السمع والكلام بإمبابة</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr"/>
@@ -3279,32 +3291,24 @@
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>مدينة نصر، القاهرة</t>
+          <t>1 شارع الطيار فكري، بجوار مستشفى الحميات، إمبابة</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
+      <c r="B184" s="6" t="n"/>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>مركز التخاطب الشامل و صعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>د. وفاء وافي</t>
-        </is>
-      </c>
+          <t>مركز Speak للتخاطب</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr"/>
       <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>مصر الجديدة</t>
+          <t>زهراء مدينة نصر - المرحلة الأولى</t>
         </is>
       </c>
     </row>
@@ -3312,85 +3316,117 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>الزمالك</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr"/>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>المركز الذهبي التخصصي (GSC)</t>
+        </is>
+      </c>
       <c r="D185" s="4" t="inlineStr"/>
       <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="inlineStr"/>
-      <c r="G185" s="4" t="inlineStr"/>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>مدينة نصر، القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>مركز الزهراء للتخاطب</t>
+        </is>
+      </c>
       <c r="D186" s="4" t="inlineStr"/>
       <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="inlineStr"/>
-      <c r="G186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>العبّاسية</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>مركز الحمد للعلاج الطبيعي والتخاطب</t>
+        </is>
+      </c>
       <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="4" t="inlineStr"/>
       <c r="F187" s="4" t="inlineStr"/>
-      <c r="G187" s="4" t="inlineStr"/>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>شارع مصطفى النحاس فوق التوحيد والنور بعد مدرسة المنهل</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>مدينة 6 أكتوبر</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr"/>
+      <c r="B188" s="6" t="n"/>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب</t>
+        </is>
+      </c>
       <c r="D188" s="4" t="inlineStr"/>
       <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr"/>
-      <c r="G188" s="4" t="inlineStr"/>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>مدينة الشروق</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr"/>
-      <c r="D189" s="4" t="inlineStr"/>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل و صعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>د. وفاء وافي</t>
+        </is>
+      </c>
       <c r="E189" s="4" t="inlineStr"/>
       <c r="F189" s="4" t="inlineStr"/>
-      <c r="G189" s="4" t="inlineStr"/>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>1 شارع المنتزه خلف مستشفى هليوبوليس</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>مدينة بدر</t>
-        </is>
-      </c>
+      <c r="B190" s="6" t="n"/>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>مركز متخصص للتخاطب</t>
+          <t>مركز هليوبوليس للتخاطب وتنمية المهارات</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr"/>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>01151194780</t>
+        </is>
+      </c>
       <c r="F190" s="4" t="inlineStr"/>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>مدينة بدر، القاهرة</t>
+          <t>28 شارع محمد عبيد من شارع النزهة، ميدان السبع عمارات</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3434,7 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>مدينة 15 مايو</t>
+          <t>الزمالك</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
@@ -3411,49 +3447,33 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب بزهراء المعادي</t>
-        </is>
-      </c>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr"/>
       <c r="D192" s="4" t="inlineStr"/>
       <c r="E192" s="4" t="inlineStr"/>
       <c r="F192" s="4" t="inlineStr"/>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t>شارع الأرقم بن الأرقم، الدائري، بستان</t>
-        </is>
-      </c>
+      <c r="G192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>مركز Almony للتخاطب</t>
-        </is>
-      </c>
+          <t>العبّاسية</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr"/>
       <c r="D193" s="4" t="inlineStr"/>
       <c r="E193" s="4" t="inlineStr"/>
       <c r="F193" s="4" t="inlineStr"/>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>حدائق حلوان</t>
-        </is>
-      </c>
+      <c r="G193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
+          <t>مدينة 6 أكتوبر</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
@@ -3466,7 +3486,7 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>القاهرة الجديدة</t>
+          <t>مدينة الشروق</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr"/>
@@ -3479,20 +3499,28 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زايد</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr"/>
+          <t>مدينة بدر</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>مركز متخصص للتخاطب</t>
+        </is>
+      </c>
       <c r="D196" s="4" t="inlineStr"/>
       <c r="E196" s="4" t="inlineStr"/>
       <c r="F196" s="4" t="inlineStr"/>
-      <c r="G196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>مدينة بدر، القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>الرحاب</t>
+          <t>مدينة 15 مايو</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr"/>
@@ -3505,59 +3533,83 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>الحي العاشر</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr"/>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>المركز المصري الكندي</t>
+        </is>
+      </c>
       <c r="D198" s="4" t="inlineStr"/>
       <c r="E198" s="4" t="inlineStr"/>
       <c r="F198" s="4" t="inlineStr"/>
-      <c r="G198" s="4" t="inlineStr"/>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>5/3 شارع اللاسلكي بجوار شركة غاز مصر</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>المنيل</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب البر والتقوى</t>
+        </is>
+      </c>
       <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="4" t="inlineStr"/>
       <c r="F199" s="4" t="inlineStr"/>
-      <c r="G199" s="4" t="inlineStr"/>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>104 برج الأوقاف، شارع ابن سندر</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>الدقي</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr"/>
+      <c r="B200" s="6" t="n"/>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>مركز كيور لجراحات الأذن والقوقعة والتخاطب</t>
+        </is>
+      </c>
       <c r="D200" s="4" t="inlineStr"/>
       <c r="E200" s="4" t="inlineStr"/>
       <c r="F200" s="4" t="inlineStr"/>
-      <c r="G200" s="4" t="inlineStr"/>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>شارع النصر، تقاطع اللاسلكي</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr"/>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>مركز Almony للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
       <c r="D201" s="4" t="inlineStr"/>
       <c r="E201" s="4" t="inlineStr"/>
       <c r="F201" s="4" t="inlineStr"/>
-      <c r="G201" s="4" t="inlineStr"/>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>8 عمارات منتصر، بجانب مسجد عبد الرحمن، حدائق حلوان</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>الموسكي</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr"/>
@@ -3570,7 +3622,7 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>الفجالة</t>
+          <t>القاهرة الجديدة</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr"/>
@@ -3583,7 +3635,7 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>باب الشعرية</t>
+          <t>الشيخ زايد</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr"/>
@@ -3596,7 +3648,7 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>الساحل</t>
+          <t>الرحاب</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr"/>
@@ -3609,7 +3661,7 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>المطرية</t>
+          <t>الحي العاشر</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr"/>
@@ -3622,7 +3674,7 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>عين شمس</t>
+          <t>المنيل</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr"/>
@@ -3635,33 +3687,45 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr"/>
+          <t>الدقي</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>فرع الدقي من مركز الحمد</t>
+        </is>
+      </c>
       <c r="D208" s="4" t="inlineStr"/>
       <c r="E208" s="4" t="inlineStr"/>
       <c r="F208" s="4" t="inlineStr"/>
-      <c r="G208" s="4" t="inlineStr"/>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>4 شارع حسين واصف، بجوار مدرسة العروبة</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>وسيط</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr"/>
+      <c r="B209" s="6" t="n"/>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب شارع التحرير</t>
+        </is>
+      </c>
       <c r="D209" s="4" t="inlineStr"/>
       <c r="E209" s="4" t="inlineStr"/>
       <c r="F209" s="4" t="inlineStr"/>
-      <c r="G209" s="4" t="inlineStr"/>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>شارع التحرير، أمام محطة مترو الدقي</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>المنصورية</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr"/>
@@ -3674,7 +3738,7 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>الدراسة</t>
+          <t>الموسكي</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr"/>
@@ -3687,7 +3751,7 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>درب الجنينة</t>
+          <t>الفجالة</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
@@ -3700,7 +3764,7 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>الشرابية</t>
+          <t>باب الشعرية</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
@@ -3713,7 +3777,7 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>النزهة</t>
+          <t>الساحل</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
@@ -3726,46 +3790,74 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>الرويسي</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr"/>
+          <t>المطرية</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل بالمطرية</t>
+        </is>
+      </c>
       <c r="D215" s="4" t="inlineStr"/>
-      <c r="E215" s="4" t="inlineStr"/>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>01270756267, 01092975341</t>
+        </is>
+      </c>
       <c r="F215" s="4" t="inlineStr"/>
-      <c r="G215" s="4" t="inlineStr"/>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>شارع منية مطر المطرية، بجوار محطة مترو المطرية</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>قصر النيل</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr"/>
+          <t>عين شمس</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب</t>
+        </is>
+      </c>
       <c r="D216" s="4" t="inlineStr"/>
       <c r="E216" s="4" t="inlineStr"/>
       <c r="F216" s="4" t="inlineStr"/>
-      <c r="G216" s="4" t="inlineStr"/>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>الفسطاط</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr"/>
+          <t>الزيتون</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>حورس للسمعيات والتخاطب</t>
+        </is>
+      </c>
       <c r="D217" s="4" t="inlineStr"/>
       <c r="E217" s="4" t="inlineStr"/>
       <c r="F217" s="4" t="inlineStr"/>
-      <c r="G217" s="4" t="inlineStr"/>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>1 ميدان المطرية، الزيتون</t>
+        </is>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="6" t="n"/>
+      <c r="A218" s="5" t="n"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>الرحاب</t>
+          <t>وسيط</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
@@ -3775,69 +3867,49 @@
       <c r="G218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>القليوبية</t>
-        </is>
-      </c>
+      <c r="A219" s="5" t="n"/>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>بنها</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب برج مكة</t>
-        </is>
-      </c>
+          <t>المنصورية</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr"/>
       <c r="D219" s="4" t="inlineStr"/>
       <c r="E219" s="4" t="inlineStr"/>
       <c r="F219" s="4" t="inlineStr"/>
-      <c r="G219" s="4" t="inlineStr">
-        <is>
-          <t>شارع جميل أمام بنك القاهرة</t>
-        </is>
-      </c>
+      <c r="G219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
-      <c r="B220" s="5" t="n"/>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الجزار</t>
-        </is>
-      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>الدراسة</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr"/>
       <c r="D220" s="4" t="inlineStr"/>
       <c r="E220" s="4" t="inlineStr"/>
       <c r="F220" s="4" t="inlineStr"/>
-      <c r="G220" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
-      <c r="B221" s="6" t="n"/>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العمار</t>
-        </is>
-      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>درب الجنينة</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr"/>
       <c r="D221" s="4" t="inlineStr"/>
       <c r="E221" s="4" t="inlineStr"/>
       <c r="F221" s="4" t="inlineStr"/>
-      <c r="G221" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>قليوب</t>
+          <t>الشرابية</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr"/>
@@ -3850,12 +3922,12 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>شبرا الخيمة</t>
+          <t>النزهة</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
+          <t>المركز المصري الكندي (فرع النزهة)</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -3863,49 +3935,41 @@
       <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>75 شارع حنفي الشيخوني</t>
+          <t>14 شارع جمال الدين علي بجوار ملاهي السندباد</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
-      <c r="B224" s="5" t="n"/>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>مركز النور الهدى الطبي</t>
-        </is>
-      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>الرويسي</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr"/>
       <c r="D224" s="4" t="inlineStr"/>
       <c r="E224" s="4" t="inlineStr"/>
       <c r="F224" s="4" t="inlineStr"/>
-      <c r="G224" s="4" t="inlineStr">
-        <is>
-          <t>شارع محمد القطان</t>
-        </is>
-      </c>
+      <c r="G224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
-      <c r="B225" s="6" t="n"/>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>مركز تواصل للتخاطب</t>
-        </is>
-      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>قصر النيل</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr"/>
       <c r="D225" s="4" t="inlineStr"/>
       <c r="E225" s="4" t="inlineStr"/>
       <c r="F225" s="4" t="inlineStr"/>
-      <c r="G225" s="4" t="inlineStr">
-        <is>
-          <t>2 شارع أحمد عبد ربه</t>
-        </is>
-      </c>
+      <c r="G225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>الخانكة</t>
+          <t>الفسطاط</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr"/>
@@ -3915,10 +3979,10 @@
       <c r="G226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="5" t="n"/>
+      <c r="A227" s="6" t="n"/>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>رمسيس</t>
+          <t>الرحاب</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr"/>
@@ -3928,49 +3992,69 @@
       <c r="G227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="n"/>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>القليوبية</t>
+        </is>
+      </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>مدينة 10 رمضان</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr"/>
+          <t>بنها</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب برج مكة</t>
+        </is>
+      </c>
       <c r="D228" s="4" t="inlineStr"/>
       <c r="E228" s="4" t="inlineStr"/>
       <c r="F228" s="4" t="inlineStr"/>
-      <c r="G228" s="4" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>شارع جميل أمام بنك القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>الشيخ زايد</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الجزار</t>
+        </is>
+      </c>
       <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr"/>
       <c r="F229" s="4" t="inlineStr"/>
-      <c r="G229" s="4" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>القناطر الخيرية</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr"/>
+      <c r="B230" s="6" t="n"/>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العمار</t>
+        </is>
+      </c>
       <c r="D230" s="4" t="inlineStr"/>
       <c r="E230" s="4" t="inlineStr"/>
       <c r="F230" s="4" t="inlineStr"/>
-      <c r="G230" s="4" t="inlineStr"/>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>قها</t>
+          <t>قليوب</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr"/>
@@ -3983,46 +4067,62 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>الدقهلية</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr"/>
+          <t>شبرا الخيمة</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
       <c r="D232" s="4" t="inlineStr"/>
       <c r="E232" s="4" t="inlineStr"/>
       <c r="F232" s="4" t="inlineStr"/>
-      <c r="G232" s="4" t="inlineStr"/>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>75 شارع حنفي الشيخوني</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>مركز النور الهدى الطبي</t>
+        </is>
+      </c>
       <c r="D233" s="4" t="inlineStr"/>
       <c r="E233" s="4" t="inlineStr"/>
       <c r="F233" s="4" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr"/>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>شارع محمد القطان</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>أوسيم</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr"/>
+      <c r="B234" s="6" t="n"/>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>مركز تواصل للتخاطب</t>
+        </is>
+      </c>
       <c r="D234" s="4" t="inlineStr"/>
       <c r="E234" s="4" t="inlineStr"/>
       <c r="F234" s="4" t="inlineStr"/>
-      <c r="G234" s="4" t="inlineStr"/>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>2 شارع أحمد عبد ربه</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>طره</t>
+          <t>الخانكة</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr"/>
@@ -4035,7 +4135,7 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>الخصوص</t>
+          <t>رمسيس</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr"/>
@@ -4045,10 +4145,10 @@
       <c r="G236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="6" t="n"/>
+      <c r="A237" s="5" t="n"/>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>القنطرة</t>
+          <t>مدينة 10 رمضان</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr"/>
@@ -4058,14 +4158,10 @@
       <c r="G237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>المنوفية</t>
-        </is>
-      </c>
+      <c r="A238" s="5" t="n"/>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>شبين الكوم</t>
+          <t>الشيخ زايد</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr"/>
@@ -4078,7 +4174,7 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>منوف</t>
+          <t>القناطر الخيرية</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr"/>
@@ -4091,7 +4187,7 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>شبين القناطر</t>
+          <t>قها</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr"/>
@@ -4104,7 +4200,7 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>مدينة السادات</t>
+          <t>الدقهلية</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -4117,7 +4213,7 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>باقور</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr"/>
@@ -4130,7 +4226,7 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>تلا</t>
+          <t>أوسيم</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr"/>
@@ -4143,7 +4239,7 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>قويسنا</t>
+          <t>طره</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr"/>
@@ -4156,28 +4252,20 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>أشمون</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب أشمون للتخاطب</t>
-        </is>
-      </c>
+          <t>الخصوص</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr"/>
       <c r="D245" s="4" t="inlineStr"/>
       <c r="E245" s="4" t="inlineStr"/>
       <c r="F245" s="4" t="inlineStr"/>
-      <c r="G245" s="4" t="inlineStr">
-        <is>
-          <t>أشمون</t>
-        </is>
-      </c>
+      <c r="G245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="n"/>
+      <c r="A246" s="6" t="n"/>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>البرجايه</t>
+          <t>القنطرة</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr"/>
@@ -4187,31 +4275,27 @@
       <c r="G246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="5" t="n"/>
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>المنوفية</t>
+        </is>
+      </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
-      <c r="C247" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب وصعوبات تعلم</t>
-        </is>
-      </c>
+          <t>شبين الكوم</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr"/>
       <c r="D247" s="4" t="inlineStr"/>
       <c r="E247" s="4" t="inlineStr"/>
       <c r="F247" s="4" t="inlineStr"/>
-      <c r="G247" s="4" t="inlineStr">
-        <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
+      <c r="G247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>منوف الجديدة</t>
+          <t>منوف</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr"/>
@@ -4221,10 +4305,10 @@
       <c r="G248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="n"/>
+      <c r="A249" s="5" t="n"/>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>شبين القناطر</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr"/>
@@ -4234,52 +4318,36 @@
       <c r="G249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="A250" s="5" t="n"/>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>المنيا</t>
-        </is>
-      </c>
-      <c r="C250" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب بني أحمد للتخاطب</t>
-        </is>
-      </c>
+          <t>مدينة السادات</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr"/>
       <c r="D250" s="4" t="inlineStr"/>
       <c r="E250" s="4" t="inlineStr"/>
       <c r="F250" s="4" t="inlineStr"/>
-      <c r="G250" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="n"/>
-      <c r="B251" s="6" t="n"/>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مقوسة للتخاطب</t>
-        </is>
-      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>باقور</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr"/>
       <c r="D251" s="4" t="inlineStr"/>
       <c r="E251" s="4" t="inlineStr"/>
       <c r="F251" s="4" t="inlineStr"/>
-      <c r="G251" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>سمالوط</t>
+          <t>تلا</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr"/>
@@ -4292,7 +4360,7 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>بني حسن</t>
+          <t>قويسنا</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr"/>
@@ -4305,20 +4373,28 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>هرموبوليس</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr"/>
+          <t>أشمون</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب أشمون للتخاطب</t>
+        </is>
+      </c>
       <c r="D254" s="4" t="inlineStr"/>
       <c r="E254" s="4" t="inlineStr"/>
       <c r="F254" s="4" t="inlineStr"/>
-      <c r="G254" s="4" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>ملوي</t>
+          <t>البرجايه</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr"/>
@@ -4331,20 +4407,28 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr"/>
+          <t>بركة السبع</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب وصعوبات تعلم</t>
+        </is>
+      </c>
       <c r="D256" s="4" t="inlineStr"/>
       <c r="E256" s="4" t="inlineStr"/>
       <c r="F256" s="4" t="inlineStr"/>
-      <c r="G256" s="4" t="inlineStr"/>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>ديروط الشريف</t>
+          <t>منوف الجديدة</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr"/>
@@ -4354,10 +4438,10 @@
       <c r="G257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="n"/>
+      <c r="A258" s="6" t="n"/>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>أبوقرقاص</t>
+          <t>كفر عبده</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr"/>
@@ -4367,36 +4451,52 @@
       <c r="G258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="n"/>
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr"/>
+          <t>المنيا</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب بني أحمد للتخاطب</t>
+        </is>
+      </c>
       <c r="D259" s="4" t="inlineStr"/>
       <c r="E259" s="4" t="inlineStr"/>
       <c r="F259" s="4" t="inlineStr"/>
-      <c r="G259" s="4" t="inlineStr"/>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>بني مازن</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="inlineStr"/>
+      <c r="B260" s="6" t="n"/>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب مقوسة للتخاطب</t>
+        </is>
+      </c>
       <c r="D260" s="4" t="inlineStr"/>
       <c r="E260" s="4" t="inlineStr"/>
       <c r="F260" s="4" t="inlineStr"/>
-      <c r="G260" s="4" t="inlineStr"/>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="6" t="n"/>
+      <c r="A261" s="5" t="n"/>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>سمالوط</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr"/>
@@ -4406,56 +4506,36 @@
       <c r="G261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>الوادي الجديد</t>
-        </is>
-      </c>
+      <c r="A262" s="5" t="n"/>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب الخارجة للتخاطب</t>
-        </is>
-      </c>
+          <t>بني حسن</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr"/>
       <c r="D262" s="4" t="inlineStr"/>
       <c r="E262" s="4" t="inlineStr"/>
       <c r="F262" s="4" t="inlineStr"/>
-      <c r="G262" s="4" t="inlineStr">
-        <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
+      <c r="G262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب باريس للتخاطب</t>
-        </is>
-      </c>
+          <t>هرموبوليس</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr"/>
       <c r="D263" s="4" t="inlineStr"/>
       <c r="E263" s="4" t="inlineStr"/>
       <c r="F263" s="4" t="inlineStr"/>
-      <c r="G263" s="4" t="inlineStr">
-        <is>
-          <t>باريس</t>
-        </is>
-      </c>
+      <c r="G263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>موط</t>
+          <t>ملوي</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr"/>
@@ -4468,7 +4548,7 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>بلاط</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr"/>
@@ -4481,7 +4561,7 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>فرافرة</t>
+          <t>ديروط الشريف</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr"/>
@@ -4494,7 +4574,7 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>أبوقرقاص</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr"/>
@@ -4507,7 +4587,7 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr"/>
@@ -4520,7 +4600,7 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>تينيدة</t>
+          <t>بني مازن</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr"/>
@@ -4533,7 +4613,7 @@
       <c r="A270" s="6" t="n"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>دوش</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr"/>
@@ -4545,17 +4625,17 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>بني سويف</t>
+          <t>الوادي الجديد</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>بني سويف</t>
+          <t>الخارجة</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب العبور للتخاطب</t>
+          <t>مركز شباب الخارجة للتخاطب</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr"/>
@@ -4563,7 +4643,7 @@
       <c r="F271" s="4" t="inlineStr"/>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>بني سويف</t>
+          <t>الخارجة</t>
         </is>
       </c>
     </row>
@@ -4571,20 +4651,28 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr"/>
+          <t>الداخلة</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب باريس للتخاطب</t>
+        </is>
+      </c>
       <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr"/>
       <c r="F272" s="4" t="inlineStr"/>
-      <c r="G272" s="4" t="inlineStr"/>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>ساماستا</t>
+          <t>موط</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr"/>
@@ -4597,7 +4685,7 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>إبشواي</t>
+          <t>بلاط</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr"/>
@@ -4610,7 +4698,7 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>الجندية</t>
+          <t>فرافرة</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr"/>
@@ -4623,7 +4711,7 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>ناصر</t>
+          <t>باريس</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr"/>
@@ -4636,7 +4724,7 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>هواره</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr"/>
@@ -4649,7 +4737,7 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>موشية</t>
+          <t>تينيدة</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr"/>
@@ -4659,10 +4747,10 @@
       <c r="G278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="n"/>
+      <c r="A279" s="6" t="n"/>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>نصار البحرية</t>
+          <t>دوش</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr"/>
@@ -4672,27 +4760,35 @@
       <c r="G279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="6" t="n"/>
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>أحمد حمزة</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr"/>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العبور للتخاطب</t>
+        </is>
+      </c>
       <c r="D280" s="4" t="inlineStr"/>
       <c r="E280" s="4" t="inlineStr"/>
       <c r="F280" s="4" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>بورسعيد</t>
-        </is>
-      </c>
+      <c r="A281" s="5" t="n"/>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr"/>
@@ -4705,7 +4801,7 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>بورفؤاد</t>
+          <t>ساماستا</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr"/>
@@ -4718,7 +4814,7 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>الجميل</t>
+          <t>إبشواي</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr"/>
@@ -4731,7 +4827,7 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>الزهور</t>
+          <t>الجندية</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr"/>
@@ -4744,7 +4840,7 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>ناصر</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr"/>
@@ -4757,7 +4853,7 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>الكنتاوي</t>
+          <t>هواره</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr"/>
@@ -4767,10 +4863,10 @@
       <c r="G286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="6" t="n"/>
+      <c r="A287" s="5" t="n"/>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>الضواحي</t>
+          <t>موشية</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr"/>
@@ -4780,14 +4876,10 @@
       <c r="G287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>جنوب سيناء</t>
-        </is>
-      </c>
+      <c r="A288" s="5" t="n"/>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>شرم الشيخ</t>
+          <t>نصار البحرية</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr"/>
@@ -4797,10 +4889,10 @@
       <c r="G288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="n"/>
+      <c r="A289" s="6" t="n"/>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>داهب</t>
+          <t>أحمد حمزة</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr"/>
@@ -4810,10 +4902,14 @@
       <c r="G289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="n"/>
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>نويبع</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr"/>
@@ -4826,7 +4922,7 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>سانت كاترين</t>
+          <t>بورفؤاد</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr"/>
@@ -4839,7 +4935,7 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>الجميل</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr"/>
@@ -4852,7 +4948,7 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>رأس محمد</t>
+          <t>الزهور</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr"/>
@@ -4865,7 +4961,7 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>أم سيد</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr"/>
@@ -4875,10 +4971,10 @@
       <c r="G294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="n"/>
+      <c r="A295" s="5" t="n"/>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>مدينة شرم الشيخ</t>
+          <t>الكنتاوي</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr"/>
@@ -4888,14 +4984,10 @@
       <c r="G295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
+      <c r="A296" s="6" t="n"/>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>الضواحي</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr"/>
@@ -4905,10 +4997,14 @@
       <c r="G296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="n"/>
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>شرم الشيخ</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr"/>
@@ -4921,7 +5017,7 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>واحة الفيوم</t>
+          <t>داهب</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr"/>
@@ -4934,7 +5030,7 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>وادي حوف</t>
+          <t>نويبع</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr"/>
@@ -4947,7 +5043,7 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>عين سخنة</t>
+          <t>سانت كاترين</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr"/>
@@ -4960,7 +5056,7 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr"/>
@@ -4973,7 +5069,7 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>رأس محمد</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr"/>
@@ -4983,10 +5079,10 @@
       <c r="G302" s="4" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="n"/>
+      <c r="A303" s="5" t="n"/>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
+          <t>أم سيد</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr"/>
@@ -4996,35 +5092,27 @@
       <c r="G303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
+      <c r="A304" s="6" t="n"/>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="C304" s="4" t="inlineStr">
-        <is>
-          <t>مركز حلم ابني للتخاطب</t>
-        </is>
-      </c>
+          <t>مدينة شرم الشيخ</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr"/>
       <c r="D304" s="4" t="inlineStr"/>
       <c r="E304" s="4" t="inlineStr"/>
       <c r="F304" s="4" t="inlineStr"/>
-      <c r="G304" s="4" t="inlineStr">
-        <is>
-          <t>دمياط ودمياط الجديدة</t>
-        </is>
-      </c>
+      <c r="G304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="5" t="n"/>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>دمياط الجديدة</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr"/>
@@ -5037,7 +5125,7 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>بورت فؤاد</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr"/>
@@ -5050,7 +5138,7 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>كفر البطة</t>
+          <t>واحة الفيوم</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr"/>
@@ -5063,7 +5151,7 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>كفر سعيد</t>
+          <t>وادي حوف</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr"/>
@@ -5076,7 +5164,7 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>عين سخنة</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr"/>
@@ -5089,7 +5177,7 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>الزرقا</t>
+          <t>الطور</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr"/>
@@ -5102,7 +5190,7 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>فارسكور</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr"/>
@@ -5115,7 +5203,7 @@
       <c r="A312" s="6" t="n"/>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>رومانية</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr"/>
@@ -5127,17 +5215,17 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>شمال سيناء</t>
+          <t>دمياط</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>العريش</t>
+          <t>دمياط</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب العريش للتخاطب</t>
+          <t>مركز حلم ابني للتخاطب</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr"/>
@@ -5145,7 +5233,7 @@
       <c r="F313" s="4" t="inlineStr"/>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب العريش</t>
+          <t>دمياط ودمياط الجديدة</t>
         </is>
       </c>
     </row>
@@ -5153,49 +5241,33 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>رفح</t>
-        </is>
-      </c>
-      <c r="C314" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب رفح</t>
-        </is>
-      </c>
+          <t>دمياط الجديدة</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr"/>
       <c r="D314" s="4" t="inlineStr"/>
       <c r="E314" s="4" t="inlineStr"/>
       <c r="F314" s="4" t="inlineStr"/>
-      <c r="G314" s="4" t="inlineStr">
-        <is>
-          <t>رفح</t>
-        </is>
-      </c>
+      <c r="G314" s="4" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
-      <c r="C315" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
-        </is>
-      </c>
+          <t>بورت فؤاد</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr"/>
       <c r="D315" s="4" t="inlineStr"/>
       <c r="E315" s="4" t="inlineStr"/>
       <c r="F315" s="4" t="inlineStr"/>
-      <c r="G315" s="4" t="inlineStr">
-        <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
+      <c r="G315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>بئر العبد</t>
+          <t>كفر البطة</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr"/>
@@ -5208,7 +5280,7 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>القنطرة، سيناء</t>
+          <t>كفر سعيد</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr"/>
@@ -5221,7 +5293,7 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>نخل</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr"/>
@@ -5234,7 +5306,7 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>جديدة، حسنة</t>
+          <t>الزرقا</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr"/>
@@ -5247,7 +5319,7 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>دهب الشرقية</t>
+          <t>فارسكور</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr"/>
@@ -5260,7 +5332,7 @@
       <c r="A321" s="6" t="n"/>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>رومانية</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr"/>
@@ -5272,17 +5344,17 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>قنا</t>
+          <t>شمال سيناء</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>قنا</t>
+          <t>العريش</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>مركز التخاطب بمدينة العمال</t>
+          <t>مركز شباب العريش للتخاطب</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr"/>
@@ -5290,16 +5362,20 @@
       <c r="F322" s="4" t="inlineStr"/>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>مدينة العمال، قنا</t>
+          <t>مركز شباب العريش</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="n"/>
-      <c r="B323" s="6" t="n"/>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب حجير خزام</t>
+          <t>مركز تخاطب رفح</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr"/>
@@ -5307,7 +5383,7 @@
       <c r="F323" s="4" t="inlineStr"/>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>قنا</t>
+          <t>رفح</t>
         </is>
       </c>
     </row>
@@ -5315,20 +5391,28 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>نجع حمادي</t>
-        </is>
-      </c>
-      <c r="C324" s="4" t="inlineStr"/>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
+        </is>
+      </c>
       <c r="D324" s="4" t="inlineStr"/>
       <c r="E324" s="4" t="inlineStr"/>
       <c r="F324" s="4" t="inlineStr"/>
-      <c r="G324" s="4" t="inlineStr"/>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>دندرة</t>
+          <t>بئر العبد</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr"/>
@@ -5341,7 +5425,7 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>أبيدوس</t>
+          <t>القنطرة، سيناء</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr"/>
@@ -5354,7 +5438,7 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>قفطي</t>
+          <t>نخل</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr"/>
@@ -5367,7 +5451,7 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>أخميم</t>
+          <t>جديدة، حسنة</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr"/>
@@ -5380,7 +5464,7 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>سوهاج القديمة</t>
+          <t>دهب الشرقية</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr"/>
@@ -5390,10 +5474,10 @@
       <c r="G329" s="4" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="5" t="n"/>
+      <c r="A330" s="6" t="n"/>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>النجع البحري</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr"/>
@@ -5403,32 +5487,36 @@
       <c r="G330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="6" t="n"/>
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>الشنقي</t>
-        </is>
-      </c>
-      <c r="C331" s="4" t="inlineStr"/>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمدينة العمال</t>
+        </is>
+      </c>
       <c r="D331" s="4" t="inlineStr"/>
       <c r="E331" s="4" t="inlineStr"/>
       <c r="F331" s="4" t="inlineStr"/>
-      <c r="G331" s="4" t="inlineStr"/>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>مدينة العمال، قنا</t>
+        </is>
+      </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="A332" s="5" t="n"/>
+      <c r="B332" s="6" t="n"/>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب كفر الشيخ للتخاطب</t>
+          <t>مركز شباب حجير خزام</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr"/>
@@ -5436,7 +5524,7 @@
       <c r="F332" s="4" t="inlineStr"/>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>كفر الشيخ</t>
+          <t>قنا</t>
         </is>
       </c>
     </row>
@@ -5444,28 +5532,20 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>دسوق</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="inlineStr">
-        <is>
-          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
-        </is>
-      </c>
+          <t>نجع حمادي</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr"/>
       <c r="D333" s="4" t="inlineStr"/>
       <c r="E333" s="4" t="inlineStr"/>
       <c r="F333" s="4" t="inlineStr"/>
-      <c r="G333" s="4" t="inlineStr">
-        <is>
-          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
-        </is>
-      </c>
+      <c r="G333" s="4" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>بلامون</t>
+          <t>دندرة</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr"/>
@@ -5478,7 +5558,7 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>الرياض</t>
+          <t>أبيدوس</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr"/>
@@ -5491,7 +5571,7 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>سيدي سالم</t>
+          <t>قفطي</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr"/>
@@ -5504,7 +5584,7 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>الحامول</t>
+          <t>أخميم</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr"/>
@@ -5517,7 +5597,7 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>برج البرلس</t>
+          <t>سوهاج القديمة</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr"/>
@@ -5530,7 +5610,7 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>مطوبس</t>
+          <t>النجع البحري</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr"/>
@@ -5540,10 +5620,10 @@
       <c r="G339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="5" t="n"/>
+      <c r="A340" s="6" t="n"/>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>المحمودية</t>
+          <t>الشنقي</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr"/>
@@ -5553,44 +5633,56 @@
       <c r="G340" s="4" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="6" t="n"/>
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>بيلا</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr"/>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الشيخ للتخاطب</t>
+        </is>
+      </c>
       <c r="D341" s="4" t="inlineStr"/>
       <c r="E341" s="4" t="inlineStr"/>
       <c r="F341" s="4" t="inlineStr"/>
-      <c r="G341" s="4" t="inlineStr"/>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A342" s="5" t="n"/>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr"/>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
+        </is>
+      </c>
       <c r="D342" s="4" t="inlineStr"/>
       <c r="E342" s="4" t="inlineStr"/>
       <c r="F342" s="4" t="inlineStr"/>
-      <c r="G342" s="4" t="inlineStr"/>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
+        </is>
+      </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A343" s="5" t="n"/>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>سيوه</t>
+          <t>بلامون</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr"/>
@@ -5600,14 +5692,10 @@
       <c r="G343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A344" s="5" t="n"/>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>السلوم</t>
+          <t>الرياض</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr"/>
@@ -5617,14 +5705,10 @@
       <c r="G344" s="4" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A345" s="5" t="n"/>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>سيدي براني</t>
+          <t>سيدي سالم</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr"/>
@@ -5634,14 +5718,10 @@
       <c r="G345" s="4" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A346" s="5" t="n"/>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>العلمين</t>
+          <t>الحامول</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr"/>
@@ -5651,14 +5731,10 @@
       <c r="G346" s="4" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A347" s="5" t="n"/>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>مارينا</t>
+          <t>برج البرلس</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr"/>
@@ -5668,14 +5744,10 @@
       <c r="G347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A348" s="5" t="n"/>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>توريدو</t>
+          <t>مطوبس</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr"/>
@@ -5685,14 +5757,10 @@
       <c r="G348" s="4" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A349" s="5" t="n"/>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>جنوب سيوه</t>
+          <t>المحمودية</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr"/>
@@ -5702,14 +5770,10 @@
       <c r="G349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A350" s="6" t="n"/>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>شمال سيوه</t>
+          <t>بيلا</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr"/>
@@ -5726,7 +5790,7 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>كشته</t>
+          <t>مطروح</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr"/>
@@ -5735,90 +5799,240 @@
       <c r="F351" s="4" t="inlineStr"/>
       <c r="G351" s="4" t="inlineStr"/>
     </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>سيوه</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr"/>
+      <c r="D352" s="4" t="inlineStr"/>
+      <c r="E352" s="4" t="inlineStr"/>
+      <c r="F352" s="4" t="inlineStr"/>
+      <c r="G352" s="4" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>السلوم</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr"/>
+      <c r="D353" s="4" t="inlineStr"/>
+      <c r="E353" s="4" t="inlineStr"/>
+      <c r="F353" s="4" t="inlineStr"/>
+      <c r="G353" s="4" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>سيدي براني</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr"/>
+      <c r="D354" s="4" t="inlineStr"/>
+      <c r="E354" s="4" t="inlineStr"/>
+      <c r="F354" s="4" t="inlineStr"/>
+      <c r="G354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>العلمين</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr"/>
+      <c r="D355" s="4" t="inlineStr"/>
+      <c r="E355" s="4" t="inlineStr"/>
+      <c r="F355" s="4" t="inlineStr"/>
+      <c r="G355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>مارينا</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr"/>
+      <c r="D356" s="4" t="inlineStr"/>
+      <c r="E356" s="4" t="inlineStr"/>
+      <c r="F356" s="4" t="inlineStr"/>
+      <c r="G356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>توريدو</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr"/>
+      <c r="D357" s="4" t="inlineStr"/>
+      <c r="E357" s="4" t="inlineStr"/>
+      <c r="F357" s="4" t="inlineStr"/>
+      <c r="G357" s="4" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>جنوب سيوه</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr"/>
+      <c r="D358" s="4" t="inlineStr"/>
+      <c r="E358" s="4" t="inlineStr"/>
+      <c r="F358" s="4" t="inlineStr"/>
+      <c r="G358" s="4" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>شمال سيوه</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr"/>
+      <c r="D359" s="4" t="inlineStr"/>
+      <c r="E359" s="4" t="inlineStr"/>
+      <c r="F359" s="4" t="inlineStr"/>
+      <c r="G359" s="4" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>كشته</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr"/>
+      <c r="D360" s="4" t="inlineStr"/>
+      <c r="E360" s="4" t="inlineStr"/>
+      <c r="F360" s="4" t="inlineStr"/>
+      <c r="G360" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="313">
     <mergeCell ref="B6"/>
     <mergeCell ref="B133"/>
     <mergeCell ref="B204"/>
-    <mergeCell ref="B198"/>
-    <mergeCell ref="B296"/>
+    <mergeCell ref="B356"/>
     <mergeCell ref="B4"/>
     <mergeCell ref="B75"/>
     <mergeCell ref="B135"/>
     <mergeCell ref="B306"/>
     <mergeCell ref="B62"/>
-    <mergeCell ref="B233"/>
-    <mergeCell ref="B227"/>
     <mergeCell ref="B72"/>
-    <mergeCell ref="B199"/>
+    <mergeCell ref="A290:A296"/>
     <mergeCell ref="B291"/>
     <mergeCell ref="B70"/>
-    <mergeCell ref="B228"/>
     <mergeCell ref="B293"/>
     <mergeCell ref="A12:A23"/>
-    <mergeCell ref="A219:A237"/>
+    <mergeCell ref="B322"/>
     <mergeCell ref="B17"/>
     <mergeCell ref="B88"/>
     <mergeCell ref="B82"/>
     <mergeCell ref="B152:B156"/>
+    <mergeCell ref="B185:B188"/>
     <mergeCell ref="B19"/>
     <mergeCell ref="B146"/>
     <mergeCell ref="B317"/>
     <mergeCell ref="B217"/>
-    <mergeCell ref="B65"/>
+    <mergeCell ref="A259:A270"/>
     <mergeCell ref="B83"/>
     <mergeCell ref="B344"/>
     <mergeCell ref="B319"/>
+    <mergeCell ref="A178:A227"/>
     <mergeCell ref="B123"/>
+    <mergeCell ref="B221"/>
     <mergeCell ref="B110"/>
-    <mergeCell ref="A262:A270"/>
     <mergeCell ref="B141"/>
     <mergeCell ref="B248"/>
     <mergeCell ref="B297"/>
+    <mergeCell ref="B108:B109"/>
     <mergeCell ref="B235"/>
     <mergeCell ref="B14"/>
+    <mergeCell ref="B331:B332"/>
     <mergeCell ref="B299"/>
     <mergeCell ref="B78"/>
+    <mergeCell ref="B249"/>
     <mergeCell ref="B243"/>
+    <mergeCell ref="A331:A340"/>
     <mergeCell ref="B314"/>
-    <mergeCell ref="A332:A341"/>
+    <mergeCell ref="A247:A258"/>
     <mergeCell ref="B167:B168"/>
     <mergeCell ref="B325"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="B91"/>
+    <mergeCell ref="B259:B260"/>
     <mergeCell ref="B25"/>
     <mergeCell ref="B327"/>
-    <mergeCell ref="A178:A218"/>
     <mergeCell ref="B149"/>
+    <mergeCell ref="B220"/>
     <mergeCell ref="B247"/>
-    <mergeCell ref="B223:B225"/>
     <mergeCell ref="B262"/>
+    <mergeCell ref="B38"/>
+    <mergeCell ref="A271:A279"/>
     <mergeCell ref="B84"/>
-    <mergeCell ref="B246"/>
-    <mergeCell ref="B40"/>
     <mergeCell ref="B338"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B313"/>
     <mergeCell ref="B104"/>
-    <mergeCell ref="B340"/>
     <mergeCell ref="B79"/>
     <mergeCell ref="B315"/>
     <mergeCell ref="B302"/>
     <mergeCell ref="B81"/>
     <mergeCell ref="B252"/>
-    <mergeCell ref="B208"/>
     <mergeCell ref="B210"/>
     <mergeCell ref="B318"/>
+    <mergeCell ref="B189:B190"/>
     <mergeCell ref="B170"/>
     <mergeCell ref="B157"/>
     <mergeCell ref="B328"/>
     <mergeCell ref="B333"/>
-    <mergeCell ref="B234"/>
-    <mergeCell ref="A322:A331"/>
+    <mergeCell ref="B66:B67"/>
     <mergeCell ref="B172"/>
     <mergeCell ref="B28"/>
     <mergeCell ref="B99"/>
-    <mergeCell ref="B186"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B257"/>
     <mergeCell ref="B30"/>
@@ -5826,18 +6040,18 @@
     <mergeCell ref="B265"/>
     <mergeCell ref="B54"/>
     <mergeCell ref="B125"/>
-    <mergeCell ref="B56"/>
+    <mergeCell ref="B323"/>
     <mergeCell ref="B176"/>
     <mergeCell ref="B120"/>
-    <mergeCell ref="B219:B221"/>
     <mergeCell ref="B147"/>
     <mergeCell ref="B245"/>
     <mergeCell ref="B9"/>
+    <mergeCell ref="B359"/>
     <mergeCell ref="B207"/>
     <mergeCell ref="B334"/>
-    <mergeCell ref="B67:B68"/>
     <mergeCell ref="B113"/>
     <mergeCell ref="B173"/>
+    <mergeCell ref="B33:B37"/>
     <mergeCell ref="B100"/>
     <mergeCell ref="B271"/>
     <mergeCell ref="B336"/>
@@ -5845,115 +6059,112 @@
     <mergeCell ref="B202"/>
     <mergeCell ref="B102"/>
     <mergeCell ref="B273"/>
+    <mergeCell ref="B232:B234"/>
     <mergeCell ref="B39"/>
-    <mergeCell ref="A67:A77"/>
     <mergeCell ref="B191"/>
     <mergeCell ref="B349"/>
     <mergeCell ref="B255"/>
     <mergeCell ref="B226"/>
     <mergeCell ref="B49"/>
     <mergeCell ref="B192"/>
+    <mergeCell ref="A280:A289"/>
     <mergeCell ref="B284"/>
     <mergeCell ref="B222"/>
     <mergeCell ref="A313:A321"/>
     <mergeCell ref="B63"/>
     <mergeCell ref="B197"/>
     <mergeCell ref="B50"/>
-    <mergeCell ref="A78:A92"/>
+    <mergeCell ref="A57:A65"/>
     <mergeCell ref="B286"/>
+    <mergeCell ref="B261"/>
     <mergeCell ref="B27"/>
     <mergeCell ref="B337"/>
+    <mergeCell ref="B352"/>
     <mergeCell ref="B103"/>
     <mergeCell ref="B174"/>
-    <mergeCell ref="B230"/>
     <mergeCell ref="B205"/>
     <mergeCell ref="B339"/>
     <mergeCell ref="B118"/>
+    <mergeCell ref="A66:A76"/>
     <mergeCell ref="B55"/>
-    <mergeCell ref="A288:A295"/>
     <mergeCell ref="B169"/>
-    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="B355"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="B129"/>
-    <mergeCell ref="B200"/>
     <mergeCell ref="B134"/>
     <mergeCell ref="B194"/>
     <mergeCell ref="B121"/>
     <mergeCell ref="B292"/>
+    <mergeCell ref="B357"/>
     <mergeCell ref="B71"/>
     <mergeCell ref="B131"/>
     <mergeCell ref="B236"/>
     <mergeCell ref="B307"/>
     <mergeCell ref="B58"/>
     <mergeCell ref="B52"/>
+    <mergeCell ref="B223"/>
     <mergeCell ref="B294"/>
-    <mergeCell ref="B350"/>
     <mergeCell ref="B2"/>
     <mergeCell ref="B195"/>
     <mergeCell ref="B60"/>
-    <mergeCell ref="A58:A66"/>
     <mergeCell ref="B231"/>
+    <mergeCell ref="B287"/>
+    <mergeCell ref="B358"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="B53"/>
+    <mergeCell ref="A341:A350"/>
     <mergeCell ref="A152:A166"/>
-    <mergeCell ref="B289"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B241"/>
     <mergeCell ref="B124"/>
+    <mergeCell ref="B178:B184"/>
     <mergeCell ref="B142"/>
     <mergeCell ref="B80"/>
     <mergeCell ref="B213"/>
     <mergeCell ref="B305"/>
-    <mergeCell ref="B188"/>
     <mergeCell ref="B126"/>
+    <mergeCell ref="B218"/>
     <mergeCell ref="B242"/>
-    <mergeCell ref="B190"/>
     <mergeCell ref="B46"/>
     <mergeCell ref="B282"/>
-    <mergeCell ref="A271:A280"/>
     <mergeCell ref="B48"/>
+    <mergeCell ref="B219"/>
     <mergeCell ref="B346"/>
+    <mergeCell ref="A297:A304"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="B73"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="B308"/>
     <mergeCell ref="B74"/>
+    <mergeCell ref="B68"/>
     <mergeCell ref="B201"/>
     <mergeCell ref="B239"/>
     <mergeCell ref="B310"/>
     <mergeCell ref="B5"/>
-    <mergeCell ref="B76"/>
     <mergeCell ref="B203"/>
-    <mergeCell ref="B232"/>
     <mergeCell ref="B150"/>
     <mergeCell ref="B326"/>
     <mergeCell ref="B215"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="B263"/>
     <mergeCell ref="B244"/>
-    <mergeCell ref="B229"/>
-    <mergeCell ref="B93:B97"/>
     <mergeCell ref="A167:A177"/>
     <mergeCell ref="B283"/>
     <mergeCell ref="B87"/>
-    <mergeCell ref="B258"/>
-    <mergeCell ref="A238:A249"/>
     <mergeCell ref="B298"/>
     <mergeCell ref="B285"/>
-    <mergeCell ref="B260"/>
     <mergeCell ref="B64"/>
     <mergeCell ref="B51"/>
     <mergeCell ref="B163"/>
     <mergeCell ref="B309"/>
-    <mergeCell ref="B209"/>
-    <mergeCell ref="B41:B43"/>
     <mergeCell ref="B165"/>
     <mergeCell ref="B140"/>
     <mergeCell ref="B311"/>
     <mergeCell ref="B238"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B77"/>
     <mergeCell ref="B253"/>
     <mergeCell ref="B240"/>
-    <mergeCell ref="B33:B38"/>
     <mergeCell ref="A2:A11"/>
     <mergeCell ref="B29"/>
     <mergeCell ref="B158"/>
@@ -5962,16 +6173,17 @@
     <mergeCell ref="B24"/>
     <mergeCell ref="B266"/>
     <mergeCell ref="B89"/>
+    <mergeCell ref="B198:B200"/>
+    <mergeCell ref="B92:B96"/>
     <mergeCell ref="B26"/>
-    <mergeCell ref="B330"/>
+    <mergeCell ref="B97"/>
     <mergeCell ref="B268"/>
     <mergeCell ref="B324"/>
+    <mergeCell ref="B224"/>
     <mergeCell ref="B90"/>
-    <mergeCell ref="B184"/>
     <mergeCell ref="B148"/>
+    <mergeCell ref="B250"/>
     <mergeCell ref="B44"/>
-    <mergeCell ref="B304"/>
-    <mergeCell ref="B279"/>
     <mergeCell ref="B115:B116"/>
     <mergeCell ref="B254"/>
     <mergeCell ref="B143"/>
@@ -5983,47 +6195,49 @@
     <mergeCell ref="B160:B162"/>
     <mergeCell ref="B159"/>
     <mergeCell ref="B272"/>
-    <mergeCell ref="B332"/>
-    <mergeCell ref="B259"/>
     <mergeCell ref="B111"/>
     <mergeCell ref="B98"/>
+    <mergeCell ref="B225"/>
     <mergeCell ref="B274"/>
     <mergeCell ref="B175"/>
+    <mergeCell ref="B228:B230"/>
     <mergeCell ref="A129:A136"/>
     <mergeCell ref="B267"/>
     <mergeCell ref="B269"/>
-    <mergeCell ref="B187"/>
-    <mergeCell ref="B178:B182"/>
-    <mergeCell ref="B189"/>
+    <mergeCell ref="B251"/>
     <mergeCell ref="B45"/>
     <mergeCell ref="B216"/>
     <mergeCell ref="B343"/>
-    <mergeCell ref="B109"/>
+    <mergeCell ref="A92:A114"/>
+    <mergeCell ref="B280"/>
     <mergeCell ref="B47"/>
+    <mergeCell ref="B351"/>
     <mergeCell ref="B345"/>
     <mergeCell ref="B59"/>
     <mergeCell ref="B22"/>
     <mergeCell ref="B193"/>
     <mergeCell ref="B264"/>
     <mergeCell ref="B320"/>
-    <mergeCell ref="A296:A303"/>
+    <mergeCell ref="B295"/>
     <mergeCell ref="B86"/>
     <mergeCell ref="B101"/>
-    <mergeCell ref="A304:A312"/>
-    <mergeCell ref="A281:A287"/>
+    <mergeCell ref="A77:A91"/>
     <mergeCell ref="B211"/>
     <mergeCell ref="B144:B145"/>
     <mergeCell ref="B300"/>
-    <mergeCell ref="B183"/>
+    <mergeCell ref="B40:B42"/>
     <mergeCell ref="B275"/>
+    <mergeCell ref="B208:B209"/>
     <mergeCell ref="B164"/>
     <mergeCell ref="B335"/>
     <mergeCell ref="B212"/>
+    <mergeCell ref="A322:A330"/>
     <mergeCell ref="B206"/>
     <mergeCell ref="B277"/>
-    <mergeCell ref="A250:A261"/>
     <mergeCell ref="B130"/>
+    <mergeCell ref="A33:A56"/>
     <mergeCell ref="B117"/>
+    <mergeCell ref="B353"/>
     <mergeCell ref="B61"/>
     <mergeCell ref="B132"/>
     <mergeCell ref="B119"/>
@@ -6031,23 +6245,26 @@
     <mergeCell ref="B69"/>
     <mergeCell ref="B196"/>
     <mergeCell ref="B112"/>
-    <mergeCell ref="A33:A57"/>
+    <mergeCell ref="B354"/>
     <mergeCell ref="B288"/>
     <mergeCell ref="B348"/>
     <mergeCell ref="B127"/>
-    <mergeCell ref="B185"/>
+    <mergeCell ref="B237"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B3"/>
+    <mergeCell ref="A228:A246"/>
     <mergeCell ref="B301"/>
     <mergeCell ref="B122"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="B105"/>
     <mergeCell ref="B276"/>
+    <mergeCell ref="B43"/>
+    <mergeCell ref="B18"/>
     <mergeCell ref="B214"/>
-    <mergeCell ref="B18"/>
+    <mergeCell ref="A305:A312"/>
+    <mergeCell ref="B341"/>
     <mergeCell ref="B347"/>
+    <mergeCell ref="B303"/>
     <mergeCell ref="B278"/>
-    <mergeCell ref="A93:A114"/>
+    <mergeCell ref="B57"/>
     <mergeCell ref="B171"/>
     <mergeCell ref="B342"/>
   </mergeCells>

--- a/Egyptian_Speech_Therapy_Centers.xlsx
+++ b/Egyptian_Speech_Therapy_Centers.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,15 @@
     <font>
       <name val="Arial"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +136,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G360"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -567,7 +585,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>أبو سمبل</t>
@@ -580,7 +597,6 @@
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>كوم أمبو</t>
@@ -593,7 +609,6 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>إدفو</t>
@@ -606,7 +621,6 @@
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>داراو</t>
@@ -619,7 +633,6 @@
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>نصر الساحل</t>
@@ -632,7 +645,6 @@
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>الشيخ علي</t>
@@ -645,7 +657,6 @@
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>توشكا</t>
@@ -658,7 +669,6 @@
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>الحمراء</t>
@@ -671,7 +681,6 @@
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>النوبة</t>
@@ -709,8 +718,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="6" t="n"/>
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>مركز شباب موشا للتخاطب</t>
@@ -726,7 +733,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>منفلوط</t>
@@ -739,7 +745,6 @@
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>ديروط</t>
@@ -752,7 +757,6 @@
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>الوقف</t>
@@ -765,7 +769,6 @@
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>أبيدوس</t>
@@ -778,7 +781,6 @@
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>سوهاج</t>
@@ -791,7 +793,6 @@
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>البدارى</t>
@@ -804,7 +805,6 @@
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>فلنج</t>
@@ -817,7 +817,6 @@
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>أراب العوامر</t>
@@ -830,7 +829,6 @@
       <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>الغنايم</t>
@@ -843,7 +841,6 @@
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>الفيوم الجديدة</t>
@@ -881,7 +878,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>الكرنك</t>
@@ -894,7 +890,6 @@
       <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>البر الغربي</t>
@@ -907,7 +902,6 @@
       <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>الضفة الغربية</t>
@@ -920,7 +914,6 @@
       <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
           <t>وادي الملوك</t>
@@ -933,7 +926,6 @@
       <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>معبد الدير البحري</t>
@@ -946,7 +938,6 @@
       <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>مدينة الأقصر</t>
@@ -959,7 +950,6 @@
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>إسنا</t>
@@ -972,7 +962,6 @@
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>أرمنت</t>
@@ -1010,8 +999,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t>مركز سموحة للتخاطب</t>
@@ -1027,8 +1014,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>مركز د/ نهى رسلان لتدريب النطق والكلام</t>
@@ -1048,8 +1033,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>مركز د/ هبة سلامة</t>
@@ -1069,8 +1052,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="6" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>أكاديمية زويل</t>
@@ -1086,7 +1067,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
           <t>برج العرب</t>
@@ -1099,7 +1079,6 @@
       <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
           <t>مونتازا</t>
@@ -1112,7 +1091,6 @@
       <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
           <t>سيدي بشر</t>
@@ -1133,8 +1111,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>عيادة تخاطب شارع الطفولة السعيدة</t>
@@ -1150,8 +1126,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="6" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>مركز تومورو للتخاطب</t>
@@ -1167,7 +1141,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>أبي قير</t>
@@ -1180,7 +1153,6 @@
       <c r="G43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
           <t>الدخيلة</t>
@@ -1193,7 +1165,6 @@
       <c r="G44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>كوم الدكة</t>
@@ -1206,7 +1177,6 @@
       <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
           <t>ستانلي</t>
@@ -1219,7 +1189,6 @@
       <c r="G46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
           <t>الشاطبي</t>
@@ -1232,7 +1201,6 @@
       <c r="G47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
           <t>رشدي</t>
@@ -1245,7 +1213,6 @@
       <c r="G48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
           <t>الرملة</t>
@@ -1258,7 +1225,6 @@
       <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
           <t>الإبراهيمية</t>
@@ -1271,7 +1237,6 @@
       <c r="G50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
           <t>القنطرة</t>
@@ -1284,7 +1249,6 @@
       <c r="G51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
           <t>كفر عبده</t>
@@ -1297,7 +1261,6 @@
       <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
           <t>الحمام</t>
@@ -1310,7 +1273,6 @@
       <c r="G53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
           <t>مارينا</t>
@@ -1323,7 +1285,6 @@
       <c r="G54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>عمومية</t>
@@ -1336,7 +1297,6 @@
       <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
           <t>ضواحي</t>
@@ -1366,7 +1326,6 @@
       <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
           <t>بورسعيد</t>
@@ -1379,7 +1338,6 @@
       <c r="G58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>السويس</t>
@@ -1392,7 +1350,6 @@
       <c r="G59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
           <t>القنطرة غرب</t>
@@ -1405,7 +1362,6 @@
       <c r="G60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
           <t>القنطرة شرق</t>
@@ -1418,7 +1374,6 @@
       <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
           <t>فايد</t>
@@ -1431,7 +1386,6 @@
       <c r="G62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
           <t>تل الكبير</t>
@@ -1444,7 +1398,6 @@
       <c r="G63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
           <t>الشلوفة</t>
@@ -1457,7 +1410,6 @@
       <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>الدفرسوار</t>
@@ -1495,8 +1447,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="6" t="n"/>
       <c r="C67" s="4" t="inlineStr">
         <is>
           <t>مركز تخاطب سفاجة</t>
@@ -1512,7 +1462,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>سفاجة</t>
@@ -1525,7 +1474,6 @@
       <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n"/>
       <c r="B69" s="3" t="inlineStr">
         <is>
           <t>القصير</t>
@@ -1538,7 +1486,6 @@
       <c r="G69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n"/>
       <c r="B70" s="3" t="inlineStr">
         <is>
           <t>مرسى علم</t>
@@ -1551,7 +1498,6 @@
       <c r="G70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
           <t>شلاتين</t>
@@ -1564,7 +1510,6 @@
       <c r="G71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
           <t>حلايب</t>
@@ -1577,7 +1522,6 @@
       <c r="G72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
           <t>أبو رماد</t>
@@ -1590,7 +1534,6 @@
       <c r="G73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n"/>
       <c r="B74" s="3" t="inlineStr">
         <is>
           <t>قصير الجديدة</t>
@@ -1603,7 +1546,6 @@
       <c r="G74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n"/>
       <c r="B75" s="3" t="inlineStr">
         <is>
           <t>رأس غارب</t>
@@ -1616,7 +1558,6 @@
       <c r="G75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n"/>
       <c r="B76" s="3" t="inlineStr">
         <is>
           <t>دهب</t>
@@ -1654,7 +1595,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n"/>
       <c r="B78" s="3" t="inlineStr">
         <is>
           <t>كفر الدوار</t>
@@ -1667,7 +1607,6 @@
       <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n"/>
       <c r="B79" s="3" t="inlineStr">
         <is>
           <t>رشيد</t>
@@ -1688,7 +1627,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
           <t>إدكو</t>
@@ -1701,7 +1639,6 @@
       <c r="G80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n"/>
       <c r="B81" s="3" t="inlineStr">
         <is>
           <t>أبو حمص</t>
@@ -1714,7 +1651,6 @@
       <c r="G81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
           <t>كوم حمادة</t>
@@ -1727,7 +1663,6 @@
       <c r="G82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n"/>
       <c r="B83" s="3" t="inlineStr">
         <is>
           <t>شبراخيت</t>
@@ -1740,7 +1675,6 @@
       <c r="G83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n"/>
       <c r="B84" s="3" t="inlineStr">
         <is>
           <t>كفر الشيخ</t>
@@ -1753,7 +1687,6 @@
       <c r="G84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n"/>
       <c r="B85" s="3" t="inlineStr">
         <is>
           <t>نوقة</t>
@@ -1766,7 +1699,6 @@
       <c r="G85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n"/>
       <c r="B86" s="3" t="inlineStr">
         <is>
           <t>الحامول</t>
@@ -1779,7 +1711,6 @@
       <c r="G86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n"/>
       <c r="B87" s="3" t="inlineStr">
         <is>
           <t>شرقية</t>
@@ -1792,7 +1723,6 @@
       <c r="G87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n"/>
       <c r="B88" s="3" t="inlineStr">
         <is>
           <t>الدلنجات</t>
@@ -1805,7 +1735,6 @@
       <c r="G88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n"/>
       <c r="B89" s="3" t="inlineStr">
         <is>
           <t>إيتاي البارود</t>
@@ -1818,7 +1747,6 @@
       <c r="G89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n"/>
       <c r="B90" s="3" t="inlineStr">
         <is>
           <t>بسيون</t>
@@ -1831,7 +1759,6 @@
       <c r="G90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n"/>
       <c r="B91" s="3" t="inlineStr">
         <is>
           <t>سنجور</t>
@@ -1869,8 +1796,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="n"/>
       <c r="C93" s="4" t="inlineStr">
         <is>
           <t>مركز تخاطب وسمع واتزان</t>
@@ -1886,8 +1811,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n"/>
-      <c r="B94" s="5" t="n"/>
       <c r="C94" s="4" t="inlineStr">
         <is>
           <t>مركز قدرات للتخاطب</t>
@@ -1903,8 +1826,6 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n"/>
-      <c r="B95" s="5" t="n"/>
       <c r="C95" s="4" t="inlineStr">
         <is>
           <t>مركز مكة للتخاطب وتنمية مهارات</t>
@@ -1920,8 +1841,6 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n"/>
-      <c r="B96" s="6" t="n"/>
       <c r="C96" s="4" t="inlineStr">
         <is>
           <t>مركز القادة للتخاطب وتنمية المهارات</t>
@@ -1937,7 +1856,6 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n"/>
       <c r="B97" s="3" t="inlineStr">
         <is>
           <t>مدينة 6 أكتوبر</t>
@@ -1950,7 +1868,6 @@
       <c r="G97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
           <t>حلوان</t>
@@ -1963,7 +1880,6 @@
       <c r="G98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n"/>
       <c r="B99" s="3" t="inlineStr">
         <is>
           <t>البدرشين</t>
@@ -1976,7 +1892,6 @@
       <c r="G99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n"/>
       <c r="B100" s="3" t="inlineStr">
         <is>
           <t>دهشور</t>
@@ -1989,7 +1904,6 @@
       <c r="G100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n"/>
       <c r="B101" s="3" t="inlineStr">
         <is>
           <t>أبو رواش</t>
@@ -2002,7 +1916,6 @@
       <c r="G101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n"/>
       <c r="B102" s="3" t="inlineStr">
         <is>
           <t>الوراق</t>
@@ -2015,7 +1928,6 @@
       <c r="G102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n"/>
       <c r="B103" s="3" t="inlineStr">
         <is>
           <t>الساحل</t>
@@ -2028,7 +1940,6 @@
       <c r="G103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n"/>
       <c r="B104" s="3" t="inlineStr">
         <is>
           <t>الكيت كات</t>
@@ -2041,7 +1952,6 @@
       <c r="G104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
       <c r="B105" s="3" t="inlineStr">
         <is>
           <t>الهرم</t>
@@ -2062,8 +1972,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n"/>
-      <c r="B106" s="5" t="n"/>
       <c r="C106" s="4" t="inlineStr">
         <is>
           <t>مركز طريقنا للتخاطب</t>
@@ -2079,8 +1987,6 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n"/>
-      <c r="B107" s="6" t="n"/>
       <c r="C107" s="4" t="inlineStr">
         <is>
           <t>مركز الأهرام للتخاطب</t>
@@ -2096,7 +2002,6 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n"/>
       <c r="B108" s="3" t="inlineStr">
         <is>
           <t>إمبابة</t>
@@ -2117,8 +2022,6 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n"/>
-      <c r="B109" s="6" t="n"/>
       <c r="C109" s="4" t="inlineStr">
         <is>
           <t>مركز تخاطب شارع عزبة الصعايدة</t>
@@ -2134,7 +2037,6 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n"/>
       <c r="B110" s="3" t="inlineStr">
         <is>
           <t>العمرانية</t>
@@ -2147,7 +2049,6 @@
       <c r="G110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n"/>
       <c r="B111" s="3" t="inlineStr">
         <is>
           <t>الحوامدية</t>
@@ -2160,7 +2061,6 @@
       <c r="G111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n"/>
       <c r="B112" s="3" t="inlineStr">
         <is>
           <t>أطفيح</t>
@@ -2173,7 +2073,6 @@
       <c r="G112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
           <t>بني سويف الجديدة</t>
@@ -2186,7 +2085,6 @@
       <c r="G113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="n"/>
       <c r="B114" s="3" t="inlineStr">
         <is>
           <t>المنيل</t>
@@ -2224,8 +2122,6 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n"/>
-      <c r="B116" s="6" t="n"/>
       <c r="C116" s="4" t="inlineStr">
         <is>
           <t>مركز الدلتا للتخاطب</t>
@@ -2241,7 +2137,6 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n"/>
       <c r="B117" s="3" t="inlineStr">
         <is>
           <t>طلخا</t>
@@ -2254,7 +2149,6 @@
       <c r="G117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n"/>
       <c r="B118" s="3" t="inlineStr">
         <is>
           <t>آجا</t>
@@ -2267,7 +2161,6 @@
       <c r="G118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n"/>
       <c r="B119" s="3" t="inlineStr">
         <is>
           <t>مِت غمر</t>
@@ -2280,7 +2173,6 @@
       <c r="G119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n"/>
       <c r="B120" s="3" t="inlineStr">
         <is>
           <t>شربين</t>
@@ -2293,7 +2185,6 @@
       <c r="G120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n"/>
       <c r="B121" s="3" t="inlineStr">
         <is>
           <t>بلقاس</t>
@@ -2306,7 +2197,6 @@
       <c r="G121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>جمصة</t>
@@ -2319,7 +2209,6 @@
       <c r="G122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n"/>
       <c r="B123" s="3" t="inlineStr">
         <is>
           <t>السنبلاوين</t>
@@ -2332,7 +2221,6 @@
       <c r="G123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n"/>
       <c r="B124" s="3" t="inlineStr">
         <is>
           <t>ميت سلسيل</t>
@@ -2345,7 +2233,6 @@
       <c r="G124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n"/>
       <c r="B125" s="3" t="inlineStr">
         <is>
           <t>أجا</t>
@@ -2358,7 +2245,6 @@
       <c r="G125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
           <t>المتينة</t>
@@ -2371,7 +2257,6 @@
       <c r="G126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n"/>
       <c r="B127" s="3" t="inlineStr">
         <is>
           <t>منية النصر</t>
@@ -2384,7 +2269,6 @@
       <c r="G127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="6" t="n"/>
       <c r="B128" s="3" t="inlineStr">
         <is>
           <t>كفر سعد</t>
@@ -2426,7 +2310,6 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n"/>
       <c r="B130" s="3" t="inlineStr">
         <is>
           <t>عين سخنة</t>
@@ -2439,7 +2322,6 @@
       <c r="G130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n"/>
       <c r="B131" s="3" t="inlineStr">
         <is>
           <t>عطاقة</t>
@@ -2452,7 +2334,6 @@
       <c r="G131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n"/>
       <c r="B132" s="3" t="inlineStr">
         <is>
           <t>الجنايين</t>
@@ -2465,7 +2346,6 @@
       <c r="G132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n"/>
       <c r="B133" s="3" t="inlineStr">
         <is>
           <t>فايد</t>
@@ -2478,7 +2358,6 @@
       <c r="G133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n"/>
       <c r="B134" s="3" t="inlineStr">
         <is>
           <t>ناقصة</t>
@@ -2491,7 +2370,6 @@
       <c r="G134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n"/>
       <c r="B135" s="3" t="inlineStr">
         <is>
           <t>القصير</t>
@@ -2504,7 +2382,6 @@
       <c r="G135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="n"/>
       <c r="B136" s="3" t="inlineStr">
         <is>
           <t>الدفرسوار</t>
@@ -2546,8 +2423,6 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n"/>
-      <c r="B138" s="5" t="n"/>
       <c r="C138" s="4" t="inlineStr">
         <is>
           <t>مركز السلام للتخاطب وتنمية المهارات</t>
@@ -2563,8 +2438,6 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n"/>
-      <c r="B139" s="6" t="n"/>
       <c r="C139" s="4" t="inlineStr">
         <is>
           <t>مركز الحياة للتخاطب وتنمية المهارات</t>
@@ -2584,7 +2457,6 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n"/>
       <c r="B140" s="3" t="inlineStr">
         <is>
           <t>الإسماعيلية</t>
@@ -2597,7 +2469,6 @@
       <c r="G140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n"/>
       <c r="B141" s="3" t="inlineStr">
         <is>
           <t>بلبيس</t>
@@ -2622,7 +2493,6 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n"/>
       <c r="B142" s="3" t="inlineStr">
         <is>
           <t>مدينة 10 رمضان</t>
@@ -2635,7 +2505,6 @@
       <c r="G142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n"/>
       <c r="B143" s="3" t="inlineStr">
         <is>
           <t>المعادي</t>
@@ -2648,7 +2517,6 @@
       <c r="G143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n"/>
       <c r="B144" s="3" t="inlineStr">
         <is>
           <t>فاقوس</t>
@@ -2669,8 +2537,6 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n"/>
-      <c r="B145" s="6" t="n"/>
       <c r="C145" s="4" t="inlineStr">
         <is>
           <t>مركز كِنان للتخاطب والتأهيل</t>
@@ -2686,7 +2552,6 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n"/>
       <c r="B146" s="3" t="inlineStr">
         <is>
           <t>القنايات</t>
@@ -2699,7 +2564,6 @@
       <c r="G146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n"/>
       <c r="B147" s="3" t="inlineStr">
         <is>
           <t>أبو حماد</t>
@@ -2712,7 +2576,6 @@
       <c r="G147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
           <t>الجزيرة</t>
@@ -2725,7 +2588,6 @@
       <c r="G148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
           <t>ههيا</t>
@@ -2738,7 +2600,6 @@
       <c r="G149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n"/>
       <c r="B150" s="3" t="inlineStr">
         <is>
           <t>درب السلام</t>
@@ -2751,7 +2612,6 @@
       <c r="G150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="n"/>
       <c r="B151" s="3" t="inlineStr">
         <is>
           <t>الصالحية</t>
@@ -2789,8 +2649,6 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n"/>
-      <c r="B153" s="5" t="n"/>
       <c r="C153" s="4" t="inlineStr">
         <is>
           <t>أكاديمية المعرفة للتخاطب</t>
@@ -2810,8 +2668,6 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n"/>
-      <c r="B154" s="5" t="n"/>
       <c r="C154" s="4" t="inlineStr">
         <is>
           <t>مركز القمة للتدريب والتأهيل</t>
@@ -2831,8 +2687,6 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n"/>
-      <c r="B155" s="5" t="n"/>
       <c r="C155" s="4" t="inlineStr">
         <is>
           <t>عيادة الدكتورة إيناس أحمد</t>
@@ -2852,8 +2706,6 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n"/>
-      <c r="B156" s="6" t="n"/>
       <c r="C156" s="4" t="inlineStr">
         <is>
           <t>مركز الدلتا لأمراض التخاطب</t>
@@ -2869,7 +2721,6 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
           <t>كفر الزيات</t>
@@ -2882,7 +2733,6 @@
       <c r="G157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n"/>
       <c r="B158" s="3" t="inlineStr">
         <is>
           <t>سمنود</t>
@@ -2895,7 +2745,6 @@
       <c r="G158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n"/>
       <c r="B159" s="3" t="inlineStr">
         <is>
           <t>زفتا</t>
@@ -2908,7 +2757,6 @@
       <c r="G159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n"/>
       <c r="B160" s="3" t="inlineStr">
         <is>
           <t>المحلة الكبرى</t>
@@ -2929,8 +2777,6 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n"/>
-      <c r="B161" s="5" t="n"/>
       <c r="C161" s="4" t="inlineStr">
         <is>
           <t>مركز كيدز الأمل للعلاج الطبيعي</t>
@@ -2946,8 +2792,6 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n"/>
-      <c r="B162" s="6" t="n"/>
       <c r="C162" s="4" t="inlineStr">
         <is>
           <t>مركز صن رايز للتخاطب</t>
@@ -2963,7 +2807,6 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="n"/>
       <c r="B163" s="3" t="inlineStr">
         <is>
           <t>قطور</t>
@@ -2976,7 +2819,6 @@
       <c r="G163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n"/>
       <c r="B164" s="3" t="inlineStr">
         <is>
           <t>سان الحجر</t>
@@ -2989,7 +2831,6 @@
       <c r="G164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="n"/>
       <c r="B165" s="3" t="inlineStr">
         <is>
           <t>بسيون</t>
@@ -3002,7 +2843,6 @@
       <c r="G165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="n"/>
       <c r="B166" s="3" t="inlineStr">
         <is>
           <t>الدلتا الجديدة</t>
@@ -3040,8 +2880,6 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="n"/>
-      <c r="B168" s="6" t="n"/>
       <c r="C168" s="4" t="inlineStr">
         <is>
           <t>مركز التخاطب بمركز شباب الشواشنة</t>
@@ -3057,7 +2895,6 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="n"/>
       <c r="B169" s="3" t="inlineStr">
         <is>
           <t>سيوه</t>
@@ -3070,7 +2907,6 @@
       <c r="G169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="n"/>
       <c r="B170" s="3" t="inlineStr">
         <is>
           <t>القرين</t>
@@ -3083,7 +2919,6 @@
       <c r="G170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="n"/>
       <c r="B171" s="3" t="inlineStr">
         <is>
           <t>إبشواي</t>
@@ -3096,7 +2931,6 @@
       <c r="G171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="n"/>
       <c r="B172" s="3" t="inlineStr">
         <is>
           <t>سنوريس</t>
@@ -3109,7 +2943,6 @@
       <c r="G172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="n"/>
       <c r="B173" s="3" t="inlineStr">
         <is>
           <t>طامية</t>
@@ -3122,7 +2955,6 @@
       <c r="G173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="n"/>
       <c r="B174" s="3" t="inlineStr">
         <is>
           <t>اطسا</t>
@@ -3135,7 +2967,6 @@
       <c r="G174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="n"/>
       <c r="B175" s="3" t="inlineStr">
         <is>
           <t>يوسف الصديق</t>
@@ -3148,7 +2979,6 @@
       <c r="G175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="n"/>
       <c r="B176" s="3" t="inlineStr">
         <is>
           <t>العدوة</t>
@@ -3161,7 +2991,6 @@
       <c r="G176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="6" t="n"/>
       <c r="B177" s="3" t="inlineStr">
         <is>
           <t>آثار</t>
@@ -3207,461 +3036,580 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="n"/>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب المرح لعلاج الأطفال والكبار</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr"/>
-      <c r="E179" s="4" t="inlineStr"/>
-      <c r="F179" s="4" t="inlineStr"/>
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل وصعوبات التعلم - فرع جديد</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr"/>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr"/>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا</t>
+          <t>شارع جميل أمام بنك القاهرة</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
-      <c r="B180" s="5" t="n"/>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب أخصائية التخاطب هبة المصري</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>د. هبة المصري</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr"/>
-      <c r="F180" s="4" t="inlineStr"/>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>مركز تخاطب البر والتقوى</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr"/>
+      <c r="D180" s="9" t="inlineStr"/>
+      <c r="E180" s="9" t="inlineStr"/>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>104 برج الأوقاف، شارع ابن سندر، سرايا القبة، القاهرة</t>
+        </is>
+      </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>ترعة القبة، مساكن الأميرية الجنوبية، حدائق القبة</t>
+          <t>بنها</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="n"/>
-      <c r="B181" s="5" t="n"/>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>مركز نور الحياة للتخاطب</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr"/>
-      <c r="E181" s="4" t="inlineStr"/>
-      <c r="F181" s="4" t="inlineStr"/>
+      <c r="A181" s="6" t="n"/>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>بيت التمريض</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr"/>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>201201120500</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr"/>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>متخصص في التخاطب وتعديل السلوك</t>
+        </is>
+      </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>شارع شبرا الخلفاوي، قسم الساحل</t>
+          <t>بنها</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="n"/>
-      <c r="B182" s="5" t="n"/>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr"/>
-      <c r="E182" s="4" t="inlineStr"/>
-      <c r="F182" s="4" t="inlineStr"/>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
-        </is>
-      </c>
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>المركز الذهبي التخصصي (GSC)</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr"/>
+      <c r="D182" s="9" t="inlineStr"/>
+      <c r="E182" s="9" t="inlineStr"/>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>مدينة نصر، متخصص في التخاطب وتعديل السلوك</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
-      <c r="B183" s="5" t="n"/>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>معهد السمع والكلام بإمبابة</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr"/>
-      <c r="E183" s="4" t="inlineStr"/>
-      <c r="F183" s="4" t="inlineStr"/>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>مركز Speak للتخاطب</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr"/>
+      <c r="D183" s="9" t="inlineStr"/>
+      <c r="E183" s="9" t="inlineStr"/>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>زهراء مدينة نصر، المرحلة الأولى، بجوار مسجد النور</t>
+        </is>
+      </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>1 شارع الطيار فكري، بجوار مستشفى الحميات، إمبابة</t>
+          <t>75 شارع حنفي الشيخوني</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>مركز Speak للتخاطب</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr"/>
-      <c r="E184" s="4" t="inlineStr"/>
-      <c r="F184" s="4" t="inlineStr"/>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>مركز الزهراء للتخاطب</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr"/>
+      <c r="D184" s="9" t="inlineStr"/>
+      <c r="E184" s="9" t="inlineStr"/>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
+        </is>
+      </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>زهراء مدينة نصر - المرحلة الأولى</t>
+          <t>شارع محمد القطان</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr"/>
+      <c r="D185" s="9" t="inlineStr"/>
+      <c r="E185" s="9" t="inlineStr"/>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>شارع مصطفى النحاس، فوق التوحيد والنور</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>2 شارع أحمد عبد ربه</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="n"/>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب - فرع مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr"/>
+      <c r="D186" s="9" t="inlineStr"/>
+      <c r="E186" s="9" t="inlineStr"/>
+      <c r="F186" s="8" t="inlineStr">
         <is>
           <t>مدينة نصر</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>المركز الذهبي التخصصي (GSC)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr"/>
-      <c r="E185" s="4" t="inlineStr"/>
-      <c r="F185" s="4" t="inlineStr"/>
-      <c r="G185" s="4" t="inlineStr">
-        <is>
-          <t>مدينة نصر، القاهرة</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="n"/>
-      <c r="B186" s="5" t="n"/>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>مركز الزهراء للتخاطب</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr"/>
-      <c r="E186" s="4" t="inlineStr"/>
-      <c r="F186" s="4" t="inlineStr"/>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
-        </is>
-      </c>
+      <c r="G186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="n"/>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>مركز الحمد للعلاج الطبيعي والتخاطب</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr"/>
-      <c r="E187" s="4" t="inlineStr"/>
-      <c r="F187" s="4" t="inlineStr"/>
-      <c r="G187" s="4" t="inlineStr">
-        <is>
-          <t>شارع مصطفى النحاس فوق التوحيد والنور بعد مدرسة المنهل</t>
-        </is>
-      </c>
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل - فرع مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr"/>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="inlineStr"/>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="n"/>
-      <c r="B188" s="6" t="n"/>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr"/>
-      <c r="E188" s="4" t="inlineStr"/>
-      <c r="F188" s="4" t="inlineStr"/>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>مدينة نصر</t>
-        </is>
-      </c>
+      <c r="A188" s="6" t="n"/>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>المركز المصري الكندي - فرع النزهة</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr"/>
+      <c r="D188" s="9" t="inlineStr"/>
+      <c r="E188" s="9" t="inlineStr"/>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>14 شارع جمال الدين على، بجوار ملاهي السندباد</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="n"/>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل و صعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>د. وفاء وافي</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr"/>
-      <c r="F189" s="4" t="inlineStr"/>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>1 شارع المنتزه خلف مستشفى هليوبوليس</t>
-        </is>
-      </c>
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>مركز كيور لجراحات الأذن والقوقعة والسمعيات والتخاطب</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr"/>
+      <c r="D189" s="9" t="inlineStr"/>
+      <c r="E189" s="9" t="inlineStr"/>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>شارع النصر، تقاطع اللاسلكي، حي المعادي</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
-      <c r="B190" s="6" t="n"/>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>مركز هليوبوليس للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>01151194780</t>
-        </is>
-      </c>
-      <c r="F190" s="4" t="inlineStr"/>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t>28 شارع محمد عبيد من شارع النزهة، ميدان السبع عمارات</t>
-        </is>
-      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>مركز الجنا للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr"/>
+      <c r="D190" s="9" t="inlineStr"/>
+      <c r="E190" s="9" t="inlineStr"/>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>شارع 76، المعادى</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="n"/>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>الزمالك</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr"/>
-      <c r="D191" s="4" t="inlineStr"/>
-      <c r="E191" s="4" t="inlineStr"/>
-      <c r="F191" s="4" t="inlineStr"/>
+      <c r="A191" s="6" t="n"/>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>المركز المصري الكندي - فرع المعادي</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr"/>
+      <c r="D191" s="9" t="inlineStr"/>
+      <c r="E191" s="9" t="inlineStr"/>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>5/3 شارع اللاسلكي، بجوار شركة غاز مصر</t>
+        </is>
+      </c>
       <c r="G191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="n"/>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr"/>
-      <c r="D192" s="4" t="inlineStr"/>
-      <c r="E192" s="4" t="inlineStr"/>
-      <c r="F192" s="4" t="inlineStr"/>
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>مركز علمني للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr"/>
+      <c r="D192" s="9" t="inlineStr"/>
+      <c r="E192" s="9" t="inlineStr"/>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>8 عمارات منتصر، الدور الأرضي، بجوار مسجد عباد الرحمن</t>
+        </is>
+      </c>
       <c r="G192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="n"/>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>العبّاسية</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr"/>
-      <c r="D193" s="4" t="inlineStr"/>
-      <c r="E193" s="4" t="inlineStr"/>
-      <c r="F193" s="4" t="inlineStr"/>
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>روض الفرج</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>مركز تخاطب المرح</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr"/>
+      <c r="D193" s="9" t="inlineStr"/>
+      <c r="E193" s="9" t="inlineStr"/>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا مصر</t>
+        </is>
+      </c>
       <c r="G193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="n"/>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>مدينة 6 أكتوبر</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr"/>
-      <c r="D194" s="4" t="inlineStr"/>
-      <c r="E194" s="4" t="inlineStr"/>
-      <c r="F194" s="4" t="inlineStr"/>
+      <c r="A194" s="6" t="n"/>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr"/>
+      <c r="D194" s="9" t="inlineStr"/>
+      <c r="E194" s="9" t="inlineStr"/>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
+        </is>
+      </c>
       <c r="G194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="n"/>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>مدينة الشروق</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr"/>
-      <c r="D195" s="4" t="inlineStr"/>
-      <c r="E195" s="4" t="inlineStr"/>
-      <c r="F195" s="4" t="inlineStr"/>
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>المطرية</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل بالمطرية</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr"/>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>01147626979</t>
+        </is>
+      </c>
+      <c r="E195" s="9" t="inlineStr"/>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>شارع منية مطر، بجوار محطة مترو المطرية</t>
+        </is>
+      </c>
       <c r="G195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="n"/>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>مدينة بدر</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>مركز متخصص للتخاطب</t>
-        </is>
-      </c>
-      <c r="D196" s="4" t="inlineStr"/>
-      <c r="E196" s="4" t="inlineStr"/>
-      <c r="F196" s="4" t="inlineStr"/>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>مدينة بدر، القاهرة</t>
-        </is>
-      </c>
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>الدقي</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع الدقي</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr"/>
+      <c r="D196" s="9" t="inlineStr"/>
+      <c r="E196" s="9" t="inlineStr"/>
+      <c r="F196" s="8" t="inlineStr">
+        <is>
+          <t>4 شارع Hussein Wassef، الدقي</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="n"/>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>مدينة 15 مايو</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr"/>
-      <c r="D197" s="4" t="inlineStr"/>
-      <c r="E197" s="4" t="inlineStr"/>
-      <c r="F197" s="4" t="inlineStr"/>
+      <c r="A197" s="6" t="n"/>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب - الدقي</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr"/>
+      <c r="D197" s="9" t="inlineStr"/>
+      <c r="E197" s="9" t="inlineStr"/>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>110 شارع التحرير، الدقي، أمام محطة مترو الدقي</t>
+        </is>
+      </c>
       <c r="G197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="n"/>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>المعادي</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>المركز المصري الكندي</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr"/>
-      <c r="E198" s="4" t="inlineStr"/>
-      <c r="F198" s="4" t="inlineStr"/>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>5/3 شارع اللاسلكي بجوار شركة غاز مصر</t>
-        </is>
-      </c>
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>الهرم</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>مركز هووب للتخاطب</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr"/>
+      <c r="D198" s="9" t="inlineStr"/>
+      <c r="E198" s="9" t="inlineStr"/>
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>الهرم، متخصص في التخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
-      <c r="B199" s="5" t="n"/>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب البر والتقوى</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr"/>
-      <c r="E199" s="4" t="inlineStr"/>
-      <c r="F199" s="4" t="inlineStr"/>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>104 برج الأوقاف، شارع ابن سندر</t>
-        </is>
-      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>مركز فرصة حياه للتأهيل للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr"/>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>01030360536</t>
+        </is>
+      </c>
+      <c r="E199" s="9" t="inlineStr"/>
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>الهرم وفيصل</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="n"/>
-      <c r="B200" s="6" t="n"/>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>مركز كيور لجراحات الأذن والقوقعة والتخاطب</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr"/>
-      <c r="E200" s="4" t="inlineStr"/>
-      <c r="F200" s="4" t="inlineStr"/>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>شارع النصر، تقاطع اللاسلكي</t>
-        </is>
-      </c>
+      <c r="A200" s="6" t="n"/>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>مركز اشراقة للتخاطب - د/اسلام سالم</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>د/اسلام سالم</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr"/>
+      <c r="E200" s="9" t="inlineStr"/>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>شارع اللبيني، الهرم الرئيسي</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="n"/>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>مركز Almony للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr"/>
-      <c r="E201" s="4" t="inlineStr"/>
-      <c r="F201" s="4" t="inlineStr"/>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>8 عمارات منتصر، بجانب مسجد عبد الرحمن، حدائق حلوان</t>
-        </is>
-      </c>
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>النزهة</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب - فرع النزهة</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr"/>
+      <c r="D201" s="9" t="inlineStr"/>
+      <c r="E201" s="9" t="inlineStr"/>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>النزهة</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="n"/>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>المقطم</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr"/>
-      <c r="D202" s="4" t="inlineStr"/>
-      <c r="E202" s="4" t="inlineStr"/>
-      <c r="F202" s="4" t="inlineStr"/>
+      <c r="A202" s="6" t="n"/>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>نور الحياة للتخاطب</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr"/>
+      <c r="D202" s="9" t="inlineStr"/>
+      <c r="E202" s="9" t="inlineStr"/>
+      <c r="F202" s="8" t="inlineStr">
+        <is>
+          <t>شارع شبرا الخلفاوى، قسم الساحل</t>
+        </is>
+      </c>
       <c r="G202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="n"/>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>القاهرة الجديدة</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr"/>
-      <c r="D203" s="4" t="inlineStr"/>
-      <c r="E203" s="4" t="inlineStr"/>
-      <c r="F203" s="4" t="inlineStr"/>
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>الزيتون</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل - فرع الزيتون</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr"/>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
+      <c r="E203" s="9" t="inlineStr"/>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>حي الزيتون</t>
+        </is>
+      </c>
       <c r="G203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="n"/>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>الشيخ زايد</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr"/>
-      <c r="D204" s="4" t="inlineStr"/>
-      <c r="E204" s="4" t="inlineStr"/>
-      <c r="F204" s="4" t="inlineStr"/>
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب - فرع عين شمس</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr"/>
+      <c r="D204" s="9" t="inlineStr"/>
+      <c r="E204" s="9" t="inlineStr"/>
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
       <c r="G204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="n"/>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>الرحاب</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr"/>
-      <c r="D205" s="4" t="inlineStr"/>
-      <c r="E205" s="4" t="inlineStr"/>
-      <c r="F205" s="4" t="inlineStr"/>
-      <c r="G205" s="4" t="inlineStr"/>
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>فيصل</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>مركز فرصة حياه - فرع فيصل</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr"/>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>01030360536</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="inlineStr"/>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>فيصل</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="n"/>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>الحي العاشر</t>
+          <t>البرجايه</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr"/>
@@ -3671,87 +3619,93 @@
       <c r="G206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="n"/>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>المنيل</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr"/>
+          <t>بركة السبع</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب وصعوبات تعلم</t>
+        </is>
+      </c>
       <c r="D207" s="4" t="inlineStr"/>
       <c r="E207" s="4" t="inlineStr"/>
       <c r="F207" s="4" t="inlineStr"/>
-      <c r="G207" s="4" t="inlineStr"/>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="n"/>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>الدقي</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>فرع الدقي من مركز الحمد</t>
-        </is>
-      </c>
+          <t>منوف الجديدة</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr"/>
       <c r="D208" s="4" t="inlineStr"/>
       <c r="E208" s="4" t="inlineStr"/>
       <c r="F208" s="4" t="inlineStr"/>
-      <c r="G208" s="4" t="inlineStr">
-        <is>
-          <t>4 شارع حسين واصف، بجوار مدرسة العروبة</t>
-        </is>
-      </c>
+      <c r="G208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="n"/>
-      <c r="B209" s="6" t="n"/>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب شارع التحرير</t>
-        </is>
-      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>كفر عبده</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr"/>
       <c r="D209" s="4" t="inlineStr"/>
       <c r="E209" s="4" t="inlineStr"/>
       <c r="F209" s="4" t="inlineStr"/>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>شارع التحرير، أمام محطة مترو الدقي</t>
-        </is>
-      </c>
+      <c r="G209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="n"/>
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C210" s="4" t="inlineStr"/>
+          <t>المنيا</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب بني أحمد للتخاطب</t>
+        </is>
+      </c>
       <c r="D210" s="4" t="inlineStr"/>
       <c r="E210" s="4" t="inlineStr"/>
       <c r="F210" s="4" t="inlineStr"/>
-      <c r="G210" s="4" t="inlineStr"/>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="n"/>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>الموسكي</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr"/>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب مقوسة للتخاطب</t>
+        </is>
+      </c>
       <c r="D211" s="4" t="inlineStr"/>
       <c r="E211" s="4" t="inlineStr"/>
       <c r="F211" s="4" t="inlineStr"/>
-      <c r="G211" s="4" t="inlineStr"/>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="n"/>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>الفجالة</t>
+          <t>سمالوط</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
@@ -3761,10 +3715,9 @@
       <c r="G212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="n"/>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>باب الشعرية</t>
+          <t>بني حسن</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
@@ -3774,10 +3727,9 @@
       <c r="G213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="n"/>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>الساحل</t>
+          <t>هرموبوليس</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
@@ -3787,77 +3739,45 @@
       <c r="G214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="n"/>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>المطرية</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل بالمطرية</t>
-        </is>
-      </c>
+          <t>ملوي</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr"/>
       <c r="D215" s="4" t="inlineStr"/>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>01270756267, 01092975341</t>
-        </is>
-      </c>
+      <c r="E215" s="4" t="inlineStr"/>
       <c r="F215" s="4" t="inlineStr"/>
-      <c r="G215" s="4" t="inlineStr">
-        <is>
-          <t>شارع منية مطر المطرية، بجوار محطة مترو المطرية</t>
-        </is>
-      </c>
+      <c r="G215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="n"/>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>عين شمس</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب</t>
-        </is>
-      </c>
+          <t>العدوة</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr"/>
       <c r="D216" s="4" t="inlineStr"/>
       <c r="E216" s="4" t="inlineStr"/>
       <c r="F216" s="4" t="inlineStr"/>
-      <c r="G216" s="4" t="inlineStr">
-        <is>
-          <t>عين شمس</t>
-        </is>
-      </c>
+      <c r="G216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="n"/>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>حورس للسمعيات والتخاطب</t>
-        </is>
-      </c>
+          <t>ديروط الشريف</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr"/>
       <c r="D217" s="4" t="inlineStr"/>
       <c r="E217" s="4" t="inlineStr"/>
       <c r="F217" s="4" t="inlineStr"/>
-      <c r="G217" s="4" t="inlineStr">
-        <is>
-          <t>1 ميدان المطرية، الزيتون</t>
-        </is>
-      </c>
+      <c r="G217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="n"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>وسيط</t>
+          <t>أبوقرقاص</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
@@ -3867,10 +3787,9 @@
       <c r="G218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="n"/>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>المنصورية</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr"/>
@@ -3880,10 +3799,9 @@
       <c r="G219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="5" t="n"/>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>الدراسة</t>
+          <t>بني مازن</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr"/>
@@ -3893,10 +3811,9 @@
       <c r="G220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="n"/>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>درب الجنينة</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr"/>
@@ -3906,28 +3823,39 @@
       <c r="G221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="n"/>
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>الوادي الجديد</t>
+        </is>
+      </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>الشرابية</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr"/>
+          <t>الخارجة</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب الخارجة للتخاطب</t>
+        </is>
+      </c>
       <c r="D222" s="4" t="inlineStr"/>
       <c r="E222" s="4" t="inlineStr"/>
       <c r="F222" s="4" t="inlineStr"/>
-      <c r="G222" s="4" t="inlineStr"/>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>الخارجة</t>
+        </is>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="n"/>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>النزهة</t>
+          <t>الداخلة</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>المركز المصري الكندي (فرع النزهة)</t>
+          <t>مركز شباب باريس للتخاطب</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -3935,15 +3863,14 @@
       <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>14 شارع جمال الدين علي بجوار ملاهي السندباد</t>
+          <t>باريس</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="n"/>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>الرويسي</t>
+          <t>موط</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr"/>
@@ -3953,10 +3880,9 @@
       <c r="G224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="n"/>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>قصر النيل</t>
+          <t>بلاط</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr"/>
@@ -3966,10 +3892,9 @@
       <c r="G225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="n"/>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>الفسطاط</t>
+          <t>فرافرة</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr"/>
@@ -3979,10 +3904,9 @@
       <c r="G226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="6" t="n"/>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>الرحاب</t>
+          <t>باريس</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr"/>
@@ -3992,137 +3916,106 @@
       <c r="G227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>القليوبية</t>
-        </is>
-      </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>بنها</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب برج مكة</t>
-        </is>
-      </c>
+          <t>القصر</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr"/>
       <c r="D228" s="4" t="inlineStr"/>
       <c r="E228" s="4" t="inlineStr"/>
       <c r="F228" s="4" t="inlineStr"/>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t>شارع جميل أمام بنك القاهرة</t>
-        </is>
-      </c>
+      <c r="G228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="n"/>
-      <c r="B229" s="5" t="n"/>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الجزار</t>
-        </is>
-      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>تينيدة</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr"/>
       <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr"/>
       <c r="F229" s="4" t="inlineStr"/>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="n"/>
-      <c r="B230" s="6" t="n"/>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العمار</t>
-        </is>
-      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>دوش</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr"/>
       <c r="D230" s="4" t="inlineStr"/>
       <c r="E230" s="4" t="inlineStr"/>
       <c r="F230" s="4" t="inlineStr"/>
-      <c r="G230" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="n"/>
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>قليوب</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr"/>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العبور للتخاطب</t>
+        </is>
+      </c>
       <c r="D231" s="4" t="inlineStr"/>
       <c r="E231" s="4" t="inlineStr"/>
       <c r="F231" s="4" t="inlineStr"/>
-      <c r="G231" s="4" t="inlineStr"/>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="n"/>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>شبرا الخيمة</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
+          <t>الفشن</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr"/>
       <c r="D232" s="4" t="inlineStr"/>
       <c r="E232" s="4" t="inlineStr"/>
       <c r="F232" s="4" t="inlineStr"/>
-      <c r="G232" s="4" t="inlineStr">
-        <is>
-          <t>75 شارع حنفي الشيخوني</t>
-        </is>
-      </c>
+      <c r="G232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="n"/>
-      <c r="B233" s="5" t="n"/>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>مركز النور الهدى الطبي</t>
-        </is>
-      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>ساماستا</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr"/>
       <c r="D233" s="4" t="inlineStr"/>
       <c r="E233" s="4" t="inlineStr"/>
       <c r="F233" s="4" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr">
-        <is>
-          <t>شارع محمد القطان</t>
-        </is>
-      </c>
+      <c r="G233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="n"/>
-      <c r="B234" s="6" t="n"/>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>مركز تواصل للتخاطب</t>
-        </is>
-      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>إبشواي</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr"/>
       <c r="D234" s="4" t="inlineStr"/>
       <c r="E234" s="4" t="inlineStr"/>
       <c r="F234" s="4" t="inlineStr"/>
-      <c r="G234" s="4" t="inlineStr">
-        <is>
-          <t>2 شارع أحمد عبد ربه</t>
-        </is>
-      </c>
+      <c r="G234" s="4" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="n"/>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>الخانكة</t>
+          <t>الجندية</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr"/>
@@ -4132,10 +4025,9 @@
       <c r="G235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="n"/>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>رمسيس</t>
+          <t>ناصر</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr"/>
@@ -4145,10 +4037,9 @@
       <c r="G236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="n"/>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>مدينة 10 رمضان</t>
+          <t>هواره</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr"/>
@@ -4158,10 +4049,9 @@
       <c r="G237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n"/>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زايد</t>
+          <t>موشية</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr"/>
@@ -4171,10 +4061,9 @@
       <c r="G238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="n"/>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>القناطر الخيرية</t>
+          <t>نصار البحرية</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr"/>
@@ -4184,10 +4073,9 @@
       <c r="G239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="n"/>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>قها</t>
+          <t>أحمد حمزة</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr"/>
@@ -4197,10 +4085,14 @@
       <c r="G240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="n"/>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>الدقهلية</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -4210,10 +4102,9 @@
       <c r="G241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="n"/>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
+          <t>بورفؤاد</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr"/>
@@ -4223,10 +4114,9 @@
       <c r="G242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="n"/>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>أوسيم</t>
+          <t>الجميل</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr"/>
@@ -4236,10 +4126,9 @@
       <c r="G243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="n"/>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>طره</t>
+          <t>الزهور</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr"/>
@@ -4249,10 +4138,9 @@
       <c r="G244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="n"/>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>الخصوص</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr"/>
@@ -4262,10 +4150,9 @@
       <c r="G245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="6" t="n"/>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>القنطرة</t>
+          <t>الكنتاوي</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr"/>
@@ -4275,14 +4162,9 @@
       <c r="G246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>المنوفية</t>
-        </is>
-      </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>شبين الكوم</t>
+          <t>الضواحي</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr"/>
@@ -4292,10 +4174,14 @@
       <c r="G247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="n"/>
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>منوف</t>
+          <t>شرم الشيخ</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr"/>
@@ -4305,10 +4191,9 @@
       <c r="G248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="n"/>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>شبين القناطر</t>
+          <t>داهب</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr"/>
@@ -4318,10 +4203,9 @@
       <c r="G249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="n"/>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>مدينة السادات</t>
+          <t>نويبع</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr"/>
@@ -4331,10 +4215,9 @@
       <c r="G250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="n"/>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>باقور</t>
+          <t>سانت كاترين</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr"/>
@@ -4344,10 +4227,9 @@
       <c r="G251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="n"/>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>تلا</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr"/>
@@ -4357,10 +4239,9 @@
       <c r="G252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="n"/>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>قويسنا</t>
+          <t>رأس محمد</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr"/>
@@ -4370,31 +4251,21 @@
       <c r="G253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="n"/>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>أشمون</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب أشمون للتخاطب</t>
-        </is>
-      </c>
+          <t>أم سيد</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr"/>
       <c r="D254" s="4" t="inlineStr"/>
       <c r="E254" s="4" t="inlineStr"/>
       <c r="F254" s="4" t="inlineStr"/>
-      <c r="G254" s="4" t="inlineStr">
-        <is>
-          <t>أشمون</t>
-        </is>
-      </c>
+      <c r="G254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="n"/>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>البرجايه</t>
+          <t>مدينة شرم الشيخ</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr"/>
@@ -4404,31 +4275,26 @@
       <c r="G255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="5" t="n"/>
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب وصعوبات تعلم</t>
-        </is>
-      </c>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr"/>
       <c r="D256" s="4" t="inlineStr"/>
       <c r="E256" s="4" t="inlineStr"/>
       <c r="F256" s="4" t="inlineStr"/>
-      <c r="G256" s="4" t="inlineStr">
-        <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
+      <c r="G256" s="4" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="n"/>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>منوف الجديدة</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr"/>
@@ -4438,10 +4304,9 @@
       <c r="G257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="n"/>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>واحة الفيوم</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr"/>
@@ -4451,52 +4316,33 @@
       <c r="G258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>المنيا</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب بني أحمد للتخاطب</t>
-        </is>
-      </c>
+          <t>وادي حوف</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr"/>
       <c r="D259" s="4" t="inlineStr"/>
       <c r="E259" s="4" t="inlineStr"/>
       <c r="F259" s="4" t="inlineStr"/>
-      <c r="G259" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="n"/>
-      <c r="B260" s="6" t="n"/>
-      <c r="C260" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مقوسة للتخاطب</t>
-        </is>
-      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>عين سخنة</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr"/>
       <c r="D260" s="4" t="inlineStr"/>
       <c r="E260" s="4" t="inlineStr"/>
       <c r="F260" s="4" t="inlineStr"/>
-      <c r="G260" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="n"/>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>سمالوط</t>
+          <t>الطور</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr"/>
@@ -4506,10 +4352,9 @@
       <c r="G261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="n"/>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>بني حسن</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr"/>
@@ -4519,10 +4364,9 @@
       <c r="G262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="n"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>هرموبوليس</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr"/>
@@ -4532,23 +4376,34 @@
       <c r="G263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="n"/>
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>ملوي</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr"/>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>مركز حلم ابني للتخاطب</t>
+        </is>
+      </c>
       <c r="D264" s="4" t="inlineStr"/>
       <c r="E264" s="4" t="inlineStr"/>
       <c r="F264" s="4" t="inlineStr"/>
-      <c r="G264" s="4" t="inlineStr"/>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>دمياط ودمياط الجديدة</t>
+        </is>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="n"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>دمياط الجديدة</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr"/>
@@ -4558,10 +4413,9 @@
       <c r="G265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="n"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>ديروط الشريف</t>
+          <t>بورت فؤاد</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr"/>
@@ -4571,10 +4425,9 @@
       <c r="G266" s="4" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="n"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>أبوقرقاص</t>
+          <t>كفر البطة</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr"/>
@@ -4584,10 +4437,9 @@
       <c r="G267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="n"/>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>كفر سعيد</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr"/>
@@ -4597,10 +4449,9 @@
       <c r="G268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="n"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>بني مازن</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr"/>
@@ -4610,10 +4461,9 @@
       <c r="G269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="n"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>الزرقا</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr"/>
@@ -4623,95 +4473,98 @@
       <c r="G270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>الوادي الجديد</t>
-        </is>
-      </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب الخارجة للتخاطب</t>
-        </is>
-      </c>
+          <t>فارسكور</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr"/>
       <c r="D271" s="4" t="inlineStr"/>
       <c r="E271" s="4" t="inlineStr"/>
       <c r="F271" s="4" t="inlineStr"/>
-      <c r="G271" s="4" t="inlineStr">
-        <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
+      <c r="G271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="5" t="n"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب باريس للتخاطب</t>
-        </is>
-      </c>
+          <t>رومانية</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr"/>
       <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr"/>
       <c r="F272" s="4" t="inlineStr"/>
-      <c r="G272" s="4" t="inlineStr">
-        <is>
-          <t>باريس</t>
-        </is>
-      </c>
+      <c r="G272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="5" t="n"/>
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>شمال سيناء</t>
+        </is>
+      </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>موط</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr"/>
+          <t>العريش</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش للتخاطب</t>
+        </is>
+      </c>
       <c r="D273" s="4" t="inlineStr"/>
       <c r="E273" s="4" t="inlineStr"/>
       <c r="F273" s="4" t="inlineStr"/>
-      <c r="G273" s="4" t="inlineStr"/>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش</t>
+        </is>
+      </c>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="n"/>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>بلاط</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr"/>
+          <t>رفح</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب رفح</t>
+        </is>
+      </c>
       <c r="D274" s="4" t="inlineStr"/>
       <c r="E274" s="4" t="inlineStr"/>
       <c r="F274" s="4" t="inlineStr"/>
-      <c r="G274" s="4" t="inlineStr"/>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="5" t="n"/>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>فرافرة</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr"/>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
+        </is>
+      </c>
       <c r="D275" s="4" t="inlineStr"/>
       <c r="E275" s="4" t="inlineStr"/>
       <c r="F275" s="4" t="inlineStr"/>
-      <c r="G275" s="4" t="inlineStr"/>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="5" t="n"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>بئر العبد</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr"/>
@@ -4721,10 +4574,9 @@
       <c r="G276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="n"/>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>القنطرة، سيناء</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr"/>
@@ -4734,10 +4586,9 @@
       <c r="G277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="n"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>تينيدة</t>
+          <t>نخل</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr"/>
@@ -4747,10 +4598,9 @@
       <c r="G278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="n"/>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>دوش</t>
+          <t>جديدة، حسنة</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr"/>
@@ -4760,35 +4610,21 @@
       <c r="G279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العبور للتخاطب</t>
-        </is>
-      </c>
+          <t>دهب الشرقية</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr"/>
       <c r="D280" s="4" t="inlineStr"/>
       <c r="E280" s="4" t="inlineStr"/>
       <c r="F280" s="4" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="G280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="n"/>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr"/>
@@ -4798,36 +4634,49 @@
       <c r="G281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="5" t="n"/>
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>ساماستا</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr"/>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمدينة العمال</t>
+        </is>
+      </c>
       <c r="D282" s="4" t="inlineStr"/>
       <c r="E282" s="4" t="inlineStr"/>
       <c r="F282" s="4" t="inlineStr"/>
-      <c r="G282" s="4" t="inlineStr"/>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>مدينة العمال، قنا</t>
+        </is>
+      </c>
     </row>
     <row r="283">
-      <c r="A283" s="5" t="n"/>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>إبشواي</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr"/>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب حجير خزام</t>
+        </is>
+      </c>
       <c r="D283" s="4" t="inlineStr"/>
       <c r="E283" s="4" t="inlineStr"/>
       <c r="F283" s="4" t="inlineStr"/>
-      <c r="G283" s="4" t="inlineStr"/>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="5" t="n"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>الجندية</t>
+          <t>نجع حمادي</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr"/>
@@ -4837,10 +4686,9 @@
       <c r="G284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="n"/>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>ناصر</t>
+          <t>دندرة</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr"/>
@@ -4850,10 +4698,9 @@
       <c r="G285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="n"/>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>هواره</t>
+          <t>أبيدوس</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr"/>
@@ -4863,10 +4710,9 @@
       <c r="G286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="n"/>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>موشية</t>
+          <t>قفطي</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr"/>
@@ -4876,10 +4722,9 @@
       <c r="G287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="n"/>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>نصار البحرية</t>
+          <t>أخميم</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr"/>
@@ -4889,10 +4734,9 @@
       <c r="G288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="n"/>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>أحمد حمزة</t>
+          <t>سوهاج القديمة</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr"/>
@@ -4902,14 +4746,9 @@
       <c r="G289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>بورسعيد</t>
-        </is>
-      </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>النجع البحري</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr"/>
@@ -4919,10 +4758,9 @@
       <c r="G290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="n"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>بورفؤاد</t>
+          <t>الشنقي</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr"/>
@@ -4932,36 +4770,54 @@
       <c r="G291" s="4" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="n"/>
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>الجميل</t>
-        </is>
-      </c>
-      <c r="C292" s="4" t="inlineStr"/>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الشيخ للتخاطب</t>
+        </is>
+      </c>
       <c r="D292" s="4" t="inlineStr"/>
       <c r="E292" s="4" t="inlineStr"/>
       <c r="F292" s="4" t="inlineStr"/>
-      <c r="G292" s="4" t="inlineStr"/>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="n"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>الزهور</t>
-        </is>
-      </c>
-      <c r="C293" s="4" t="inlineStr"/>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
+        </is>
+      </c>
       <c r="D293" s="4" t="inlineStr"/>
       <c r="E293" s="4" t="inlineStr"/>
       <c r="F293" s="4" t="inlineStr"/>
-      <c r="G293" s="4" t="inlineStr"/>
+      <c r="G293" s="4" t="inlineStr">
+        <is>
+          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
+        </is>
+      </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>بلامون</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr"/>
@@ -4971,10 +4827,9 @@
       <c r="G294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="n"/>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>الكنتاوي</t>
+          <t>الرياض</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr"/>
@@ -4984,10 +4839,9 @@
       <c r="G295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="n"/>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>الضواحي</t>
+          <t>سيدي سالم</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr"/>
@@ -4997,14 +4851,9 @@
       <c r="G296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>جنوب سيناء</t>
-        </is>
-      </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>شرم الشيخ</t>
+          <t>الحامول</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr"/>
@@ -5014,10 +4863,9 @@
       <c r="G297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="n"/>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>داهب</t>
+          <t>برج البرلس</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr"/>
@@ -5027,10 +4875,9 @@
       <c r="G298" s="4" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="5" t="n"/>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>نويبع</t>
+          <t>مطوبس</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr"/>
@@ -5040,10 +4887,9 @@
       <c r="G299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="5" t="n"/>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>سانت كاترين</t>
+          <t>المحمودية</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr"/>
@@ -5053,10 +4899,9 @@
       <c r="G300" s="4" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="5" t="n"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>بيلا</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr"/>
@@ -5066,10 +4911,14 @@
       <c r="G301" s="4" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="5" t="n"/>
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>رأس محمد</t>
+          <t>مطروح</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr"/>
@@ -5079,10 +4928,14 @@
       <c r="G302" s="4" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="n"/>
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>أم سيد</t>
+          <t>سيوه</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr"/>
@@ -5092,10 +4945,14 @@
       <c r="G303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="6" t="n"/>
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>مدينة شرم الشيخ</t>
+          <t>السلوم</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr"/>
@@ -5107,12 +4964,12 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>مطروح</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>سيدي براني</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr"/>
@@ -5122,10 +4979,14 @@
       <c r="G305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="5" t="n"/>
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>العلمين</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr"/>
@@ -5135,10 +4996,14 @@
       <c r="G306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="5" t="n"/>
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>واحة الفيوم</t>
+          <t>مارينا</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr"/>
@@ -5148,10 +5013,14 @@
       <c r="G307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="5" t="n"/>
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>وادي حوف</t>
+          <t>توريدو</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr"/>
@@ -5161,10 +5030,14 @@
       <c r="G308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="5" t="n"/>
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>عين سخنة</t>
+          <t>جنوب سيوه</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr"/>
@@ -5174,10 +5047,14 @@
       <c r="G309" s="4" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="5" t="n"/>
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>شمال سيوه</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr"/>
@@ -5187,10 +5064,14 @@
       <c r="G310" s="4" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="5" t="n"/>
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>كشته</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr"/>
@@ -5199,1074 +5080,16 @@
       <c r="F311" s="4" t="inlineStr"/>
       <c r="G311" s="4" t="inlineStr"/>
     </row>
-    <row r="312">
-      <c r="A312" s="6" t="n"/>
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>المقطم</t>
-        </is>
-      </c>
-      <c r="C312" s="4" t="inlineStr"/>
-      <c r="D312" s="4" t="inlineStr"/>
-      <c r="E312" s="4" t="inlineStr"/>
-      <c r="F312" s="4" t="inlineStr"/>
-      <c r="G312" s="4" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr">
-        <is>
-          <t>مركز حلم ابني للتخاطب</t>
-        </is>
-      </c>
-      <c r="D313" s="4" t="inlineStr"/>
-      <c r="E313" s="4" t="inlineStr"/>
-      <c r="F313" s="4" t="inlineStr"/>
-      <c r="G313" s="4" t="inlineStr">
-        <is>
-          <t>دمياط ودمياط الجديدة</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="5" t="n"/>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>دمياط الجديدة</t>
-        </is>
-      </c>
-      <c r="C314" s="4" t="inlineStr"/>
-      <c r="D314" s="4" t="inlineStr"/>
-      <c r="E314" s="4" t="inlineStr"/>
-      <c r="F314" s="4" t="inlineStr"/>
-      <c r="G314" s="4" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="5" t="n"/>
-      <c r="B315" s="3" t="inlineStr">
-        <is>
-          <t>بورت فؤاد</t>
-        </is>
-      </c>
-      <c r="C315" s="4" t="inlineStr"/>
-      <c r="D315" s="4" t="inlineStr"/>
-      <c r="E315" s="4" t="inlineStr"/>
-      <c r="F315" s="4" t="inlineStr"/>
-      <c r="G315" s="4" t="inlineStr"/>
-    </row>
-    <row r="316">
-      <c r="A316" s="5" t="n"/>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>كفر البطة</t>
-        </is>
-      </c>
-      <c r="C316" s="4" t="inlineStr"/>
-      <c r="D316" s="4" t="inlineStr"/>
-      <c r="E316" s="4" t="inlineStr"/>
-      <c r="F316" s="4" t="inlineStr"/>
-      <c r="G316" s="4" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" s="5" t="n"/>
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>كفر سعيد</t>
-        </is>
-      </c>
-      <c r="C317" s="4" t="inlineStr"/>
-      <c r="D317" s="4" t="inlineStr"/>
-      <c r="E317" s="4" t="inlineStr"/>
-      <c r="F317" s="4" t="inlineStr"/>
-      <c r="G317" s="4" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="5" t="n"/>
-      <c r="B318" s="3" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="C318" s="4" t="inlineStr"/>
-      <c r="D318" s="4" t="inlineStr"/>
-      <c r="E318" s="4" t="inlineStr"/>
-      <c r="F318" s="4" t="inlineStr"/>
-      <c r="G318" s="4" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="5" t="n"/>
-      <c r="B319" s="3" t="inlineStr">
-        <is>
-          <t>الزرقا</t>
-        </is>
-      </c>
-      <c r="C319" s="4" t="inlineStr"/>
-      <c r="D319" s="4" t="inlineStr"/>
-      <c r="E319" s="4" t="inlineStr"/>
-      <c r="F319" s="4" t="inlineStr"/>
-      <c r="G319" s="4" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="5" t="n"/>
-      <c r="B320" s="3" t="inlineStr">
-        <is>
-          <t>فارسكور</t>
-        </is>
-      </c>
-      <c r="C320" s="4" t="inlineStr"/>
-      <c r="D320" s="4" t="inlineStr"/>
-      <c r="E320" s="4" t="inlineStr"/>
-      <c r="F320" s="4" t="inlineStr"/>
-      <c r="G320" s="4" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="6" t="n"/>
-      <c r="B321" s="3" t="inlineStr">
-        <is>
-          <t>رومانية</t>
-        </is>
-      </c>
-      <c r="C321" s="4" t="inlineStr"/>
-      <c r="D321" s="4" t="inlineStr"/>
-      <c r="E321" s="4" t="inlineStr"/>
-      <c r="F321" s="4" t="inlineStr"/>
-      <c r="G321" s="4" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>شمال سيناء</t>
-        </is>
-      </c>
-      <c r="B322" s="3" t="inlineStr">
-        <is>
-          <t>العريش</t>
-        </is>
-      </c>
-      <c r="C322" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش للتخاطب</t>
-        </is>
-      </c>
-      <c r="D322" s="4" t="inlineStr"/>
-      <c r="E322" s="4" t="inlineStr"/>
-      <c r="F322" s="4" t="inlineStr"/>
-      <c r="G322" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="5" t="n"/>
-      <c r="B323" s="3" t="inlineStr">
-        <is>
-          <t>رفح</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب رفح</t>
-        </is>
-      </c>
-      <c r="D323" s="4" t="inlineStr"/>
-      <c r="E323" s="4" t="inlineStr"/>
-      <c r="F323" s="4" t="inlineStr"/>
-      <c r="G323" s="4" t="inlineStr">
-        <is>
-          <t>رفح</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="5" t="n"/>
-      <c r="B324" s="3" t="inlineStr">
-        <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
-      <c r="C324" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
-        </is>
-      </c>
-      <c r="D324" s="4" t="inlineStr"/>
-      <c r="E324" s="4" t="inlineStr"/>
-      <c r="F324" s="4" t="inlineStr"/>
-      <c r="G324" s="4" t="inlineStr">
-        <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="5" t="n"/>
-      <c r="B325" s="3" t="inlineStr">
-        <is>
-          <t>بئر العبد</t>
-        </is>
-      </c>
-      <c r="C325" s="4" t="inlineStr"/>
-      <c r="D325" s="4" t="inlineStr"/>
-      <c r="E325" s="4" t="inlineStr"/>
-      <c r="F325" s="4" t="inlineStr"/>
-      <c r="G325" s="4" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="5" t="n"/>
-      <c r="B326" s="3" t="inlineStr">
-        <is>
-          <t>القنطرة، سيناء</t>
-        </is>
-      </c>
-      <c r="C326" s="4" t="inlineStr"/>
-      <c r="D326" s="4" t="inlineStr"/>
-      <c r="E326" s="4" t="inlineStr"/>
-      <c r="F326" s="4" t="inlineStr"/>
-      <c r="G326" s="4" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="5" t="n"/>
-      <c r="B327" s="3" t="inlineStr">
-        <is>
-          <t>نخل</t>
-        </is>
-      </c>
-      <c r="C327" s="4" t="inlineStr"/>
-      <c r="D327" s="4" t="inlineStr"/>
-      <c r="E327" s="4" t="inlineStr"/>
-      <c r="F327" s="4" t="inlineStr"/>
-      <c r="G327" s="4" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="5" t="n"/>
-      <c r="B328" s="3" t="inlineStr">
-        <is>
-          <t>جديدة، حسنة</t>
-        </is>
-      </c>
-      <c r="C328" s="4" t="inlineStr"/>
-      <c r="D328" s="4" t="inlineStr"/>
-      <c r="E328" s="4" t="inlineStr"/>
-      <c r="F328" s="4" t="inlineStr"/>
-      <c r="G328" s="4" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" s="5" t="n"/>
-      <c r="B329" s="3" t="inlineStr">
-        <is>
-          <t>دهب الشرقية</t>
-        </is>
-      </c>
-      <c r="C329" s="4" t="inlineStr"/>
-      <c r="D329" s="4" t="inlineStr"/>
-      <c r="E329" s="4" t="inlineStr"/>
-      <c r="F329" s="4" t="inlineStr"/>
-      <c r="G329" s="4" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" s="6" t="n"/>
-      <c r="B330" s="3" t="inlineStr">
-        <is>
-          <t>طابا</t>
-        </is>
-      </c>
-      <c r="C330" s="4" t="inlineStr"/>
-      <c r="D330" s="4" t="inlineStr"/>
-      <c r="E330" s="4" t="inlineStr"/>
-      <c r="F330" s="4" t="inlineStr"/>
-      <c r="G330" s="4" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
-      <c r="B331" s="3" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
-      <c r="C331" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بمدينة العمال</t>
-        </is>
-      </c>
-      <c r="D331" s="4" t="inlineStr"/>
-      <c r="E331" s="4" t="inlineStr"/>
-      <c r="F331" s="4" t="inlineStr"/>
-      <c r="G331" s="4" t="inlineStr">
-        <is>
-          <t>مدينة العمال، قنا</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="5" t="n"/>
-      <c r="B332" s="6" t="n"/>
-      <c r="C332" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب حجير خزام</t>
-        </is>
-      </c>
-      <c r="D332" s="4" t="inlineStr"/>
-      <c r="E332" s="4" t="inlineStr"/>
-      <c r="F332" s="4" t="inlineStr"/>
-      <c r="G332" s="4" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="5" t="n"/>
-      <c r="B333" s="3" t="inlineStr">
-        <is>
-          <t>نجع حمادي</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="inlineStr"/>
-      <c r="D333" s="4" t="inlineStr"/>
-      <c r="E333" s="4" t="inlineStr"/>
-      <c r="F333" s="4" t="inlineStr"/>
-      <c r="G333" s="4" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="5" t="n"/>
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>دندرة</t>
-        </is>
-      </c>
-      <c r="C334" s="4" t="inlineStr"/>
-      <c r="D334" s="4" t="inlineStr"/>
-      <c r="E334" s="4" t="inlineStr"/>
-      <c r="F334" s="4" t="inlineStr"/>
-      <c r="G334" s="4" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" s="5" t="n"/>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>أبيدوس</t>
-        </is>
-      </c>
-      <c r="C335" s="4" t="inlineStr"/>
-      <c r="D335" s="4" t="inlineStr"/>
-      <c r="E335" s="4" t="inlineStr"/>
-      <c r="F335" s="4" t="inlineStr"/>
-      <c r="G335" s="4" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="5" t="n"/>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>قفطي</t>
-        </is>
-      </c>
-      <c r="C336" s="4" t="inlineStr"/>
-      <c r="D336" s="4" t="inlineStr"/>
-      <c r="E336" s="4" t="inlineStr"/>
-      <c r="F336" s="4" t="inlineStr"/>
-      <c r="G336" s="4" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="5" t="n"/>
-      <c r="B337" s="3" t="inlineStr">
-        <is>
-          <t>أخميم</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr"/>
-      <c r="D337" s="4" t="inlineStr"/>
-      <c r="E337" s="4" t="inlineStr"/>
-      <c r="F337" s="4" t="inlineStr"/>
-      <c r="G337" s="4" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="5" t="n"/>
-      <c r="B338" s="3" t="inlineStr">
-        <is>
-          <t>سوهاج القديمة</t>
-        </is>
-      </c>
-      <c r="C338" s="4" t="inlineStr"/>
-      <c r="D338" s="4" t="inlineStr"/>
-      <c r="E338" s="4" t="inlineStr"/>
-      <c r="F338" s="4" t="inlineStr"/>
-      <c r="G338" s="4" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" s="5" t="n"/>
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>النجع البحري</t>
-        </is>
-      </c>
-      <c r="C339" s="4" t="inlineStr"/>
-      <c r="D339" s="4" t="inlineStr"/>
-      <c r="E339" s="4" t="inlineStr"/>
-      <c r="F339" s="4" t="inlineStr"/>
-      <c r="G339" s="4" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="6" t="n"/>
-      <c r="B340" s="3" t="inlineStr">
-        <is>
-          <t>الشنقي</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="inlineStr"/>
-      <c r="D340" s="4" t="inlineStr"/>
-      <c r="E340" s="4" t="inlineStr"/>
-      <c r="F340" s="4" t="inlineStr"/>
-      <c r="G340" s="4" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="B341" s="3" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الشيخ للتخاطب</t>
-        </is>
-      </c>
-      <c r="D341" s="4" t="inlineStr"/>
-      <c r="E341" s="4" t="inlineStr"/>
-      <c r="F341" s="4" t="inlineStr"/>
-      <c r="G341" s="4" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="5" t="n"/>
-      <c r="B342" s="3" t="inlineStr">
-        <is>
-          <t>دسوق</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
-        </is>
-      </c>
-      <c r="D342" s="4" t="inlineStr"/>
-      <c r="E342" s="4" t="inlineStr"/>
-      <c r="F342" s="4" t="inlineStr"/>
-      <c r="G342" s="4" t="inlineStr">
-        <is>
-          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="5" t="n"/>
-      <c r="B343" s="3" t="inlineStr">
-        <is>
-          <t>بلامون</t>
-        </is>
-      </c>
-      <c r="C343" s="4" t="inlineStr"/>
-      <c r="D343" s="4" t="inlineStr"/>
-      <c r="E343" s="4" t="inlineStr"/>
-      <c r="F343" s="4" t="inlineStr"/>
-      <c r="G343" s="4" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="5" t="n"/>
-      <c r="B344" s="3" t="inlineStr">
-        <is>
-          <t>الرياض</t>
-        </is>
-      </c>
-      <c r="C344" s="4" t="inlineStr"/>
-      <c r="D344" s="4" t="inlineStr"/>
-      <c r="E344" s="4" t="inlineStr"/>
-      <c r="F344" s="4" t="inlineStr"/>
-      <c r="G344" s="4" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="5" t="n"/>
-      <c r="B345" s="3" t="inlineStr">
-        <is>
-          <t>سيدي سالم</t>
-        </is>
-      </c>
-      <c r="C345" s="4" t="inlineStr"/>
-      <c r="D345" s="4" t="inlineStr"/>
-      <c r="E345" s="4" t="inlineStr"/>
-      <c r="F345" s="4" t="inlineStr"/>
-      <c r="G345" s="4" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="5" t="n"/>
-      <c r="B346" s="3" t="inlineStr">
-        <is>
-          <t>الحامول</t>
-        </is>
-      </c>
-      <c r="C346" s="4" t="inlineStr"/>
-      <c r="D346" s="4" t="inlineStr"/>
-      <c r="E346" s="4" t="inlineStr"/>
-      <c r="F346" s="4" t="inlineStr"/>
-      <c r="G346" s="4" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="5" t="n"/>
-      <c r="B347" s="3" t="inlineStr">
-        <is>
-          <t>برج البرلس</t>
-        </is>
-      </c>
-      <c r="C347" s="4" t="inlineStr"/>
-      <c r="D347" s="4" t="inlineStr"/>
-      <c r="E347" s="4" t="inlineStr"/>
-      <c r="F347" s="4" t="inlineStr"/>
-      <c r="G347" s="4" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" s="5" t="n"/>
-      <c r="B348" s="3" t="inlineStr">
-        <is>
-          <t>مطوبس</t>
-        </is>
-      </c>
-      <c r="C348" s="4" t="inlineStr"/>
-      <c r="D348" s="4" t="inlineStr"/>
-      <c r="E348" s="4" t="inlineStr"/>
-      <c r="F348" s="4" t="inlineStr"/>
-      <c r="G348" s="4" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="5" t="n"/>
-      <c r="B349" s="3" t="inlineStr">
-        <is>
-          <t>المحمودية</t>
-        </is>
-      </c>
-      <c r="C349" s="4" t="inlineStr"/>
-      <c r="D349" s="4" t="inlineStr"/>
-      <c r="E349" s="4" t="inlineStr"/>
-      <c r="F349" s="4" t="inlineStr"/>
-      <c r="G349" s="4" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="6" t="n"/>
-      <c r="B350" s="3" t="inlineStr">
-        <is>
-          <t>بيلا</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr"/>
-      <c r="D350" s="4" t="inlineStr"/>
-      <c r="E350" s="4" t="inlineStr"/>
-      <c r="F350" s="4" t="inlineStr"/>
-      <c r="G350" s="4" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B351" s="3" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="C351" s="4" t="inlineStr"/>
-      <c r="D351" s="4" t="inlineStr"/>
-      <c r="E351" s="4" t="inlineStr"/>
-      <c r="F351" s="4" t="inlineStr"/>
-      <c r="G351" s="4" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>سيوه</t>
-        </is>
-      </c>
-      <c r="C352" s="4" t="inlineStr"/>
-      <c r="D352" s="4" t="inlineStr"/>
-      <c r="E352" s="4" t="inlineStr"/>
-      <c r="F352" s="4" t="inlineStr"/>
-      <c r="G352" s="4" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B353" s="3" t="inlineStr">
-        <is>
-          <t>السلوم</t>
-        </is>
-      </c>
-      <c r="C353" s="4" t="inlineStr"/>
-      <c r="D353" s="4" t="inlineStr"/>
-      <c r="E353" s="4" t="inlineStr"/>
-      <c r="F353" s="4" t="inlineStr"/>
-      <c r="G353" s="4" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B354" s="3" t="inlineStr">
-        <is>
-          <t>سيدي براني</t>
-        </is>
-      </c>
-      <c r="C354" s="4" t="inlineStr"/>
-      <c r="D354" s="4" t="inlineStr"/>
-      <c r="E354" s="4" t="inlineStr"/>
-      <c r="F354" s="4" t="inlineStr"/>
-      <c r="G354" s="4" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B355" s="3" t="inlineStr">
-        <is>
-          <t>العلمين</t>
-        </is>
-      </c>
-      <c r="C355" s="4" t="inlineStr"/>
-      <c r="D355" s="4" t="inlineStr"/>
-      <c r="E355" s="4" t="inlineStr"/>
-      <c r="F355" s="4" t="inlineStr"/>
-      <c r="G355" s="4" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B356" s="3" t="inlineStr">
-        <is>
-          <t>مارينا</t>
-        </is>
-      </c>
-      <c r="C356" s="4" t="inlineStr"/>
-      <c r="D356" s="4" t="inlineStr"/>
-      <c r="E356" s="4" t="inlineStr"/>
-      <c r="F356" s="4" t="inlineStr"/>
-      <c r="G356" s="4" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B357" s="3" t="inlineStr">
-        <is>
-          <t>توريدو</t>
-        </is>
-      </c>
-      <c r="C357" s="4" t="inlineStr"/>
-      <c r="D357" s="4" t="inlineStr"/>
-      <c r="E357" s="4" t="inlineStr"/>
-      <c r="F357" s="4" t="inlineStr"/>
-      <c r="G357" s="4" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B358" s="3" t="inlineStr">
-        <is>
-          <t>جنوب سيوه</t>
-        </is>
-      </c>
-      <c r="C358" s="4" t="inlineStr"/>
-      <c r="D358" s="4" t="inlineStr"/>
-      <c r="E358" s="4" t="inlineStr"/>
-      <c r="F358" s="4" t="inlineStr"/>
-      <c r="G358" s="4" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B359" s="3" t="inlineStr">
-        <is>
-          <t>شمال سيوه</t>
-        </is>
-      </c>
-      <c r="C359" s="4" t="inlineStr"/>
-      <c r="D359" s="4" t="inlineStr"/>
-      <c r="E359" s="4" t="inlineStr"/>
-      <c r="F359" s="4" t="inlineStr"/>
-      <c r="G359" s="4" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B360" s="3" t="inlineStr">
-        <is>
-          <t>كشته</t>
-        </is>
-      </c>
-      <c r="C360" s="4" t="inlineStr"/>
-      <c r="D360" s="4" t="inlineStr"/>
-      <c r="E360" s="4" t="inlineStr"/>
-      <c r="F360" s="4" t="inlineStr"/>
-      <c r="G360" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="313">
-    <mergeCell ref="B6"/>
-    <mergeCell ref="B133"/>
-    <mergeCell ref="B204"/>
-    <mergeCell ref="B356"/>
-    <mergeCell ref="B4"/>
-    <mergeCell ref="B75"/>
-    <mergeCell ref="B135"/>
-    <mergeCell ref="B306"/>
-    <mergeCell ref="B62"/>
-    <mergeCell ref="B72"/>
-    <mergeCell ref="A290:A296"/>
-    <mergeCell ref="B291"/>
-    <mergeCell ref="B70"/>
-    <mergeCell ref="B293"/>
-    <mergeCell ref="A12:A23"/>
-    <mergeCell ref="B322"/>
-    <mergeCell ref="B17"/>
-    <mergeCell ref="B88"/>
-    <mergeCell ref="B82"/>
-    <mergeCell ref="B152:B156"/>
-    <mergeCell ref="B185:B188"/>
-    <mergeCell ref="B19"/>
-    <mergeCell ref="B146"/>
-    <mergeCell ref="B317"/>
-    <mergeCell ref="B217"/>
-    <mergeCell ref="A259:A270"/>
-    <mergeCell ref="B83"/>
-    <mergeCell ref="B344"/>
-    <mergeCell ref="B319"/>
-    <mergeCell ref="A178:A227"/>
-    <mergeCell ref="B123"/>
-    <mergeCell ref="B221"/>
-    <mergeCell ref="B110"/>
-    <mergeCell ref="B141"/>
-    <mergeCell ref="B248"/>
-    <mergeCell ref="B297"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="B235"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="B331:B332"/>
-    <mergeCell ref="B299"/>
-    <mergeCell ref="B78"/>
-    <mergeCell ref="B249"/>
-    <mergeCell ref="B243"/>
-    <mergeCell ref="A331:A340"/>
-    <mergeCell ref="B314"/>
-    <mergeCell ref="A247:A258"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B325"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B25"/>
-    <mergeCell ref="B327"/>
-    <mergeCell ref="B149"/>
-    <mergeCell ref="B220"/>
-    <mergeCell ref="B247"/>
-    <mergeCell ref="B262"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="A271:A279"/>
-    <mergeCell ref="B84"/>
-    <mergeCell ref="B338"/>
-    <mergeCell ref="B15"/>
-    <mergeCell ref="B313"/>
-    <mergeCell ref="B104"/>
-    <mergeCell ref="B79"/>
-    <mergeCell ref="B315"/>
-    <mergeCell ref="B302"/>
-    <mergeCell ref="B81"/>
-    <mergeCell ref="B252"/>
-    <mergeCell ref="B210"/>
-    <mergeCell ref="B318"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="B170"/>
-    <mergeCell ref="B157"/>
-    <mergeCell ref="B328"/>
-    <mergeCell ref="B333"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B172"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B99"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B257"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="A115:A128"/>
-    <mergeCell ref="B265"/>
-    <mergeCell ref="B54"/>
-    <mergeCell ref="B125"/>
-    <mergeCell ref="B323"/>
-    <mergeCell ref="B176"/>
-    <mergeCell ref="B120"/>
-    <mergeCell ref="B147"/>
-    <mergeCell ref="B245"/>
-    <mergeCell ref="B9"/>
-    <mergeCell ref="B359"/>
-    <mergeCell ref="B207"/>
-    <mergeCell ref="B334"/>
-    <mergeCell ref="B113"/>
-    <mergeCell ref="B173"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="B100"/>
-    <mergeCell ref="B271"/>
-    <mergeCell ref="B336"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B202"/>
-    <mergeCell ref="B102"/>
-    <mergeCell ref="B273"/>
-    <mergeCell ref="B232:B234"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B191"/>
-    <mergeCell ref="B349"/>
-    <mergeCell ref="B255"/>
-    <mergeCell ref="B226"/>
-    <mergeCell ref="B49"/>
-    <mergeCell ref="B192"/>
-    <mergeCell ref="A280:A289"/>
-    <mergeCell ref="B284"/>
-    <mergeCell ref="B222"/>
-    <mergeCell ref="A313:A321"/>
-    <mergeCell ref="B63"/>
-    <mergeCell ref="B197"/>
-    <mergeCell ref="B50"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="B286"/>
-    <mergeCell ref="B261"/>
-    <mergeCell ref="B27"/>
-    <mergeCell ref="B337"/>
-    <mergeCell ref="B352"/>
-    <mergeCell ref="B103"/>
-    <mergeCell ref="B174"/>
-    <mergeCell ref="B205"/>
-    <mergeCell ref="B339"/>
-    <mergeCell ref="B118"/>
-    <mergeCell ref="A66:A76"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="B169"/>
-    <mergeCell ref="B355"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="B129"/>
-    <mergeCell ref="B134"/>
-    <mergeCell ref="B194"/>
-    <mergeCell ref="B121"/>
-    <mergeCell ref="B292"/>
-    <mergeCell ref="B357"/>
-    <mergeCell ref="B71"/>
-    <mergeCell ref="B131"/>
-    <mergeCell ref="B236"/>
-    <mergeCell ref="B307"/>
-    <mergeCell ref="B58"/>
-    <mergeCell ref="B52"/>
-    <mergeCell ref="B223"/>
-    <mergeCell ref="B294"/>
-    <mergeCell ref="B2"/>
-    <mergeCell ref="B195"/>
-    <mergeCell ref="B60"/>
-    <mergeCell ref="B231"/>
-    <mergeCell ref="B287"/>
-    <mergeCell ref="B358"/>
-    <mergeCell ref="A24:A32"/>
-    <mergeCell ref="B53"/>
-    <mergeCell ref="A341:A350"/>
-    <mergeCell ref="A152:A166"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B241"/>
-    <mergeCell ref="B124"/>
-    <mergeCell ref="B178:B184"/>
-    <mergeCell ref="B142"/>
-    <mergeCell ref="B80"/>
-    <mergeCell ref="B213"/>
-    <mergeCell ref="B305"/>
-    <mergeCell ref="B126"/>
-    <mergeCell ref="B218"/>
-    <mergeCell ref="B242"/>
-    <mergeCell ref="B46"/>
-    <mergeCell ref="B282"/>
-    <mergeCell ref="B48"/>
-    <mergeCell ref="B219"/>
-    <mergeCell ref="B346"/>
-    <mergeCell ref="A297:A304"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="B73"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="B308"/>
-    <mergeCell ref="B74"/>
-    <mergeCell ref="B68"/>
-    <mergeCell ref="B201"/>
-    <mergeCell ref="B239"/>
-    <mergeCell ref="B310"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="B203"/>
-    <mergeCell ref="B150"/>
-    <mergeCell ref="B326"/>
-    <mergeCell ref="B215"/>
-    <mergeCell ref="B21"/>
-    <mergeCell ref="B263"/>
-    <mergeCell ref="B244"/>
-    <mergeCell ref="A167:A177"/>
-    <mergeCell ref="B283"/>
-    <mergeCell ref="B87"/>
-    <mergeCell ref="B298"/>
-    <mergeCell ref="B285"/>
-    <mergeCell ref="B64"/>
-    <mergeCell ref="B51"/>
-    <mergeCell ref="B163"/>
-    <mergeCell ref="B309"/>
-    <mergeCell ref="B165"/>
-    <mergeCell ref="B140"/>
-    <mergeCell ref="B311"/>
-    <mergeCell ref="B238"/>
-    <mergeCell ref="B105:B107"/>
-    <mergeCell ref="B77"/>
-    <mergeCell ref="B253"/>
-    <mergeCell ref="B240"/>
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B158"/>
-    <mergeCell ref="B329"/>
-    <mergeCell ref="B316"/>
-    <mergeCell ref="B24"/>
-    <mergeCell ref="B266"/>
-    <mergeCell ref="B89"/>
-    <mergeCell ref="B198:B200"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="B26"/>
-    <mergeCell ref="B97"/>
-    <mergeCell ref="B268"/>
-    <mergeCell ref="B324"/>
-    <mergeCell ref="B224"/>
-    <mergeCell ref="B90"/>
-    <mergeCell ref="B148"/>
-    <mergeCell ref="B250"/>
-    <mergeCell ref="B44"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="B254"/>
-    <mergeCell ref="B143"/>
-    <mergeCell ref="B281"/>
-    <mergeCell ref="B20"/>
-    <mergeCell ref="B85"/>
-    <mergeCell ref="B256"/>
-    <mergeCell ref="A137:A151"/>
-    <mergeCell ref="B160:B162"/>
-    <mergeCell ref="B159"/>
-    <mergeCell ref="B272"/>
-    <mergeCell ref="B111"/>
-    <mergeCell ref="B98"/>
-    <mergeCell ref="B225"/>
-    <mergeCell ref="B274"/>
-    <mergeCell ref="B175"/>
-    <mergeCell ref="B228:B230"/>
-    <mergeCell ref="A129:A136"/>
-    <mergeCell ref="B267"/>
-    <mergeCell ref="B269"/>
-    <mergeCell ref="B251"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="B216"/>
-    <mergeCell ref="B343"/>
-    <mergeCell ref="A92:A114"/>
-    <mergeCell ref="B280"/>
-    <mergeCell ref="B47"/>
-    <mergeCell ref="B351"/>
-    <mergeCell ref="B345"/>
-    <mergeCell ref="B59"/>
-    <mergeCell ref="B22"/>
-    <mergeCell ref="B193"/>
-    <mergeCell ref="B264"/>
-    <mergeCell ref="B320"/>
-    <mergeCell ref="B295"/>
-    <mergeCell ref="B86"/>
-    <mergeCell ref="B101"/>
-    <mergeCell ref="A77:A91"/>
-    <mergeCell ref="B211"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="B300"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B275"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="B164"/>
-    <mergeCell ref="B335"/>
-    <mergeCell ref="B212"/>
-    <mergeCell ref="A322:A330"/>
-    <mergeCell ref="B206"/>
-    <mergeCell ref="B277"/>
-    <mergeCell ref="B130"/>
-    <mergeCell ref="A33:A56"/>
-    <mergeCell ref="B117"/>
-    <mergeCell ref="B353"/>
-    <mergeCell ref="B61"/>
-    <mergeCell ref="B132"/>
-    <mergeCell ref="B119"/>
-    <mergeCell ref="B290"/>
-    <mergeCell ref="B69"/>
-    <mergeCell ref="B196"/>
-    <mergeCell ref="B112"/>
-    <mergeCell ref="B354"/>
-    <mergeCell ref="B288"/>
-    <mergeCell ref="B348"/>
-    <mergeCell ref="B127"/>
-    <mergeCell ref="B237"/>
-    <mergeCell ref="B16"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="A228:A246"/>
-    <mergeCell ref="B301"/>
-    <mergeCell ref="B122"/>
-    <mergeCell ref="B276"/>
-    <mergeCell ref="B43"/>
-    <mergeCell ref="B18"/>
-    <mergeCell ref="B214"/>
-    <mergeCell ref="A305:A312"/>
-    <mergeCell ref="B341"/>
-    <mergeCell ref="B347"/>
-    <mergeCell ref="B303"/>
-    <mergeCell ref="B278"/>
-    <mergeCell ref="B57"/>
-    <mergeCell ref="B171"/>
-    <mergeCell ref="B342"/>
+  <mergeCells count="8">
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A189:A191"/>
+    <mergeCell ref="A198:A200"/>
+    <mergeCell ref="A187:A188"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Egyptian_Speech_Therapy_Centers.xlsx
+++ b/Egyptian_Speech_Therapy_Centers.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,15 +44,6 @@
     <font>
       <name val="Arial"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -120,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,15 +127,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G311"/>
+  <dimension ref="A1:G360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -585,6 +567,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" s="5" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>أبو سمبل</t>
@@ -597,6 +580,7 @@
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
+      <c r="A4" s="5" t="n"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>كوم أمبو</t>
@@ -609,6 +593,7 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
+      <c r="A5" s="5" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>إدفو</t>
@@ -621,6 +606,7 @@
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" s="5" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>داراو</t>
@@ -633,6 +619,7 @@
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" s="5" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>نصر الساحل</t>
@@ -645,6 +632,7 @@
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" s="5" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>الشيخ علي</t>
@@ -657,6 +645,7 @@
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
+      <c r="A9" s="5" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>توشكا</t>
@@ -669,6 +658,7 @@
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" s="5" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>الحمراء</t>
@@ -681,6 +671,7 @@
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" s="6" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>النوبة</t>
@@ -718,6 +709,8 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>مركز شباب موشا للتخاطب</t>
@@ -733,6 +726,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="5" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>منفلوط</t>
@@ -745,6 +739,7 @@
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
+      <c r="A15" s="5" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>ديروط</t>
@@ -757,6 +752,7 @@
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="5" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>الوقف</t>
@@ -769,6 +765,7 @@
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
+      <c r="A17" s="5" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>أبيدوس</t>
@@ -781,6 +778,7 @@
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
+      <c r="A18" s="5" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>سوهاج</t>
@@ -793,6 +791,7 @@
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
+      <c r="A19" s="5" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>البدارى</t>
@@ -805,6 +804,7 @@
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
+      <c r="A20" s="5" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>فلنج</t>
@@ -817,6 +817,7 @@
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
+      <c r="A21" s="5" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>أراب العوامر</t>
@@ -829,6 +830,7 @@
       <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
+      <c r="A22" s="5" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>الغنايم</t>
@@ -841,6 +843,7 @@
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
+      <c r="A23" s="6" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>الفيوم الجديدة</t>
@@ -878,6 +881,7 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" s="5" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>الكرنك</t>
@@ -890,6 +894,7 @@
       <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
+      <c r="A26" s="5" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>البر الغربي</t>
@@ -902,6 +907,7 @@
       <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
+      <c r="A27" s="5" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>الضفة الغربية</t>
@@ -914,6 +920,7 @@
       <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
+      <c r="A28" s="5" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
           <t>وادي الملوك</t>
@@ -926,6 +933,7 @@
       <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
+      <c r="A29" s="5" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>معبد الدير البحري</t>
@@ -938,6 +946,7 @@
       <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
+      <c r="A30" s="5" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>مدينة الأقصر</t>
@@ -950,6 +959,7 @@
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
+      <c r="A31" s="5" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>إسنا</t>
@@ -962,6 +972,7 @@
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
+      <c r="A32" s="6" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>أرمنت</t>
@@ -999,6 +1010,8 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t>مركز سموحة للتخاطب</t>
@@ -1014,6 +1027,8 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>مركز د/ نهى رسلان لتدريب النطق والكلام</t>
@@ -1033,6 +1048,8 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>مركز د/ هبة سلامة</t>
@@ -1052,6 +1069,8 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="6" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>أكاديمية زويل</t>
@@ -1067,6 +1086,7 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" s="5" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
           <t>برج العرب</t>
@@ -1079,6 +1099,7 @@
       <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
+      <c r="A39" s="5" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
           <t>مونتازا</t>
@@ -1091,6 +1112,7 @@
       <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
+      <c r="A40" s="5" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
           <t>سيدي بشر</t>
@@ -1111,6 +1133,8 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>عيادة تخاطب شارع الطفولة السعيدة</t>
@@ -1126,6 +1150,8 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="6" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>مركز تومورو للتخاطب</t>
@@ -1141,6 +1167,7 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" s="5" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>أبي قير</t>
@@ -1153,6 +1180,7 @@
       <c r="G43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
+      <c r="A44" s="5" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
           <t>الدخيلة</t>
@@ -1165,6 +1193,7 @@
       <c r="G44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
+      <c r="A45" s="5" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>كوم الدكة</t>
@@ -1177,6 +1206,7 @@
       <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
+      <c r="A46" s="5" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
           <t>ستانلي</t>
@@ -1189,6 +1219,7 @@
       <c r="G46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
+      <c r="A47" s="5" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
           <t>الشاطبي</t>
@@ -1201,6 +1232,7 @@
       <c r="G47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
+      <c r="A48" s="5" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
           <t>رشدي</t>
@@ -1213,6 +1245,7 @@
       <c r="G48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
+      <c r="A49" s="5" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
           <t>الرملة</t>
@@ -1225,6 +1258,7 @@
       <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
+      <c r="A50" s="5" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
           <t>الإبراهيمية</t>
@@ -1237,6 +1271,7 @@
       <c r="G50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
+      <c r="A51" s="5" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
           <t>القنطرة</t>
@@ -1249,6 +1284,7 @@
       <c r="G51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
+      <c r="A52" s="5" t="n"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
           <t>كفر عبده</t>
@@ -1261,6 +1297,7 @@
       <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
+      <c r="A53" s="5" t="n"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
           <t>الحمام</t>
@@ -1273,6 +1310,7 @@
       <c r="G53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
+      <c r="A54" s="5" t="n"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
           <t>مارينا</t>
@@ -1285,6 +1323,7 @@
       <c r="G54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
+      <c r="A55" s="5" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>عمومية</t>
@@ -1297,6 +1336,7 @@
       <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
+      <c r="A56" s="6" t="n"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
           <t>ضواحي</t>
@@ -1326,6 +1366,7 @@
       <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
+      <c r="A58" s="5" t="n"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
           <t>بورسعيد</t>
@@ -1338,6 +1379,7 @@
       <c r="G58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
+      <c r="A59" s="5" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>السويس</t>
@@ -1350,6 +1392,7 @@
       <c r="G59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
+      <c r="A60" s="5" t="n"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
           <t>القنطرة غرب</t>
@@ -1362,6 +1405,7 @@
       <c r="G60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
+      <c r="A61" s="5" t="n"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
           <t>القنطرة شرق</t>
@@ -1374,6 +1418,7 @@
       <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
+      <c r="A62" s="5" t="n"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
           <t>فايد</t>
@@ -1386,6 +1431,7 @@
       <c r="G62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
+      <c r="A63" s="5" t="n"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
           <t>تل الكبير</t>
@@ -1398,6 +1444,7 @@
       <c r="G63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
+      <c r="A64" s="5" t="n"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
           <t>الشلوفة</t>
@@ -1410,6 +1457,7 @@
       <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
+      <c r="A65" s="6" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>الدفرسوار</t>
@@ -1447,6 +1495,8 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="6" t="n"/>
       <c r="C67" s="4" t="inlineStr">
         <is>
           <t>مركز تخاطب سفاجة</t>
@@ -1462,6 +1512,7 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" s="5" t="n"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>سفاجة</t>
@@ -1474,6 +1525,7 @@
       <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
+      <c r="A69" s="5" t="n"/>
       <c r="B69" s="3" t="inlineStr">
         <is>
           <t>القصير</t>
@@ -1486,6 +1538,7 @@
       <c r="G69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
+      <c r="A70" s="5" t="n"/>
       <c r="B70" s="3" t="inlineStr">
         <is>
           <t>مرسى علم</t>
@@ -1498,6 +1551,7 @@
       <c r="G70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
+      <c r="A71" s="5" t="n"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
           <t>شلاتين</t>
@@ -1510,6 +1564,7 @@
       <c r="G71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
+      <c r="A72" s="5" t="n"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
           <t>حلايب</t>
@@ -1522,6 +1577,7 @@
       <c r="G72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
+      <c r="A73" s="5" t="n"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
           <t>أبو رماد</t>
@@ -1534,6 +1590,7 @@
       <c r="G73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
+      <c r="A74" s="5" t="n"/>
       <c r="B74" s="3" t="inlineStr">
         <is>
           <t>قصير الجديدة</t>
@@ -1546,6 +1603,7 @@
       <c r="G74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
+      <c r="A75" s="5" t="n"/>
       <c r="B75" s="3" t="inlineStr">
         <is>
           <t>رأس غارب</t>
@@ -1558,6 +1616,7 @@
       <c r="G75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
+      <c r="A76" s="6" t="n"/>
       <c r="B76" s="3" t="inlineStr">
         <is>
           <t>دهب</t>
@@ -1595,6 +1654,7 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" s="5" t="n"/>
       <c r="B78" s="3" t="inlineStr">
         <is>
           <t>كفر الدوار</t>
@@ -1607,6 +1667,7 @@
       <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
+      <c r="A79" s="5" t="n"/>
       <c r="B79" s="3" t="inlineStr">
         <is>
           <t>رشيد</t>
@@ -1627,6 +1688,7 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" s="5" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
           <t>إدكو</t>
@@ -1639,6 +1701,7 @@
       <c r="G80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
+      <c r="A81" s="5" t="n"/>
       <c r="B81" s="3" t="inlineStr">
         <is>
           <t>أبو حمص</t>
@@ -1651,6 +1714,7 @@
       <c r="G81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
+      <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
           <t>كوم حمادة</t>
@@ -1663,6 +1727,7 @@
       <c r="G82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
+      <c r="A83" s="5" t="n"/>
       <c r="B83" s="3" t="inlineStr">
         <is>
           <t>شبراخيت</t>
@@ -1675,6 +1740,7 @@
       <c r="G83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
+      <c r="A84" s="5" t="n"/>
       <c r="B84" s="3" t="inlineStr">
         <is>
           <t>كفر الشيخ</t>
@@ -1687,6 +1753,7 @@
       <c r="G84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
+      <c r="A85" s="5" t="n"/>
       <c r="B85" s="3" t="inlineStr">
         <is>
           <t>نوقة</t>
@@ -1699,6 +1766,7 @@
       <c r="G85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
+      <c r="A86" s="5" t="n"/>
       <c r="B86" s="3" t="inlineStr">
         <is>
           <t>الحامول</t>
@@ -1711,6 +1779,7 @@
       <c r="G86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
+      <c r="A87" s="5" t="n"/>
       <c r="B87" s="3" t="inlineStr">
         <is>
           <t>شرقية</t>
@@ -1723,6 +1792,7 @@
       <c r="G87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
+      <c r="A88" s="5" t="n"/>
       <c r="B88" s="3" t="inlineStr">
         <is>
           <t>الدلنجات</t>
@@ -1735,6 +1805,7 @@
       <c r="G88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
+      <c r="A89" s="5" t="n"/>
       <c r="B89" s="3" t="inlineStr">
         <is>
           <t>إيتاي البارود</t>
@@ -1747,6 +1818,7 @@
       <c r="G89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
+      <c r="A90" s="5" t="n"/>
       <c r="B90" s="3" t="inlineStr">
         <is>
           <t>بسيون</t>
@@ -1759,6 +1831,7 @@
       <c r="G90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
+      <c r="A91" s="6" t="n"/>
       <c r="B91" s="3" t="inlineStr">
         <is>
           <t>سنجور</t>
@@ -1796,6 +1869,8 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
       <c r="C93" s="4" t="inlineStr">
         <is>
           <t>مركز تخاطب وسمع واتزان</t>
@@ -1811,6 +1886,8 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="5" t="n"/>
       <c r="C94" s="4" t="inlineStr">
         <is>
           <t>مركز قدرات للتخاطب</t>
@@ -1826,6 +1903,8 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="n"/>
       <c r="C95" s="4" t="inlineStr">
         <is>
           <t>مركز مكة للتخاطب وتنمية مهارات</t>
@@ -1841,6 +1920,8 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="6" t="n"/>
       <c r="C96" s="4" t="inlineStr">
         <is>
           <t>مركز القادة للتخاطب وتنمية المهارات</t>
@@ -1856,6 +1937,7 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" s="5" t="n"/>
       <c r="B97" s="3" t="inlineStr">
         <is>
           <t>مدينة 6 أكتوبر</t>
@@ -1868,6 +1950,7 @@
       <c r="G97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
+      <c r="A98" s="5" t="n"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
           <t>حلوان</t>
@@ -1880,6 +1963,7 @@
       <c r="G98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
+      <c r="A99" s="5" t="n"/>
       <c r="B99" s="3" t="inlineStr">
         <is>
           <t>البدرشين</t>
@@ -1892,6 +1976,7 @@
       <c r="G99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
+      <c r="A100" s="5" t="n"/>
       <c r="B100" s="3" t="inlineStr">
         <is>
           <t>دهشور</t>
@@ -1904,6 +1989,7 @@
       <c r="G100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
+      <c r="A101" s="5" t="n"/>
       <c r="B101" s="3" t="inlineStr">
         <is>
           <t>أبو رواش</t>
@@ -1916,6 +2002,7 @@
       <c r="G101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
+      <c r="A102" s="5" t="n"/>
       <c r="B102" s="3" t="inlineStr">
         <is>
           <t>الوراق</t>
@@ -1928,6 +2015,7 @@
       <c r="G102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
+      <c r="A103" s="5" t="n"/>
       <c r="B103" s="3" t="inlineStr">
         <is>
           <t>الساحل</t>
@@ -1940,6 +2028,7 @@
       <c r="G103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
+      <c r="A104" s="5" t="n"/>
       <c r="B104" s="3" t="inlineStr">
         <is>
           <t>الكيت كات</t>
@@ -1952,6 +2041,7 @@
       <c r="G104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
+      <c r="A105" s="5" t="n"/>
       <c r="B105" s="3" t="inlineStr">
         <is>
           <t>الهرم</t>
@@ -1972,6 +2062,8 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="5" t="n"/>
       <c r="C106" s="4" t="inlineStr">
         <is>
           <t>مركز طريقنا للتخاطب</t>
@@ -1987,6 +2079,8 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="6" t="n"/>
       <c r="C107" s="4" t="inlineStr">
         <is>
           <t>مركز الأهرام للتخاطب</t>
@@ -2002,6 +2096,7 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" s="5" t="n"/>
       <c r="B108" s="3" t="inlineStr">
         <is>
           <t>إمبابة</t>
@@ -2022,6 +2117,8 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="6" t="n"/>
       <c r="C109" s="4" t="inlineStr">
         <is>
           <t>مركز تخاطب شارع عزبة الصعايدة</t>
@@ -2037,6 +2134,7 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" s="5" t="n"/>
       <c r="B110" s="3" t="inlineStr">
         <is>
           <t>العمرانية</t>
@@ -2049,6 +2147,7 @@
       <c r="G110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
+      <c r="A111" s="5" t="n"/>
       <c r="B111" s="3" t="inlineStr">
         <is>
           <t>الحوامدية</t>
@@ -2061,6 +2160,7 @@
       <c r="G111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
+      <c r="A112" s="5" t="n"/>
       <c r="B112" s="3" t="inlineStr">
         <is>
           <t>أطفيح</t>
@@ -2073,6 +2173,7 @@
       <c r="G112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
+      <c r="A113" s="5" t="n"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
           <t>بني سويف الجديدة</t>
@@ -2085,6 +2186,7 @@
       <c r="G113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
+      <c r="A114" s="6" t="n"/>
       <c r="B114" s="3" t="inlineStr">
         <is>
           <t>المنيل</t>
@@ -2122,6 +2224,8 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="6" t="n"/>
       <c r="C116" s="4" t="inlineStr">
         <is>
           <t>مركز الدلتا للتخاطب</t>
@@ -2137,6 +2241,7 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" s="5" t="n"/>
       <c r="B117" s="3" t="inlineStr">
         <is>
           <t>طلخا</t>
@@ -2149,6 +2254,7 @@
       <c r="G117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
+      <c r="A118" s="5" t="n"/>
       <c r="B118" s="3" t="inlineStr">
         <is>
           <t>آجا</t>
@@ -2161,6 +2267,7 @@
       <c r="G118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
+      <c r="A119" s="5" t="n"/>
       <c r="B119" s="3" t="inlineStr">
         <is>
           <t>مِت غمر</t>
@@ -2173,6 +2280,7 @@
       <c r="G119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
+      <c r="A120" s="5" t="n"/>
       <c r="B120" s="3" t="inlineStr">
         <is>
           <t>شربين</t>
@@ -2185,6 +2293,7 @@
       <c r="G120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
+      <c r="A121" s="5" t="n"/>
       <c r="B121" s="3" t="inlineStr">
         <is>
           <t>بلقاس</t>
@@ -2197,6 +2306,7 @@
       <c r="G121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
+      <c r="A122" s="5" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>جمصة</t>
@@ -2209,6 +2319,7 @@
       <c r="G122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
+      <c r="A123" s="5" t="n"/>
       <c r="B123" s="3" t="inlineStr">
         <is>
           <t>السنبلاوين</t>
@@ -2221,6 +2332,7 @@
       <c r="G123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
+      <c r="A124" s="5" t="n"/>
       <c r="B124" s="3" t="inlineStr">
         <is>
           <t>ميت سلسيل</t>
@@ -2233,6 +2345,7 @@
       <c r="G124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
+      <c r="A125" s="5" t="n"/>
       <c r="B125" s="3" t="inlineStr">
         <is>
           <t>أجا</t>
@@ -2245,6 +2358,7 @@
       <c r="G125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
+      <c r="A126" s="5" t="n"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
           <t>المتينة</t>
@@ -2257,6 +2371,7 @@
       <c r="G126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
+      <c r="A127" s="5" t="n"/>
       <c r="B127" s="3" t="inlineStr">
         <is>
           <t>منية النصر</t>
@@ -2269,6 +2384,7 @@
       <c r="G127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
+      <c r="A128" s="6" t="n"/>
       <c r="B128" s="3" t="inlineStr">
         <is>
           <t>كفر سعد</t>
@@ -2310,6 +2426,7 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" s="5" t="n"/>
       <c r="B130" s="3" t="inlineStr">
         <is>
           <t>عين سخنة</t>
@@ -2322,6 +2439,7 @@
       <c r="G130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
+      <c r="A131" s="5" t="n"/>
       <c r="B131" s="3" t="inlineStr">
         <is>
           <t>عطاقة</t>
@@ -2334,6 +2452,7 @@
       <c r="G131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
+      <c r="A132" s="5" t="n"/>
       <c r="B132" s="3" t="inlineStr">
         <is>
           <t>الجنايين</t>
@@ -2346,6 +2465,7 @@
       <c r="G132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
+      <c r="A133" s="5" t="n"/>
       <c r="B133" s="3" t="inlineStr">
         <is>
           <t>فايد</t>
@@ -2358,6 +2478,7 @@
       <c r="G133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
+      <c r="A134" s="5" t="n"/>
       <c r="B134" s="3" t="inlineStr">
         <is>
           <t>ناقصة</t>
@@ -2370,6 +2491,7 @@
       <c r="G134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
+      <c r="A135" s="5" t="n"/>
       <c r="B135" s="3" t="inlineStr">
         <is>
           <t>القصير</t>
@@ -2382,6 +2504,7 @@
       <c r="G135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
+      <c r="A136" s="6" t="n"/>
       <c r="B136" s="3" t="inlineStr">
         <is>
           <t>الدفرسوار</t>
@@ -2423,6 +2546,8 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" s="5" t="n"/>
+      <c r="B138" s="5" t="n"/>
       <c r="C138" s="4" t="inlineStr">
         <is>
           <t>مركز السلام للتخاطب وتنمية المهارات</t>
@@ -2438,6 +2563,8 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="6" t="n"/>
       <c r="C139" s="4" t="inlineStr">
         <is>
           <t>مركز الحياة للتخاطب وتنمية المهارات</t>
@@ -2457,6 +2584,7 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" s="5" t="n"/>
       <c r="B140" s="3" t="inlineStr">
         <is>
           <t>الإسماعيلية</t>
@@ -2469,6 +2597,7 @@
       <c r="G140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
+      <c r="A141" s="5" t="n"/>
       <c r="B141" s="3" t="inlineStr">
         <is>
           <t>بلبيس</t>
@@ -2493,6 +2622,7 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" s="5" t="n"/>
       <c r="B142" s="3" t="inlineStr">
         <is>
           <t>مدينة 10 رمضان</t>
@@ -2505,6 +2635,7 @@
       <c r="G142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
+      <c r="A143" s="5" t="n"/>
       <c r="B143" s="3" t="inlineStr">
         <is>
           <t>المعادي</t>
@@ -2517,6 +2648,7 @@
       <c r="G143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
+      <c r="A144" s="5" t="n"/>
       <c r="B144" s="3" t="inlineStr">
         <is>
           <t>فاقوس</t>
@@ -2537,6 +2669,8 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" s="5" t="n"/>
+      <c r="B145" s="6" t="n"/>
       <c r="C145" s="4" t="inlineStr">
         <is>
           <t>مركز كِنان للتخاطب والتأهيل</t>
@@ -2552,6 +2686,7 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" s="5" t="n"/>
       <c r="B146" s="3" t="inlineStr">
         <is>
           <t>القنايات</t>
@@ -2564,6 +2699,7 @@
       <c r="G146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
+      <c r="A147" s="5" t="n"/>
       <c r="B147" s="3" t="inlineStr">
         <is>
           <t>أبو حماد</t>
@@ -2576,6 +2712,7 @@
       <c r="G147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
+      <c r="A148" s="5" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
           <t>الجزيرة</t>
@@ -2588,6 +2725,7 @@
       <c r="G148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
+      <c r="A149" s="5" t="n"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
           <t>ههيا</t>
@@ -2600,6 +2738,7 @@
       <c r="G149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
+      <c r="A150" s="5" t="n"/>
       <c r="B150" s="3" t="inlineStr">
         <is>
           <t>درب السلام</t>
@@ -2612,6 +2751,7 @@
       <c r="G150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
+      <c r="A151" s="6" t="n"/>
       <c r="B151" s="3" t="inlineStr">
         <is>
           <t>الصالحية</t>
@@ -2649,6 +2789,8 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" s="5" t="n"/>
+      <c r="B153" s="5" t="n"/>
       <c r="C153" s="4" t="inlineStr">
         <is>
           <t>أكاديمية المعرفة للتخاطب</t>
@@ -2668,6 +2810,8 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" s="5" t="n"/>
+      <c r="B154" s="5" t="n"/>
       <c r="C154" s="4" t="inlineStr">
         <is>
           <t>مركز القمة للتدريب والتأهيل</t>
@@ -2687,6 +2831,8 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" s="5" t="n"/>
+      <c r="B155" s="5" t="n"/>
       <c r="C155" s="4" t="inlineStr">
         <is>
           <t>عيادة الدكتورة إيناس أحمد</t>
@@ -2706,6 +2852,8 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" s="5" t="n"/>
+      <c r="B156" s="6" t="n"/>
       <c r="C156" s="4" t="inlineStr">
         <is>
           <t>مركز الدلتا لأمراض التخاطب</t>
@@ -2721,6 +2869,7 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" s="5" t="n"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
           <t>كفر الزيات</t>
@@ -2733,6 +2882,7 @@
       <c r="G157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
+      <c r="A158" s="5" t="n"/>
       <c r="B158" s="3" t="inlineStr">
         <is>
           <t>سمنود</t>
@@ -2745,6 +2895,7 @@
       <c r="G158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
+      <c r="A159" s="5" t="n"/>
       <c r="B159" s="3" t="inlineStr">
         <is>
           <t>زفتا</t>
@@ -2757,6 +2908,7 @@
       <c r="G159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
+      <c r="A160" s="5" t="n"/>
       <c r="B160" s="3" t="inlineStr">
         <is>
           <t>المحلة الكبرى</t>
@@ -2777,6 +2929,8 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" s="5" t="n"/>
+      <c r="B161" s="5" t="n"/>
       <c r="C161" s="4" t="inlineStr">
         <is>
           <t>مركز كيدز الأمل للعلاج الطبيعي</t>
@@ -2792,6 +2946,8 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="6" t="n"/>
       <c r="C162" s="4" t="inlineStr">
         <is>
           <t>مركز صن رايز للتخاطب</t>
@@ -2807,6 +2963,7 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" s="5" t="n"/>
       <c r="B163" s="3" t="inlineStr">
         <is>
           <t>قطور</t>
@@ -2819,6 +2976,7 @@
       <c r="G163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
+      <c r="A164" s="5" t="n"/>
       <c r="B164" s="3" t="inlineStr">
         <is>
           <t>سان الحجر</t>
@@ -2831,6 +2989,7 @@
       <c r="G164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
+      <c r="A165" s="5" t="n"/>
       <c r="B165" s="3" t="inlineStr">
         <is>
           <t>بسيون</t>
@@ -2843,6 +3002,7 @@
       <c r="G165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
+      <c r="A166" s="6" t="n"/>
       <c r="B166" s="3" t="inlineStr">
         <is>
           <t>الدلتا الجديدة</t>
@@ -2880,6 +3040,8 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" s="5" t="n"/>
+      <c r="B168" s="6" t="n"/>
       <c r="C168" s="4" t="inlineStr">
         <is>
           <t>مركز التخاطب بمركز شباب الشواشنة</t>
@@ -2895,6 +3057,7 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" s="5" t="n"/>
       <c r="B169" s="3" t="inlineStr">
         <is>
           <t>سيوه</t>
@@ -2907,6 +3070,7 @@
       <c r="G169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
+      <c r="A170" s="5" t="n"/>
       <c r="B170" s="3" t="inlineStr">
         <is>
           <t>القرين</t>
@@ -2919,6 +3083,7 @@
       <c r="G170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
+      <c r="A171" s="5" t="n"/>
       <c r="B171" s="3" t="inlineStr">
         <is>
           <t>إبشواي</t>
@@ -2931,6 +3096,7 @@
       <c r="G171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
+      <c r="A172" s="5" t="n"/>
       <c r="B172" s="3" t="inlineStr">
         <is>
           <t>سنوريس</t>
@@ -2943,6 +3109,7 @@
       <c r="G172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
+      <c r="A173" s="5" t="n"/>
       <c r="B173" s="3" t="inlineStr">
         <is>
           <t>طامية</t>
@@ -2955,6 +3122,7 @@
       <c r="G173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
+      <c r="A174" s="5" t="n"/>
       <c r="B174" s="3" t="inlineStr">
         <is>
           <t>اطسا</t>
@@ -2967,6 +3135,7 @@
       <c r="G174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
+      <c r="A175" s="5" t="n"/>
       <c r="B175" s="3" t="inlineStr">
         <is>
           <t>يوسف الصديق</t>
@@ -2979,6 +3148,7 @@
       <c r="G175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
+      <c r="A176" s="5" t="n"/>
       <c r="B176" s="3" t="inlineStr">
         <is>
           <t>العدوة</t>
@@ -2991,6 +3161,7 @@
       <c r="G176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
+      <c r="A177" s="6" t="n"/>
       <c r="B177" s="3" t="inlineStr">
         <is>
           <t>آثار</t>
@@ -3036,580 +3207,461 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>القاهرة</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل وصعوبات التعلم - فرع جديد</t>
-        </is>
-      </c>
-      <c r="C179" s="8" t="inlineStr"/>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>0222406301</t>
-        </is>
-      </c>
-      <c r="E179" s="9" t="inlineStr"/>
-      <c r="F179" s="8" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب المرح لعلاج الأطفال والكبار</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
+      <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>شارع جميل أمام بنك القاهرة</t>
+          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>مركز تخاطب البر والتقوى</t>
-        </is>
-      </c>
-      <c r="C180" s="8" t="inlineStr"/>
-      <c r="D180" s="9" t="inlineStr"/>
-      <c r="E180" s="9" t="inlineStr"/>
-      <c r="F180" s="8" t="inlineStr">
-        <is>
-          <t>104 برج الأوقاف، شارع ابن سندر، سرايا القبة، القاهرة</t>
-        </is>
-      </c>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب أخصائية التخاطب هبة المصري</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>د. هبة المصري</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr"/>
+      <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>بنها</t>
+          <t>ترعة القبة، مساكن الأميرية الجنوبية، حدائق القبة</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="n"/>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>بيت التمريض</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="inlineStr"/>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>201201120500</t>
-        </is>
-      </c>
-      <c r="E181" s="9" t="inlineStr"/>
-      <c r="F181" s="8" t="inlineStr">
-        <is>
-          <t>متخصص في التخاطب وتعديل السلوك</t>
-        </is>
-      </c>
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>مركز نور الحياة للتخاطب</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
+      <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>بنها</t>
+          <t>شارع شبرا الخلفاوي، قسم الساحل</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t>مدينة نصر</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>المركز الذهبي التخصصي (GSC)</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="inlineStr"/>
-      <c r="D182" s="9" t="inlineStr"/>
-      <c r="E182" s="9" t="inlineStr"/>
-      <c r="F182" s="8" t="inlineStr">
-        <is>
-          <t>مدينة نصر، متخصص في التخاطب وتعديل السلوك</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="inlineStr"/>
+      <c r="A182" s="5" t="n"/>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
+      <c r="F182" s="4" t="inlineStr"/>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>مركز Speak للتخاطب</t>
-        </is>
-      </c>
-      <c r="C183" s="8" t="inlineStr"/>
-      <c r="D183" s="9" t="inlineStr"/>
-      <c r="E183" s="9" t="inlineStr"/>
-      <c r="F183" s="8" t="inlineStr">
-        <is>
-          <t>زهراء مدينة نصر، المرحلة الأولى، بجوار مسجد النور</t>
-        </is>
-      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>معهد السمع والكلام بإمبابة</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
+      <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>75 شارع حنفي الشيخوني</t>
+          <t>1 شارع الطيار فكري، بجوار مستشفى الحميات، إمبابة</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>مركز الزهراء للتخاطب</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr"/>
-      <c r="D184" s="9" t="inlineStr"/>
-      <c r="E184" s="9" t="inlineStr"/>
-      <c r="F184" s="8" t="inlineStr">
-        <is>
-          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
-        </is>
-      </c>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>مركز Speak للتخاطب</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
+      <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>شارع محمد القطان</t>
+          <t>زهراء مدينة نصر - المرحلة الأولى</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع مدينة نصر</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="inlineStr"/>
-      <c r="D185" s="9" t="inlineStr"/>
-      <c r="E185" s="9" t="inlineStr"/>
-      <c r="F185" s="8" t="inlineStr">
-        <is>
-          <t>شارع مصطفى النحاس، فوق التوحيد والنور</t>
-        </is>
-      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>المركز الذهبي التخصصي (GSC)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
+      <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>2 شارع أحمد عبد ربه</t>
+          <t>مدينة نصر، القاهرة</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="n"/>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب - فرع مدينة نصر</t>
-        </is>
-      </c>
-      <c r="C186" s="8" t="inlineStr"/>
-      <c r="D186" s="9" t="inlineStr"/>
-      <c r="E186" s="9" t="inlineStr"/>
-      <c r="F186" s="8" t="inlineStr">
+      <c r="A186" s="5" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>مركز الزهراء للتخاطب</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr"/>
+      <c r="E186" s="4" t="inlineStr"/>
+      <c r="F186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>مركز الحمد للعلاج الطبيعي والتخاطب</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr"/>
+      <c r="E187" s="4" t="inlineStr"/>
+      <c r="F187" s="4" t="inlineStr"/>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>شارع مصطفى النحاس فوق التوحيد والنور بعد مدرسة المنهل</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n"/>
+      <c r="B188" s="6" t="n"/>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr"/>
+      <c r="E188" s="4" t="inlineStr"/>
+      <c r="F188" s="4" t="inlineStr"/>
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>مدينة نصر</t>
         </is>
       </c>
-      <c r="G186" s="4" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n"/>
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>مصر الجديدة</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل - فرع مصر الجديدة</t>
-        </is>
-      </c>
-      <c r="C187" s="8" t="inlineStr"/>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>0222406301</t>
-        </is>
-      </c>
-      <c r="E187" s="9" t="inlineStr"/>
-      <c r="F187" s="8" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="6" t="n"/>
-      <c r="B188" s="8" t="inlineStr">
-        <is>
-          <t>المركز المصري الكندي - فرع النزهة</t>
-        </is>
-      </c>
-      <c r="C188" s="8" t="inlineStr"/>
-      <c r="D188" s="9" t="inlineStr"/>
-      <c r="E188" s="9" t="inlineStr"/>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>14 شارع جمال الدين على، بجوار ملاهي السندباد</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t>المعادي</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="inlineStr">
-        <is>
-          <t>مركز كيور لجراحات الأذن والقوقعة والسمعيات والتخاطب</t>
-        </is>
-      </c>
-      <c r="C189" s="8" t="inlineStr"/>
-      <c r="D189" s="9" t="inlineStr"/>
-      <c r="E189" s="9" t="inlineStr"/>
-      <c r="F189" s="8" t="inlineStr">
-        <is>
-          <t>شارع النصر، تقاطع اللاسلكي، حي المعادي</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr"/>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل و صعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>د. وفاء وافي</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr"/>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>1 شارع المنتزه خلف مستشفى هليوبوليس</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
-      <c r="B190" s="8" t="inlineStr">
-        <is>
-          <t>مركز الجنا للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="C190" s="8" t="inlineStr"/>
-      <c r="D190" s="9" t="inlineStr"/>
-      <c r="E190" s="9" t="inlineStr"/>
-      <c r="F190" s="8" t="inlineStr">
-        <is>
-          <t>شارع 76، المعادى</t>
-        </is>
-      </c>
-      <c r="G190" s="4" t="inlineStr"/>
+      <c r="B190" s="6" t="n"/>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>مركز هليوبوليس للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr"/>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>01151194780</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>28 شارع محمد عبيد من شارع النزهة، ميدان السبع عمارات</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="n"/>
-      <c r="B191" s="8" t="inlineStr">
-        <is>
-          <t>المركز المصري الكندي - فرع المعادي</t>
-        </is>
-      </c>
-      <c r="C191" s="8" t="inlineStr"/>
-      <c r="D191" s="9" t="inlineStr"/>
-      <c r="E191" s="9" t="inlineStr"/>
-      <c r="F191" s="8" t="inlineStr">
-        <is>
-          <t>5/3 شارع اللاسلكي، بجوار شركة غاز مصر</t>
-        </is>
-      </c>
+      <c r="A191" s="5" t="n"/>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>الزمالك</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr"/>
+      <c r="D191" s="4" t="inlineStr"/>
+      <c r="E191" s="4" t="inlineStr"/>
+      <c r="F191" s="4" t="inlineStr"/>
       <c r="G191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="7" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr">
-        <is>
-          <t>مركز علمني للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="C192" s="8" t="inlineStr"/>
-      <c r="D192" s="9" t="inlineStr"/>
-      <c r="E192" s="9" t="inlineStr"/>
-      <c r="F192" s="8" t="inlineStr">
-        <is>
-          <t>8 عمارات منتصر، الدور الأرضي، بجوار مسجد عباد الرحمن</t>
-        </is>
-      </c>
+      <c r="A192" s="5" t="n"/>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr"/>
+      <c r="D192" s="4" t="inlineStr"/>
+      <c r="E192" s="4" t="inlineStr"/>
+      <c r="F192" s="4" t="inlineStr"/>
       <c r="G192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t>روض الفرج</t>
-        </is>
-      </c>
-      <c r="B193" s="8" t="inlineStr">
-        <is>
-          <t>مركز تخاطب المرح</t>
-        </is>
-      </c>
-      <c r="C193" s="8" t="inlineStr"/>
-      <c r="D193" s="9" t="inlineStr"/>
-      <c r="E193" s="9" t="inlineStr"/>
-      <c r="F193" s="8" t="inlineStr">
-        <is>
-          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا مصر</t>
-        </is>
-      </c>
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>العبّاسية</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr"/>
+      <c r="D193" s="4" t="inlineStr"/>
+      <c r="E193" s="4" t="inlineStr"/>
+      <c r="F193" s="4" t="inlineStr"/>
       <c r="G193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="6" t="n"/>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="C194" s="8" t="inlineStr"/>
-      <c r="D194" s="9" t="inlineStr"/>
-      <c r="E194" s="9" t="inlineStr"/>
-      <c r="F194" s="8" t="inlineStr">
-        <is>
-          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
-        </is>
-      </c>
+      <c r="A194" s="5" t="n"/>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>مدينة 6 أكتوبر</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr"/>
+      <c r="D194" s="4" t="inlineStr"/>
+      <c r="E194" s="4" t="inlineStr"/>
+      <c r="F194" s="4" t="inlineStr"/>
       <c r="G194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="7" t="inlineStr">
-        <is>
-          <t>المطرية</t>
-        </is>
-      </c>
-      <c r="B195" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل بالمطرية</t>
-        </is>
-      </c>
-      <c r="C195" s="8" t="inlineStr"/>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>01147626979</t>
-        </is>
-      </c>
-      <c r="E195" s="9" t="inlineStr"/>
-      <c r="F195" s="8" t="inlineStr">
-        <is>
-          <t>شارع منية مطر، بجوار محطة مترو المطرية</t>
-        </is>
-      </c>
+      <c r="A195" s="5" t="n"/>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>مدينة الشروق</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr"/>
+      <c r="D195" s="4" t="inlineStr"/>
+      <c r="E195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="inlineStr"/>
       <c r="G195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="7" t="inlineStr">
-        <is>
-          <t>الدقي</t>
-        </is>
-      </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع الدقي</t>
-        </is>
-      </c>
-      <c r="C196" s="8" t="inlineStr"/>
-      <c r="D196" s="9" t="inlineStr"/>
-      <c r="E196" s="9" t="inlineStr"/>
-      <c r="F196" s="8" t="inlineStr">
-        <is>
-          <t>4 شارع Hussein Wassef، الدقي</t>
-        </is>
-      </c>
-      <c r="G196" s="4" t="inlineStr"/>
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>مدينة بدر</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>مركز متخصص للتخاطب</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr"/>
+      <c r="E196" s="4" t="inlineStr"/>
+      <c r="F196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>مدينة بدر، القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="6" t="n"/>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب - الدقي</t>
-        </is>
-      </c>
-      <c r="C197" s="8" t="inlineStr"/>
-      <c r="D197" s="9" t="inlineStr"/>
-      <c r="E197" s="9" t="inlineStr"/>
-      <c r="F197" s="8" t="inlineStr">
-        <is>
-          <t>110 شارع التحرير، الدقي، أمام محطة مترو الدقي</t>
-        </is>
-      </c>
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>مدينة 15 مايو</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr"/>
+      <c r="D197" s="4" t="inlineStr"/>
+      <c r="E197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="inlineStr"/>
       <c r="G197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="7" t="inlineStr">
-        <is>
-          <t>الهرم</t>
-        </is>
-      </c>
-      <c r="B198" s="8" t="inlineStr">
-        <is>
-          <t>مركز هووب للتخاطب</t>
-        </is>
-      </c>
-      <c r="C198" s="8" t="inlineStr"/>
-      <c r="D198" s="9" t="inlineStr"/>
-      <c r="E198" s="9" t="inlineStr"/>
-      <c r="F198" s="8" t="inlineStr">
-        <is>
-          <t>الهرم، متخصص في التخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr"/>
+      <c r="A198" s="5" t="n"/>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>المركز المصري الكندي</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr"/>
+      <c r="E198" s="4" t="inlineStr"/>
+      <c r="F198" s="4" t="inlineStr"/>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>5/3 شارع اللاسلكي بجوار شركة غاز مصر</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
-      <c r="B199" s="8" t="inlineStr">
-        <is>
-          <t>مركز فرصة حياه للتأهيل للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="C199" s="8" t="inlineStr"/>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>01030360536</t>
-        </is>
-      </c>
-      <c r="E199" s="9" t="inlineStr"/>
-      <c r="F199" s="8" t="inlineStr">
-        <is>
-          <t>الهرم وفيصل</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب البر والتقوى</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr"/>
+      <c r="E199" s="4" t="inlineStr"/>
+      <c r="F199" s="4" t="inlineStr"/>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>104 برج الأوقاف، شارع ابن سندر</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="6" t="n"/>
-      <c r="B200" s="8" t="inlineStr">
-        <is>
-          <t>مركز اشراقة للتخاطب - د/اسلام سالم</t>
-        </is>
-      </c>
-      <c r="C200" s="8" t="inlineStr">
-        <is>
-          <t>د/اسلام سالم</t>
-        </is>
-      </c>
-      <c r="D200" s="9" t="inlineStr"/>
-      <c r="E200" s="9" t="inlineStr"/>
-      <c r="F200" s="8" t="inlineStr">
-        <is>
-          <t>شارع اللبيني، الهرم الرئيسي</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr"/>
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="6" t="n"/>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>مركز كيور لجراحات الأذن والقوقعة والتخاطب</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr"/>
+      <c r="E200" s="4" t="inlineStr"/>
+      <c r="F200" s="4" t="inlineStr"/>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>شارع النصر، تقاطع اللاسلكي</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="inlineStr">
-        <is>
-          <t>النزهة</t>
-        </is>
-      </c>
-      <c r="B201" s="8" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب - فرع النزهة</t>
-        </is>
-      </c>
-      <c r="C201" s="8" t="inlineStr"/>
-      <c r="D201" s="9" t="inlineStr"/>
-      <c r="E201" s="9" t="inlineStr"/>
-      <c r="F201" s="8" t="inlineStr">
-        <is>
-          <t>النزهة</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr"/>
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>مركز Almony للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr"/>
+      <c r="E201" s="4" t="inlineStr"/>
+      <c r="F201" s="4" t="inlineStr"/>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>8 عمارات منتصر، بجانب مسجد عبد الرحمن، حدائق حلوان</t>
+        </is>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="6" t="n"/>
-      <c r="B202" s="8" t="inlineStr">
-        <is>
-          <t>نور الحياة للتخاطب</t>
-        </is>
-      </c>
-      <c r="C202" s="8" t="inlineStr"/>
-      <c r="D202" s="9" t="inlineStr"/>
-      <c r="E202" s="9" t="inlineStr"/>
-      <c r="F202" s="8" t="inlineStr">
-        <is>
-          <t>شارع شبرا الخلفاوى، قسم الساحل</t>
-        </is>
-      </c>
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>المقطم</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr"/>
+      <c r="D202" s="4" t="inlineStr"/>
+      <c r="E202" s="4" t="inlineStr"/>
+      <c r="F202" s="4" t="inlineStr"/>
       <c r="G202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="7" t="inlineStr">
-        <is>
-          <t>الزيتون</t>
-        </is>
-      </c>
-      <c r="B203" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل - فرع الزيتون</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr"/>
-      <c r="D203" s="9" t="inlineStr">
-        <is>
-          <t>0222406301</t>
-        </is>
-      </c>
-      <c r="E203" s="9" t="inlineStr"/>
-      <c r="F203" s="8" t="inlineStr">
-        <is>
-          <t>حي الزيتون</t>
-        </is>
-      </c>
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>القاهرة الجديدة</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr"/>
+      <c r="D203" s="4" t="inlineStr"/>
+      <c r="E203" s="4" t="inlineStr"/>
+      <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="7" t="inlineStr">
-        <is>
-          <t>عين شمس</t>
-        </is>
-      </c>
-      <c r="B204" s="8" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب - فرع عين شمس</t>
-        </is>
-      </c>
-      <c r="C204" s="8" t="inlineStr"/>
-      <c r="D204" s="9" t="inlineStr"/>
-      <c r="E204" s="9" t="inlineStr"/>
-      <c r="F204" s="8" t="inlineStr">
-        <is>
-          <t>عين شمس</t>
-        </is>
-      </c>
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>الشيخ زايد</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr"/>
+      <c r="D204" s="4" t="inlineStr"/>
+      <c r="E204" s="4" t="inlineStr"/>
+      <c r="F204" s="4" t="inlineStr"/>
       <c r="G204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t>فيصل</t>
-        </is>
-      </c>
-      <c r="B205" s="8" t="inlineStr">
-        <is>
-          <t>مركز فرصة حياه - فرع فيصل</t>
-        </is>
-      </c>
-      <c r="C205" s="8" t="inlineStr"/>
-      <c r="D205" s="9" t="inlineStr">
-        <is>
-          <t>01030360536</t>
-        </is>
-      </c>
-      <c r="E205" s="9" t="inlineStr"/>
-      <c r="F205" s="8" t="inlineStr">
-        <is>
-          <t>فيصل</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>أشمون</t>
-        </is>
-      </c>
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>الرحاب</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr"/>
+      <c r="D205" s="4" t="inlineStr"/>
+      <c r="E205" s="4" t="inlineStr"/>
+      <c r="F205" s="4" t="inlineStr"/>
+      <c r="G205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
+      <c r="A206" s="5" t="n"/>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>البرجايه</t>
+          <t>الحي العاشر</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr"/>
@@ -3619,93 +3671,87 @@
       <c r="G206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
+      <c r="A207" s="5" t="n"/>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب وصعوبات تعلم</t>
-        </is>
-      </c>
+          <t>المنيل</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr"/>
       <c r="D207" s="4" t="inlineStr"/>
       <c r="E207" s="4" t="inlineStr"/>
       <c r="F207" s="4" t="inlineStr"/>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
+      <c r="G207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
+      <c r="A208" s="5" t="n"/>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>منوف الجديدة</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr"/>
+          <t>الدقي</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>فرع الدقي من مركز الحمد</t>
+        </is>
+      </c>
       <c r="D208" s="4" t="inlineStr"/>
       <c r="E208" s="4" t="inlineStr"/>
       <c r="F208" s="4" t="inlineStr"/>
-      <c r="G208" s="4" t="inlineStr"/>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>4 شارع حسين واصف، بجوار مدرسة العروبة</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>كفر عبده</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr"/>
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="6" t="n"/>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب شارع التحرير</t>
+        </is>
+      </c>
       <c r="D209" s="4" t="inlineStr"/>
       <c r="E209" s="4" t="inlineStr"/>
       <c r="F209" s="4" t="inlineStr"/>
-      <c r="G209" s="4" t="inlineStr"/>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>شارع التحرير، أمام محطة مترو الدقي</t>
+        </is>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="A210" s="5" t="n"/>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>المنيا</t>
-        </is>
-      </c>
-      <c r="C210" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب بني أحمد للتخاطب</t>
-        </is>
-      </c>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr"/>
       <c r="D210" s="4" t="inlineStr"/>
       <c r="E210" s="4" t="inlineStr"/>
       <c r="F210" s="4" t="inlineStr"/>
-      <c r="G210" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مقوسة للتخاطب</t>
-        </is>
-      </c>
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>الموسكي</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr"/>
       <c r="D211" s="4" t="inlineStr"/>
       <c r="E211" s="4" t="inlineStr"/>
       <c r="F211" s="4" t="inlineStr"/>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
+      <c r="A212" s="5" t="n"/>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>سمالوط</t>
+          <t>الفجالة</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr"/>
@@ -3715,9 +3761,10 @@
       <c r="G212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
+      <c r="A213" s="5" t="n"/>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>بني حسن</t>
+          <t>باب الشعرية</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
@@ -3727,9 +3774,10 @@
       <c r="G213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
+      <c r="A214" s="5" t="n"/>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>هرموبوليس</t>
+          <t>الساحل</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
@@ -3739,45 +3787,77 @@
       <c r="G214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
+      <c r="A215" s="5" t="n"/>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>ملوي</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr"/>
+          <t>المطرية</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل بالمطرية</t>
+        </is>
+      </c>
       <c r="D215" s="4" t="inlineStr"/>
-      <c r="E215" s="4" t="inlineStr"/>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>01270756267, 01092975341</t>
+        </is>
+      </c>
       <c r="F215" s="4" t="inlineStr"/>
-      <c r="G215" s="4" t="inlineStr"/>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>شارع منية مطر المطرية، بجوار محطة مترو المطرية</t>
+        </is>
+      </c>
     </row>
     <row r="216">
+      <c r="A216" s="5" t="n"/>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr"/>
+          <t>عين شمس</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب</t>
+        </is>
+      </c>
       <c r="D216" s="4" t="inlineStr"/>
       <c r="E216" s="4" t="inlineStr"/>
       <c r="F216" s="4" t="inlineStr"/>
-      <c r="G216" s="4" t="inlineStr"/>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
     </row>
     <row r="217">
+      <c r="A217" s="5" t="n"/>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>ديروط الشريف</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr"/>
+          <t>الزيتون</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>حورس للسمعيات والتخاطب</t>
+        </is>
+      </c>
       <c r="D217" s="4" t="inlineStr"/>
       <c r="E217" s="4" t="inlineStr"/>
       <c r="F217" s="4" t="inlineStr"/>
-      <c r="G217" s="4" t="inlineStr"/>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>1 ميدان المطرية، الزيتون</t>
+        </is>
+      </c>
     </row>
     <row r="218">
+      <c r="A218" s="5" t="n"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>أبوقرقاص</t>
+          <t>وسيط</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
@@ -3787,9 +3867,10 @@
       <c r="G218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
+      <c r="A219" s="5" t="n"/>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>المنصورية</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr"/>
@@ -3799,9 +3880,10 @@
       <c r="G219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
+      <c r="A220" s="5" t="n"/>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>بني مازن</t>
+          <t>الدراسة</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr"/>
@@ -3811,9 +3893,10 @@
       <c r="G220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
+      <c r="A221" s="5" t="n"/>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>درب الجنينة</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr"/>
@@ -3823,39 +3906,28 @@
       <c r="G221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>الوادي الجديد</t>
-        </is>
-      </c>
+      <c r="A222" s="5" t="n"/>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب الخارجة للتخاطب</t>
-        </is>
-      </c>
+          <t>الشرابية</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr"/>
       <c r="D222" s="4" t="inlineStr"/>
       <c r="E222" s="4" t="inlineStr"/>
       <c r="F222" s="4" t="inlineStr"/>
-      <c r="G222" s="4" t="inlineStr">
-        <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
+      <c r="G222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
+      <c r="A223" s="5" t="n"/>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>الداخلة</t>
+          <t>النزهة</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب باريس للتخاطب</t>
+          <t>المركز المصري الكندي (فرع النزهة)</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -3863,14 +3935,15 @@
       <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>14 شارع جمال الدين علي بجوار ملاهي السندباد</t>
         </is>
       </c>
     </row>
     <row r="224">
+      <c r="A224" s="5" t="n"/>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>موط</t>
+          <t>الرويسي</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr"/>
@@ -3880,9 +3953,10 @@
       <c r="G224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
+      <c r="A225" s="5" t="n"/>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>بلاط</t>
+          <t>قصر النيل</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr"/>
@@ -3892,9 +3966,10 @@
       <c r="G225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
+      <c r="A226" s="5" t="n"/>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>فرافرة</t>
+          <t>الفسطاط</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr"/>
@@ -3904,9 +3979,10 @@
       <c r="G226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
+      <c r="A227" s="6" t="n"/>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>الرحاب</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr"/>
@@ -3916,106 +3992,137 @@
       <c r="G227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>القليوبية</t>
+        </is>
+      </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>القصر</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr"/>
+          <t>بنها</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب برج مكة</t>
+        </is>
+      </c>
       <c r="D228" s="4" t="inlineStr"/>
       <c r="E228" s="4" t="inlineStr"/>
       <c r="F228" s="4" t="inlineStr"/>
-      <c r="G228" s="4" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>شارع جميل أمام بنك القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="229">
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>تينيدة</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr"/>
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الجزار</t>
+        </is>
+      </c>
       <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr"/>
       <c r="F229" s="4" t="inlineStr"/>
-      <c r="G229" s="4" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
     </row>
     <row r="230">
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>دوش</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr"/>
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="6" t="n"/>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العمار</t>
+        </is>
+      </c>
       <c r="D230" s="4" t="inlineStr"/>
       <c r="E230" s="4" t="inlineStr"/>
       <c r="F230" s="4" t="inlineStr"/>
-      <c r="G230" s="4" t="inlineStr"/>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="A231" s="5" t="n"/>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العبور للتخاطب</t>
-        </is>
-      </c>
+          <t>قليوب</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr"/>
       <c r="D231" s="4" t="inlineStr"/>
       <c r="E231" s="4" t="inlineStr"/>
       <c r="F231" s="4" t="inlineStr"/>
-      <c r="G231" s="4" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="G231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
+      <c r="A232" s="5" t="n"/>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr"/>
+          <t>شبرا الخيمة</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
       <c r="D232" s="4" t="inlineStr"/>
       <c r="E232" s="4" t="inlineStr"/>
       <c r="F232" s="4" t="inlineStr"/>
-      <c r="G232" s="4" t="inlineStr"/>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>75 شارع حنفي الشيخوني</t>
+        </is>
+      </c>
     </row>
     <row r="233">
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>ساماستا</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr"/>
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>مركز النور الهدى الطبي</t>
+        </is>
+      </c>
       <c r="D233" s="4" t="inlineStr"/>
       <c r="E233" s="4" t="inlineStr"/>
       <c r="F233" s="4" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr"/>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>شارع محمد القطان</t>
+        </is>
+      </c>
     </row>
     <row r="234">
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>إبشواي</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr"/>
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="6" t="n"/>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>مركز تواصل للتخاطب</t>
+        </is>
+      </c>
       <c r="D234" s="4" t="inlineStr"/>
       <c r="E234" s="4" t="inlineStr"/>
       <c r="F234" s="4" t="inlineStr"/>
-      <c r="G234" s="4" t="inlineStr"/>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>2 شارع أحمد عبد ربه</t>
+        </is>
+      </c>
     </row>
     <row r="235">
+      <c r="A235" s="5" t="n"/>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>الجندية</t>
+          <t>الخانكة</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr"/>
@@ -4025,9 +4132,10 @@
       <c r="G235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
+      <c r="A236" s="5" t="n"/>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>ناصر</t>
+          <t>رمسيس</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr"/>
@@ -4037,9 +4145,10 @@
       <c r="G236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
+      <c r="A237" s="5" t="n"/>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>هواره</t>
+          <t>مدينة 10 رمضان</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr"/>
@@ -4049,9 +4158,10 @@
       <c r="G237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
+      <c r="A238" s="5" t="n"/>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>موشية</t>
+          <t>الشيخ زايد</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr"/>
@@ -4061,9 +4171,10 @@
       <c r="G238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
+      <c r="A239" s="5" t="n"/>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>نصار البحرية</t>
+          <t>القناطر الخيرية</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr"/>
@@ -4073,9 +4184,10 @@
       <c r="G239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
+      <c r="A240" s="5" t="n"/>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>أحمد حمزة</t>
+          <t>قها</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr"/>
@@ -4085,14 +4197,10 @@
       <c r="G240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>بورسعيد</t>
-        </is>
-      </c>
+      <c r="A241" s="5" t="n"/>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>الدقهلية</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -4102,9 +4210,10 @@
       <c r="G241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
+      <c r="A242" s="5" t="n"/>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>بورفؤاد</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr"/>
@@ -4114,9 +4223,10 @@
       <c r="G242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
+      <c r="A243" s="5" t="n"/>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>الجميل</t>
+          <t>أوسيم</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr"/>
@@ -4126,9 +4236,10 @@
       <c r="G243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
+      <c r="A244" s="5" t="n"/>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>الزهور</t>
+          <t>طره</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr"/>
@@ -4138,9 +4249,10 @@
       <c r="G244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
+      <c r="A245" s="5" t="n"/>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>الخصوص</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr"/>
@@ -4150,9 +4262,10 @@
       <c r="G245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
+      <c r="A246" s="6" t="n"/>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>الكنتاوي</t>
+          <t>القنطرة</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr"/>
@@ -4162,9 +4275,14 @@
       <c r="G246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>المنوفية</t>
+        </is>
+      </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>الضواحي</t>
+          <t>شبين الكوم</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr"/>
@@ -4174,14 +4292,10 @@
       <c r="G247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>جنوب سيناء</t>
-        </is>
-      </c>
+      <c r="A248" s="5" t="n"/>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>شرم الشيخ</t>
+          <t>منوف</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr"/>
@@ -4191,9 +4305,10 @@
       <c r="G248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
+      <c r="A249" s="5" t="n"/>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>داهب</t>
+          <t>شبين القناطر</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr"/>
@@ -4203,9 +4318,10 @@
       <c r="G249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
+      <c r="A250" s="5" t="n"/>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>نويبع</t>
+          <t>مدينة السادات</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr"/>
@@ -4215,9 +4331,10 @@
       <c r="G250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
+      <c r="A251" s="5" t="n"/>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>سانت كاترين</t>
+          <t>باقور</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr"/>
@@ -4227,9 +4344,10 @@
       <c r="G251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
+      <c r="A252" s="5" t="n"/>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>تلا</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr"/>
@@ -4239,9 +4357,10 @@
       <c r="G252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
+      <c r="A253" s="5" t="n"/>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>رأس محمد</t>
+          <t>قويسنا</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr"/>
@@ -4251,21 +4370,31 @@
       <c r="G253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
+      <c r="A254" s="5" t="n"/>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>أم سيد</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr"/>
+          <t>أشمون</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب أشمون للتخاطب</t>
+        </is>
+      </c>
       <c r="D254" s="4" t="inlineStr"/>
       <c r="E254" s="4" t="inlineStr"/>
       <c r="F254" s="4" t="inlineStr"/>
-      <c r="G254" s="4" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
     </row>
     <row r="255">
+      <c r="A255" s="5" t="n"/>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>مدينة شرم الشيخ</t>
+          <t>البرجايه</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr"/>
@@ -4275,26 +4404,31 @@
       <c r="G255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
+      <c r="A256" s="5" t="n"/>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr"/>
+          <t>بركة السبع</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب وصعوبات تعلم</t>
+        </is>
+      </c>
       <c r="D256" s="4" t="inlineStr"/>
       <c r="E256" s="4" t="inlineStr"/>
       <c r="F256" s="4" t="inlineStr"/>
-      <c r="G256" s="4" t="inlineStr"/>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
     </row>
     <row r="257">
+      <c r="A257" s="5" t="n"/>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>منوف الجديدة</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr"/>
@@ -4304,9 +4438,10 @@
       <c r="G257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
+      <c r="A258" s="6" t="n"/>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>واحة الفيوم</t>
+          <t>كفر عبده</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr"/>
@@ -4316,33 +4451,52 @@
       <c r="G258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>وادي حوف</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr"/>
+          <t>المنيا</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب بني أحمد للتخاطب</t>
+        </is>
+      </c>
       <c r="D259" s="4" t="inlineStr"/>
       <c r="E259" s="4" t="inlineStr"/>
       <c r="F259" s="4" t="inlineStr"/>
-      <c r="G259" s="4" t="inlineStr"/>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="260">
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>عين سخنة</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="inlineStr"/>
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="6" t="n"/>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب مقوسة للتخاطب</t>
+        </is>
+      </c>
       <c r="D260" s="4" t="inlineStr"/>
       <c r="E260" s="4" t="inlineStr"/>
       <c r="F260" s="4" t="inlineStr"/>
-      <c r="G260" s="4" t="inlineStr"/>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="261">
+      <c r="A261" s="5" t="n"/>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>سمالوط</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr"/>
@@ -4352,9 +4506,10 @@
       <c r="G261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
+      <c r="A262" s="5" t="n"/>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>بني حسن</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr"/>
@@ -4364,9 +4519,10 @@
       <c r="G262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
+      <c r="A263" s="5" t="n"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
+          <t>هرموبوليس</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr"/>
@@ -4376,34 +4532,23 @@
       <c r="G263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
+      <c r="A264" s="5" t="n"/>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr">
-        <is>
-          <t>مركز حلم ابني للتخاطب</t>
-        </is>
-      </c>
+          <t>ملوي</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr"/>
       <c r="D264" s="4" t="inlineStr"/>
       <c r="E264" s="4" t="inlineStr"/>
       <c r="F264" s="4" t="inlineStr"/>
-      <c r="G264" s="4" t="inlineStr">
-        <is>
-          <t>دمياط ودمياط الجديدة</t>
-        </is>
-      </c>
+      <c r="G264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
+      <c r="A265" s="5" t="n"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>دمياط الجديدة</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr"/>
@@ -4413,9 +4558,10 @@
       <c r="G265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
+      <c r="A266" s="5" t="n"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>بورت فؤاد</t>
+          <t>ديروط الشريف</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr"/>
@@ -4425,9 +4571,10 @@
       <c r="G266" s="4" t="inlineStr"/>
     </row>
     <row r="267">
+      <c r="A267" s="5" t="n"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>كفر البطة</t>
+          <t>أبوقرقاص</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr"/>
@@ -4437,9 +4584,10 @@
       <c r="G267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
+      <c r="A268" s="5" t="n"/>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>كفر سعيد</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr"/>
@@ -4449,9 +4597,10 @@
       <c r="G268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
+      <c r="A269" s="5" t="n"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>بني مازن</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr"/>
@@ -4461,9 +4610,10 @@
       <c r="G269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
+      <c r="A270" s="6" t="n"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>الزرقا</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr"/>
@@ -4473,98 +4623,95 @@
       <c r="G270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>الوادي الجديد</t>
+        </is>
+      </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>فارسكور</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr"/>
+          <t>الخارجة</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب الخارجة للتخاطب</t>
+        </is>
+      </c>
       <c r="D271" s="4" t="inlineStr"/>
       <c r="E271" s="4" t="inlineStr"/>
       <c r="F271" s="4" t="inlineStr"/>
-      <c r="G271" s="4" t="inlineStr"/>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>الخارجة</t>
+        </is>
+      </c>
     </row>
     <row r="272">
+      <c r="A272" s="5" t="n"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>رومانية</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr"/>
+          <t>الداخلة</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب باريس للتخاطب</t>
+        </is>
+      </c>
       <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr"/>
       <c r="F272" s="4" t="inlineStr"/>
-      <c r="G272" s="4" t="inlineStr"/>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>شمال سيناء</t>
-        </is>
-      </c>
+      <c r="A273" s="5" t="n"/>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>العريش</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش للتخاطب</t>
-        </is>
-      </c>
+          <t>موط</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr"/>
       <c r="D273" s="4" t="inlineStr"/>
       <c r="E273" s="4" t="inlineStr"/>
       <c r="F273" s="4" t="inlineStr"/>
-      <c r="G273" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش</t>
-        </is>
-      </c>
+      <c r="G273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
+      <c r="A274" s="5" t="n"/>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>رفح</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب رفح</t>
-        </is>
-      </c>
+          <t>بلاط</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr"/>
       <c r="D274" s="4" t="inlineStr"/>
       <c r="E274" s="4" t="inlineStr"/>
       <c r="F274" s="4" t="inlineStr"/>
-      <c r="G274" s="4" t="inlineStr">
-        <is>
-          <t>رفح</t>
-        </is>
-      </c>
+      <c r="G274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
+      <c r="A275" s="5" t="n"/>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
-        </is>
-      </c>
+          <t>فرافرة</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr"/>
       <c r="D275" s="4" t="inlineStr"/>
       <c r="E275" s="4" t="inlineStr"/>
       <c r="F275" s="4" t="inlineStr"/>
-      <c r="G275" s="4" t="inlineStr">
-        <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
+      <c r="G275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
+      <c r="A276" s="5" t="n"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>بئر العبد</t>
+          <t>باريس</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr"/>
@@ -4574,9 +4721,10 @@
       <c r="G276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
+      <c r="A277" s="5" t="n"/>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>القنطرة، سيناء</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr"/>
@@ -4586,9 +4734,10 @@
       <c r="G277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
+      <c r="A278" s="5" t="n"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>نخل</t>
+          <t>تينيدة</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr"/>
@@ -4598,9 +4747,10 @@
       <c r="G278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
+      <c r="A279" s="6" t="n"/>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>جديدة، حسنة</t>
+          <t>دوش</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr"/>
@@ -4610,21 +4760,35 @@
       <c r="G279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>دهب الشرقية</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr"/>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العبور للتخاطب</t>
+        </is>
+      </c>
       <c r="D280" s="4" t="inlineStr"/>
       <c r="E280" s="4" t="inlineStr"/>
       <c r="F280" s="4" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
     </row>
     <row r="281">
+      <c r="A281" s="5" t="n"/>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr"/>
@@ -4634,49 +4798,36 @@
       <c r="G281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="A282" s="5" t="n"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>قنا</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بمدينة العمال</t>
-        </is>
-      </c>
+          <t>ساماستا</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr"/>
       <c r="D282" s="4" t="inlineStr"/>
       <c r="E282" s="4" t="inlineStr"/>
       <c r="F282" s="4" t="inlineStr"/>
-      <c r="G282" s="4" t="inlineStr">
-        <is>
-          <t>مدينة العمال، قنا</t>
-        </is>
-      </c>
+      <c r="G282" s="4" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب حجير خزام</t>
-        </is>
-      </c>
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>إبشواي</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr"/>
       <c r="D283" s="4" t="inlineStr"/>
       <c r="E283" s="4" t="inlineStr"/>
       <c r="F283" s="4" t="inlineStr"/>
-      <c r="G283" s="4" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="G283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
+      <c r="A284" s="5" t="n"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>نجع حمادي</t>
+          <t>الجندية</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr"/>
@@ -4686,9 +4837,10 @@
       <c r="G284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
+      <c r="A285" s="5" t="n"/>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>دندرة</t>
+          <t>ناصر</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr"/>
@@ -4698,9 +4850,10 @@
       <c r="G285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
+      <c r="A286" s="5" t="n"/>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>أبيدوس</t>
+          <t>هواره</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr"/>
@@ -4710,9 +4863,10 @@
       <c r="G286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
+      <c r="A287" s="5" t="n"/>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>قفطي</t>
+          <t>موشية</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr"/>
@@ -4722,9 +4876,10 @@
       <c r="G287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
+      <c r="A288" s="5" t="n"/>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>أخميم</t>
+          <t>نصار البحرية</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr"/>
@@ -4734,9 +4889,10 @@
       <c r="G288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
+      <c r="A289" s="6" t="n"/>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>سوهاج القديمة</t>
+          <t>أحمد حمزة</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr"/>
@@ -4746,9 +4902,14 @@
       <c r="G289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>النجع البحري</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr"/>
@@ -4758,9 +4919,10 @@
       <c r="G290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
+      <c r="A291" s="5" t="n"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>الشنقي</t>
+          <t>بورفؤاد</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr"/>
@@ -4770,54 +4932,36 @@
       <c r="G291" s="4" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="A292" s="5" t="n"/>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="C292" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الشيخ للتخاطب</t>
-        </is>
-      </c>
+          <t>الجميل</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr"/>
       <c r="D292" s="4" t="inlineStr"/>
       <c r="E292" s="4" t="inlineStr"/>
       <c r="F292" s="4" t="inlineStr"/>
-      <c r="G292" s="4" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="G292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
+      <c r="A293" s="5" t="n"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>دسوق</t>
-        </is>
-      </c>
-      <c r="C293" s="4" t="inlineStr">
-        <is>
-          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
-        </is>
-      </c>
+          <t>الزهور</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr"/>
       <c r="D293" s="4" t="inlineStr"/>
       <c r="E293" s="4" t="inlineStr"/>
       <c r="F293" s="4" t="inlineStr"/>
-      <c r="G293" s="4" t="inlineStr">
-        <is>
-          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
-        </is>
-      </c>
+      <c r="G293" s="4" t="inlineStr"/>
     </row>
     <row r="294">
+      <c r="A294" s="5" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>بلامون</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr"/>
@@ -4827,9 +4971,10 @@
       <c r="G294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
+      <c r="A295" s="5" t="n"/>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>الرياض</t>
+          <t>الكنتاوي</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr"/>
@@ -4839,9 +4984,10 @@
       <c r="G295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
+      <c r="A296" s="6" t="n"/>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>سيدي سالم</t>
+          <t>الضواحي</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr"/>
@@ -4851,9 +4997,14 @@
       <c r="G296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>الحامول</t>
+          <t>شرم الشيخ</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr"/>
@@ -4863,9 +5014,10 @@
       <c r="G297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
+      <c r="A298" s="5" t="n"/>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>برج البرلس</t>
+          <t>داهب</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr"/>
@@ -4875,9 +5027,10 @@
       <c r="G298" s="4" t="inlineStr"/>
     </row>
     <row r="299">
+      <c r="A299" s="5" t="n"/>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>مطوبس</t>
+          <t>نويبع</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr"/>
@@ -4887,9 +5040,10 @@
       <c r="G299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
+      <c r="A300" s="5" t="n"/>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>المحمودية</t>
+          <t>سانت كاترين</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr"/>
@@ -4899,9 +5053,10 @@
       <c r="G300" s="4" t="inlineStr"/>
     </row>
     <row r="301">
+      <c r="A301" s="5" t="n"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>بيلا</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr"/>
@@ -4911,14 +5066,10 @@
       <c r="G301" s="4" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A302" s="5" t="n"/>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>مطروح</t>
+          <t>رأس محمد</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr"/>
@@ -4928,14 +5079,10 @@
       <c r="G302" s="4" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A303" s="5" t="n"/>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>سيوه</t>
+          <t>أم سيد</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr"/>
@@ -4945,14 +5092,10 @@
       <c r="G303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A304" s="6" t="n"/>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>السلوم</t>
+          <t>مدينة شرم الشيخ</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr"/>
@@ -4964,12 +5107,12 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>مطروح</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>سيدي براني</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr"/>
@@ -4979,14 +5122,10 @@
       <c r="G305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A306" s="5" t="n"/>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>العلمين</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr"/>
@@ -4996,14 +5135,10 @@
       <c r="G306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A307" s="5" t="n"/>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>مارينا</t>
+          <t>واحة الفيوم</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr"/>
@@ -5013,14 +5148,10 @@
       <c r="G307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A308" s="5" t="n"/>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>توريدو</t>
+          <t>وادي حوف</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr"/>
@@ -5030,14 +5161,10 @@
       <c r="G308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A309" s="5" t="n"/>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>جنوب سيوه</t>
+          <t>عين سخنة</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr"/>
@@ -5047,14 +5174,10 @@
       <c r="G309" s="4" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A310" s="5" t="n"/>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>شمال سيوه</t>
+          <t>الطور</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr"/>
@@ -5064,14 +5187,10 @@
       <c r="G310" s="4" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A311" s="5" t="n"/>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>كشته</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr"/>
@@ -5080,16 +5199,1074 @@
       <c r="F311" s="4" t="inlineStr"/>
       <c r="G311" s="4" t="inlineStr"/>
     </row>
+    <row r="312">
+      <c r="A312" s="6" t="n"/>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>المقطم</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr"/>
+      <c r="D312" s="4" t="inlineStr"/>
+      <c r="E312" s="4" t="inlineStr"/>
+      <c r="F312" s="4" t="inlineStr"/>
+      <c r="G312" s="4" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>مركز حلم ابني للتخاطب</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr"/>
+      <c r="E313" s="4" t="inlineStr"/>
+      <c r="F313" s="4" t="inlineStr"/>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>دمياط ودمياط الجديدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="n"/>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>دمياط الجديدة</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr"/>
+      <c r="D314" s="4" t="inlineStr"/>
+      <c r="E314" s="4" t="inlineStr"/>
+      <c r="F314" s="4" t="inlineStr"/>
+      <c r="G314" s="4" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="n"/>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>بورت فؤاد</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr"/>
+      <c r="D315" s="4" t="inlineStr"/>
+      <c r="E315" s="4" t="inlineStr"/>
+      <c r="F315" s="4" t="inlineStr"/>
+      <c r="G315" s="4" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="n"/>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>كفر البطة</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr"/>
+      <c r="D316" s="4" t="inlineStr"/>
+      <c r="E316" s="4" t="inlineStr"/>
+      <c r="F316" s="4" t="inlineStr"/>
+      <c r="G316" s="4" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="n"/>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>كفر سعيد</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr"/>
+      <c r="D317" s="4" t="inlineStr"/>
+      <c r="E317" s="4" t="inlineStr"/>
+      <c r="F317" s="4" t="inlineStr"/>
+      <c r="G317" s="4" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="n"/>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>الروضة</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr"/>
+      <c r="D318" s="4" t="inlineStr"/>
+      <c r="E318" s="4" t="inlineStr"/>
+      <c r="F318" s="4" t="inlineStr"/>
+      <c r="G318" s="4" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="n"/>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>الزرقا</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr"/>
+      <c r="D319" s="4" t="inlineStr"/>
+      <c r="E319" s="4" t="inlineStr"/>
+      <c r="F319" s="4" t="inlineStr"/>
+      <c r="G319" s="4" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="n"/>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>فارسكور</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr"/>
+      <c r="D320" s="4" t="inlineStr"/>
+      <c r="E320" s="4" t="inlineStr"/>
+      <c r="F320" s="4" t="inlineStr"/>
+      <c r="G320" s="4" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="6" t="n"/>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>رومانية</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr"/>
+      <c r="D321" s="4" t="inlineStr"/>
+      <c r="E321" s="4" t="inlineStr"/>
+      <c r="F321" s="4" t="inlineStr"/>
+      <c r="G321" s="4" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>شمال سيناء</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>العريش</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش للتخاطب</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr"/>
+      <c r="E322" s="4" t="inlineStr"/>
+      <c r="F322" s="4" t="inlineStr"/>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="n"/>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب رفح</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr"/>
+      <c r="E323" s="4" t="inlineStr"/>
+      <c r="F323" s="4" t="inlineStr"/>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="n"/>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="inlineStr"/>
+      <c r="E324" s="4" t="inlineStr"/>
+      <c r="F324" s="4" t="inlineStr"/>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="n"/>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>بئر العبد</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr"/>
+      <c r="D325" s="4" t="inlineStr"/>
+      <c r="E325" s="4" t="inlineStr"/>
+      <c r="F325" s="4" t="inlineStr"/>
+      <c r="G325" s="4" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="n"/>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>القنطرة، سيناء</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr"/>
+      <c r="D326" s="4" t="inlineStr"/>
+      <c r="E326" s="4" t="inlineStr"/>
+      <c r="F326" s="4" t="inlineStr"/>
+      <c r="G326" s="4" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="n"/>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>نخل</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr"/>
+      <c r="D327" s="4" t="inlineStr"/>
+      <c r="E327" s="4" t="inlineStr"/>
+      <c r="F327" s="4" t="inlineStr"/>
+      <c r="G327" s="4" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="n"/>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>جديدة، حسنة</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr"/>
+      <c r="D328" s="4" t="inlineStr"/>
+      <c r="E328" s="4" t="inlineStr"/>
+      <c r="F328" s="4" t="inlineStr"/>
+      <c r="G328" s="4" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="n"/>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>دهب الشرقية</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr"/>
+      <c r="D329" s="4" t="inlineStr"/>
+      <c r="E329" s="4" t="inlineStr"/>
+      <c r="F329" s="4" t="inlineStr"/>
+      <c r="G329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="6" t="n"/>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>طابا</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr"/>
+      <c r="D330" s="4" t="inlineStr"/>
+      <c r="E330" s="4" t="inlineStr"/>
+      <c r="F330" s="4" t="inlineStr"/>
+      <c r="G330" s="4" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمدينة العمال</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr"/>
+      <c r="E331" s="4" t="inlineStr"/>
+      <c r="F331" s="4" t="inlineStr"/>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>مدينة العمال، قنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="n"/>
+      <c r="B332" s="6" t="n"/>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب حجير خزام</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="inlineStr"/>
+      <c r="E332" s="4" t="inlineStr"/>
+      <c r="F332" s="4" t="inlineStr"/>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="n"/>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>نجع حمادي</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr"/>
+      <c r="D333" s="4" t="inlineStr"/>
+      <c r="E333" s="4" t="inlineStr"/>
+      <c r="F333" s="4" t="inlineStr"/>
+      <c r="G333" s="4" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="n"/>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>دندرة</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr"/>
+      <c r="D334" s="4" t="inlineStr"/>
+      <c r="E334" s="4" t="inlineStr"/>
+      <c r="F334" s="4" t="inlineStr"/>
+      <c r="G334" s="4" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="n"/>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>أبيدوس</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr"/>
+      <c r="D335" s="4" t="inlineStr"/>
+      <c r="E335" s="4" t="inlineStr"/>
+      <c r="F335" s="4" t="inlineStr"/>
+      <c r="G335" s="4" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="n"/>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>قفطي</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr"/>
+      <c r="D336" s="4" t="inlineStr"/>
+      <c r="E336" s="4" t="inlineStr"/>
+      <c r="F336" s="4" t="inlineStr"/>
+      <c r="G336" s="4" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="n"/>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>أخميم</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr"/>
+      <c r="D337" s="4" t="inlineStr"/>
+      <c r="E337" s="4" t="inlineStr"/>
+      <c r="F337" s="4" t="inlineStr"/>
+      <c r="G337" s="4" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="n"/>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>سوهاج القديمة</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr"/>
+      <c r="D338" s="4" t="inlineStr"/>
+      <c r="E338" s="4" t="inlineStr"/>
+      <c r="F338" s="4" t="inlineStr"/>
+      <c r="G338" s="4" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="n"/>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>النجع البحري</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr"/>
+      <c r="D339" s="4" t="inlineStr"/>
+      <c r="E339" s="4" t="inlineStr"/>
+      <c r="F339" s="4" t="inlineStr"/>
+      <c r="G339" s="4" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="6" t="n"/>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>الشنقي</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr"/>
+      <c r="D340" s="4" t="inlineStr"/>
+      <c r="E340" s="4" t="inlineStr"/>
+      <c r="F340" s="4" t="inlineStr"/>
+      <c r="G340" s="4" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الشيخ للتخاطب</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr"/>
+      <c r="E341" s="4" t="inlineStr"/>
+      <c r="F341" s="4" t="inlineStr"/>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="n"/>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr"/>
+      <c r="E342" s="4" t="inlineStr"/>
+      <c r="F342" s="4" t="inlineStr"/>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="n"/>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>بلامون</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr"/>
+      <c r="D343" s="4" t="inlineStr"/>
+      <c r="E343" s="4" t="inlineStr"/>
+      <c r="F343" s="4" t="inlineStr"/>
+      <c r="G343" s="4" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="n"/>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr"/>
+      <c r="D344" s="4" t="inlineStr"/>
+      <c r="E344" s="4" t="inlineStr"/>
+      <c r="F344" s="4" t="inlineStr"/>
+      <c r="G344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="n"/>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>سيدي سالم</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr"/>
+      <c r="D345" s="4" t="inlineStr"/>
+      <c r="E345" s="4" t="inlineStr"/>
+      <c r="F345" s="4" t="inlineStr"/>
+      <c r="G345" s="4" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="n"/>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>الحامول</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr"/>
+      <c r="D346" s="4" t="inlineStr"/>
+      <c r="E346" s="4" t="inlineStr"/>
+      <c r="F346" s="4" t="inlineStr"/>
+      <c r="G346" s="4" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="n"/>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>برج البرلس</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr"/>
+      <c r="D347" s="4" t="inlineStr"/>
+      <c r="E347" s="4" t="inlineStr"/>
+      <c r="F347" s="4" t="inlineStr"/>
+      <c r="G347" s="4" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="n"/>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>مطوبس</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr"/>
+      <c r="D348" s="4" t="inlineStr"/>
+      <c r="E348" s="4" t="inlineStr"/>
+      <c r="F348" s="4" t="inlineStr"/>
+      <c r="G348" s="4" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="n"/>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>المحمودية</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr"/>
+      <c r="D349" s="4" t="inlineStr"/>
+      <c r="E349" s="4" t="inlineStr"/>
+      <c r="F349" s="4" t="inlineStr"/>
+      <c r="G349" s="4" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="6" t="n"/>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>بيلا</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr"/>
+      <c r="D350" s="4" t="inlineStr"/>
+      <c r="E350" s="4" t="inlineStr"/>
+      <c r="F350" s="4" t="inlineStr"/>
+      <c r="G350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr"/>
+      <c r="D351" s="4" t="inlineStr"/>
+      <c r="E351" s="4" t="inlineStr"/>
+      <c r="F351" s="4" t="inlineStr"/>
+      <c r="G351" s="4" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>سيوه</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr"/>
+      <c r="D352" s="4" t="inlineStr"/>
+      <c r="E352" s="4" t="inlineStr"/>
+      <c r="F352" s="4" t="inlineStr"/>
+      <c r="G352" s="4" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>السلوم</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr"/>
+      <c r="D353" s="4" t="inlineStr"/>
+      <c r="E353" s="4" t="inlineStr"/>
+      <c r="F353" s="4" t="inlineStr"/>
+      <c r="G353" s="4" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>سيدي براني</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr"/>
+      <c r="D354" s="4" t="inlineStr"/>
+      <c r="E354" s="4" t="inlineStr"/>
+      <c r="F354" s="4" t="inlineStr"/>
+      <c r="G354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>العلمين</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr"/>
+      <c r="D355" s="4" t="inlineStr"/>
+      <c r="E355" s="4" t="inlineStr"/>
+      <c r="F355" s="4" t="inlineStr"/>
+      <c r="G355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>مارينا</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr"/>
+      <c r="D356" s="4" t="inlineStr"/>
+      <c r="E356" s="4" t="inlineStr"/>
+      <c r="F356" s="4" t="inlineStr"/>
+      <c r="G356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>توريدو</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr"/>
+      <c r="D357" s="4" t="inlineStr"/>
+      <c r="E357" s="4" t="inlineStr"/>
+      <c r="F357" s="4" t="inlineStr"/>
+      <c r="G357" s="4" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>جنوب سيوه</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr"/>
+      <c r="D358" s="4" t="inlineStr"/>
+      <c r="E358" s="4" t="inlineStr"/>
+      <c r="F358" s="4" t="inlineStr"/>
+      <c r="G358" s="4" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>شمال سيوه</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr"/>
+      <c r="D359" s="4" t="inlineStr"/>
+      <c r="E359" s="4" t="inlineStr"/>
+      <c r="F359" s="4" t="inlineStr"/>
+      <c r="G359" s="4" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>كشته</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr"/>
+      <c r="D360" s="4" t="inlineStr"/>
+      <c r="E360" s="4" t="inlineStr"/>
+      <c r="F360" s="4" t="inlineStr"/>
+      <c r="G360" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="A182:A186"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A189:A191"/>
-    <mergeCell ref="A198:A200"/>
-    <mergeCell ref="A187:A188"/>
+  <mergeCells count="313">
+    <mergeCell ref="B6"/>
+    <mergeCell ref="B133"/>
+    <mergeCell ref="B204"/>
+    <mergeCell ref="B356"/>
+    <mergeCell ref="B4"/>
+    <mergeCell ref="B75"/>
+    <mergeCell ref="B135"/>
+    <mergeCell ref="B306"/>
+    <mergeCell ref="B62"/>
+    <mergeCell ref="B72"/>
+    <mergeCell ref="A290:A296"/>
+    <mergeCell ref="B291"/>
+    <mergeCell ref="B70"/>
+    <mergeCell ref="B293"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="B322"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="B88"/>
+    <mergeCell ref="B82"/>
+    <mergeCell ref="B152:B156"/>
+    <mergeCell ref="B185:B188"/>
+    <mergeCell ref="B19"/>
+    <mergeCell ref="B146"/>
+    <mergeCell ref="B317"/>
+    <mergeCell ref="B217"/>
+    <mergeCell ref="A259:A270"/>
+    <mergeCell ref="B83"/>
+    <mergeCell ref="B344"/>
+    <mergeCell ref="B319"/>
+    <mergeCell ref="A178:A227"/>
+    <mergeCell ref="B123"/>
+    <mergeCell ref="B221"/>
+    <mergeCell ref="B110"/>
+    <mergeCell ref="B141"/>
+    <mergeCell ref="B248"/>
+    <mergeCell ref="B297"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="B235"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B331:B332"/>
+    <mergeCell ref="B299"/>
+    <mergeCell ref="B78"/>
+    <mergeCell ref="B249"/>
+    <mergeCell ref="B243"/>
+    <mergeCell ref="A331:A340"/>
+    <mergeCell ref="B314"/>
+    <mergeCell ref="A247:A258"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B325"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B25"/>
+    <mergeCell ref="B327"/>
+    <mergeCell ref="B149"/>
+    <mergeCell ref="B220"/>
+    <mergeCell ref="B247"/>
+    <mergeCell ref="B262"/>
+    <mergeCell ref="B38"/>
+    <mergeCell ref="A271:A279"/>
+    <mergeCell ref="B84"/>
+    <mergeCell ref="B338"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B313"/>
+    <mergeCell ref="B104"/>
+    <mergeCell ref="B79"/>
+    <mergeCell ref="B315"/>
+    <mergeCell ref="B302"/>
+    <mergeCell ref="B81"/>
+    <mergeCell ref="B252"/>
+    <mergeCell ref="B210"/>
+    <mergeCell ref="B318"/>
+    <mergeCell ref="B189:B190"/>
+    <mergeCell ref="B170"/>
+    <mergeCell ref="B157"/>
+    <mergeCell ref="B328"/>
+    <mergeCell ref="B333"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B172"/>
+    <mergeCell ref="B28"/>
+    <mergeCell ref="B99"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B257"/>
+    <mergeCell ref="B30"/>
+    <mergeCell ref="A115:A128"/>
+    <mergeCell ref="B265"/>
+    <mergeCell ref="B54"/>
+    <mergeCell ref="B125"/>
+    <mergeCell ref="B323"/>
+    <mergeCell ref="B176"/>
+    <mergeCell ref="B120"/>
+    <mergeCell ref="B147"/>
+    <mergeCell ref="B245"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B359"/>
+    <mergeCell ref="B207"/>
+    <mergeCell ref="B334"/>
+    <mergeCell ref="B113"/>
+    <mergeCell ref="B173"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="B100"/>
+    <mergeCell ref="B271"/>
+    <mergeCell ref="B336"/>
+    <mergeCell ref="B31"/>
+    <mergeCell ref="B202"/>
+    <mergeCell ref="B102"/>
+    <mergeCell ref="B273"/>
+    <mergeCell ref="B232:B234"/>
+    <mergeCell ref="B39"/>
+    <mergeCell ref="B191"/>
+    <mergeCell ref="B349"/>
+    <mergeCell ref="B255"/>
+    <mergeCell ref="B226"/>
+    <mergeCell ref="B49"/>
+    <mergeCell ref="B192"/>
+    <mergeCell ref="A280:A289"/>
+    <mergeCell ref="B284"/>
+    <mergeCell ref="B222"/>
+    <mergeCell ref="A313:A321"/>
+    <mergeCell ref="B63"/>
+    <mergeCell ref="B197"/>
+    <mergeCell ref="B50"/>
+    <mergeCell ref="A57:A65"/>
+    <mergeCell ref="B286"/>
+    <mergeCell ref="B261"/>
+    <mergeCell ref="B27"/>
+    <mergeCell ref="B337"/>
+    <mergeCell ref="B352"/>
+    <mergeCell ref="B103"/>
+    <mergeCell ref="B174"/>
+    <mergeCell ref="B205"/>
+    <mergeCell ref="B339"/>
+    <mergeCell ref="B118"/>
+    <mergeCell ref="A66:A76"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="B169"/>
+    <mergeCell ref="B355"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B129"/>
+    <mergeCell ref="B134"/>
+    <mergeCell ref="B194"/>
+    <mergeCell ref="B121"/>
+    <mergeCell ref="B292"/>
+    <mergeCell ref="B357"/>
+    <mergeCell ref="B71"/>
+    <mergeCell ref="B131"/>
+    <mergeCell ref="B236"/>
+    <mergeCell ref="B307"/>
+    <mergeCell ref="B58"/>
+    <mergeCell ref="B52"/>
+    <mergeCell ref="B223"/>
+    <mergeCell ref="B294"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="B195"/>
+    <mergeCell ref="B60"/>
+    <mergeCell ref="B231"/>
+    <mergeCell ref="B287"/>
+    <mergeCell ref="B358"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B53"/>
+    <mergeCell ref="A341:A350"/>
+    <mergeCell ref="A152:A166"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B241"/>
+    <mergeCell ref="B124"/>
+    <mergeCell ref="B178:B184"/>
+    <mergeCell ref="B142"/>
+    <mergeCell ref="B80"/>
+    <mergeCell ref="B213"/>
+    <mergeCell ref="B305"/>
+    <mergeCell ref="B126"/>
+    <mergeCell ref="B218"/>
+    <mergeCell ref="B242"/>
+    <mergeCell ref="B46"/>
+    <mergeCell ref="B282"/>
+    <mergeCell ref="B48"/>
+    <mergeCell ref="B219"/>
+    <mergeCell ref="B346"/>
+    <mergeCell ref="A297:A304"/>
+    <mergeCell ref="B8"/>
+    <mergeCell ref="B73"/>
+    <mergeCell ref="B10"/>
+    <mergeCell ref="B308"/>
+    <mergeCell ref="B74"/>
+    <mergeCell ref="B68"/>
+    <mergeCell ref="B201"/>
+    <mergeCell ref="B239"/>
+    <mergeCell ref="B310"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="B203"/>
+    <mergeCell ref="B150"/>
+    <mergeCell ref="B326"/>
+    <mergeCell ref="B215"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="B263"/>
+    <mergeCell ref="B244"/>
+    <mergeCell ref="A167:A177"/>
+    <mergeCell ref="B283"/>
+    <mergeCell ref="B87"/>
+    <mergeCell ref="B298"/>
+    <mergeCell ref="B285"/>
+    <mergeCell ref="B64"/>
+    <mergeCell ref="B51"/>
+    <mergeCell ref="B163"/>
+    <mergeCell ref="B309"/>
+    <mergeCell ref="B165"/>
+    <mergeCell ref="B140"/>
+    <mergeCell ref="B311"/>
+    <mergeCell ref="B238"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B77"/>
+    <mergeCell ref="B253"/>
+    <mergeCell ref="B240"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="B29"/>
+    <mergeCell ref="B158"/>
+    <mergeCell ref="B329"/>
+    <mergeCell ref="B316"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="B266"/>
+    <mergeCell ref="B89"/>
+    <mergeCell ref="B198:B200"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="B26"/>
+    <mergeCell ref="B97"/>
+    <mergeCell ref="B268"/>
+    <mergeCell ref="B324"/>
+    <mergeCell ref="B224"/>
+    <mergeCell ref="B90"/>
+    <mergeCell ref="B148"/>
+    <mergeCell ref="B250"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="B254"/>
+    <mergeCell ref="B143"/>
+    <mergeCell ref="B281"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="B85"/>
+    <mergeCell ref="B256"/>
+    <mergeCell ref="A137:A151"/>
+    <mergeCell ref="B160:B162"/>
+    <mergeCell ref="B159"/>
+    <mergeCell ref="B272"/>
+    <mergeCell ref="B111"/>
+    <mergeCell ref="B98"/>
+    <mergeCell ref="B225"/>
+    <mergeCell ref="B274"/>
+    <mergeCell ref="B175"/>
+    <mergeCell ref="B228:B230"/>
+    <mergeCell ref="A129:A136"/>
+    <mergeCell ref="B267"/>
+    <mergeCell ref="B269"/>
+    <mergeCell ref="B251"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="B216"/>
+    <mergeCell ref="B343"/>
+    <mergeCell ref="A92:A114"/>
+    <mergeCell ref="B280"/>
+    <mergeCell ref="B47"/>
+    <mergeCell ref="B351"/>
+    <mergeCell ref="B345"/>
+    <mergeCell ref="B59"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="B193"/>
+    <mergeCell ref="B264"/>
+    <mergeCell ref="B320"/>
+    <mergeCell ref="B295"/>
+    <mergeCell ref="B86"/>
+    <mergeCell ref="B101"/>
+    <mergeCell ref="A77:A91"/>
+    <mergeCell ref="B211"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="B300"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B275"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="B164"/>
+    <mergeCell ref="B335"/>
+    <mergeCell ref="B212"/>
+    <mergeCell ref="A322:A330"/>
+    <mergeCell ref="B206"/>
+    <mergeCell ref="B277"/>
+    <mergeCell ref="B130"/>
+    <mergeCell ref="A33:A56"/>
+    <mergeCell ref="B117"/>
+    <mergeCell ref="B353"/>
+    <mergeCell ref="B61"/>
+    <mergeCell ref="B132"/>
+    <mergeCell ref="B119"/>
+    <mergeCell ref="B290"/>
+    <mergeCell ref="B69"/>
+    <mergeCell ref="B196"/>
+    <mergeCell ref="B112"/>
+    <mergeCell ref="B354"/>
+    <mergeCell ref="B288"/>
+    <mergeCell ref="B348"/>
+    <mergeCell ref="B127"/>
+    <mergeCell ref="B237"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="B3"/>
+    <mergeCell ref="A228:A246"/>
+    <mergeCell ref="B301"/>
+    <mergeCell ref="B122"/>
+    <mergeCell ref="B276"/>
+    <mergeCell ref="B43"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B214"/>
+    <mergeCell ref="A305:A312"/>
+    <mergeCell ref="B341"/>
+    <mergeCell ref="B347"/>
+    <mergeCell ref="B303"/>
+    <mergeCell ref="B278"/>
+    <mergeCell ref="B57"/>
+    <mergeCell ref="B171"/>
+    <mergeCell ref="B342"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Egyptian_Speech_Therapy_Centers.xlsx
+++ b/Egyptian_Speech_Therapy_Centers.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,15 @@
     <font>
       <name val="Arial"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +136,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G360"/>
+  <dimension ref="A1:G387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3992,427 +4010,552 @@
       <c r="G227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>القليوبية</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب برج مكة</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr"/>
-      <c r="E228" s="4" t="inlineStr"/>
-      <c r="F228" s="4" t="inlineStr"/>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t>شارع جميل أمام بنك القاهرة</t>
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>القاهرة</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل وصعوبات التعلم - فرع جديد</t>
+        </is>
+      </c>
+      <c r="C228" s="8" t="inlineStr"/>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr"/>
+      <c r="F228" s="8" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
-      <c r="B229" s="5" t="n"/>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الجزار</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr"/>
-      <c r="E229" s="4" t="inlineStr"/>
-      <c r="F229" s="4" t="inlineStr"/>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>مركز تخاطب البر والتقوى</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr"/>
+      <c r="D229" s="9" t="inlineStr"/>
+      <c r="E229" s="9" t="inlineStr"/>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>104 برج الأوقاف، شارع ابن سندر، سرايا القبة، القاهرة</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="n"/>
-      <c r="B230" s="6" t="n"/>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العمار</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr"/>
-      <c r="E230" s="4" t="inlineStr"/>
-      <c r="F230" s="4" t="inlineStr"/>
-      <c r="G230" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
+      <c r="A230" s="6" t="n"/>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>بيت التمريض</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr"/>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>201201120500</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr"/>
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>متخصص في التخاطب وتعديل السلوك</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="n"/>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>قليوب</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr"/>
-      <c r="D231" s="4" t="inlineStr"/>
-      <c r="E231" s="4" t="inlineStr"/>
-      <c r="F231" s="4" t="inlineStr"/>
-      <c r="G231" s="4" t="inlineStr"/>
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>المركز الذهبي التخصصي (GSC)</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr"/>
+      <c r="D231" s="9" t="inlineStr"/>
+      <c r="E231" s="9" t="inlineStr"/>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>مدينة نصر، متخصص في التخاطب وتعديل السلوك</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>شبرا الخيمة</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="D232" s="4" t="inlineStr"/>
-      <c r="E232" s="4" t="inlineStr"/>
-      <c r="F232" s="4" t="inlineStr"/>
-      <c r="G232" s="4" t="inlineStr">
-        <is>
-          <t>75 شارع حنفي الشيخوني</t>
+      <c r="B232" s="8" t="inlineStr">
+        <is>
+          <t>مركز Speak للتخاطب</t>
+        </is>
+      </c>
+      <c r="C232" s="8" t="inlineStr"/>
+      <c r="D232" s="9" t="inlineStr"/>
+      <c r="E232" s="9" t="inlineStr"/>
+      <c r="F232" s="8" t="inlineStr">
+        <is>
+          <t>زهراء مدينة نصر، المرحلة الأولى، بجوار مسجد النور</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
-      <c r="B233" s="5" t="n"/>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>مركز النور الهدى الطبي</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="inlineStr"/>
-      <c r="E233" s="4" t="inlineStr"/>
-      <c r="F233" s="4" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr">
-        <is>
-          <t>شارع محمد القطان</t>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>مركز الزهراء للتخاطب</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr"/>
+      <c r="D233" s="9" t="inlineStr"/>
+      <c r="E233" s="9" t="inlineStr"/>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
-      <c r="B234" s="6" t="n"/>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>مركز تواصل للتخاطب</t>
-        </is>
-      </c>
-      <c r="D234" s="4" t="inlineStr"/>
-      <c r="E234" s="4" t="inlineStr"/>
-      <c r="F234" s="4" t="inlineStr"/>
-      <c r="G234" s="4" t="inlineStr">
-        <is>
-          <t>2 شارع أحمد عبد ربه</t>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C234" s="8" t="inlineStr"/>
+      <c r="D234" s="9" t="inlineStr"/>
+      <c r="E234" s="9" t="inlineStr"/>
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>شارع مصطفى النحاس، فوق التوحيد والنور</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="n"/>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>الخانكة</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="inlineStr"/>
-      <c r="D235" s="4" t="inlineStr"/>
-      <c r="E235" s="4" t="inlineStr"/>
-      <c r="F235" s="4" t="inlineStr"/>
-      <c r="G235" s="4" t="inlineStr"/>
+      <c r="A235" s="6" t="n"/>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب - فرع مدينة نصر</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr"/>
+      <c r="D235" s="9" t="inlineStr"/>
+      <c r="E235" s="9" t="inlineStr"/>
+      <c r="F235" s="8" t="inlineStr">
+        <is>
+          <t>مدينة نصر</t>
+        </is>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="n"/>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>رمسيس</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr"/>
-      <c r="D236" s="4" t="inlineStr"/>
-      <c r="E236" s="4" t="inlineStr"/>
-      <c r="F236" s="4" t="inlineStr"/>
-      <c r="G236" s="4" t="inlineStr"/>
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل - فرع مصر الجديدة</t>
+        </is>
+      </c>
+      <c r="C236" s="8" t="inlineStr"/>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr"/>
+      <c r="F236" s="8" t="inlineStr">
+        <is>
+          <t>مصر الجديدة</t>
+        </is>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="n"/>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>مدينة 10 رمضان</t>
-        </is>
-      </c>
-      <c r="C237" s="4" t="inlineStr"/>
-      <c r="D237" s="4" t="inlineStr"/>
-      <c r="E237" s="4" t="inlineStr"/>
-      <c r="F237" s="4" t="inlineStr"/>
-      <c r="G237" s="4" t="inlineStr"/>
+      <c r="A237" s="6" t="n"/>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>المركز المصري الكندي - فرع النزهة</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr"/>
+      <c r="D237" s="9" t="inlineStr"/>
+      <c r="E237" s="9" t="inlineStr"/>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>14 شارع جمال الدين على، بجوار ملاهي السندباد</t>
+        </is>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n"/>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>الشيخ زايد</t>
-        </is>
-      </c>
-      <c r="C238" s="4" t="inlineStr"/>
-      <c r="D238" s="4" t="inlineStr"/>
-      <c r="E238" s="4" t="inlineStr"/>
-      <c r="F238" s="4" t="inlineStr"/>
-      <c r="G238" s="4" t="inlineStr"/>
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>المعادي</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>مركز كيور لجراحات الأذن والقوقعة والسمعيات والتخاطب</t>
+        </is>
+      </c>
+      <c r="C238" s="8" t="inlineStr"/>
+      <c r="D238" s="9" t="inlineStr"/>
+      <c r="E238" s="9" t="inlineStr"/>
+      <c r="F238" s="8" t="inlineStr">
+        <is>
+          <t>شارع النصر، تقاطع اللاسلكي، حي المعادي</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>القناطر الخيرية</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr"/>
-      <c r="D239" s="4" t="inlineStr"/>
-      <c r="E239" s="4" t="inlineStr"/>
-      <c r="F239" s="4" t="inlineStr"/>
-      <c r="G239" s="4" t="inlineStr"/>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>مركز الجنا للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr"/>
+      <c r="D239" s="9" t="inlineStr"/>
+      <c r="E239" s="9" t="inlineStr"/>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>شارع 76، المعادى</t>
+        </is>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="n"/>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>قها</t>
-        </is>
-      </c>
-      <c r="C240" s="4" t="inlineStr"/>
-      <c r="D240" s="4" t="inlineStr"/>
-      <c r="E240" s="4" t="inlineStr"/>
-      <c r="F240" s="4" t="inlineStr"/>
-      <c r="G240" s="4" t="inlineStr"/>
+      <c r="A240" s="6" t="n"/>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
+          <t>المركز المصري الكندي - فرع المعادي</t>
+        </is>
+      </c>
+      <c r="C240" s="8" t="inlineStr"/>
+      <c r="D240" s="9" t="inlineStr"/>
+      <c r="E240" s="9" t="inlineStr"/>
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>5/3 شارع اللاسلكي، بجوار شركة غاز مصر</t>
+        </is>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="n"/>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>الدقهلية</t>
-        </is>
-      </c>
-      <c r="C241" s="4" t="inlineStr"/>
-      <c r="D241" s="4" t="inlineStr"/>
-      <c r="E241" s="4" t="inlineStr"/>
-      <c r="F241" s="4" t="inlineStr"/>
-      <c r="G241" s="4" t="inlineStr"/>
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>مركز علمني للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr"/>
+      <c r="D241" s="9" t="inlineStr"/>
+      <c r="E241" s="9" t="inlineStr"/>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>8 عمارات منتصر، الدور الأرضي، بجوار مسجد عباد الرحمن</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="n"/>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>الجيزة</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr"/>
-      <c r="D242" s="4" t="inlineStr"/>
-      <c r="E242" s="4" t="inlineStr"/>
-      <c r="F242" s="4" t="inlineStr"/>
-      <c r="G242" s="4" t="inlineStr"/>
+      <c r="A242" s="7" t="inlineStr">
+        <is>
+          <t>روض الفرج</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t>مركز تخاطب المرح</t>
+        </is>
+      </c>
+      <c r="C242" s="8" t="inlineStr"/>
+      <c r="D242" s="9" t="inlineStr"/>
+      <c r="E242" s="9" t="inlineStr"/>
+      <c r="F242" s="8" t="inlineStr">
+        <is>
+          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا مصر</t>
+        </is>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="n"/>
-      <c r="B243" s="3" t="inlineStr">
-        <is>
-          <t>أوسيم</t>
-        </is>
-      </c>
-      <c r="C243" s="4" t="inlineStr"/>
-      <c r="D243" s="4" t="inlineStr"/>
-      <c r="E243" s="4" t="inlineStr"/>
-      <c r="F243" s="4" t="inlineStr"/>
-      <c r="G243" s="4" t="inlineStr"/>
+      <c r="A243" s="6" t="n"/>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr"/>
+      <c r="D243" s="9" t="inlineStr"/>
+      <c r="E243" s="9" t="inlineStr"/>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="n"/>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>طره</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr"/>
-      <c r="D244" s="4" t="inlineStr"/>
-      <c r="E244" s="4" t="inlineStr"/>
-      <c r="F244" s="4" t="inlineStr"/>
-      <c r="G244" s="4" t="inlineStr"/>
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>المطرية</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل بالمطرية</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr"/>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>01147626979</t>
+        </is>
+      </c>
+      <c r="E244" s="9" t="inlineStr"/>
+      <c r="F244" s="8" t="inlineStr">
+        <is>
+          <t>شارع منية مطر، بجوار محطة مترو المطرية</t>
+        </is>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="n"/>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>الخصوص</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr"/>
-      <c r="D245" s="4" t="inlineStr"/>
-      <c r="E245" s="4" t="inlineStr"/>
-      <c r="F245" s="4" t="inlineStr"/>
-      <c r="G245" s="4" t="inlineStr"/>
+      <c r="A245" s="7" t="inlineStr">
+        <is>
+          <t>الدقي</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع الدقي</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr"/>
+      <c r="D245" s="9" t="inlineStr"/>
+      <c r="E245" s="9" t="inlineStr"/>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>4 شارع Hussein Wassef، الدقي</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n"/>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>القنطرة</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr"/>
-      <c r="D246" s="4" t="inlineStr"/>
-      <c r="E246" s="4" t="inlineStr"/>
-      <c r="F246" s="4" t="inlineStr"/>
-      <c r="G246" s="4" t="inlineStr"/>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب - الدقي</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr"/>
+      <c r="D246" s="9" t="inlineStr"/>
+      <c r="E246" s="9" t="inlineStr"/>
+      <c r="F246" s="8" t="inlineStr">
+        <is>
+          <t>110 شارع التحرير، الدقي، أمام محطة مترو الدقي</t>
+        </is>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>المنوفية</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="inlineStr">
-        <is>
-          <t>شبين الكوم</t>
-        </is>
-      </c>
-      <c r="C247" s="4" t="inlineStr"/>
-      <c r="D247" s="4" t="inlineStr"/>
-      <c r="E247" s="4" t="inlineStr"/>
-      <c r="F247" s="4" t="inlineStr"/>
-      <c r="G247" s="4" t="inlineStr"/>
+      <c r="A247" s="7" t="inlineStr">
+        <is>
+          <t>الهرم</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>مركز هووب للتخاطب</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr"/>
+      <c r="D247" s="9" t="inlineStr"/>
+      <c r="E247" s="9" t="inlineStr"/>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>الهرم، متخصص في التخاطب وتنمية المهارات</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>منوف</t>
-        </is>
-      </c>
-      <c r="C248" s="4" t="inlineStr"/>
-      <c r="D248" s="4" t="inlineStr"/>
-      <c r="E248" s="4" t="inlineStr"/>
-      <c r="F248" s="4" t="inlineStr"/>
-      <c r="G248" s="4" t="inlineStr"/>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>مركز فرصة حياه للتأهيل للتخاطب وتنمية المهارات</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr"/>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>01030360536</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr"/>
+      <c r="F248" s="8" t="inlineStr">
+        <is>
+          <t>الهرم وفيصل</t>
+        </is>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="n"/>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>شبين القناطر</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr"/>
-      <c r="D249" s="4" t="inlineStr"/>
-      <c r="E249" s="4" t="inlineStr"/>
-      <c r="F249" s="4" t="inlineStr"/>
-      <c r="G249" s="4" t="inlineStr"/>
+      <c r="A249" s="6" t="n"/>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>مركز اشراقة للتخاطب - د/اسلام سالم</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>د/اسلام سالم</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr"/>
+      <c r="E249" s="9" t="inlineStr"/>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>شارع اللبيني، الهرم الرئيسي</t>
+        </is>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="n"/>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>مدينة السادات</t>
-        </is>
-      </c>
-      <c r="C250" s="4" t="inlineStr"/>
-      <c r="D250" s="4" t="inlineStr"/>
-      <c r="E250" s="4" t="inlineStr"/>
-      <c r="F250" s="4" t="inlineStr"/>
-      <c r="G250" s="4" t="inlineStr"/>
+      <c r="A250" s="7" t="inlineStr">
+        <is>
+          <t>النزهة</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب - فرع النزهة</t>
+        </is>
+      </c>
+      <c r="C250" s="8" t="inlineStr"/>
+      <c r="D250" s="9" t="inlineStr"/>
+      <c r="E250" s="9" t="inlineStr"/>
+      <c r="F250" s="8" t="inlineStr">
+        <is>
+          <t>النزهة</t>
+        </is>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="n"/>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>باقور</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr"/>
-      <c r="D251" s="4" t="inlineStr"/>
-      <c r="E251" s="4" t="inlineStr"/>
-      <c r="F251" s="4" t="inlineStr"/>
-      <c r="G251" s="4" t="inlineStr"/>
+      <c r="A251" s="6" t="n"/>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>نور الحياة للتخاطب</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr"/>
+      <c r="D251" s="9" t="inlineStr"/>
+      <c r="E251" s="9" t="inlineStr"/>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>شارع شبرا الخلفاوى، قسم الساحل</t>
+        </is>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="n"/>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>تلا</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="inlineStr"/>
-      <c r="D252" s="4" t="inlineStr"/>
-      <c r="E252" s="4" t="inlineStr"/>
-      <c r="F252" s="4" t="inlineStr"/>
-      <c r="G252" s="4" t="inlineStr"/>
+      <c r="A252" s="7" t="inlineStr">
+        <is>
+          <t>الزيتون</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
+          <t>مركز التخاطب الشامل - فرع الزيتون</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr"/>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>0222406301</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr"/>
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>حي الزيتون</t>
+        </is>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="n"/>
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>قويسنا</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="inlineStr"/>
-      <c r="D253" s="4" t="inlineStr"/>
-      <c r="E253" s="4" t="inlineStr"/>
-      <c r="F253" s="4" t="inlineStr"/>
-      <c r="G253" s="4" t="inlineStr"/>
+      <c r="A253" s="7" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>مركز الشمس للتخاطب - فرع عين شمس</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr"/>
+      <c r="D253" s="9" t="inlineStr"/>
+      <c r="E253" s="9" t="inlineStr"/>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>عين شمس</t>
+        </is>
+      </c>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="n"/>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>أشمون</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب أشمون للتخاطب</t>
-        </is>
-      </c>
-      <c r="D254" s="4" t="inlineStr"/>
-      <c r="E254" s="4" t="inlineStr"/>
-      <c r="F254" s="4" t="inlineStr"/>
-      <c r="G254" s="4" t="inlineStr">
-        <is>
-          <t>أشمون</t>
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>فيصل</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
+        <is>
+          <t>مركز فرصة حياه - فرع فيصل</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr"/>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>01030360536</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr"/>
+      <c r="F254" s="8" t="inlineStr">
+        <is>
+          <t>فيصل</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="n"/>
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>القليوبية</t>
+        </is>
+      </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>البرجايه</t>
-        </is>
-      </c>
-      <c r="C255" s="4" t="inlineStr"/>
+          <t>بنها</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب برج مكة</t>
+        </is>
+      </c>
       <c r="D255" s="4" t="inlineStr"/>
       <c r="E255" s="4" t="inlineStr"/>
       <c r="F255" s="4" t="inlineStr"/>
-      <c r="G255" s="4" t="inlineStr"/>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>شارع جميل أمام بنك القاهرة</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n"/>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
+      <c r="B256" s="5" t="n"/>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>مركز تخاطب وصعوبات تعلم</t>
+          <t>مركز شباب كفر الجزار</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr"/>
@@ -4420,28 +4563,32 @@
       <c r="F256" s="4" t="inlineStr"/>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>بركة السبع</t>
+          <t>بنها</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n"/>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>منوف الجديدة</t>
-        </is>
-      </c>
-      <c r="C257" s="4" t="inlineStr"/>
+      <c r="B257" s="6" t="n"/>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العمار</t>
+        </is>
+      </c>
       <c r="D257" s="4" t="inlineStr"/>
       <c r="E257" s="4" t="inlineStr"/>
       <c r="F257" s="4" t="inlineStr"/>
-      <c r="G257" s="4" t="inlineStr"/>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="n"/>
+      <c r="A258" s="5" t="n"/>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>قليوب</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr"/>
@@ -4451,19 +4598,15 @@
       <c r="G258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="A259" s="5" t="n"/>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>المنيا</t>
+          <t>شبرا الخيمة</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب بني أحمد للتخاطب</t>
+          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr"/>
@@ -4471,16 +4614,16 @@
       <c r="F259" s="4" t="inlineStr"/>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>المنيا</t>
+          <t>75 شارع حنفي الشيخوني</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
-      <c r="B260" s="6" t="n"/>
+      <c r="B260" s="5" t="n"/>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب مقوسة للتخاطب</t>
+          <t>مركز النور الهدى الطبي</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr"/>
@@ -4488,28 +4631,32 @@
       <c r="F260" s="4" t="inlineStr"/>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>المنيا</t>
+          <t>شارع محمد القطان</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n"/>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>سمالوط</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="inlineStr"/>
+      <c r="B261" s="6" t="n"/>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>مركز تواصل للتخاطب</t>
+        </is>
+      </c>
       <c r="D261" s="4" t="inlineStr"/>
       <c r="E261" s="4" t="inlineStr"/>
       <c r="F261" s="4" t="inlineStr"/>
-      <c r="G261" s="4" t="inlineStr"/>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>2 شارع أحمد عبد ربه</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>بني حسن</t>
+          <t>الخانكة</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr"/>
@@ -4522,7 +4669,7 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>هرموبوليس</t>
+          <t>رمسيس</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr"/>
@@ -4535,7 +4682,7 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>ملوي</t>
+          <t>مدينة 10 رمضان</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr"/>
@@ -4548,7 +4695,7 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>الشيخ زايد</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr"/>
@@ -4561,7 +4708,7 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>ديروط الشريف</t>
+          <t>القناطر الخيرية</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr"/>
@@ -4574,7 +4721,7 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>أبوقرقاص</t>
+          <t>قها</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr"/>
@@ -4587,7 +4734,7 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>الدقهلية</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr"/>
@@ -4600,7 +4747,7 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>بني مازن</t>
+          <t>الجيزة</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr"/>
@@ -4610,10 +4757,10 @@
       <c r="G269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="n"/>
+      <c r="A270" s="5" t="n"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>أوسيم</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr"/>
@@ -4623,56 +4770,36 @@
       <c r="G270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>الوادي الجديد</t>
-        </is>
-      </c>
+      <c r="A271" s="5" t="n"/>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب الخارجة للتخاطب</t>
-        </is>
-      </c>
+          <t>طره</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr"/>
       <c r="D271" s="4" t="inlineStr"/>
       <c r="E271" s="4" t="inlineStr"/>
       <c r="F271" s="4" t="inlineStr"/>
-      <c r="G271" s="4" t="inlineStr">
-        <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
+      <c r="G271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب باريس للتخاطب</t>
-        </is>
-      </c>
+          <t>الخصوص</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr"/>
       <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr"/>
       <c r="F272" s="4" t="inlineStr"/>
-      <c r="G272" s="4" t="inlineStr">
-        <is>
-          <t>باريس</t>
-        </is>
-      </c>
+      <c r="G272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="5" t="n"/>
+      <c r="A273" s="6" t="n"/>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>موط</t>
+          <t>القنطرة</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr"/>
@@ -4682,10 +4809,14 @@
       <c r="G273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="n"/>
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>المنوفية</t>
+        </is>
+      </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>بلاط</t>
+          <t>شبين الكوم</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr"/>
@@ -4698,7 +4829,7 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>فرافرة</t>
+          <t>منوف</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr"/>
@@ -4711,7 +4842,7 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>شبين القناطر</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr"/>
@@ -4724,7 +4855,7 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>مدينة السادات</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr"/>
@@ -4737,7 +4868,7 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>تينيدة</t>
+          <t>باقور</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr"/>
@@ -4747,10 +4878,10 @@
       <c r="G278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="n"/>
+      <c r="A279" s="5" t="n"/>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>دوش</t>
+          <t>تلا</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr"/>
@@ -4760,48 +4891,44 @@
       <c r="G279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="A280" s="5" t="n"/>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العبور للتخاطب</t>
-        </is>
-      </c>
+          <t>قويسنا</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr"/>
       <c r="D280" s="4" t="inlineStr"/>
       <c r="E280" s="4" t="inlineStr"/>
       <c r="F280" s="4" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="G280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr"/>
+          <t>أشمون</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب أشمون للتخاطب</t>
+        </is>
+      </c>
       <c r="D281" s="4" t="inlineStr"/>
       <c r="E281" s="4" t="inlineStr"/>
       <c r="F281" s="4" t="inlineStr"/>
-      <c r="G281" s="4" t="inlineStr"/>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>ساماستا</t>
+          <t>البرجايه</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr"/>
@@ -4814,20 +4941,28 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>إبشواي</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr"/>
+          <t>بركة السبع</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب وصعوبات تعلم</t>
+        </is>
+      </c>
       <c r="D283" s="4" t="inlineStr"/>
       <c r="E283" s="4" t="inlineStr"/>
       <c r="F283" s="4" t="inlineStr"/>
-      <c r="G283" s="4" t="inlineStr"/>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>الجندية</t>
+          <t>منوف الجديدة</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr"/>
@@ -4837,10 +4972,10 @@
       <c r="G284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="n"/>
+      <c r="A285" s="6" t="n"/>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>ناصر</t>
+          <t>كفر عبده</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr"/>
@@ -4850,36 +4985,52 @@
       <c r="G285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="n"/>
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>هواره</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="inlineStr"/>
+          <t>المنيا</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب بني أحمد للتخاطب</t>
+        </is>
+      </c>
       <c r="D286" s="4" t="inlineStr"/>
       <c r="E286" s="4" t="inlineStr"/>
       <c r="F286" s="4" t="inlineStr"/>
-      <c r="G286" s="4" t="inlineStr"/>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="n"/>
-      <c r="B287" s="3" t="inlineStr">
-        <is>
-          <t>موشية</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="inlineStr"/>
+      <c r="B287" s="6" t="n"/>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب مقوسة للتخاطب</t>
+        </is>
+      </c>
       <c r="D287" s="4" t="inlineStr"/>
       <c r="E287" s="4" t="inlineStr"/>
       <c r="F287" s="4" t="inlineStr"/>
-      <c r="G287" s="4" t="inlineStr"/>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>نصار البحرية</t>
+          <t>سمالوط</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr"/>
@@ -4889,10 +5040,10 @@
       <c r="G288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="n"/>
+      <c r="A289" s="5" t="n"/>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>أحمد حمزة</t>
+          <t>بني حسن</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr"/>
@@ -4902,14 +5053,10 @@
       <c r="G289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>بورسعيد</t>
-        </is>
-      </c>
+      <c r="A290" s="5" t="n"/>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>هرموبوليس</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr"/>
@@ -4922,7 +5069,7 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>بورفؤاد</t>
+          <t>ملوي</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr"/>
@@ -4935,7 +5082,7 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>الجميل</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr"/>
@@ -4948,7 +5095,7 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>الزهور</t>
+          <t>ديروط الشريف</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr"/>
@@ -4961,7 +5108,7 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>أبوقرقاص</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr"/>
@@ -4974,7 +5121,7 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>الكنتاوي</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr"/>
@@ -4984,10 +5131,10 @@
       <c r="G295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="n"/>
+      <c r="A296" s="5" t="n"/>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>الضواحي</t>
+          <t>بني مازن</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr"/>
@@ -4997,14 +5144,10 @@
       <c r="G296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>جنوب سيناء</t>
-        </is>
-      </c>
+      <c r="A297" s="6" t="n"/>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>شرم الشيخ</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr"/>
@@ -5014,36 +5157,56 @@
       <c r="G297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="n"/>
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>الوادي الجديد</t>
+        </is>
+      </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>داهب</t>
-        </is>
-      </c>
-      <c r="C298" s="4" t="inlineStr"/>
+          <t>الخارجة</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب الخارجة للتخاطب</t>
+        </is>
+      </c>
       <c r="D298" s="4" t="inlineStr"/>
       <c r="E298" s="4" t="inlineStr"/>
       <c r="F298" s="4" t="inlineStr"/>
-      <c r="G298" s="4" t="inlineStr"/>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>الخارجة</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>نويبع</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr"/>
+          <t>الداخلة</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب باريس للتخاطب</t>
+        </is>
+      </c>
       <c r="D299" s="4" t="inlineStr"/>
       <c r="E299" s="4" t="inlineStr"/>
       <c r="F299" s="4" t="inlineStr"/>
-      <c r="G299" s="4" t="inlineStr"/>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>سانت كاترين</t>
+          <t>موط</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr"/>
@@ -5056,7 +5219,7 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>بلاط</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr"/>
@@ -5069,7 +5232,7 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>رأس محمد</t>
+          <t>فرافرة</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr"/>
@@ -5082,7 +5245,7 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>أم سيد</t>
+          <t>باريس</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr"/>
@@ -5092,10 +5255,10 @@
       <c r="G303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="6" t="n"/>
+      <c r="A304" s="5" t="n"/>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>مدينة شرم الشيخ</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr"/>
@@ -5105,14 +5268,10 @@
       <c r="G304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
+      <c r="A305" s="5" t="n"/>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>حلوان</t>
+          <t>تينيدة</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr"/>
@@ -5122,10 +5281,10 @@
       <c r="G305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="5" t="n"/>
+      <c r="A306" s="6" t="n"/>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>دوش</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr"/>
@@ -5135,23 +5294,35 @@
       <c r="G306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="5" t="n"/>
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>واحة الفيوم</t>
-        </is>
-      </c>
-      <c r="C307" s="4" t="inlineStr"/>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العبور للتخاطب</t>
+        </is>
+      </c>
       <c r="D307" s="4" t="inlineStr"/>
       <c r="E307" s="4" t="inlineStr"/>
       <c r="F307" s="4" t="inlineStr"/>
-      <c r="G307" s="4" t="inlineStr"/>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>وادي حوف</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr"/>
@@ -5164,7 +5335,7 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>عين سخنة</t>
+          <t>ساماستا</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr"/>
@@ -5177,7 +5348,7 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>إبشواي</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr"/>
@@ -5190,7 +5361,7 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>الجندية</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr"/>
@@ -5200,10 +5371,10 @@
       <c r="G311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="6" t="n"/>
+      <c r="A312" s="5" t="n"/>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
+          <t>ناصر</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr"/>
@@ -5213,35 +5384,23 @@
       <c r="G312" s="4" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
+      <c r="A313" s="5" t="n"/>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr">
-        <is>
-          <t>مركز حلم ابني للتخاطب</t>
-        </is>
-      </c>
+          <t>هواره</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr"/>
       <c r="D313" s="4" t="inlineStr"/>
       <c r="E313" s="4" t="inlineStr"/>
       <c r="F313" s="4" t="inlineStr"/>
-      <c r="G313" s="4" t="inlineStr">
-        <is>
-          <t>دمياط ودمياط الجديدة</t>
-        </is>
-      </c>
+      <c r="G313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>دمياط الجديدة</t>
+          <t>موشية</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr"/>
@@ -5254,7 +5413,7 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>بورت فؤاد</t>
+          <t>نصار البحرية</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr"/>
@@ -5264,10 +5423,10 @@
       <c r="G315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="5" t="n"/>
+      <c r="A316" s="6" t="n"/>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>كفر البطة</t>
+          <t>أحمد حمزة</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr"/>
@@ -5277,10 +5436,14 @@
       <c r="G316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="n"/>
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>كفر سعيد</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr"/>
@@ -5293,7 +5456,7 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>بورفؤاد</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr"/>
@@ -5306,7 +5469,7 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>الزرقا</t>
+          <t>الجميل</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr"/>
@@ -5319,7 +5482,7 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>فارسكور</t>
+          <t>الزهور</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr"/>
@@ -5329,10 +5492,10 @@
       <c r="G320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="n"/>
+      <c r="A321" s="5" t="n"/>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>رومانية</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr"/>
@@ -5342,77 +5505,53 @@
       <c r="G321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>شمال سيناء</t>
-        </is>
-      </c>
+      <c r="A322" s="5" t="n"/>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>العريش</t>
-        </is>
-      </c>
-      <c r="C322" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش للتخاطب</t>
-        </is>
-      </c>
+          <t>الكنتاوي</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr"/>
       <c r="D322" s="4" t="inlineStr"/>
       <c r="E322" s="4" t="inlineStr"/>
       <c r="F322" s="4" t="inlineStr"/>
-      <c r="G322" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش</t>
-        </is>
-      </c>
+      <c r="G322" s="4" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="n"/>
+      <c r="A323" s="6" t="n"/>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>رفح</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب رفح</t>
-        </is>
-      </c>
+          <t>الضواحي</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr"/>
       <c r="D323" s="4" t="inlineStr"/>
       <c r="E323" s="4" t="inlineStr"/>
       <c r="F323" s="4" t="inlineStr"/>
-      <c r="G323" s="4" t="inlineStr">
-        <is>
-          <t>رفح</t>
-        </is>
-      </c>
+      <c r="G323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="n"/>
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
-      <c r="C324" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
-        </is>
-      </c>
+          <t>شرم الشيخ</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr"/>
       <c r="D324" s="4" t="inlineStr"/>
       <c r="E324" s="4" t="inlineStr"/>
       <c r="F324" s="4" t="inlineStr"/>
-      <c r="G324" s="4" t="inlineStr">
-        <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
+      <c r="G324" s="4" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>بئر العبد</t>
+          <t>داهب</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr"/>
@@ -5425,7 +5564,7 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>القنطرة، سيناء</t>
+          <t>نويبع</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr"/>
@@ -5438,7 +5577,7 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>نخل</t>
+          <t>سانت كاترين</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr"/>
@@ -5451,7 +5590,7 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>جديدة، حسنة</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr"/>
@@ -5464,7 +5603,7 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>دهب الشرقية</t>
+          <t>رأس محمد</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr"/>
@@ -5474,10 +5613,10 @@
       <c r="G329" s="4" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="6" t="n"/>
+      <c r="A330" s="5" t="n"/>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>أم سيد</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr"/>
@@ -5487,52 +5626,40 @@
       <c r="G330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="A331" s="6" t="n"/>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>قنا</t>
-        </is>
-      </c>
-      <c r="C331" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بمدينة العمال</t>
-        </is>
-      </c>
+          <t>مدينة شرم الشيخ</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr"/>
       <c r="D331" s="4" t="inlineStr"/>
       <c r="E331" s="4" t="inlineStr"/>
       <c r="F331" s="4" t="inlineStr"/>
-      <c r="G331" s="4" t="inlineStr">
-        <is>
-          <t>مدينة العمال، قنا</t>
-        </is>
-      </c>
+      <c r="G331" s="4" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="5" t="n"/>
-      <c r="B332" s="6" t="n"/>
-      <c r="C332" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب حجير خزام</t>
-        </is>
-      </c>
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr"/>
       <c r="D332" s="4" t="inlineStr"/>
       <c r="E332" s="4" t="inlineStr"/>
       <c r="F332" s="4" t="inlineStr"/>
-      <c r="G332" s="4" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="G332" s="4" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>نجع حمادي</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr"/>
@@ -5545,7 +5672,7 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>دندرة</t>
+          <t>واحة الفيوم</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr"/>
@@ -5558,7 +5685,7 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>أبيدوس</t>
+          <t>وادي حوف</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr"/>
@@ -5571,7 +5698,7 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>قفطي</t>
+          <t>عين سخنة</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr"/>
@@ -5584,7 +5711,7 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>أخميم</t>
+          <t>الطور</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr"/>
@@ -5597,7 +5724,7 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>سوهاج القديمة</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr"/>
@@ -5607,10 +5734,10 @@
       <c r="G338" s="4" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="5" t="n"/>
+      <c r="A339" s="6" t="n"/>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>النجع البحري</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr"/>
@@ -5620,69 +5747,61 @@
       <c r="G339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="6" t="n"/>
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>الشنقي</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="inlineStr"/>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>مركز حلم ابني للتخاطب</t>
+        </is>
+      </c>
       <c r="D340" s="4" t="inlineStr"/>
       <c r="E340" s="4" t="inlineStr"/>
       <c r="F340" s="4" t="inlineStr"/>
-      <c r="G340" s="4" t="inlineStr"/>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>دمياط ودمياط الجديدة</t>
+        </is>
+      </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="A341" s="5" t="n"/>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الشيخ للتخاطب</t>
-        </is>
-      </c>
+          <t>دمياط الجديدة</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr"/>
       <c r="D341" s="4" t="inlineStr"/>
       <c r="E341" s="4" t="inlineStr"/>
       <c r="F341" s="4" t="inlineStr"/>
-      <c r="G341" s="4" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
+      <c r="G341" s="4" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>دسوق</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
-        </is>
-      </c>
+          <t>بورت فؤاد</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr"/>
       <c r="D342" s="4" t="inlineStr"/>
       <c r="E342" s="4" t="inlineStr"/>
       <c r="F342" s="4" t="inlineStr"/>
-      <c r="G342" s="4" t="inlineStr">
-        <is>
-          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
-        </is>
-      </c>
+      <c r="G342" s="4" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>بلامون</t>
+          <t>كفر البطة</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr"/>
@@ -5695,7 +5814,7 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>الرياض</t>
+          <t>كفر سعيد</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr"/>
@@ -5708,7 +5827,7 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>سيدي سالم</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr"/>
@@ -5721,7 +5840,7 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>الحامول</t>
+          <t>الزرقا</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr"/>
@@ -5734,7 +5853,7 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>برج البرلس</t>
+          <t>فارسكور</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr"/>
@@ -5744,10 +5863,10 @@
       <c r="G347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="5" t="n"/>
+      <c r="A348" s="6" t="n"/>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>مطوبس</t>
+          <t>رومانية</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr"/>
@@ -5757,57 +5876,77 @@
       <c r="G348" s="4" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="5" t="n"/>
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>شمال سيناء</t>
+        </is>
+      </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>المحمودية</t>
-        </is>
-      </c>
-      <c r="C349" s="4" t="inlineStr"/>
+          <t>العريش</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش للتخاطب</t>
+        </is>
+      </c>
       <c r="D349" s="4" t="inlineStr"/>
       <c r="E349" s="4" t="inlineStr"/>
       <c r="F349" s="4" t="inlineStr"/>
-      <c r="G349" s="4" t="inlineStr"/>
+      <c r="G349" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش</t>
+        </is>
+      </c>
     </row>
     <row r="350">
-      <c r="A350" s="6" t="n"/>
+      <c r="A350" s="5" t="n"/>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>بيلا</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr"/>
+          <t>رفح</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب رفح</t>
+        </is>
+      </c>
       <c r="D350" s="4" t="inlineStr"/>
       <c r="E350" s="4" t="inlineStr"/>
       <c r="F350" s="4" t="inlineStr"/>
-      <c r="G350" s="4" t="inlineStr"/>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A351" s="5" t="n"/>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="C351" s="4" t="inlineStr"/>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
+        </is>
+      </c>
       <c r="D351" s="4" t="inlineStr"/>
       <c r="E351" s="4" t="inlineStr"/>
       <c r="F351" s="4" t="inlineStr"/>
-      <c r="G351" s="4" t="inlineStr"/>
+      <c r="G351" s="4" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A352" s="5" t="n"/>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>سيوه</t>
+          <t>بئر العبد</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr"/>
@@ -5817,14 +5956,10 @@
       <c r="G352" s="4" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A353" s="5" t="n"/>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>السلوم</t>
+          <t>القنطرة، سيناء</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr"/>
@@ -5834,14 +5969,10 @@
       <c r="G353" s="4" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A354" s="5" t="n"/>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>سيدي براني</t>
+          <t>نخل</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr"/>
@@ -5851,14 +5982,10 @@
       <c r="G354" s="4" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A355" s="5" t="n"/>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>العلمين</t>
+          <t>جديدة، حسنة</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr"/>
@@ -5868,14 +5995,10 @@
       <c r="G355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A356" s="5" t="n"/>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>مارينا</t>
+          <t>دهب الشرقية</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr"/>
@@ -5885,14 +6008,10 @@
       <c r="G356" s="4" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A357" s="6" t="n"/>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>توريدو</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr"/>
@@ -5904,46 +6023,50 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>مطروح</t>
+          <t>قنا</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>جنوب سيوه</t>
-        </is>
-      </c>
-      <c r="C358" s="4" t="inlineStr"/>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمدينة العمال</t>
+        </is>
+      </c>
       <c r="D358" s="4" t="inlineStr"/>
       <c r="E358" s="4" t="inlineStr"/>
       <c r="F358" s="4" t="inlineStr"/>
-      <c r="G358" s="4" t="inlineStr"/>
+      <c r="G358" s="4" t="inlineStr">
+        <is>
+          <t>مدينة العمال، قنا</t>
+        </is>
+      </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B359" s="3" t="inlineStr">
-        <is>
-          <t>شمال سيوه</t>
-        </is>
-      </c>
-      <c r="C359" s="4" t="inlineStr"/>
+      <c r="A359" s="5" t="n"/>
+      <c r="B359" s="6" t="n"/>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب حجير خزام</t>
+        </is>
+      </c>
       <c r="D359" s="4" t="inlineStr"/>
       <c r="E359" s="4" t="inlineStr"/>
       <c r="F359" s="4" t="inlineStr"/>
-      <c r="G359" s="4" t="inlineStr"/>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
+      <c r="A360" s="5" t="n"/>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>كشته</t>
+          <t>نجع حمادي</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr"/>
@@ -5951,6 +6074,417 @@
       <c r="E360" s="4" t="inlineStr"/>
       <c r="F360" s="4" t="inlineStr"/>
       <c r="G360" s="4" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="n"/>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>دندرة</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr"/>
+      <c r="D361" s="4" t="inlineStr"/>
+      <c r="E361" s="4" t="inlineStr"/>
+      <c r="F361" s="4" t="inlineStr"/>
+      <c r="G361" s="4" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="n"/>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>أبيدوس</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr"/>
+      <c r="D362" s="4" t="inlineStr"/>
+      <c r="E362" s="4" t="inlineStr"/>
+      <c r="F362" s="4" t="inlineStr"/>
+      <c r="G362" s="4" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="n"/>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>قفطي</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr"/>
+      <c r="D363" s="4" t="inlineStr"/>
+      <c r="E363" s="4" t="inlineStr"/>
+      <c r="F363" s="4" t="inlineStr"/>
+      <c r="G363" s="4" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="n"/>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>أخميم</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr"/>
+      <c r="D364" s="4" t="inlineStr"/>
+      <c r="E364" s="4" t="inlineStr"/>
+      <c r="F364" s="4" t="inlineStr"/>
+      <c r="G364" s="4" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="5" t="n"/>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>سوهاج القديمة</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr"/>
+      <c r="D365" s="4" t="inlineStr"/>
+      <c r="E365" s="4" t="inlineStr"/>
+      <c r="F365" s="4" t="inlineStr"/>
+      <c r="G365" s="4" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="5" t="n"/>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>النجع البحري</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr"/>
+      <c r="D366" s="4" t="inlineStr"/>
+      <c r="E366" s="4" t="inlineStr"/>
+      <c r="F366" s="4" t="inlineStr"/>
+      <c r="G366" s="4" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="6" t="n"/>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>الشنقي</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr"/>
+      <c r="D367" s="4" t="inlineStr"/>
+      <c r="E367" s="4" t="inlineStr"/>
+      <c r="F367" s="4" t="inlineStr"/>
+      <c r="G367" s="4" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الشيخ للتخاطب</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="inlineStr"/>
+      <c r="E368" s="4" t="inlineStr"/>
+      <c r="F368" s="4" t="inlineStr"/>
+      <c r="G368" s="4" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="n"/>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr"/>
+      <c r="E369" s="4" t="inlineStr"/>
+      <c r="F369" s="4" t="inlineStr"/>
+      <c r="G369" s="4" t="inlineStr">
+        <is>
+          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="n"/>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>بلامون</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr"/>
+      <c r="D370" s="4" t="inlineStr"/>
+      <c r="E370" s="4" t="inlineStr"/>
+      <c r="F370" s="4" t="inlineStr"/>
+      <c r="G370" s="4" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="n"/>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="inlineStr"/>
+      <c r="D371" s="4" t="inlineStr"/>
+      <c r="E371" s="4" t="inlineStr"/>
+      <c r="F371" s="4" t="inlineStr"/>
+      <c r="G371" s="4" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="n"/>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>سيدي سالم</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr"/>
+      <c r="D372" s="4" t="inlineStr"/>
+      <c r="E372" s="4" t="inlineStr"/>
+      <c r="F372" s="4" t="inlineStr"/>
+      <c r="G372" s="4" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="n"/>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>الحامول</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr"/>
+      <c r="D373" s="4" t="inlineStr"/>
+      <c r="E373" s="4" t="inlineStr"/>
+      <c r="F373" s="4" t="inlineStr"/>
+      <c r="G373" s="4" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="5" t="n"/>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>برج البرلس</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr"/>
+      <c r="D374" s="4" t="inlineStr"/>
+      <c r="E374" s="4" t="inlineStr"/>
+      <c r="F374" s="4" t="inlineStr"/>
+      <c r="G374" s="4" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="n"/>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>مطوبس</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr"/>
+      <c r="D375" s="4" t="inlineStr"/>
+      <c r="E375" s="4" t="inlineStr"/>
+      <c r="F375" s="4" t="inlineStr"/>
+      <c r="G375" s="4" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="n"/>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>المحمودية</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr"/>
+      <c r="D376" s="4" t="inlineStr"/>
+      <c r="E376" s="4" t="inlineStr"/>
+      <c r="F376" s="4" t="inlineStr"/>
+      <c r="G376" s="4" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="6" t="n"/>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>بيلا</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr"/>
+      <c r="D377" s="4" t="inlineStr"/>
+      <c r="E377" s="4" t="inlineStr"/>
+      <c r="F377" s="4" t="inlineStr"/>
+      <c r="G377" s="4" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr"/>
+      <c r="D378" s="4" t="inlineStr"/>
+      <c r="E378" s="4" t="inlineStr"/>
+      <c r="F378" s="4" t="inlineStr"/>
+      <c r="G378" s="4" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>سيوه</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr"/>
+      <c r="D379" s="4" t="inlineStr"/>
+      <c r="E379" s="4" t="inlineStr"/>
+      <c r="F379" s="4" t="inlineStr"/>
+      <c r="G379" s="4" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>السلوم</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr"/>
+      <c r="D380" s="4" t="inlineStr"/>
+      <c r="E380" s="4" t="inlineStr"/>
+      <c r="F380" s="4" t="inlineStr"/>
+      <c r="G380" s="4" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>سيدي براني</t>
+        </is>
+      </c>
+      <c r="C381" s="4" t="inlineStr"/>
+      <c r="D381" s="4" t="inlineStr"/>
+      <c r="E381" s="4" t="inlineStr"/>
+      <c r="F381" s="4" t="inlineStr"/>
+      <c r="G381" s="4" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>العلمين</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr"/>
+      <c r="D382" s="4" t="inlineStr"/>
+      <c r="E382" s="4" t="inlineStr"/>
+      <c r="F382" s="4" t="inlineStr"/>
+      <c r="G382" s="4" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>مارينا</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr"/>
+      <c r="D383" s="4" t="inlineStr"/>
+      <c r="E383" s="4" t="inlineStr"/>
+      <c r="F383" s="4" t="inlineStr"/>
+      <c r="G383" s="4" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>توريدو</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr"/>
+      <c r="D384" s="4" t="inlineStr"/>
+      <c r="E384" s="4" t="inlineStr"/>
+      <c r="F384" s="4" t="inlineStr"/>
+      <c r="G384" s="4" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>جنوب سيوه</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="inlineStr"/>
+      <c r="D385" s="4" t="inlineStr"/>
+      <c r="E385" s="4" t="inlineStr"/>
+      <c r="F385" s="4" t="inlineStr"/>
+      <c r="G385" s="4" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>شمال سيوه</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="inlineStr"/>
+      <c r="D386" s="4" t="inlineStr"/>
+      <c r="E386" s="4" t="inlineStr"/>
+      <c r="F386" s="4" t="inlineStr"/>
+      <c r="G386" s="4" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>كشته</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr"/>
+      <c r="D387" s="4" t="inlineStr"/>
+      <c r="E387" s="4" t="inlineStr"/>
+      <c r="F387" s="4" t="inlineStr"/>
+      <c r="G387" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="313">

--- a/Egyptian_Speech_Therapy_Centers.xlsx
+++ b/Egyptian_Speech_Therapy_Centers.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,15 +44,6 @@
     <font>
       <name val="Arial"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -120,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,15 +127,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G387"/>
+  <dimension ref="A1:G360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4010,552 +3992,427 @@
       <c r="G227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="7" t="inlineStr">
-        <is>
-          <t>القاهرة</t>
-        </is>
-      </c>
-      <c r="B228" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل وصعوبات التعلم - فرع جديد</t>
-        </is>
-      </c>
-      <c r="C228" s="8" t="inlineStr"/>
-      <c r="D228" s="9" t="inlineStr">
-        <is>
-          <t>0222406301</t>
-        </is>
-      </c>
-      <c r="E228" s="9" t="inlineStr"/>
-      <c r="F228" s="8" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>القليوبية</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>بنها</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب برج مكة</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr"/>
+      <c r="E228" s="4" t="inlineStr"/>
+      <c r="F228" s="4" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>شارع جميل أمام بنك القاهرة</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
-      <c r="B229" s="8" t="inlineStr">
-        <is>
-          <t>مركز تخاطب البر والتقوى</t>
-        </is>
-      </c>
-      <c r="C229" s="8" t="inlineStr"/>
-      <c r="D229" s="9" t="inlineStr"/>
-      <c r="E229" s="9" t="inlineStr"/>
-      <c r="F229" s="8" t="inlineStr">
-        <is>
-          <t>104 برج الأوقاف، شارع ابن سندر، سرايا القبة، القاهرة</t>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الجزار</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr"/>
+      <c r="E229" s="4" t="inlineStr"/>
+      <c r="F229" s="4" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="6" t="n"/>
-      <c r="B230" s="8" t="inlineStr">
-        <is>
-          <t>بيت التمريض</t>
-        </is>
-      </c>
-      <c r="C230" s="8" t="inlineStr"/>
-      <c r="D230" s="9" t="inlineStr">
-        <is>
-          <t>201201120500</t>
-        </is>
-      </c>
-      <c r="E230" s="9" t="inlineStr"/>
-      <c r="F230" s="8" t="inlineStr">
-        <is>
-          <t>متخصص في التخاطب وتعديل السلوك</t>
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="6" t="n"/>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العمار</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr"/>
+      <c r="E230" s="4" t="inlineStr"/>
+      <c r="F230" s="4" t="inlineStr"/>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>بنها</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="7" t="inlineStr">
-        <is>
-          <t>مدينة نصر</t>
-        </is>
-      </c>
-      <c r="B231" s="8" t="inlineStr">
-        <is>
-          <t>المركز الذهبي التخصصي (GSC)</t>
-        </is>
-      </c>
-      <c r="C231" s="8" t="inlineStr"/>
-      <c r="D231" s="9" t="inlineStr"/>
-      <c r="E231" s="9" t="inlineStr"/>
-      <c r="F231" s="8" t="inlineStr">
-        <is>
-          <t>مدينة نصر، متخصص في التخاطب وتعديل السلوك</t>
-        </is>
-      </c>
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>قليوب</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr"/>
+      <c r="D231" s="4" t="inlineStr"/>
+      <c r="E231" s="4" t="inlineStr"/>
+      <c r="F231" s="4" t="inlineStr"/>
+      <c r="G231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
-      <c r="B232" s="8" t="inlineStr">
-        <is>
-          <t>مركز Speak للتخاطب</t>
-        </is>
-      </c>
-      <c r="C232" s="8" t="inlineStr"/>
-      <c r="D232" s="9" t="inlineStr"/>
-      <c r="E232" s="9" t="inlineStr"/>
-      <c r="F232" s="8" t="inlineStr">
-        <is>
-          <t>زهراء مدينة نصر، المرحلة الأولى، بجوار مسجد النور</t>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>شبرا الخيمة</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr"/>
+      <c r="E232" s="4" t="inlineStr"/>
+      <c r="F232" s="4" t="inlineStr"/>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>75 شارع حنفي الشيخوني</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
-      <c r="B233" s="8" t="inlineStr">
-        <is>
-          <t>مركز الزهراء للتخاطب</t>
-        </is>
-      </c>
-      <c r="C233" s="8" t="inlineStr"/>
-      <c r="D233" s="9" t="inlineStr"/>
-      <c r="E233" s="9" t="inlineStr"/>
-      <c r="F233" s="8" t="inlineStr">
-        <is>
-          <t>5 شارع الصواف، المنطقة العاشرة، مدينة نصر</t>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>مركز النور الهدى الطبي</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr"/>
+      <c r="E233" s="4" t="inlineStr"/>
+      <c r="F233" s="4" t="inlineStr"/>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>شارع محمد القطان</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
-      <c r="B234" s="8" t="inlineStr">
-        <is>
-          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع مدينة نصر</t>
-        </is>
-      </c>
-      <c r="C234" s="8" t="inlineStr"/>
-      <c r="D234" s="9" t="inlineStr"/>
-      <c r="E234" s="9" t="inlineStr"/>
-      <c r="F234" s="8" t="inlineStr">
-        <is>
-          <t>شارع مصطفى النحاس، فوق التوحيد والنور</t>
+      <c r="B234" s="6" t="n"/>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>مركز تواصل للتخاطب</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr"/>
+      <c r="E234" s="4" t="inlineStr"/>
+      <c r="F234" s="4" t="inlineStr"/>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>2 شارع أحمد عبد ربه</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="6" t="n"/>
-      <c r="B235" s="8" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب - فرع مدينة نصر</t>
-        </is>
-      </c>
-      <c r="C235" s="8" t="inlineStr"/>
-      <c r="D235" s="9" t="inlineStr"/>
-      <c r="E235" s="9" t="inlineStr"/>
-      <c r="F235" s="8" t="inlineStr">
-        <is>
-          <t>مدينة نصر</t>
-        </is>
-      </c>
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>الخانكة</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr"/>
+      <c r="D235" s="4" t="inlineStr"/>
+      <c r="E235" s="4" t="inlineStr"/>
+      <c r="F235" s="4" t="inlineStr"/>
+      <c r="G235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="7" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل - فرع مصر الجديدة</t>
-        </is>
-      </c>
-      <c r="C236" s="8" t="inlineStr"/>
-      <c r="D236" s="9" t="inlineStr">
-        <is>
-          <t>0222406301</t>
-        </is>
-      </c>
-      <c r="E236" s="9" t="inlineStr"/>
-      <c r="F236" s="8" t="inlineStr">
-        <is>
-          <t>مصر الجديدة</t>
-        </is>
-      </c>
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>رمسيس</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr"/>
+      <c r="D236" s="4" t="inlineStr"/>
+      <c r="E236" s="4" t="inlineStr"/>
+      <c r="F236" s="4" t="inlineStr"/>
+      <c r="G236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="6" t="n"/>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>المركز المصري الكندي - فرع النزهة</t>
-        </is>
-      </c>
-      <c r="C237" s="8" t="inlineStr"/>
-      <c r="D237" s="9" t="inlineStr"/>
-      <c r="E237" s="9" t="inlineStr"/>
-      <c r="F237" s="8" t="inlineStr">
-        <is>
-          <t>14 شارع جمال الدين على، بجوار ملاهي السندباد</t>
-        </is>
-      </c>
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>مدينة 10 رمضان</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr"/>
+      <c r="D237" s="4" t="inlineStr"/>
+      <c r="E237" s="4" t="inlineStr"/>
+      <c r="F237" s="4" t="inlineStr"/>
+      <c r="G237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="7" t="inlineStr">
-        <is>
-          <t>المعادي</t>
-        </is>
-      </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>مركز كيور لجراحات الأذن والقوقعة والسمعيات والتخاطب</t>
-        </is>
-      </c>
-      <c r="C238" s="8" t="inlineStr"/>
-      <c r="D238" s="9" t="inlineStr"/>
-      <c r="E238" s="9" t="inlineStr"/>
-      <c r="F238" s="8" t="inlineStr">
-        <is>
-          <t>شارع النصر، تقاطع اللاسلكي، حي المعادي</t>
-        </is>
-      </c>
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>الشيخ زايد</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr"/>
+      <c r="D238" s="4" t="inlineStr"/>
+      <c r="E238" s="4" t="inlineStr"/>
+      <c r="F238" s="4" t="inlineStr"/>
+      <c r="G238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
-      <c r="B239" s="8" t="inlineStr">
-        <is>
-          <t>مركز الجنا للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="C239" s="8" t="inlineStr"/>
-      <c r="D239" s="9" t="inlineStr"/>
-      <c r="E239" s="9" t="inlineStr"/>
-      <c r="F239" s="8" t="inlineStr">
-        <is>
-          <t>شارع 76، المعادى</t>
-        </is>
-      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>القناطر الخيرية</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr"/>
+      <c r="D239" s="4" t="inlineStr"/>
+      <c r="E239" s="4" t="inlineStr"/>
+      <c r="F239" s="4" t="inlineStr"/>
+      <c r="G239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="n"/>
-      <c r="B240" s="8" t="inlineStr">
-        <is>
-          <t>المركز المصري الكندي - فرع المعادي</t>
-        </is>
-      </c>
-      <c r="C240" s="8" t="inlineStr"/>
-      <c r="D240" s="9" t="inlineStr"/>
-      <c r="E240" s="9" t="inlineStr"/>
-      <c r="F240" s="8" t="inlineStr">
-        <is>
-          <t>5/3 شارع اللاسلكي، بجوار شركة غاز مصر</t>
-        </is>
-      </c>
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>قها</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr"/>
+      <c r="D240" s="4" t="inlineStr"/>
+      <c r="E240" s="4" t="inlineStr"/>
+      <c r="F240" s="4" t="inlineStr"/>
+      <c r="G240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="7" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="B241" s="8" t="inlineStr">
-        <is>
-          <t>مركز علمني للتخاطب وصعوبات التعلم</t>
-        </is>
-      </c>
-      <c r="C241" s="8" t="inlineStr"/>
-      <c r="D241" s="9" t="inlineStr"/>
-      <c r="E241" s="9" t="inlineStr"/>
-      <c r="F241" s="8" t="inlineStr">
-        <is>
-          <t>8 عمارات منتصر، الدور الأرضي، بجوار مسجد عباد الرحمن</t>
-        </is>
-      </c>
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>الدقهلية</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr"/>
+      <c r="D241" s="4" t="inlineStr"/>
+      <c r="E241" s="4" t="inlineStr"/>
+      <c r="F241" s="4" t="inlineStr"/>
+      <c r="G241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="7" t="inlineStr">
-        <is>
-          <t>روض الفرج</t>
-        </is>
-      </c>
-      <c r="B242" s="8" t="inlineStr">
-        <is>
-          <t>مركز تخاطب المرح</t>
-        </is>
-      </c>
-      <c r="C242" s="8" t="inlineStr"/>
-      <c r="D242" s="9" t="inlineStr"/>
-      <c r="E242" s="9" t="inlineStr"/>
-      <c r="F242" s="8" t="inlineStr">
-        <is>
-          <t>محطة مترو مسرة، 14 شارع علي أمين عبده، شبرا مصر</t>
-        </is>
-      </c>
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>الجيزة</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr"/>
+      <c r="D242" s="4" t="inlineStr"/>
+      <c r="E242" s="4" t="inlineStr"/>
+      <c r="F242" s="4" t="inlineStr"/>
+      <c r="G242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="n"/>
-      <c r="B243" s="8" t="inlineStr">
-        <is>
-          <t>مركز الرضا للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="C243" s="8" t="inlineStr"/>
-      <c r="D243" s="9" t="inlineStr"/>
-      <c r="E243" s="9" t="inlineStr"/>
-      <c r="F243" s="8" t="inlineStr">
-        <is>
-          <t>شارع ترعة جزيرة بدران، قسم روض الفرج</t>
-        </is>
-      </c>
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>أوسيم</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr"/>
+      <c r="D243" s="4" t="inlineStr"/>
+      <c r="E243" s="4" t="inlineStr"/>
+      <c r="F243" s="4" t="inlineStr"/>
+      <c r="G243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="7" t="inlineStr">
-        <is>
-          <t>المطرية</t>
-        </is>
-      </c>
-      <c r="B244" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل بالمطرية</t>
-        </is>
-      </c>
-      <c r="C244" s="8" t="inlineStr"/>
-      <c r="D244" s="9" t="inlineStr">
-        <is>
-          <t>01147626979</t>
-        </is>
-      </c>
-      <c r="E244" s="9" t="inlineStr"/>
-      <c r="F244" s="8" t="inlineStr">
-        <is>
-          <t>شارع منية مطر، بجوار محطة مترو المطرية</t>
-        </is>
-      </c>
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>طره</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr"/>
+      <c r="D244" s="4" t="inlineStr"/>
+      <c r="E244" s="4" t="inlineStr"/>
+      <c r="F244" s="4" t="inlineStr"/>
+      <c r="G244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="7" t="inlineStr">
-        <is>
-          <t>الدقي</t>
-        </is>
-      </c>
-      <c r="B245" s="8" t="inlineStr">
-        <is>
-          <t>مركز الحمد للعلاج الطبيعي والتخاطب - فرع الدقي</t>
-        </is>
-      </c>
-      <c r="C245" s="8" t="inlineStr"/>
-      <c r="D245" s="9" t="inlineStr"/>
-      <c r="E245" s="9" t="inlineStr"/>
-      <c r="F245" s="8" t="inlineStr">
-        <is>
-          <t>4 شارع Hussein Wassef، الدقي</t>
-        </is>
-      </c>
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>الخصوص</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr"/>
+      <c r="D245" s="4" t="inlineStr"/>
+      <c r="E245" s="4" t="inlineStr"/>
+      <c r="F245" s="4" t="inlineStr"/>
+      <c r="G245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n"/>
-      <c r="B246" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب - الدقي</t>
-        </is>
-      </c>
-      <c r="C246" s="8" t="inlineStr"/>
-      <c r="D246" s="9" t="inlineStr"/>
-      <c r="E246" s="9" t="inlineStr"/>
-      <c r="F246" s="8" t="inlineStr">
-        <is>
-          <t>110 شارع التحرير، الدقي، أمام محطة مترو الدقي</t>
-        </is>
-      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>القنطرة</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr"/>
+      <c r="D246" s="4" t="inlineStr"/>
+      <c r="E246" s="4" t="inlineStr"/>
+      <c r="F246" s="4" t="inlineStr"/>
+      <c r="G246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="7" t="inlineStr">
-        <is>
-          <t>الهرم</t>
-        </is>
-      </c>
-      <c r="B247" s="8" t="inlineStr">
-        <is>
-          <t>مركز هووب للتخاطب</t>
-        </is>
-      </c>
-      <c r="C247" s="8" t="inlineStr"/>
-      <c r="D247" s="9" t="inlineStr"/>
-      <c r="E247" s="9" t="inlineStr"/>
-      <c r="F247" s="8" t="inlineStr">
-        <is>
-          <t>الهرم، متخصص في التخاطب وتنمية المهارات</t>
-        </is>
-      </c>
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>المنوفية</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>شبين الكوم</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr"/>
+      <c r="D247" s="4" t="inlineStr"/>
+      <c r="E247" s="4" t="inlineStr"/>
+      <c r="F247" s="4" t="inlineStr"/>
+      <c r="G247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
-      <c r="B248" s="8" t="inlineStr">
-        <is>
-          <t>مركز فرصة حياه للتأهيل للتخاطب وتنمية المهارات</t>
-        </is>
-      </c>
-      <c r="C248" s="8" t="inlineStr"/>
-      <c r="D248" s="9" t="inlineStr">
-        <is>
-          <t>01030360536</t>
-        </is>
-      </c>
-      <c r="E248" s="9" t="inlineStr"/>
-      <c r="F248" s="8" t="inlineStr">
-        <is>
-          <t>الهرم وفيصل</t>
-        </is>
-      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>منوف</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr"/>
+      <c r="D248" s="4" t="inlineStr"/>
+      <c r="E248" s="4" t="inlineStr"/>
+      <c r="F248" s="4" t="inlineStr"/>
+      <c r="G248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="n"/>
-      <c r="B249" s="8" t="inlineStr">
-        <is>
-          <t>مركز اشراقة للتخاطب - د/اسلام سالم</t>
-        </is>
-      </c>
-      <c r="C249" s="8" t="inlineStr">
-        <is>
-          <t>د/اسلام سالم</t>
-        </is>
-      </c>
-      <c r="D249" s="9" t="inlineStr"/>
-      <c r="E249" s="9" t="inlineStr"/>
-      <c r="F249" s="8" t="inlineStr">
-        <is>
-          <t>شارع اللبيني، الهرم الرئيسي</t>
-        </is>
-      </c>
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>شبين القناطر</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr"/>
+      <c r="D249" s="4" t="inlineStr"/>
+      <c r="E249" s="4" t="inlineStr"/>
+      <c r="F249" s="4" t="inlineStr"/>
+      <c r="G249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="7" t="inlineStr">
-        <is>
-          <t>النزهة</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب - فرع النزهة</t>
-        </is>
-      </c>
-      <c r="C250" s="8" t="inlineStr"/>
-      <c r="D250" s="9" t="inlineStr"/>
-      <c r="E250" s="9" t="inlineStr"/>
-      <c r="F250" s="8" t="inlineStr">
-        <is>
-          <t>النزهة</t>
-        </is>
-      </c>
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>مدينة السادات</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr"/>
+      <c r="D250" s="4" t="inlineStr"/>
+      <c r="E250" s="4" t="inlineStr"/>
+      <c r="F250" s="4" t="inlineStr"/>
+      <c r="G250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="n"/>
-      <c r="B251" s="8" t="inlineStr">
-        <is>
-          <t>نور الحياة للتخاطب</t>
-        </is>
-      </c>
-      <c r="C251" s="8" t="inlineStr"/>
-      <c r="D251" s="9" t="inlineStr"/>
-      <c r="E251" s="9" t="inlineStr"/>
-      <c r="F251" s="8" t="inlineStr">
-        <is>
-          <t>شارع شبرا الخلفاوى، قسم الساحل</t>
-        </is>
-      </c>
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>باقور</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr"/>
+      <c r="D251" s="4" t="inlineStr"/>
+      <c r="E251" s="4" t="inlineStr"/>
+      <c r="F251" s="4" t="inlineStr"/>
+      <c r="G251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="7" t="inlineStr">
-        <is>
-          <t>الزيتون</t>
-        </is>
-      </c>
-      <c r="B252" s="8" t="inlineStr">
-        <is>
-          <t>مركز التخاطب الشامل - فرع الزيتون</t>
-        </is>
-      </c>
-      <c r="C252" s="8" t="inlineStr"/>
-      <c r="D252" s="9" t="inlineStr">
-        <is>
-          <t>0222406301</t>
-        </is>
-      </c>
-      <c r="E252" s="9" t="inlineStr"/>
-      <c r="F252" s="8" t="inlineStr">
-        <is>
-          <t>حي الزيتون</t>
-        </is>
-      </c>
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>تلا</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr"/>
+      <c r="D252" s="4" t="inlineStr"/>
+      <c r="E252" s="4" t="inlineStr"/>
+      <c r="F252" s="4" t="inlineStr"/>
+      <c r="G252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="7" t="inlineStr">
-        <is>
-          <t>عين شمس</t>
-        </is>
-      </c>
-      <c r="B253" s="8" t="inlineStr">
-        <is>
-          <t>مركز الشمس للتخاطب - فرع عين شمس</t>
-        </is>
-      </c>
-      <c r="C253" s="8" t="inlineStr"/>
-      <c r="D253" s="9" t="inlineStr"/>
-      <c r="E253" s="9" t="inlineStr"/>
-      <c r="F253" s="8" t="inlineStr">
-        <is>
-          <t>عين شمس</t>
-        </is>
-      </c>
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>قويسنا</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr"/>
+      <c r="D253" s="4" t="inlineStr"/>
+      <c r="E253" s="4" t="inlineStr"/>
+      <c r="F253" s="4" t="inlineStr"/>
+      <c r="G253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="7" t="inlineStr">
-        <is>
-          <t>فيصل</t>
-        </is>
-      </c>
-      <c r="B254" s="8" t="inlineStr">
-        <is>
-          <t>مركز فرصة حياه - فرع فيصل</t>
-        </is>
-      </c>
-      <c r="C254" s="8" t="inlineStr"/>
-      <c r="D254" s="9" t="inlineStr">
-        <is>
-          <t>01030360536</t>
-        </is>
-      </c>
-      <c r="E254" s="9" t="inlineStr"/>
-      <c r="F254" s="8" t="inlineStr">
-        <is>
-          <t>فيصل</t>
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>أشمون</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب أشمون للتخاطب</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr"/>
+      <c r="E254" s="4" t="inlineStr"/>
+      <c r="F254" s="4" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>أشمون</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>القليوبية</t>
-        </is>
-      </c>
+      <c r="A255" s="5" t="n"/>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>بنها</t>
-        </is>
-      </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب برج مكة</t>
-        </is>
-      </c>
+          <t>البرجايه</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr"/>
       <c r="D255" s="4" t="inlineStr"/>
       <c r="E255" s="4" t="inlineStr"/>
       <c r="F255" s="4" t="inlineStr"/>
-      <c r="G255" s="4" t="inlineStr">
-        <is>
-          <t>شارع جميل أمام بنك القاهرة</t>
-        </is>
-      </c>
+      <c r="G255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n"/>
-      <c r="B256" s="5" t="n"/>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>بركة السبع</t>
+        </is>
+      </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>مركز شباب كفر الجزار</t>
+          <t>مركز تخاطب وصعوبات تعلم</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr"/>
@@ -4563,32 +4420,28 @@
       <c r="F256" s="4" t="inlineStr"/>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>بنها</t>
+          <t>بركة السبع</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n"/>
-      <c r="B257" s="6" t="n"/>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العمار</t>
-        </is>
-      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>منوف الجديدة</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr"/>
       <c r="D257" s="4" t="inlineStr"/>
       <c r="E257" s="4" t="inlineStr"/>
       <c r="F257" s="4" t="inlineStr"/>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>بنها</t>
-        </is>
-      </c>
+      <c r="G257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="n"/>
+      <c r="A258" s="6" t="n"/>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>قليوب</t>
+          <t>كفر عبده</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr"/>
@@ -4598,15 +4451,19 @@
       <c r="G258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="n"/>
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>المنيا</t>
+        </is>
+      </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>شبرا الخيمة</t>
+          <t>المنيا</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>مركز الغد للتخاطب وصعوبات التعلم</t>
+          <t>مركز شباب بني أحمد للتخاطب</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr"/>
@@ -4614,16 +4471,16 @@
       <c r="F259" s="4" t="inlineStr"/>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>75 شارع حنفي الشيخوني</t>
+          <t>المنيا</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
-      <c r="B260" s="5" t="n"/>
+      <c r="B260" s="6" t="n"/>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>مركز النور الهدى الطبي</t>
+          <t>مركز شباب مقوسة للتخاطب</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr"/>
@@ -4631,32 +4488,28 @@
       <c r="F260" s="4" t="inlineStr"/>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>شارع محمد القطان</t>
+          <t>المنيا</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n"/>
-      <c r="B261" s="6" t="n"/>
-      <c r="C261" s="4" t="inlineStr">
-        <is>
-          <t>مركز تواصل للتخاطب</t>
-        </is>
-      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>سمالوط</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr"/>
       <c r="D261" s="4" t="inlineStr"/>
       <c r="E261" s="4" t="inlineStr"/>
       <c r="F261" s="4" t="inlineStr"/>
-      <c r="G261" s="4" t="inlineStr">
-        <is>
-          <t>2 شارع أحمد عبد ربه</t>
-        </is>
-      </c>
+      <c r="G261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>الخانكة</t>
+          <t>بني حسن</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr"/>
@@ -4669,7 +4522,7 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>رمسيس</t>
+          <t>هرموبوليس</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr"/>
@@ -4682,7 +4535,7 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>مدينة 10 رمضان</t>
+          <t>ملوي</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr"/>
@@ -4695,7 +4548,7 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زايد</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr"/>
@@ -4708,7 +4561,7 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>القناطر الخيرية</t>
+          <t>ديروط الشريف</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr"/>
@@ -4721,7 +4574,7 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>قها</t>
+          <t>أبوقرقاص</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr"/>
@@ -4734,7 +4587,7 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>الدقهلية</t>
+          <t>الفشن</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr"/>
@@ -4747,7 +4600,7 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>الجيزة</t>
+          <t>بني مازن</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr"/>
@@ -4757,10 +4610,10 @@
       <c r="G269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="n"/>
+      <c r="A270" s="6" t="n"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>أوسيم</t>
+          <t>العدوة</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr"/>
@@ -4770,36 +4623,56 @@
       <c r="G270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="n"/>
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>الوادي الجديد</t>
+        </is>
+      </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>طره</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr"/>
+          <t>الخارجة</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب الخارجة للتخاطب</t>
+        </is>
+      </c>
       <c r="D271" s="4" t="inlineStr"/>
       <c r="E271" s="4" t="inlineStr"/>
       <c r="F271" s="4" t="inlineStr"/>
-      <c r="G271" s="4" t="inlineStr"/>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>الخارجة</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>الخصوص</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr"/>
+          <t>الداخلة</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب باريس للتخاطب</t>
+        </is>
+      </c>
       <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr"/>
       <c r="F272" s="4" t="inlineStr"/>
-      <c r="G272" s="4" t="inlineStr"/>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="n"/>
+      <c r="A273" s="5" t="n"/>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>القنطرة</t>
+          <t>موط</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr"/>
@@ -4809,14 +4682,10 @@
       <c r="G273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>المنوفية</t>
-        </is>
-      </c>
+      <c r="A274" s="5" t="n"/>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>شبين الكوم</t>
+          <t>بلاط</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr"/>
@@ -4829,7 +4698,7 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>منوف</t>
+          <t>فرافرة</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr"/>
@@ -4842,7 +4711,7 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>شبين القناطر</t>
+          <t>باريس</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr"/>
@@ -4855,7 +4724,7 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>مدينة السادات</t>
+          <t>القصر</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr"/>
@@ -4868,7 +4737,7 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>باقور</t>
+          <t>تينيدة</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr"/>
@@ -4878,10 +4747,10 @@
       <c r="G278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="n"/>
+      <c r="A279" s="6" t="n"/>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>تلا</t>
+          <t>دوش</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr"/>
@@ -4891,44 +4760,48 @@
       <c r="G279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="n"/>
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>قويسنا</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr"/>
+          <t>بني سويف</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العبور للتخاطب</t>
+        </is>
+      </c>
       <c r="D280" s="4" t="inlineStr"/>
       <c r="E280" s="4" t="inlineStr"/>
       <c r="F280" s="4" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>بني سويف</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>أشمون</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب أشمون للتخاطب</t>
-        </is>
-      </c>
+          <t>الفشن</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr"/>
       <c r="D281" s="4" t="inlineStr"/>
       <c r="E281" s="4" t="inlineStr"/>
       <c r="F281" s="4" t="inlineStr"/>
-      <c r="G281" s="4" t="inlineStr">
-        <is>
-          <t>أشمون</t>
-        </is>
-      </c>
+      <c r="G281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>البرجايه</t>
+          <t>ساماستا</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr"/>
@@ -4941,28 +4814,20 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب وصعوبات تعلم</t>
-        </is>
-      </c>
+          <t>إبشواي</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr"/>
       <c r="D283" s="4" t="inlineStr"/>
       <c r="E283" s="4" t="inlineStr"/>
       <c r="F283" s="4" t="inlineStr"/>
-      <c r="G283" s="4" t="inlineStr">
-        <is>
-          <t>بركة السبع</t>
-        </is>
-      </c>
+      <c r="G283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>منوف الجديدة</t>
+          <t>الجندية</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr"/>
@@ -4972,10 +4837,10 @@
       <c r="G284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="6" t="n"/>
+      <c r="A285" s="5" t="n"/>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>كفر عبده</t>
+          <t>ناصر</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr"/>
@@ -4985,52 +4850,36 @@
       <c r="G285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="A286" s="5" t="n"/>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>المنيا</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب بني أحمد للتخاطب</t>
-        </is>
-      </c>
+          <t>هواره</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr"/>
       <c r="D286" s="4" t="inlineStr"/>
       <c r="E286" s="4" t="inlineStr"/>
       <c r="F286" s="4" t="inlineStr"/>
-      <c r="G286" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="5" t="n"/>
-      <c r="B287" s="6" t="n"/>
-      <c r="C287" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب مقوسة للتخاطب</t>
-        </is>
-      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>موشية</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr"/>
       <c r="D287" s="4" t="inlineStr"/>
       <c r="E287" s="4" t="inlineStr"/>
       <c r="F287" s="4" t="inlineStr"/>
-      <c r="G287" s="4" t="inlineStr">
-        <is>
-          <t>المنيا</t>
-        </is>
-      </c>
+      <c r="G287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>سمالوط</t>
+          <t>نصار البحرية</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr"/>
@@ -5040,10 +4889,10 @@
       <c r="G288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="n"/>
+      <c r="A289" s="6" t="n"/>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>بني حسن</t>
+          <t>أحمد حمزة</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr"/>
@@ -5053,10 +4902,14 @@
       <c r="G289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="n"/>
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>بورسعيد</t>
+        </is>
+      </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>هرموبوليس</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr"/>
@@ -5069,7 +4922,7 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>ملوي</t>
+          <t>بورفؤاد</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr"/>
@@ -5082,7 +4935,7 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>الجميل</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr"/>
@@ -5095,7 +4948,7 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>ديروط الشريف</t>
+          <t>الزهور</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr"/>
@@ -5108,7 +4961,7 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>أبوقرقاص</t>
+          <t>بورسعيد</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr"/>
@@ -5121,7 +4974,7 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>الكنتاوي</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr"/>
@@ -5131,10 +4984,10 @@
       <c r="G295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="n"/>
+      <c r="A296" s="6" t="n"/>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>بني مازن</t>
+          <t>الضواحي</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr"/>
@@ -5144,10 +4997,14 @@
       <c r="G296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="n"/>
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>جنوب سيناء</t>
+        </is>
+      </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>العدوة</t>
+          <t>شرم الشيخ</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr"/>
@@ -5157,56 +5014,36 @@
       <c r="G297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>الوادي الجديد</t>
-        </is>
-      </c>
+      <c r="A298" s="5" t="n"/>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
-      <c r="C298" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب الخارجة للتخاطب</t>
-        </is>
-      </c>
+          <t>داهب</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr"/>
       <c r="D298" s="4" t="inlineStr"/>
       <c r="E298" s="4" t="inlineStr"/>
       <c r="F298" s="4" t="inlineStr"/>
-      <c r="G298" s="4" t="inlineStr">
-        <is>
-          <t>الخارجة</t>
-        </is>
-      </c>
+      <c r="G298" s="4" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب باريس للتخاطب</t>
-        </is>
-      </c>
+          <t>نويبع</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr"/>
       <c r="D299" s="4" t="inlineStr"/>
       <c r="E299" s="4" t="inlineStr"/>
       <c r="F299" s="4" t="inlineStr"/>
-      <c r="G299" s="4" t="inlineStr">
-        <is>
-          <t>باريس</t>
-        </is>
-      </c>
+      <c r="G299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>موط</t>
+          <t>سانت كاترين</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr"/>
@@ -5219,7 +5056,7 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>بلاط</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr"/>
@@ -5232,7 +5069,7 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>فرافرة</t>
+          <t>رأس محمد</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr"/>
@@ -5245,7 +5082,7 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>باريس</t>
+          <t>أم سيد</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr"/>
@@ -5255,10 +5092,10 @@
       <c r="G303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="n"/>
+      <c r="A304" s="6" t="n"/>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>القصر</t>
+          <t>مدينة شرم الشيخ</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr"/>
@@ -5268,10 +5105,14 @@
       <c r="G304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="5" t="n"/>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>حلوان</t>
+        </is>
+      </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>تينيدة</t>
+          <t>حلوان</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr"/>
@@ -5281,10 +5122,10 @@
       <c r="G305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="6" t="n"/>
+      <c r="A306" s="5" t="n"/>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>دوش</t>
+          <t>المعادي</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr"/>
@@ -5294,35 +5135,23 @@
       <c r="G306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="A307" s="5" t="n"/>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
-      <c r="C307" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العبور للتخاطب</t>
-        </is>
-      </c>
+          <t>واحة الفيوم</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr"/>
       <c r="D307" s="4" t="inlineStr"/>
       <c r="E307" s="4" t="inlineStr"/>
       <c r="F307" s="4" t="inlineStr"/>
-      <c r="G307" s="4" t="inlineStr">
-        <is>
-          <t>بني سويف</t>
-        </is>
-      </c>
+      <c r="G307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>الفشن</t>
+          <t>وادي حوف</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr"/>
@@ -5335,7 +5164,7 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>ساماستا</t>
+          <t>عين سخنة</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr"/>
@@ -5348,7 +5177,7 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>إبشواي</t>
+          <t>الطور</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr"/>
@@ -5361,7 +5190,7 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>الجندية</t>
+          <t>الزيتون</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr"/>
@@ -5371,10 +5200,10 @@
       <c r="G311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="5" t="n"/>
+      <c r="A312" s="6" t="n"/>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>ناصر</t>
+          <t>المقطم</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr"/>
@@ -5384,23 +5213,35 @@
       <c r="G312" s="4" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="5" t="n"/>
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>دمياط</t>
+        </is>
+      </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>هواره</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr"/>
+          <t>دمياط</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>مركز حلم ابني للتخاطب</t>
+        </is>
+      </c>
       <c r="D313" s="4" t="inlineStr"/>
       <c r="E313" s="4" t="inlineStr"/>
       <c r="F313" s="4" t="inlineStr"/>
-      <c r="G313" s="4" t="inlineStr"/>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>دمياط ودمياط الجديدة</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>موشية</t>
+          <t>دمياط الجديدة</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr"/>
@@ -5413,7 +5254,7 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>نصار البحرية</t>
+          <t>بورت فؤاد</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr"/>
@@ -5423,10 +5264,10 @@
       <c r="G315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="6" t="n"/>
+      <c r="A316" s="5" t="n"/>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>أحمد حمزة</t>
+          <t>كفر البطة</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr"/>
@@ -5436,14 +5277,10 @@
       <c r="G316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>بورسعيد</t>
-        </is>
-      </c>
+      <c r="A317" s="5" t="n"/>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>كفر سعيد</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr"/>
@@ -5456,7 +5293,7 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>بورفؤاد</t>
+          <t>الروضة</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr"/>
@@ -5469,7 +5306,7 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>الجميل</t>
+          <t>الزرقا</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr"/>
@@ -5482,7 +5319,7 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>الزهور</t>
+          <t>فارسكور</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr"/>
@@ -5492,10 +5329,10 @@
       <c r="G320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="n"/>
+      <c r="A321" s="6" t="n"/>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>بورسعيد</t>
+          <t>رومانية</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr"/>
@@ -5505,53 +5342,77 @@
       <c r="G321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="n"/>
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>شمال سيناء</t>
+        </is>
+      </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>الكنتاوي</t>
-        </is>
-      </c>
-      <c r="C322" s="4" t="inlineStr"/>
+          <t>العريش</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش للتخاطب</t>
+        </is>
+      </c>
       <c r="D322" s="4" t="inlineStr"/>
       <c r="E322" s="4" t="inlineStr"/>
       <c r="F322" s="4" t="inlineStr"/>
-      <c r="G322" s="4" t="inlineStr"/>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب العريش</t>
+        </is>
+      </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="n"/>
+      <c r="A323" s="5" t="n"/>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>الضواحي</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr"/>
+          <t>رفح</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب رفح</t>
+        </is>
+      </c>
       <c r="D323" s="4" t="inlineStr"/>
       <c r="E323" s="4" t="inlineStr"/>
       <c r="F323" s="4" t="inlineStr"/>
-      <c r="G323" s="4" t="inlineStr"/>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>رفح</t>
+        </is>
+      </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>جنوب سيناء</t>
-        </is>
-      </c>
+      <c r="A324" s="5" t="n"/>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>شرم الشيخ</t>
-        </is>
-      </c>
-      <c r="C324" s="4" t="inlineStr"/>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
+        </is>
+      </c>
       <c r="D324" s="4" t="inlineStr"/>
       <c r="E324" s="4" t="inlineStr"/>
       <c r="F324" s="4" t="inlineStr"/>
-      <c r="G324" s="4" t="inlineStr"/>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>الشيخ زويد</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>داهب</t>
+          <t>بئر العبد</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr"/>
@@ -5564,7 +5425,7 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>نويبع</t>
+          <t>القنطرة، سيناء</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr"/>
@@ -5577,7 +5438,7 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>سانت كاترين</t>
+          <t>نخل</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr"/>
@@ -5590,7 +5451,7 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>جديدة، حسنة</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr"/>
@@ -5603,7 +5464,7 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>رأس محمد</t>
+          <t>دهب الشرقية</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr"/>
@@ -5613,10 +5474,10 @@
       <c r="G329" s="4" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="5" t="n"/>
+      <c r="A330" s="6" t="n"/>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>أم سيد</t>
+          <t>طابا</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr"/>
@@ -5626,40 +5487,52 @@
       <c r="G330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="6" t="n"/>
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>مدينة شرم الشيخ</t>
-        </is>
-      </c>
-      <c r="C331" s="4" t="inlineStr"/>
+          <t>قنا</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>مركز التخاطب بمدينة العمال</t>
+        </is>
+      </c>
       <c r="D331" s="4" t="inlineStr"/>
       <c r="E331" s="4" t="inlineStr"/>
       <c r="F331" s="4" t="inlineStr"/>
-      <c r="G331" s="4" t="inlineStr"/>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>مدينة العمال، قنا</t>
+        </is>
+      </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>حلوان</t>
-        </is>
-      </c>
-      <c r="C332" s="4" t="inlineStr"/>
+      <c r="A332" s="5" t="n"/>
+      <c r="B332" s="6" t="n"/>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب حجير خزام</t>
+        </is>
+      </c>
       <c r="D332" s="4" t="inlineStr"/>
       <c r="E332" s="4" t="inlineStr"/>
       <c r="F332" s="4" t="inlineStr"/>
-      <c r="G332" s="4" t="inlineStr"/>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>قنا</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>المعادي</t>
+          <t>نجع حمادي</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr"/>
@@ -5672,7 +5545,7 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>واحة الفيوم</t>
+          <t>دندرة</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr"/>
@@ -5685,7 +5558,7 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>وادي حوف</t>
+          <t>أبيدوس</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr"/>
@@ -5698,7 +5571,7 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>عين سخنة</t>
+          <t>قفطي</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr"/>
@@ -5711,7 +5584,7 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>الطور</t>
+          <t>أخميم</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr"/>
@@ -5724,7 +5597,7 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>الزيتون</t>
+          <t>سوهاج القديمة</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr"/>
@@ -5734,10 +5607,10 @@
       <c r="G338" s="4" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="6" t="n"/>
+      <c r="A339" s="5" t="n"/>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>المقطم</t>
+          <t>النجع البحري</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr"/>
@@ -5747,61 +5620,69 @@
       <c r="G339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>دمياط</t>
-        </is>
-      </c>
+      <c r="A340" s="6" t="n"/>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>دمياط</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="inlineStr">
-        <is>
-          <t>مركز حلم ابني للتخاطب</t>
-        </is>
-      </c>
+          <t>الشنقي</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr"/>
       <c r="D340" s="4" t="inlineStr"/>
       <c r="E340" s="4" t="inlineStr"/>
       <c r="F340" s="4" t="inlineStr"/>
-      <c r="G340" s="4" t="inlineStr">
-        <is>
-          <t>دمياط ودمياط الجديدة</t>
-        </is>
-      </c>
+      <c r="G340" s="4" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="5" t="n"/>
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>دمياط الجديدة</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr"/>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>مركز شباب كفر الشيخ للتخاطب</t>
+        </is>
+      </c>
       <c r="D341" s="4" t="inlineStr"/>
       <c r="E341" s="4" t="inlineStr"/>
       <c r="F341" s="4" t="inlineStr"/>
-      <c r="G341" s="4" t="inlineStr"/>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>كفر الشيخ</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>بورت فؤاد</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr"/>
+          <t>دسوق</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
+        </is>
+      </c>
       <c r="D342" s="4" t="inlineStr"/>
       <c r="E342" s="4" t="inlineStr"/>
       <c r="F342" s="4" t="inlineStr"/>
-      <c r="G342" s="4" t="inlineStr"/>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>كفر البطة</t>
+          <t>بلامون</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr"/>
@@ -5814,7 +5695,7 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>كفر سعيد</t>
+          <t>الرياض</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr"/>
@@ -5827,7 +5708,7 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>الروضة</t>
+          <t>سيدي سالم</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr"/>
@@ -5840,7 +5721,7 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>الزرقا</t>
+          <t>الحامول</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr"/>
@@ -5853,7 +5734,7 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>فارسكور</t>
+          <t>برج البرلس</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr"/>
@@ -5863,10 +5744,10 @@
       <c r="G347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="6" t="n"/>
+      <c r="A348" s="5" t="n"/>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>رومانية</t>
+          <t>مطوبس</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr"/>
@@ -5876,77 +5757,57 @@
       <c r="G348" s="4" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>شمال سيناء</t>
-        </is>
-      </c>
+      <c r="A349" s="5" t="n"/>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>العريش</t>
-        </is>
-      </c>
-      <c r="C349" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش للتخاطب</t>
-        </is>
-      </c>
+          <t>المحمودية</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr"/>
       <c r="D349" s="4" t="inlineStr"/>
       <c r="E349" s="4" t="inlineStr"/>
       <c r="F349" s="4" t="inlineStr"/>
-      <c r="G349" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب العريش</t>
-        </is>
-      </c>
+      <c r="G349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="5" t="n"/>
+      <c r="A350" s="6" t="n"/>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>رفح</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب رفح</t>
-        </is>
-      </c>
+          <t>بيلا</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr"/>
       <c r="D350" s="4" t="inlineStr"/>
       <c r="E350" s="4" t="inlineStr"/>
       <c r="F350" s="4" t="inlineStr"/>
-      <c r="G350" s="4" t="inlineStr">
-        <is>
-          <t>رفح</t>
-        </is>
-      </c>
+      <c r="G350" s="4" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="5" t="n"/>
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
-      <c r="C351" s="4" t="inlineStr">
-        <is>
-          <t>مركز تخاطب الشيخ زويد (قيد الإنشاء)</t>
-        </is>
-      </c>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr"/>
       <c r="D351" s="4" t="inlineStr"/>
       <c r="E351" s="4" t="inlineStr"/>
       <c r="F351" s="4" t="inlineStr"/>
-      <c r="G351" s="4" t="inlineStr">
-        <is>
-          <t>الشيخ زويد</t>
-        </is>
-      </c>
+      <c r="G351" s="4" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="5" t="n"/>
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>بئر العبد</t>
+          <t>سيوه</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr"/>
@@ -5956,10 +5817,14 @@
       <c r="G352" s="4" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="5" t="n"/>
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>القنطرة، سيناء</t>
+          <t>السلوم</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr"/>
@@ -5969,10 +5834,14 @@
       <c r="G353" s="4" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="5" t="n"/>
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>نخل</t>
+          <t>سيدي براني</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr"/>
@@ -5982,10 +5851,14 @@
       <c r="G354" s="4" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="5" t="n"/>
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>جديدة، حسنة</t>
+          <t>العلمين</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr"/>
@@ -5995,10 +5868,14 @@
       <c r="G355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="5" t="n"/>
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>دهب الشرقية</t>
+          <t>مارينا</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr"/>
@@ -6008,10 +5885,14 @@
       <c r="G356" s="4" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="6" t="n"/>
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>طابا</t>
+          <t>توريدو</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr"/>
@@ -6023,50 +5904,46 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>قنا</t>
+          <t>مطروح</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>قنا</t>
-        </is>
-      </c>
-      <c r="C358" s="4" t="inlineStr">
-        <is>
-          <t>مركز التخاطب بمدينة العمال</t>
-        </is>
-      </c>
+          <t>جنوب سيوه</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr"/>
       <c r="D358" s="4" t="inlineStr"/>
       <c r="E358" s="4" t="inlineStr"/>
       <c r="F358" s="4" t="inlineStr"/>
-      <c r="G358" s="4" t="inlineStr">
-        <is>
-          <t>مدينة العمال، قنا</t>
-        </is>
-      </c>
+      <c r="G358" s="4" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="5" t="n"/>
-      <c r="B359" s="6" t="n"/>
-      <c r="C359" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب حجير خزام</t>
-        </is>
-      </c>
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>شمال سيوه</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr"/>
       <c r="D359" s="4" t="inlineStr"/>
       <c r="E359" s="4" t="inlineStr"/>
       <c r="F359" s="4" t="inlineStr"/>
-      <c r="G359" s="4" t="inlineStr">
-        <is>
-          <t>قنا</t>
-        </is>
-      </c>
+      <c r="G359" s="4" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="5" t="n"/>
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>مطروح</t>
+        </is>
+      </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>نجع حمادي</t>
+          <t>كشته</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr"/>
@@ -6074,417 +5951,6 @@
       <c r="E360" s="4" t="inlineStr"/>
       <c r="F360" s="4" t="inlineStr"/>
       <c r="G360" s="4" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="5" t="n"/>
-      <c r="B361" s="3" t="inlineStr">
-        <is>
-          <t>دندرة</t>
-        </is>
-      </c>
-      <c r="C361" s="4" t="inlineStr"/>
-      <c r="D361" s="4" t="inlineStr"/>
-      <c r="E361" s="4" t="inlineStr"/>
-      <c r="F361" s="4" t="inlineStr"/>
-      <c r="G361" s="4" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="5" t="n"/>
-      <c r="B362" s="3" t="inlineStr">
-        <is>
-          <t>أبيدوس</t>
-        </is>
-      </c>
-      <c r="C362" s="4" t="inlineStr"/>
-      <c r="D362" s="4" t="inlineStr"/>
-      <c r="E362" s="4" t="inlineStr"/>
-      <c r="F362" s="4" t="inlineStr"/>
-      <c r="G362" s="4" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="5" t="n"/>
-      <c r="B363" s="3" t="inlineStr">
-        <is>
-          <t>قفطي</t>
-        </is>
-      </c>
-      <c r="C363" s="4" t="inlineStr"/>
-      <c r="D363" s="4" t="inlineStr"/>
-      <c r="E363" s="4" t="inlineStr"/>
-      <c r="F363" s="4" t="inlineStr"/>
-      <c r="G363" s="4" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" s="5" t="n"/>
-      <c r="B364" s="3" t="inlineStr">
-        <is>
-          <t>أخميم</t>
-        </is>
-      </c>
-      <c r="C364" s="4" t="inlineStr"/>
-      <c r="D364" s="4" t="inlineStr"/>
-      <c r="E364" s="4" t="inlineStr"/>
-      <c r="F364" s="4" t="inlineStr"/>
-      <c r="G364" s="4" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" s="5" t="n"/>
-      <c r="B365" s="3" t="inlineStr">
-        <is>
-          <t>سوهاج القديمة</t>
-        </is>
-      </c>
-      <c r="C365" s="4" t="inlineStr"/>
-      <c r="D365" s="4" t="inlineStr"/>
-      <c r="E365" s="4" t="inlineStr"/>
-      <c r="F365" s="4" t="inlineStr"/>
-      <c r="G365" s="4" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" s="5" t="n"/>
-      <c r="B366" s="3" t="inlineStr">
-        <is>
-          <t>النجع البحري</t>
-        </is>
-      </c>
-      <c r="C366" s="4" t="inlineStr"/>
-      <c r="D366" s="4" t="inlineStr"/>
-      <c r="E366" s="4" t="inlineStr"/>
-      <c r="F366" s="4" t="inlineStr"/>
-      <c r="G366" s="4" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="6" t="n"/>
-      <c r="B367" s="3" t="inlineStr">
-        <is>
-          <t>الشنقي</t>
-        </is>
-      </c>
-      <c r="C367" s="4" t="inlineStr"/>
-      <c r="D367" s="4" t="inlineStr"/>
-      <c r="E367" s="4" t="inlineStr"/>
-      <c r="F367" s="4" t="inlineStr"/>
-      <c r="G367" s="4" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="2" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="B368" s="3" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-      <c r="C368" s="4" t="inlineStr">
-        <is>
-          <t>مركز شباب كفر الشيخ للتخاطب</t>
-        </is>
-      </c>
-      <c r="D368" s="4" t="inlineStr"/>
-      <c r="E368" s="4" t="inlineStr"/>
-      <c r="F368" s="4" t="inlineStr"/>
-      <c r="G368" s="4" t="inlineStr">
-        <is>
-          <t>كفر الشيخ</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="5" t="n"/>
-      <c r="B369" s="3" t="inlineStr">
-        <is>
-          <t>دسوق</t>
-        </is>
-      </c>
-      <c r="C369" s="4" t="inlineStr">
-        <is>
-          <t>مركز رعايه للتخاطب والتدخل المبكر</t>
-        </is>
-      </c>
-      <c r="D369" s="4" t="inlineStr"/>
-      <c r="E369" s="4" t="inlineStr"/>
-      <c r="F369" s="4" t="inlineStr"/>
-      <c r="G369" s="4" t="inlineStr">
-        <is>
-          <t>شارع شهداء المغربي، خلف جمعية الشروق</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="5" t="n"/>
-      <c r="B370" s="3" t="inlineStr">
-        <is>
-          <t>بلامون</t>
-        </is>
-      </c>
-      <c r="C370" s="4" t="inlineStr"/>
-      <c r="D370" s="4" t="inlineStr"/>
-      <c r="E370" s="4" t="inlineStr"/>
-      <c r="F370" s="4" t="inlineStr"/>
-      <c r="G370" s="4" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="5" t="n"/>
-      <c r="B371" s="3" t="inlineStr">
-        <is>
-          <t>الرياض</t>
-        </is>
-      </c>
-      <c r="C371" s="4" t="inlineStr"/>
-      <c r="D371" s="4" t="inlineStr"/>
-      <c r="E371" s="4" t="inlineStr"/>
-      <c r="F371" s="4" t="inlineStr"/>
-      <c r="G371" s="4" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="5" t="n"/>
-      <c r="B372" s="3" t="inlineStr">
-        <is>
-          <t>سيدي سالم</t>
-        </is>
-      </c>
-      <c r="C372" s="4" t="inlineStr"/>
-      <c r="D372" s="4" t="inlineStr"/>
-      <c r="E372" s="4" t="inlineStr"/>
-      <c r="F372" s="4" t="inlineStr"/>
-      <c r="G372" s="4" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="5" t="n"/>
-      <c r="B373" s="3" t="inlineStr">
-        <is>
-          <t>الحامول</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="inlineStr"/>
-      <c r="D373" s="4" t="inlineStr"/>
-      <c r="E373" s="4" t="inlineStr"/>
-      <c r="F373" s="4" t="inlineStr"/>
-      <c r="G373" s="4" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" s="5" t="n"/>
-      <c r="B374" s="3" t="inlineStr">
-        <is>
-          <t>برج البرلس</t>
-        </is>
-      </c>
-      <c r="C374" s="4" t="inlineStr"/>
-      <c r="D374" s="4" t="inlineStr"/>
-      <c r="E374" s="4" t="inlineStr"/>
-      <c r="F374" s="4" t="inlineStr"/>
-      <c r="G374" s="4" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="5" t="n"/>
-      <c r="B375" s="3" t="inlineStr">
-        <is>
-          <t>مطوبس</t>
-        </is>
-      </c>
-      <c r="C375" s="4" t="inlineStr"/>
-      <c r="D375" s="4" t="inlineStr"/>
-      <c r="E375" s="4" t="inlineStr"/>
-      <c r="F375" s="4" t="inlineStr"/>
-      <c r="G375" s="4" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="5" t="n"/>
-      <c r="B376" s="3" t="inlineStr">
-        <is>
-          <t>المحمودية</t>
-        </is>
-      </c>
-      <c r="C376" s="4" t="inlineStr"/>
-      <c r="D376" s="4" t="inlineStr"/>
-      <c r="E376" s="4" t="inlineStr"/>
-      <c r="F376" s="4" t="inlineStr"/>
-      <c r="G376" s="4" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="6" t="n"/>
-      <c r="B377" s="3" t="inlineStr">
-        <is>
-          <t>بيلا</t>
-        </is>
-      </c>
-      <c r="C377" s="4" t="inlineStr"/>
-      <c r="D377" s="4" t="inlineStr"/>
-      <c r="E377" s="4" t="inlineStr"/>
-      <c r="F377" s="4" t="inlineStr"/>
-      <c r="G377" s="4" t="inlineStr"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B378" s="3" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="C378" s="4" t="inlineStr"/>
-      <c r="D378" s="4" t="inlineStr"/>
-      <c r="E378" s="4" t="inlineStr"/>
-      <c r="F378" s="4" t="inlineStr"/>
-      <c r="G378" s="4" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B379" s="3" t="inlineStr">
-        <is>
-          <t>سيوه</t>
-        </is>
-      </c>
-      <c r="C379" s="4" t="inlineStr"/>
-      <c r="D379" s="4" t="inlineStr"/>
-      <c r="E379" s="4" t="inlineStr"/>
-      <c r="F379" s="4" t="inlineStr"/>
-      <c r="G379" s="4" t="inlineStr"/>
-    </row>
-    <row r="380">
-      <c r="A380" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B380" s="3" t="inlineStr">
-        <is>
-          <t>السلوم</t>
-        </is>
-      </c>
-      <c r="C380" s="4" t="inlineStr"/>
-      <c r="D380" s="4" t="inlineStr"/>
-      <c r="E380" s="4" t="inlineStr"/>
-      <c r="F380" s="4" t="inlineStr"/>
-      <c r="G380" s="4" t="inlineStr"/>
-    </row>
-    <row r="381">
-      <c r="A381" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B381" s="3" t="inlineStr">
-        <is>
-          <t>سيدي براني</t>
-        </is>
-      </c>
-      <c r="C381" s="4" t="inlineStr"/>
-      <c r="D381" s="4" t="inlineStr"/>
-      <c r="E381" s="4" t="inlineStr"/>
-      <c r="F381" s="4" t="inlineStr"/>
-      <c r="G381" s="4" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B382" s="3" t="inlineStr">
-        <is>
-          <t>العلمين</t>
-        </is>
-      </c>
-      <c r="C382" s="4" t="inlineStr"/>
-      <c r="D382" s="4" t="inlineStr"/>
-      <c r="E382" s="4" t="inlineStr"/>
-      <c r="F382" s="4" t="inlineStr"/>
-      <c r="G382" s="4" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B383" s="3" t="inlineStr">
-        <is>
-          <t>مارينا</t>
-        </is>
-      </c>
-      <c r="C383" s="4" t="inlineStr"/>
-      <c r="D383" s="4" t="inlineStr"/>
-      <c r="E383" s="4" t="inlineStr"/>
-      <c r="F383" s="4" t="inlineStr"/>
-      <c r="G383" s="4" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B384" s="3" t="inlineStr">
-        <is>
-          <t>توريدو</t>
-        </is>
-      </c>
-      <c r="C384" s="4" t="inlineStr"/>
-      <c r="D384" s="4" t="inlineStr"/>
-      <c r="E384" s="4" t="inlineStr"/>
-      <c r="F384" s="4" t="inlineStr"/>
-      <c r="G384" s="4" t="inlineStr"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B385" s="3" t="inlineStr">
-        <is>
-          <t>جنوب سيوه</t>
-        </is>
-      </c>
-      <c r="C385" s="4" t="inlineStr"/>
-      <c r="D385" s="4" t="inlineStr"/>
-      <c r="E385" s="4" t="inlineStr"/>
-      <c r="F385" s="4" t="inlineStr"/>
-      <c r="G385" s="4" t="inlineStr"/>
-    </row>
-    <row r="386">
-      <c r="A386" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B386" s="3" t="inlineStr">
-        <is>
-          <t>شمال سيوه</t>
-        </is>
-      </c>
-      <c r="C386" s="4" t="inlineStr"/>
-      <c r="D386" s="4" t="inlineStr"/>
-      <c r="E386" s="4" t="inlineStr"/>
-      <c r="F386" s="4" t="inlineStr"/>
-      <c r="G386" s="4" t="inlineStr"/>
-    </row>
-    <row r="387">
-      <c r="A387" s="2" t="inlineStr">
-        <is>
-          <t>مطروح</t>
-        </is>
-      </c>
-      <c r="B387" s="3" t="inlineStr">
-        <is>
-          <t>كشته</t>
-        </is>
-      </c>
-      <c r="C387" s="4" t="inlineStr"/>
-      <c r="D387" s="4" t="inlineStr"/>
-      <c r="E387" s="4" t="inlineStr"/>
-      <c r="F387" s="4" t="inlineStr"/>
-      <c r="G387" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="313">
